--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -591,7 +591,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>28-Jul 18:35</t>
+          <t>28-Jul 19:31</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>28-Jul 18:32</t>
+          <t>28-Jul 19:36</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>28-Jul 18:33</t>
+          <t>28-Jul 19:34</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>28-Jul 18:35</t>
+          <t>28-Jul 19:32</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>28-Jul 18:28</t>
+          <t>28-Jul 19:30</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>28-Jul 18:30</t>
+          <t>28-Jul 19:29</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>28-Jul 18:29</t>
+          <t>28-Jul 19:37</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>28-Jul 18:33</t>
+          <t>28-Jul 19:37</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>28-Jul 18:31</t>
+          <t>28-Jul 19:28</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>28-Jul 18:30</t>
+          <t>28-Jul 19:36</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>28-Jul 18:34</t>
+          <t>28-Jul 19:35</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>28-Jul 18:37</t>
+          <t>28-Jul 19:33</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹14 (3.29%) 7 ↓ / 56 ↑</t>
+          <t>₹15 (3.53%) 7 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>28-Jul 18:28</t>
+          <t>28-Jul 19:37</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>28-Jul 18:35</t>
+          <t>28-Jul 19:29</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>28-Jul 18:28</t>
+          <t>28-Jul 19:36</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>28-Jul 18:32</t>
+          <t>28-Jul 19:34</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>28-Jul 18:36</t>
+          <t>28-Jul 19:30</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -519,16 +519,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>53</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹425.87 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>281</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5-Aug</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7-Aug</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>10-Aug</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>12-Aug</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>28-Jul 5:55</t>
+          <t>29-Jul 10:54</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -540,12 +564,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fusion Klassroom Edutech BSE SMEU</t>
+          <t>Aegeus Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -559,39 +583,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>159</v>
+        <v>105</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹39.04 Cr</t>
+          <t>₹23.71 Cr</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>28-Jul 19:31</t>
+          <t>29-Jul 9:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -603,12 +627,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEU</t>
+          <t>Anawil Wire &amp; Engineering NSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹22 (16.92%) 18 ↓ / 22 ↑</t>
+          <t>₹30 (11.11%) 30 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -622,39 +646,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>130</v>
+        <v>270</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹177.81 Cr</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>28-Jul 19:36</t>
+          <t>29-Jul 10:58</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -666,17 +690,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dhaval Packaging BSE SMEU</t>
+          <t>Fusion Klassroom Edutech BSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹8 (8.25%) 8 ↓ / 8 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -685,39 +709,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹36.36 Cr</t>
+          <t>₹39.04 Cr</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>31-Jul</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>28-Jul 19:34</t>
+          <t>29-Jul 11:01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -729,17 +753,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MV Electrosystems IPOU</t>
+          <t>G.V. Electricals BSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹105 (24.71%) 60 ↓ / 105 ↑</t>
+          <t>₹22 (16.92%) 18 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -748,39 +772,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>425</v>
+        <v>130</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹290.00 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>31-Jul</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>28-Jul 19:32</t>
+          <t>29-Jul 11:02</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -792,17 +816,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Juniper Green Energy IPOU</t>
+          <t>Oneindig Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹13 (5.78%) 13 ↓ / 13 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -811,15 +835,15 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>225</v>
+        <v>96</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹1800.00 Cr</t>
+          <t>₹27.65 Cr</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>66</v>
+        <v>1200</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -843,7 +867,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>28-Jul 19:30</t>
+          <t>29-Jul 10:53</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -855,17 +879,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Oneindig Technologies BSE SMEU</t>
+          <t>Dhaval Packaging BSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹8 (8.25%) 8 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -874,11 +898,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹27.65 Cr</t>
+          <t>₹36.36 Cr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -906,7 +930,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>28-Jul 19:29</t>
+          <t>29-Jul 11:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -918,17 +942,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H.R. Hygiene Products BSE SMEU</t>
+          <t>MV Electrosystems IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹2 (2.27%) 2 ↓ / 2 ↑</t>
+          <t>₹106 (24.94%) 60 ↓ / 106 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -937,39 +961,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>88</v>
+        <v>425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹53.95 Cr</t>
+          <t>₹290.00 Cr</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1600</v>
+        <v>34</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>28-Jul 19:37</t>
+          <t>29-Jul 11:00</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -981,17 +1005,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Manipal Health Enterprises IPOU</t>
+          <t>Juniper Green Energy IPOU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹9 (1.53%) 9 ↓ / 35 ↑</t>
+          <t>₹17 (7.56%) 17 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1000,39 +1024,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>590</v>
+        <v>225</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹9275.22 Cr</t>
+          <t>₹1800.00 Cr</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>28-Jul 19:37</t>
+          <t>29-Jul 10:54</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1044,58 +1068,58 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Poojaa Precision Engg. BSE SMEO</t>
+          <t>H.R. Hygiene Products BSE SMEO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹300 (99.67%) 195 ↓ / 300 ↑</t>
+          <t>₹2 (2.27%) 2 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.53x</t>
+          <t>0.22x</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>301</v>
+        <v>88</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹159.83 Cr</t>
+          <t>₹53.95 Cr</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>400</v>
+        <v>1600</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 300</t>
+          <t>29-Jul GMP: 2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>31-Jul</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>28-Jul 19:28</t>
+          <t>29-Jul 10:57</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1107,12 +1131,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Propshop Events &amp; Exhibitions NSE SMEO</t>
+          <t>Manipal Health Enterprises IPOO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹10 (1.69%) 10 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1122,118 +1146,118 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.39x</t>
+          <t>0.03x</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>69</v>
+        <v>590</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹28.57 Cr</t>
+          <t>₹9275.22 Cr</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2000</v>
+        <v>25</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 0</t>
+          <t>29-Jul GMP: 10</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>31-Jul</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>28-Jul 19:36</t>
+          <t>29-Jul 10:55</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Advance Technoforge BSE SMEO</t>
+          <t>Poojaa Precision Engg. BSE SMEO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹8 (8.42%) 3.50 ↓ / 9 ↑</t>
+          <t>₹300 (99.67%) 195 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.44x</t>
+          <t>20.17x</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>95</v>
+        <v>301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹24.03 Cr</t>
+          <t>₹159.83 Cr</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 9</t>
+          <t>28-Jul GMP: 300</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>31-Jul</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>28-Jul 19:35</t>
+          <t>29-Jul 11:00</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Silverstorm Parks &amp; Resorts BSE SMEC</t>
+          <t>Propshop Events &amp; Exhibitions NSE SMECT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1248,169 +1272,169 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.91x</t>
+          <t>0.53x</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹82.43 Cr</t>
+          <t>₹28.57 Cr</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 0</t>
+          <t>27-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 0</t>
+          <t>29-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>28-Jul 19:33</t>
+          <t>29-Jul 11:01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lohia Corp IPOC</t>
+          <t>Advance Technoforge BSE SMECT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹15 (3.53%) 7 ↓ / 56 ↑</t>
+          <t>₹8 (8.42%) 3.50 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.26x</t>
+          <t>0.81x</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>425</v>
+        <v>95</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹1101.28 Cr</t>
+          <t>₹24.03 Cr</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>35</v>
+        <v>1200</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 12</t>
+          <t>27-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 11.5</t>
+          <t>29-Jul GMP: 8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>28-Jul</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>28-Jul 19:37</t>
+          <t>29-Jul 10:55</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Indo-MIM IPOC</t>
+          <t>Silverstorm Parks &amp; Resorts BSE SMEC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹185 (38.14%) 168 ↓ / 213 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>72.37x</t>
+          <t>1.91x</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>485</v>
+        <v>133</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹3811.21 Cr</t>
+          <t>₹82.43 Cr</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 170</t>
+          <t>24-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 190</t>
+          <t>28-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>28-Jul</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>31-Jul</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>28-Jul 19:29</t>
+          <t>29-Jul 10:55</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1422,12 +1446,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Xtranet Technologies IPOC</t>
+          <t>Lohia Corp IPOCAllotted</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹9.5 (7.48%) 7.50 ↓ / 26 ↑</t>
+          <t>₹21.5 (5.06%) 7 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1437,28 +1461,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12.24x</t>
+          <t>7.26x</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>127</v>
+        <v>425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>₹166.80 Cr</t>
+          <t>₹1101.28 Cr</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 8</t>
+          <t>23-Jul GMP: 12</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 7.7</t>
+          <t>27-Jul GMP: 11.5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1473,7 +1497,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>28-Jul 19:36</t>
+          <t>29-Jul 10:55</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1485,58 +1509,58 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Shree Balaji Mala BSE SMECAllotted</t>
+          <t>Xtranet Technologies IPOCAllotted</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹15 (21.43%) 11 ↓ / 19 ↑</t>
+          <t>₹11.5 (9.06%) 7.50 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>200.34x</t>
+          <t>12.24x</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>70</v>
+        <v>127</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹18.90 Cr</t>
+          <t>₹166.80 Cr</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2000</v>
+        <v>110</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 16</t>
+          <t>23-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 13</t>
+          <t>27-Jul GMP: 7.7</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>27-Jul</t>
+          <t>28-Jul</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>28-Jul 19:34</t>
+          <t>29-Jul 10:58</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1548,58 +1572,58 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cube Highways Trust InvIT IPOC</t>
+          <t>Indo-MIM IPOCAllotted</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
+          <t>₹175 (36.08%) 168 ↓ / 213 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9.35x</t>
+          <t>72.37x</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>152</v>
+        <v>485</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹5000.00 Cr</t>
+          <t>₹3811.21 Cr</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 0</t>
+          <t>23-Jul GMP: 170</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 1.75</t>
+          <t>27-Jul GMP: 190</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>28-Jul</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>28-Jul 19:30</t>
+          <t>29-Jul 10:56</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1611,58 +1635,58 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Metalic Technoforge NSE SMEL@87.00 (12.99%)</t>
+          <t>Cube Highways Trust InvIT IPOC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹6 (7.79%) 6 ↓ / 8.10 ↑</t>
+          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.47x</t>
+          <t>9.35x</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹49.96 Cr</t>
+          <t>₹5000.00 Cr</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1600</v>
+        <v>95</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 0</t>
+          <t>22-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 6</t>
+          <t>24-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>24-Jul</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 6</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>28-Jul 9:29</t>
+          <t>29-Jul 10:53</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1674,121 +1698,121 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Gulf Lloyds BSE SMEL@100.00 (0%)</t>
+          <t>Shree Balaji Mala BSE SMEL@133.00 (90%)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹1 (1.00%) 1 ↓ / 25 ↑</t>
+          <t>₹56 (80.00%) 11 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10.85x</t>
+          <t>200.34x</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹18.19 Cr</t>
+          <t>₹18.90 Cr</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>20-Jul GMP: 10</t>
+          <t>22-Jul GMP: 16</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 1</t>
+          <t>24-Jul GMP: 13</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>23-Jul</t>
+          <t>27-Jul</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 1</t>
+          <t>29-Jul GMP: 56</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>27-Jul 9:29</t>
+          <t>29-Jul 9:29</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Caliber Mining IPOL@500.25 (17.98%)</t>
+          <t>Metalic Technoforge NSE SMEL@87.00 (12.99%)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹60 (14.15%) 60 ↓ / 117 ↑</t>
+          <t>₹6 (7.79%) 6 ↓ / 8.10 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>154.66x</t>
+          <t>8.47x</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>424</v>
+        <v>77</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹450.00 Cr</t>
+          <t>₹49.96 Cr</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>35</v>
+        <v>1600</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>17-Jul GMP: 116</t>
+          <t>21-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 71</t>
+          <t>23-Jul GMP: 6</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>22-Jul</t>
+          <t>24-Jul</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 60</t>
+          <t>28-Jul GMP: 6</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>24-Jul 9:35</t>
+          <t>28-Jul 9:29</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1800,12 +1824,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sotefin Bharat BSE SMEL@205.00 (9.63%)</t>
+          <t>Gulf Lloyds BSE SMEL@100.00 (0%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹2.5 (1.34%) 1 ↓ / 27 ↑</t>
+          <t>₹1 (1.00%) 1 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1815,60 +1839,60 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3.99x</t>
+          <t>10.85x</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>187</v>
+        <v>100</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹89.76 Cr</t>
+          <t>₹18.19 Cr</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 18</t>
+          <t>20-Jul GMP: 10</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20-Jul GMP: 1</t>
+          <t>22-Jul GMP: 1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>21-Jul</t>
+          <t>23-Jul</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 2.5</t>
+          <t>27-Jul GMP: 1</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>23-Jul 9:34</t>
+          <t>27-Jul 9:29</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SBI Funds Management IPOL@613.30 (6.85%)</t>
+          <t>Caliber Mining IPOL@500.25 (17.98%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹65 (11.32%) 65 ↓ / 140 ↑</t>
+          <t>₹60 (14.15%) 60 ↓ / 117 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1878,43 +1902,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>41.73x</t>
+          <t>154.66x</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>574</v>
+        <v>424</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹9812.91 Cr</t>
+          <t>₹450.00 Cr</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>14-Jul GMP: 88</t>
+          <t>17-Jul GMP: 116</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 97</t>
+          <t>21-Jul GMP: 71</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>17-Jul</t>
+          <t>22-Jul</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 65</t>
+          <t>24-Jul GMP: 60</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>21-Jul 9:35</t>
+          <t>24-Jul 9:35</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1926,58 +1950,58 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Millworks Technologies BSE SMEL@628.90 (90%)</t>
+          <t>Sotefin Bharat BSE SMEL@205.00 (9.63%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹395 (119.34%) 300 ↓ / 400 ↑</t>
+          <t>₹2.5 (1.34%) 1 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>219.54x</t>
+          <t>3.99x</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>331</v>
+        <v>187</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹160.34 Cr</t>
+          <t>₹89.76 Cr</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>14-Jul GMP: 300</t>
+          <t>16-Jul GMP: 18</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 380</t>
+          <t>20-Jul GMP: 1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>17-Jul</t>
+          <t>21-Jul</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 395</t>
+          <t>23-Jul GMP: 2.5</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>21-Jul 9:32</t>
+          <t>23-Jul 9:34</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -1989,43 +2013,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alpine Texworld IPOL@105.00 (0%)</t>
+          <t>Millworks Technologies BSE SMEL@628.90 (90%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹1 (0.95%) 1 ↓ / 5 ↑</t>
+          <t>₹395 (119.34%) 300 ↓ / 400 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>219.54x</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105</v>
+        <v>331</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹126.25 Cr</t>
+          <t>₹160.34 Cr</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>142</v>
+        <v>400</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>14-Jul GMP: 5</t>
+          <t>14-Jul GMP: 300</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 1</t>
+          <t>16-Jul GMP: 380</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2035,75 +2059,75 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 1</t>
+          <t>21-Jul GMP: 395</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>21-Jul 9:35</t>
+          <t>21-Jul 9:32</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Devson Catalyst BSE SMEL@196.15 (66.23%)</t>
+          <t>SBI Funds Management IPOL@613.30 (6.85%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹49 (41.53%) 8 ↓ / 51 ↑</t>
+          <t>₹65 (11.32%) 65 ↓ / 140 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>220.35x</t>
+          <t>41.73x</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>118</v>
+        <v>574</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹42.34 Cr</t>
+          <t>₹9812.91 Cr</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1200</v>
+        <v>26</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>9-Jul GMP: 45</t>
+          <t>14-Jul GMP: 88</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>13-Jul GMP: 49</t>
+          <t>16-Jul GMP: 97</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>14-Jul</t>
+          <t>17-Jul</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 49</t>
+          <t>21-Jul GMP: 65</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>16-Jul 9:37</t>
+          <t>21-Jul 9:35</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2115,75 +2139,75 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Laser Power &amp; Infra IPOL@250.00 (16.82%)</t>
+          <t>Alpine Texworld IPOL@105.00 (0%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹39 (18.22%) 15 ↓ / 42 ↑</t>
+          <t>₹1 (0.95%) 1 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>41.05x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>214</v>
+        <v>105</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹742.00 Cr</t>
+          <t>₹126.25 Cr</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>70</v>
+        <v>142</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>9-Jul GMP: 24</t>
+          <t>14-Jul GMP: 5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>13-Jul GMP: 40.5</t>
+          <t>16-Jul GMP: 1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>14-Jul</t>
+          <t>17-Jul</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 39</t>
+          <t>21-Jul GMP: 1</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>16-Jul 9:29</t>
+          <t>21-Jul 9:35</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Happy Steels NSE SMEL@68.00 (3.03%)</t>
+          <t>Laser Power &amp; Infra IPOL@250.00 (16.82%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹10 (15.15%) 7 ↓ / 14 ↑</t>
+          <t>₹39 (18.22%) 15 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2193,28 +2217,28 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>77.81x</t>
+          <t>41.05x</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>66</v>
+        <v>214</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹25.00 Cr</t>
+          <t>₹742.00 Cr</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2000</v>
+        <v>70</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>9-Jul GMP: 8</t>
+          <t>9-Jul GMP: 24</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>13-Jul GMP: 8</t>
+          <t>13-Jul GMP: 40.5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2224,7 +2248,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 10</t>
+          <t>16-Jul GMP: 39</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2241,12 +2265,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kusumgar IPOL@569.00 (35.8%)</t>
+          <t>Devson Catalyst BSE SMEL@196.15 (66.23%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹161 (38.42%) 135 ↓ / 171 ↑</t>
+          <t>₹49 (41.53%) 8 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2256,43 +2280,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>135.8x</t>
+          <t>220.35x</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>419</v>
+        <v>118</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹650.36 Cr</t>
+          <t>₹42.34 Cr</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>35</v>
+        <v>1200</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8-Jul GMP: 160</t>
+          <t>9-Jul GMP: 45</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10-Jul GMP: 165</t>
+          <t>13-Jul GMP: 49</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>13-Jul</t>
+          <t>14-Jul</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>15-Jul GMP: 161</t>
+          <t>16-Jul GMP: 49</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>15-Jul 9:33</t>
+          <t>16-Jul 9:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2304,58 +2328,58 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IC Electricals NSE SMEL@166.00 (67.68%)</t>
+          <t>Happy Steels NSE SMEL@68.00 (3.03%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹47 (47.47%) 28 ↓ / 55 ↑</t>
+          <t>₹10 (15.15%) 7 ↓ / 14 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>295.08x</t>
+          <t>77.81x</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹47.91 Cr</t>
+          <t>₹25.00 Cr</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3-Jul GMP: 45</t>
+          <t>9-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>7-Jul GMP: 42</t>
+          <t>13-Jul GMP: 8</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>8-Jul</t>
+          <t>14-Jul</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>10-Jul GMP: 47</t>
+          <t>16-Jul GMP: 10</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>10-Jul 9:35</t>
+          <t>16-Jul 9:29</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,12 +506,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹13 (24.53%) 13 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>29-Jul 10:54</t>
+          <t>29-Jul 16:33</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>29-Jul 9:00</t>
+          <t>29-Jul 16:31</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹30 (11.11%) 30 ↓ / 30 ↑</t>
+          <t>₹50 (18.52%) 50 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>29-Jul 10:58</t>
+          <t>29-Jul 16:30</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>29-Jul 11:01</t>
+          <t>29-Jul 16:36</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>29-Jul 11:02</t>
+          <t>29-Jul 16:35</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>29-Jul 10:53</t>
+          <t>29-Jul 16:29</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>29-Jul 11:02</t>
+          <t>29-Jul 16:34</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>29-Jul 11:00</t>
+          <t>29-Jul 16:30</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>29-Jul 10:54</t>
+          <t>29-Jul 16:30</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.22x</t>
+          <t>1.41x</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>29-Jul 10:57</t>
+          <t>29-Jul 16:36</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹10 (1.69%) 10 ↓ / 35 ↑</t>
+          <t>₹9 (1.53%) 9 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.03x</t>
+          <t>0.15x</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 10</t>
+          <t>29-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>29-Jul 10:55</t>
+          <t>29-Jul 16:30</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹300 (99.67%) 195 ↓ / 300 ↑</t>
+          <t>₹275 (91.36%) 195 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20.17x</t>
+          <t>61.5x</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>29-Jul 11:00</t>
+          <t>29-Jul 16:35</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.53x</t>
+          <t>1.52x</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>29-Jul 11:01</t>
+          <t>29-Jul 16:29</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹8 (8.42%) 3.50 ↓ / 9 ↑</t>
+          <t>₹1 (1.05%) 1 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.81x</t>
+          <t>1.55x</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 8</t>
+          <t>29-Jul GMP: 1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>29-Jul 10:55</t>
+          <t>29-Jul 16:34</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>29-Jul 10:55</t>
+          <t>29-Jul 16:34</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹21.5 (5.06%) 7 ↓ / 56 ↑</t>
+          <t>₹19.5 (4.59%) 7 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>29-Jul 10:55</t>
+          <t>29-Jul 16:32</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹11.5 (9.06%) 7.50 ↓ / 26 ↑</t>
+          <t>₹12 (9.45%) 7.50 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>29-Jul 10:58</t>
+          <t>29-Jul 16:28</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹175 (36.08%) 168 ↓ / 213 ↑</t>
+          <t>₹174 (35.88%) 168 ↓ / 213 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>29-Jul 10:56</t>
+          <t>29-Jul 16:37</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>29-Jul 10:53</t>
+          <t>29-Jul 16:36</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>29-Jul 16:33</t>
+          <t>30-Jul 10:59</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>29-Jul 16:31</t>
+          <t>30-Jul 10:57</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -632,12 +632,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹50 (18.52%) 50 ↓ / 50 ↑</t>
+          <t>₹60 (22.22%) 60 ↓ / 60 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>29-Jul 16:30</t>
+          <t>30-Jul 10:57</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -690,17 +690,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fusion Klassroom Edutech BSE SMEU</t>
+          <t>G.V. Electricals BSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹22 (16.92%) 18 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -709,15 +709,15 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹39.04 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>29-Jul 16:36</t>
+          <t>30-Jul 11:02</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -753,17 +753,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEU</t>
+          <t>Fusion Klassroom Edutech BSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹22 (16.92%) 18 ↓ / 22 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -772,15 +772,15 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹39.04 Cr</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>29-Jul 16:35</t>
+          <t>30-Jul 11:01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Oneindig Technologies BSE SMEU</t>
+          <t>Oneindig Technologies BSE SMEO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.06x</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -847,7 +847,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>30-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>29-Jul 16:29</t>
+          <t>30-Jul 10:57</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -879,12 +879,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dhaval Packaging BSE SMEU</t>
+          <t>Juniper Green Energy IPOO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹8 (8.25%) 8 ↓ / 8 ↑</t>
+          <t>₹17 (7.56%) 17 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -894,23 +894,23 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.03x</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹36.36 Cr</t>
+          <t>₹1800.00 Cr</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1200</v>
+        <v>66</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>30-Jul GMP: 17</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>29-Jul 16:34</t>
+          <t>30-Jul 10:55</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -942,12 +942,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MV Electrosystems IPOU</t>
+          <t>MV Electrosystems IPOO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹106 (24.94%) 60 ↓ / 106 ↑</t>
+          <t>₹100 (23.53%) 60 ↓ / 106 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4x</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -973,7 +973,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>30-Jul GMP: 100</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>29-Jul 16:30</t>
+          <t>30-Jul 10:57</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1005,38 +1005,38 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Juniper Green Energy IPOU</t>
+          <t>Dhaval Packaging BSE SMEO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹17 (7.56%) 17 ↓ / 17 ↑</t>
+          <t>₹12 (12.37%) 8 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.08x</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>225</v>
+        <v>97</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹1800.00 Cr</t>
+          <t>₹36.36 Cr</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>66</v>
+        <v>1200</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>30-Jul GMP: 12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>29-Jul 16:30</t>
+          <t>30-Jul 10:57</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.41x</t>
+          <t>1.46x</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>29-Jul 16:36</t>
+          <t>30-Jul 11:02</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹9 (1.53%) 9 ↓ / 35 ↑</t>
+          <t>₹7 (1.19%) 7 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.15x</t>
+          <t>0.18x</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>29-Jul 16:30</t>
+          <t>30-Jul 10:56</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1194,22 +1194,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Poojaa Precision Engg. BSE SMEO</t>
+          <t>Poojaa Precision Engg. BSE SMECT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹275 (91.36%) 195 ↓ / 300 ↑</t>
+          <t>₹120 (39.87%) 120 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>61.5x</t>
+          <t>102.07x</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>30-Jul GMP: 120</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>29-Jul 16:35</t>
+          <t>30-Jul 10:59</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1257,7 +1257,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Propshop Events &amp; Exhibitions NSE SMECT</t>
+          <t>Propshop Events &amp; Exhibitions NSE SMEC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.52x</t>
+          <t>1.53x</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>29-Jul 16:29</t>
+          <t>30-Jul 10:57</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1320,17 +1320,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Advance Technoforge BSE SMECT</t>
+          <t>Advance Technoforge BSE SMEC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹1 (1.05%) 1 ↓ / 9 ↑</t>
+          <t>₹8 (8.42%) 3.50 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 1</t>
+          <t>29-Jul GMP: 8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>29-Jul 16:34</t>
+          <t>30-Jul 11:02</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1383,7 +1383,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Silverstorm Parks &amp; Resorts BSE SMEC</t>
+          <t>Silverstorm Parks &amp; Resorts BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>29-Jul 16:34</t>
+          <t>30-Jul 11:02</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1446,12 +1446,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lohia Corp IPOCAllotted</t>
+          <t>Cube Highways Trust InvIT IPOC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹19.5 (4.59%) 7 ↓ / 56 ↑</t>
+          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1461,43 +1461,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7.26x</t>
+          <t>9.35x</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>425</v>
+        <v>152</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>₹1101.28 Cr</t>
+          <t>₹5000.00 Cr</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 12</t>
+          <t>22-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 11.5</t>
+          <t>24-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>28-Jul</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>29-Jul 16:32</t>
+          <t>30-Jul 11:00</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1509,17 +1509,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Xtranet Technologies IPOCAllotted</t>
+          <t>Xtranet Technologies IPOL@136.00 (7.09%)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹12 (9.45%) 7.50 ↓ / 26 ↑</t>
+          <t>₹14.5 (11.42%) 7.50 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>30-Jul GMP: 14.5</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>29-Jul 16:28</t>
+          <t>30-Jul 9:31</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1572,43 +1572,43 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Indo-MIM IPOCAllotted</t>
+          <t>Lohia Corp IPOL@461.00 (8.47%)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹174 (35.88%) 168 ↓ / 213 ↑</t>
+          <t>₹17 (4.00%) 7 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>72.37x</t>
+          <t>7.26x</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>485</v>
+        <v>425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹3811.21 Cr</t>
+          <t>₹1101.28 Cr</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 170</t>
+          <t>23-Jul GMP: 12</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 190</t>
+          <t>27-Jul GMP: 11.5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1618,12 +1618,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>30-Jul GMP: 17</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>29-Jul 16:37</t>
+          <t>30-Jul 9:30</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1635,58 +1635,58 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cube Highways Trust InvIT IPOC</t>
+          <t>Indo-MIM IPOL@700.00 (44.33%)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
+          <t>₹184 (37.94%) 168 ↓ / 213 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9.35x</t>
+          <t>72.37x</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>152</v>
+        <v>485</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹5000.00 Cr</t>
+          <t>₹3811.21 Cr</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 0</t>
+          <t>23-Jul GMP: 170</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 1.75</t>
+          <t>27-Jul GMP: 190</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>28-Jul</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>30-Jul GMP: 184</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>29-Jul 16:36</t>
+          <t>30-Jul 9:36</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2013,43 +2013,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Millworks Technologies BSE SMEL@628.90 (90%)</t>
+          <t>Alpine Texworld IPOL@105.00 (0%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹395 (119.34%) 300 ↓ / 400 ↑</t>
+          <t>₹1 (0.95%) 1 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>219.54x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>331</v>
+        <v>105</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹160.34 Cr</t>
+          <t>₹126.25 Cr</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>400</v>
+        <v>142</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>14-Jul GMP: 300</t>
+          <t>14-Jul GMP: 5</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 380</t>
+          <t>16-Jul GMP: 1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 395</t>
+          <t>21-Jul GMP: 1</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>21-Jul 9:32</t>
+          <t>21-Jul 9:35</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -2139,43 +2139,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alpine Texworld IPOL@105.00 (0%)</t>
+          <t>Millworks Technologies BSE SMEL@628.90 (90%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹1 (0.95%) 1 ↓ / 5 ↑</t>
+          <t>₹395 (119.34%) 300 ↓ / 400 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>219.54x</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>105</v>
+        <v>331</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹126.25 Cr</t>
+          <t>₹160.34 Cr</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>142</v>
+        <v>400</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>14-Jul GMP: 5</t>
+          <t>14-Jul GMP: 300</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 1</t>
+          <t>16-Jul GMP: 380</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2185,17 +2185,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 1</t>
+          <t>21-Jul GMP: 395</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>21-Jul 9:35</t>
+          <t>21-Jul 9:32</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,12 +506,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹13 (24.53%) 13 ↓ / 13 ↑</t>
+          <t>₹10 (18.87%) 10 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>30-Jul 10:59</t>
+          <t>30-Jul 16:31</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>30-Jul 10:57</t>
+          <t>30-Jul 16:29</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹60 (22.22%) 60 ↓ / 60 ↑</t>
+          <t>₹70 (25.93%) 60 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>30-Jul 10:57</t>
+          <t>30-Jul 16:37</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹22 (16.92%) 18 ↓ / 22 ↑</t>
+          <t>₹25 (19.23%) 18 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>30-Jul 11:02</t>
+          <t>30-Jul 16:33</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>30-Jul 11:01</t>
+          <t>30-Jul 16:29</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.06x</t>
+          <t>0.35x</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -867,7 +867,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>30-Jul 10:57</t>
+          <t>30-Jul 16:34</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -884,17 +884,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹17 (7.56%) 17 ↓ / 17 ↑</t>
+          <t>₹9 (4.00%) 9 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.03x</t>
+          <t>0.38x</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -910,7 +910,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 17</t>
+          <t>30-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>30-Jul 10:55</t>
+          <t>30-Jul 16:35</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹100 (23.53%) 60 ↓ / 106 ↑</t>
+          <t>₹116 (27.29%) 60 ↓ / 116 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4x</t>
+          <t>3.78x</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -973,7 +973,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 100</t>
+          <t>30-Jul GMP: 116</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30-Jul 10:57</t>
+          <t>30-Jul 16:35</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹12 (12.37%) 8 ↓ / 12 ↑</t>
+          <t>₹13 (13.40%) 8 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.08x</t>
+          <t>0.48x</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 12</t>
+          <t>30-Jul GMP: 13</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>30-Jul 10:57</t>
+          <t>30-Jul 16:36</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.46x</t>
+          <t>1.74x</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>30-Jul 11:02</t>
+          <t>30-Jul 16:31</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹7 (1.19%) 7 ↓ / 35 ↑</t>
+          <t>₹5 (0.85%) 5 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.18x</t>
+          <t>0.47x</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>30-Jul 10:56</t>
+          <t>30-Jul 16:36</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹120 (39.87%) 120 ↓ / 300 ↑</t>
+          <t>₹225 (74.75%) 195 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>102.07x</t>
+          <t>278.32x</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 120</t>
+          <t>30-Jul GMP: 225</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>30-Jul 10:59</t>
+          <t>30-Jul 16:36</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>30-Jul 10:57</t>
+          <t>30-Jul 16:35</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹8 (8.42%) 3.50 ↓ / 9 ↑</t>
+          <t>₹14 (14.74%) 3.50 ↓ / 14 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>30-Jul 11:02</t>
+          <t>30-Jul 16:37</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>30-Jul 11:02</t>
+          <t>30-Jul 16:34</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1446,7 +1446,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cube Highways Trust InvIT IPOC</t>
+          <t>Cube Highways Trust InvIT IPOCAllotted</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>30-Jul 11:00</t>
+          <t>30-Jul 16:32</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>30-Jul 16:31</t>
+          <t>30-Jul 18:58</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>30-Jul 16:29</t>
+          <t>30-Jul 19:01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>30-Jul 16:37</t>
+          <t>30-Jul 18:55</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>30-Jul 16:33</t>
+          <t>30-Jul 19:02</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>30-Jul 16:29</t>
+          <t>30-Jul 18:53</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.35x</t>
+          <t>0.42x</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -867,7 +867,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>30-Jul 16:34</t>
+          <t>30-Jul 18:59</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹9 (4.00%) 9 ↓ / 17 ↑</t>
+          <t>₹8 (3.56%) 8 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 9</t>
+          <t>30-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>30-Jul 16:35</t>
+          <t>30-Jul 18:54</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹116 (27.29%) 60 ↓ / 116 ↑</t>
+          <t>₹120 (28.24%) 60 ↓ / 120 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.78x</t>
+          <t>3.87x</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -973,7 +973,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 116</t>
+          <t>30-Jul GMP: 120</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30-Jul 16:35</t>
+          <t>30-Jul 18:53</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.48x</t>
+          <t>0.49x</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>30-Jul 16:36</t>
+          <t>30-Jul 19:02</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.74x</t>
+          <t>1.77x</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>30-Jul 16:31</t>
+          <t>30-Jul 18:59</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹5 (0.85%) 5 ↓ / 35 ↑</t>
+          <t>₹4.5 (0.76%) 4.50 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>30-Jul 16:36</t>
+          <t>30-Jul 18:59</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Poojaa Precision Engg. BSE SMECT</t>
+          <t>Poojaa Precision Engg. BSE SMEC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>278.32x</t>
+          <t>278.83x</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>30-Jul 16:36</t>
+          <t>30-Jul 19:00</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>30-Jul 16:35</t>
+          <t>30-Jul 18:54</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹14 (14.74%) 3.50 ↓ / 14 ↑</t>
+          <t>₹18 (18.95%) 3.50 ↓ / 18 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>30-Jul 16:37</t>
+          <t>30-Jul 19:01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>30-Jul 16:34</t>
+          <t>30-Jul 18:59</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>30-Jul 16:32</t>
+          <t>30-Jul 19:00</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,17 +501,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOU</t>
+          <t>LAPL Automotive BSE SMEU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹10 (18.87%) 10 ↓ / 13 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -520,39 +520,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
+          <t>₹32.40 Cr</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>281</v>
+        <v>1200</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>30-Jul 18:58</t>
+          <t>31-Jul 11:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -564,17 +564,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aegeus Technologies BSE SMEU</t>
+          <t>Ardee Industries IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹13 (24.53%) 13 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -583,39 +583,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹23.71 Cr</t>
+          <t>₹425.87 Cr</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1200</v>
+        <v>281</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>30-Jul 19:01</t>
+          <t>31-Jul 11:34</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -627,17 +627,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Anawil Wire &amp; Engineering NSE SMEU</t>
+          <t>Aegeus Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹70 (25.93%) 60 ↓ / 70 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -646,39 +646,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>270</v>
+        <v>105</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹177.81 Cr</t>
+          <t>₹23.71 Cr</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>30-Jul 18:55</t>
+          <t>31-Jul 11:37</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -690,17 +690,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEU</t>
+          <t>Anawil Wire &amp; Engineering NSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹25 (19.23%) 18 ↓ / 25 ↑</t>
+          <t>₹65 (24.07%) 60 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -709,39 +709,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>130</v>
+        <v>270</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹177.81 Cr</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>30-Jul 19:02</t>
+          <t>31-Jul 11:31</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -753,38 +753,38 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fusion Klassroom Edutech BSE SMEU</t>
+          <t>G.V. Electricals BSE SMEO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹25 (19.23%) 18 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.23x</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹39.04 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>31-Jul GMP: 25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>30-Jul 18:53</t>
+          <t>31-Jul 11:31</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -816,58 +816,58 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Oneindig Technologies BSE SMEO</t>
+          <t>Fusion Klassroom Edutech BSE SMEO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹9 (5.66%) 9 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.42x</t>
+          <t>0.14x</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96</v>
+        <v>159</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹27.65 Cr</t>
+          <t>₹39.04 Cr</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 0</t>
+          <t>31-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>30-Jul 18:59</t>
+          <t>31-Jul 11:31</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -879,12 +879,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Juniper Green Energy IPOO</t>
+          <t>Oneindig Technologies BSE SMEO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹8 (3.56%) 8 ↓ / 17 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -894,23 +894,23 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.38x</t>
+          <t>0.42x</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>225</v>
+        <v>96</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹1800.00 Cr</t>
+          <t>₹27.65 Cr</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>66</v>
+        <v>1200</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 8</t>
+          <t>30-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>30-Jul 18:54</t>
+          <t>31-Jul 11:29</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -942,38 +942,38 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MV Electrosystems IPOO</t>
+          <t>Dhaval Packaging BSE SMEO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹120 (28.24%) 60 ↓ / 120 ↑</t>
+          <t>₹12 (12.37%) 8 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.87x</t>
+          <t>0.64x</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>425</v>
+        <v>97</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹290.00 Cr</t>
+          <t>₹36.36 Cr</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>34</v>
+        <v>1200</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 120</t>
+          <t>30-Jul GMP: 15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30-Jul 18:53</t>
+          <t>31-Jul 11:28</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1005,38 +1005,38 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dhaval Packaging BSE SMEO</t>
+          <t>MV Electrosystems IPOO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹13 (13.40%) 8 ↓ / 13 ↑</t>
+          <t>₹133 (31.29%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.49x</t>
+          <t>6.77x</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>97</v>
+        <v>425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹36.36 Cr</t>
+          <t>₹290.00 Cr</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1200</v>
+        <v>34</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 13</t>
+          <t>30-Jul GMP: 125</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>30-Jul 19:02</t>
+          <t>31-Jul 11:28</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1068,12 +1068,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>H.R. Hygiene Products BSE SMEO</t>
+          <t>Juniper Green Energy IPOO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹2 (2.27%) 2 ↓ / 2 ↑</t>
+          <t>₹6 (2.67%) 6 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1083,43 +1083,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.77x</t>
+          <t>0.43x</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>88</v>
+        <v>225</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹53.95 Cr</t>
+          <t>₹1800.00 Cr</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1600</v>
+        <v>66</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 2</t>
+          <t>30-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>30-Jul 18:59</t>
+          <t>31-Jul 11:30</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1131,12 +1131,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Manipal Health Enterprises IPOO</t>
+          <t>Manipal Health Enterprises IPOCT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹4.5 (0.76%) 4.50 ↓ / 35 ↑</t>
+          <t>₹3.75 (0.64%) 3.75 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.47x</t>
+          <t>0.55x</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>31-Jul GMP: 3.75</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>30-Jul 18:59</t>
+          <t>31-Jul 11:32</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1194,58 +1194,58 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Poojaa Precision Engg. BSE SMEC</t>
+          <t>H.R. Hygiene Products BSE SMECT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹225 (74.75%) 195 ↓ / 300 ↑</t>
+          <t>₹2 (2.27%) 2 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>278.83x</t>
+          <t>2.17x</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>301</v>
+        <v>88</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹159.83 Cr</t>
+          <t>₹53.95 Cr</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>400</v>
+        <v>1600</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 300</t>
+          <t>29-Jul GMP: 2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 225</t>
+          <t>31-Jul GMP: 2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>30-Jul 19:00</t>
+          <t>31-Jul 11:36</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1257,63 +1257,63 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Propshop Events &amp; Exhibitions NSE SMEC</t>
+          <t>Poojaa Precision Engg. BSE SMEC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹225 (74.75%) 195 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.53x</t>
+          <t>278.83x</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>69</v>
+        <v>301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹28.57 Cr</t>
+          <t>₹159.83 Cr</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 0</t>
+          <t>28-Jul GMP: 300</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 0</t>
+          <t>30-Jul GMP: 225</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>31-Jul</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>30-Jul 18:54</t>
+          <t>31-Jul 11:34</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹18 (18.95%) 3.50 ↓ / 18 ↑</t>
+          <t>₹5 (5.26%) 3.50 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>30-Jul 19:01</t>
+          <t>31-Jul 11:30</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1383,7 +1383,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Silverstorm Parks &amp; Resorts BSE SMECAllotted</t>
+          <t>Propshop Events &amp; Exhibitions NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,55 +1398,55 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.91x</t>
+          <t>1.53x</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹82.43 Cr</t>
+          <t>₹28.57 Cr</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 0</t>
+          <t>27-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 0</t>
+          <t>29-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>30-Jul 18:59</t>
+          <t>31-Jul 11:35</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cube Highways Trust InvIT IPOCAllotted</t>
+          <t>Cube Highways Trust InvIT IPOLT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>31-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>30-Jul 19:00</t>
+          <t>31-Jul 9:31</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1509,58 +1509,58 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Xtranet Technologies IPOL@136.00 (7.09%)</t>
+          <t>Silverstorm Parks &amp; Resorts BSE SMEL@132.90 (-0.08%)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹14.5 (11.42%) 7.50 ↓ / 26 ↑</t>
+          <t>₹5 (3.76%) 5 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>12.24x</t>
+          <t>1.91x</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹166.80 Cr</t>
+          <t>₹82.43 Cr</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 8</t>
+          <t>24-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 7.7</t>
+          <t>28-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>28-Jul</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 14.5</t>
+          <t>31-Jul GMP: 5</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>30-Jul 9:31</t>
+          <t>31-Jul 9:34</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1572,43 +1572,43 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lohia Corp IPOL@461.00 (8.47%)</t>
+          <t>Xtranet Technologies IPOL@136.00 (7.09%)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹17 (4.00%) 7 ↓ / 56 ↑</t>
+          <t>₹14.5 (11.42%) 7.50 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.26x</t>
+          <t>12.24x</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>425</v>
+        <v>127</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹1101.28 Cr</t>
+          <t>₹166.80 Cr</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 12</t>
+          <t>23-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 11.5</t>
+          <t>27-Jul GMP: 7.7</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1618,12 +1618,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 17</t>
+          <t>30-Jul GMP: 14.5</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>30-Jul 9:30</t>
+          <t>30-Jul 9:31</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1635,43 +1635,43 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Indo-MIM IPOL@700.00 (44.33%)</t>
+          <t>Lohia Corp IPOL@461.00 (8.47%)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹184 (37.94%) 168 ↓ / 213 ↑</t>
+          <t>₹17 (4.00%) 7 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>72.37x</t>
+          <t>7.26x</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>485</v>
+        <v>425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹3811.21 Cr</t>
+          <t>₹1101.28 Cr</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 170</t>
+          <t>23-Jul GMP: 12</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 190</t>
+          <t>27-Jul GMP: 11.5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 184</t>
+          <t>30-Jul GMP: 17</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>30-Jul 9:36</t>
+          <t>30-Jul 9:30</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1698,58 +1698,58 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Shree Balaji Mala BSE SMEL@133.00 (90%)</t>
+          <t>Indo-MIM IPOL@700.00 (44.33%)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹56 (80.00%) 11 ↓ / 56 ↑</t>
+          <t>₹184 (37.94%) 168 ↓ / 213 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>200.34x</t>
+          <t>72.37x</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>70</v>
+        <v>485</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹18.90 Cr</t>
+          <t>₹3811.21 Cr</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2000</v>
+        <v>30</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 16</t>
+          <t>23-Jul GMP: 170</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 13</t>
+          <t>27-Jul GMP: 190</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>27-Jul</t>
+          <t>28-Jul</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 56</t>
+          <t>30-Jul GMP: 184</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>29-Jul 9:29</t>
+          <t>30-Jul 9:36</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1761,58 +1761,58 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Metalic Technoforge NSE SMEL@87.00 (12.99%)</t>
+          <t>Shree Balaji Mala BSE SMEL@133.00 (90%)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹6 (7.79%) 6 ↓ / 8.10 ↑</t>
+          <t>₹56 (80.00%) 11 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.47x</t>
+          <t>200.34x</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹49.96 Cr</t>
+          <t>₹18.90 Cr</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 0</t>
+          <t>22-Jul GMP: 16</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 6</t>
+          <t>24-Jul GMP: 13</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>24-Jul</t>
+          <t>27-Jul</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 6</t>
+          <t>29-Jul GMP: 56</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>28-Jul 9:29</t>
+          <t>29-Jul 9:29</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1824,184 +1824,184 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gulf Lloyds BSE SMEL@100.00 (0%)</t>
+          <t>Metalic Technoforge NSE SMEL@87.00 (12.99%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹1 (1.00%) 1 ↓ / 25 ↑</t>
+          <t>₹6 (7.79%) 6 ↓ / 8.10 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10.85x</t>
+          <t>8.47x</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹18.19 Cr</t>
+          <t>₹49.96 Cr</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>20-Jul GMP: 10</t>
+          <t>21-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 1</t>
+          <t>23-Jul GMP: 6</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>23-Jul</t>
+          <t>24-Jul</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 1</t>
+          <t>28-Jul GMP: 6</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>27-Jul 9:29</t>
+          <t>28-Jul 9:29</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Caliber Mining IPOL@500.25 (17.98%)</t>
+          <t>Gulf Lloyds BSE SMEL@100.00 (0%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹60 (14.15%) 60 ↓ / 117 ↑</t>
+          <t>₹1 (1.00%) 1 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>154.66x</t>
+          <t>10.85x</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>424</v>
+        <v>100</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹450.00 Cr</t>
+          <t>₹18.19 Cr</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>35</v>
+        <v>1200</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>17-Jul GMP: 116</t>
+          <t>20-Jul GMP: 10</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 71</t>
+          <t>22-Jul GMP: 1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>22-Jul</t>
+          <t>23-Jul</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 60</t>
+          <t>27-Jul GMP: 1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>24-Jul 9:35</t>
+          <t>27-Jul 9:29</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sotefin Bharat BSE SMEL@205.00 (9.63%)</t>
+          <t>Caliber Mining IPOL@500.25 (17.98%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹2.5 (1.34%) 1 ↓ / 27 ↑</t>
+          <t>₹60 (14.15%) 60 ↓ / 117 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3.99x</t>
+          <t>154.66x</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>187</v>
+        <v>424</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹89.76 Cr</t>
+          <t>₹450.00 Cr</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>600</v>
+        <v>35</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 18</t>
+          <t>17-Jul GMP: 116</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20-Jul GMP: 1</t>
+          <t>21-Jul GMP: 71</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>21-Jul</t>
+          <t>22-Jul</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 2.5</t>
+          <t>24-Jul GMP: 60</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>23-Jul 9:34</t>
+          <t>24-Jul 9:35</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2013,12 +2013,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alpine Texworld IPOL@105.00 (0%)</t>
+          <t>Sotefin Bharat BSE SMEL@205.00 (9.63%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹1 (0.95%) 1 ↓ / 5 ↑</t>
+          <t>₹2.5 (1.34%) 1 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2028,48 +2028,48 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>3.99x</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹126.25 Cr</t>
+          <t>₹89.76 Cr</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>142</v>
+        <v>600</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>14-Jul GMP: 5</t>
+          <t>16-Jul GMP: 18</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 1</t>
+          <t>20-Jul GMP: 1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>17-Jul</t>
+          <t>21-Jul</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 1</t>
+          <t>23-Jul GMP: 2.5</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>21-Jul 9:35</t>
+          <t>23-Jul 9:34</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -2139,43 +2139,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Millworks Technologies BSE SMEL@628.90 (90%)</t>
+          <t>Alpine Texworld IPOL@105.00 (0%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹395 (119.34%) 300 ↓ / 400 ↑</t>
+          <t>₹1 (0.95%) 1 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>219.54x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>331</v>
+        <v>105</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹160.34 Cr</t>
+          <t>₹126.25 Cr</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>400</v>
+        <v>142</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>14-Jul GMP: 300</t>
+          <t>14-Jul GMP: 5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 380</t>
+          <t>16-Jul GMP: 1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2185,75 +2185,75 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 395</t>
+          <t>21-Jul GMP: 1</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>21-Jul 9:32</t>
+          <t>21-Jul 9:35</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Laser Power &amp; Infra IPOL@250.00 (16.82%)</t>
+          <t>Millworks Technologies BSE SMEL@628.90 (90%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹39 (18.22%) 15 ↓ / 42 ↑</t>
+          <t>₹395 (119.34%) 300 ↓ / 400 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>41.05x</t>
+          <t>219.54x</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>214</v>
+        <v>331</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹742.00 Cr</t>
+          <t>₹160.34 Cr</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>70</v>
+        <v>400</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>9-Jul GMP: 24</t>
+          <t>14-Jul GMP: 300</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>13-Jul GMP: 40.5</t>
+          <t>16-Jul GMP: 380</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>14-Jul</t>
+          <t>17-Jul</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 39</t>
+          <t>21-Jul GMP: 395</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>16-Jul 9:29</t>
+          <t>21-Jul 9:32</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,12 +501,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LAPL Automotive BSE SMEU</t>
+          <t>Technocraft Ventures IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -519,40 +519,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>94</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹32.40 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1200</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>31-Jul 11:37</t>
+          <t>31-Jul 14:40</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -564,17 +560,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOU</t>
+          <t>Optimystix Entertainment NSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹13 (24.53%) 13 ↓ / 13 ↑</t>
+          <t>₹-- (%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -582,40 +578,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>53</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>281</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>31-Jul 11:34</t>
+          <t>31-Jul 15:30</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -627,17 +619,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aegeus Technologies BSE SMEU</t>
+          <t>LAPL Automotive BSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹7 (7.45%) 7 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -646,11 +638,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹23.71 Cr</t>
+          <t>₹32.40 Cr</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -658,27 +650,27 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>31-Jul 11:37</t>
+          <t>31-Jul 16:36</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -690,17 +682,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Anawil Wire &amp; Engineering NSE SMEU</t>
+          <t>Ardee Industries IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹65 (24.07%) 60 ↓ / 70 ↑</t>
+          <t>₹10 (18.87%) 10 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -709,39 +701,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>270</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹177.81 Cr</t>
+          <t>₹425.87 Cr</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>400</v>
+        <v>281</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>31-Jul 11:31</t>
+          <t>31-Jul 16:28</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -753,58 +745,58 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEO</t>
+          <t>Aegeus Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹25 (19.23%) 18 ↓ / 25 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.23x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹23.71 Cr</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 25</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>31-Jul 11:31</t>
+          <t>31-Jul 16:29</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -816,58 +808,58 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fusion Klassroom Edutech BSE SMEO</t>
+          <t>Anawil Wire &amp; Engineering NSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹9 (5.66%) 9 ↓ / 9 ↑</t>
+          <t>₹65 (24.07%) 60 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.14x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>159</v>
+        <v>270</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹39.04 Cr</t>
+          <t>₹177.81 Cr</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 9</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>31-Jul 11:31</t>
+          <t>31-Jul 16:31</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -879,58 +871,58 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Oneindig Technologies BSE SMEO</t>
+          <t>G.V. Electricals BSE SMEO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹25 (19.23%) 18 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.42x</t>
+          <t>2.2x</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹27.65 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 0</t>
+          <t>31-Jul GMP: 25</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>31-Jul 11:29</t>
+          <t>31-Jul 16:30</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -942,58 +934,58 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dhaval Packaging BSE SMEO</t>
+          <t>Fusion Klassroom Edutech BSE SMEO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹12 (12.37%) 8 ↓ / 15 ↑</t>
+          <t>₹7 (4.40%) 7 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.64x</t>
+          <t>0.76x</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹36.36 Cr</t>
+          <t>₹39.04 Cr</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 15</t>
+          <t>31-Jul GMP: 7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>31-Jul 11:28</t>
+          <t>31-Jul 16:34</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1005,38 +997,38 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MV Electrosystems IPOO</t>
+          <t>Dhaval Packaging BSE SMEO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹133 (31.29%) 60 ↓ / 133 ↑</t>
+          <t>₹12 (12.37%) 8 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6.77x</t>
+          <t>1.33x</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>425</v>
+        <v>97</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹290.00 Cr</t>
+          <t>₹36.36 Cr</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>34</v>
+        <v>1200</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 125</t>
+          <t>30-Jul GMP: 15</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1056,7 +1048,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>31-Jul 11:28</t>
+          <t>31-Jul 16:31</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1068,38 +1060,38 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Juniper Green Energy IPOO</t>
+          <t>MV Electrosystems IPOO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹6 (2.67%) 6 ↓ / 17 ↑</t>
+          <t>₹133 (31.29%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.43x</t>
+          <t>12.22x</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>225</v>
+        <v>425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹1800.00 Cr</t>
+          <t>₹290.00 Cr</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 8</t>
+          <t>30-Jul GMP: 125</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1119,7 +1111,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>31-Jul 11:30</t>
+          <t>31-Jul 16:29</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1131,12 +1123,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Manipal Health Enterprises IPOCT</t>
+          <t>Juniper Green Energy IPOO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹3.75 (0.64%) 3.75 ↓ / 35 ↑</t>
+          <t>₹5.5 (2.44%) 5.50 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1146,43 +1138,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.55x</t>
+          <t>0.49x</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>590</v>
+        <v>225</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹9275.22 Cr</t>
+          <t>₹1800.00 Cr</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 9</t>
+          <t>30-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 3.75</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>31-Jul 11:32</t>
+          <t>31-Jul 16:31</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1194,12 +1186,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H.R. Hygiene Products BSE SMECT</t>
+          <t>Oneindig Technologies BSE SMEO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹2 (2.27%) 2 ↓ / 2 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1209,43 +1201,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.17x</t>
+          <t>0.79x</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹53.95 Cr</t>
+          <t>₹27.65 Cr</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 2</t>
+          <t>30-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 2</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>31-Jul 11:36</t>
+          <t>31-Jul 16:33</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1257,58 +1249,58 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Poojaa Precision Engg. BSE SMEC</t>
+          <t>H.R. Hygiene Products BSE SMECT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹225 (74.75%) 195 ↓ / 300 ↑</t>
+          <t>₹2 (2.27%) 2 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>278.83x</t>
+          <t>6.61x</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>301</v>
+        <v>88</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹159.83 Cr</t>
+          <t>₹53.95 Cr</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>400</v>
+        <v>1600</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 300</t>
+          <t>29-Jul GMP: 2</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 225</t>
+          <t>31-Jul GMP: 2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>31-Jul 11:34</t>
+          <t>31-Jul 16:37</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1320,138 +1312,138 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Advance Technoforge BSE SMEC</t>
+          <t>Manipal Health Enterprises IPOCT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹5 (5.26%) 3.50 ↓ / 9 ↑</t>
+          <t>₹3 (0.51%) 3 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.55x</t>
+          <t>5.11x</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>95</v>
+        <v>590</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹24.03 Cr</t>
+          <t>₹9275.22 Cr</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1200</v>
+        <v>25</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 9</t>
+          <t>29-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 8</t>
+          <t>31-Jul GMP: 3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>31-Jul 11:30</t>
+          <t>31-Jul 16:36</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Propshop Events &amp; Exhibitions NSE SMECAllotted</t>
+          <t>Poojaa Precision Engg. BSE SMEC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹225 (74.75%) 195 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.53x</t>
+          <t>278.83x</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>69</v>
+        <v>301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹28.57 Cr</t>
+          <t>₹159.83 Cr</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 0</t>
+          <t>28-Jul GMP: 300</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 0</t>
+          <t>30-Jul GMP: 225</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>31-Jul</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>31-Jul 11:35</t>
+          <t>31-Jul 16:37</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cube Highways Trust InvIT IPOLT</t>
+          <t>Propshop Events &amp; Exhibitions NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1461,169 +1453,169 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9.35x</t>
+          <t>1.53x</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>₹5000.00 Cr</t>
+          <t>₹28.57 Cr</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>95</v>
+        <v>2000</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 0</t>
+          <t>27-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 1.75</t>
+          <t>29-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 1.75</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>31-Jul 9:31</t>
+          <t>31-Jul 16:35</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Silverstorm Parks &amp; Resorts BSE SMEL@132.90 (-0.08%)</t>
+          <t>Advance Technoforge BSE SMEC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹5 (3.76%) 5 ↓ / 5 ↑</t>
+          <t>₹5 (5.26%) 3.50 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.91x</t>
+          <t>1.55x</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹82.43 Cr</t>
+          <t>₹24.03 Cr</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 0</t>
+          <t>27-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 0</t>
+          <t>29-Jul GMP: 8</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 5</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>31-Jul 9:34</t>
+          <t>31-Jul 16:29</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Xtranet Technologies IPOL@136.00 (7.09%)</t>
+          <t>Silverstorm Parks &amp; Resorts BSE SMEL@132.90 (-0.08%)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹14.5 (11.42%) 7.50 ↓ / 26 ↑</t>
+          <t>₹5 (3.76%) 5 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>12.24x</t>
+          <t>1.91x</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹166.80 Cr</t>
+          <t>₹82.43 Cr</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 8</t>
+          <t>24-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 7.7</t>
+          <t>28-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>28-Jul</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 14.5</t>
+          <t>31-Jul GMP: 5</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>30-Jul 9:31</t>
+          <t>31-Jul 9:34</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1635,43 +1627,43 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lohia Corp IPOL@461.00 (8.47%)</t>
+          <t>Xtranet Technologies IPOL@136.00 (7.09%)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹17 (4.00%) 7 ↓ / 56 ↑</t>
+          <t>₹14.5 (11.42%) 7.50 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7.26x</t>
+          <t>12.24x</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>425</v>
+        <v>127</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹1101.28 Cr</t>
+          <t>₹166.80 Cr</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 12</t>
+          <t>23-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 11.5</t>
+          <t>27-Jul GMP: 7.7</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1681,12 +1673,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 17</t>
+          <t>30-Jul GMP: 14.5</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>30-Jul 9:30</t>
+          <t>30-Jul 9:31</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1698,43 +1690,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Indo-MIM IPOL@700.00 (44.33%)</t>
+          <t>Lohia Corp IPOL@461.00 (8.47%)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹184 (37.94%) 168 ↓ / 213 ↑</t>
+          <t>₹17 (4.00%) 7 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>72.37x</t>
+          <t>7.26x</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>485</v>
+        <v>425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹3811.21 Cr</t>
+          <t>₹1101.28 Cr</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 170</t>
+          <t>23-Jul GMP: 12</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 190</t>
+          <t>27-Jul GMP: 11.5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1744,12 +1736,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 184</t>
+          <t>30-Jul GMP: 17</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>30-Jul 9:36</t>
+          <t>30-Jul 9:30</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1761,58 +1753,58 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Shree Balaji Mala BSE SMEL@133.00 (90%)</t>
+          <t>Indo-MIM IPOL@700.00 (44.33%)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹56 (80.00%) 11 ↓ / 56 ↑</t>
+          <t>₹184 (37.94%) 168 ↓ / 213 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>200.34x</t>
+          <t>72.37x</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>70</v>
+        <v>485</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹18.90 Cr</t>
+          <t>₹3811.21 Cr</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2000</v>
+        <v>30</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 16</t>
+          <t>23-Jul GMP: 170</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 13</t>
+          <t>27-Jul GMP: 190</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>27-Jul</t>
+          <t>28-Jul</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 56</t>
+          <t>30-Jul GMP: 184</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>29-Jul 9:29</t>
+          <t>30-Jul 9:36</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1824,58 +1816,58 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Metalic Technoforge NSE SMEL@87.00 (12.99%)</t>
+          <t>Shree Balaji Mala BSE SMEL@133.00 (90%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹6 (7.79%) 6 ↓ / 8.10 ↑</t>
+          <t>₹56 (80.00%) 11 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.47x</t>
+          <t>200.34x</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹49.96 Cr</t>
+          <t>₹18.90 Cr</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 0</t>
+          <t>22-Jul GMP: 16</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 6</t>
+          <t>24-Jul GMP: 13</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>24-Jul</t>
+          <t>27-Jul</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 6</t>
+          <t>29-Jul GMP: 56</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>28-Jul 9:29</t>
+          <t>29-Jul 9:29</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1887,12 +1879,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gulf Lloyds BSE SMEL@100.00 (0%)</t>
+          <t>Cube Highways Trust InvIT IPOLT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹1 (1.00%) 1 ↓ / 25 ↑</t>
+          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1902,106 +1894,106 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10.85x</t>
+          <t>9.35x</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹18.19 Cr</t>
+          <t>₹5000.00 Cr</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1200</v>
+        <v>95</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>20-Jul GMP: 10</t>
+          <t>22-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 1</t>
+          <t>24-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>23-Jul</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 1</t>
+          <t>31-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>27-Jul 9:29</t>
+          <t>31-Jul 9:31</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Caliber Mining IPOL@500.25 (17.98%)</t>
+          <t>Metalic Technoforge NSE SMEL@87.00 (12.99%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹60 (14.15%) 60 ↓ / 117 ↑</t>
+          <t>₹6 (7.79%) 6 ↓ / 8.10 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>154.66x</t>
+          <t>8.47x</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>424</v>
+        <v>77</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹450.00 Cr</t>
+          <t>₹49.96 Cr</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>35</v>
+        <v>1600</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>17-Jul GMP: 116</t>
+          <t>21-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 71</t>
+          <t>23-Jul GMP: 6</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>22-Jul</t>
+          <t>24-Jul</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 60</t>
+          <t>28-Jul GMP: 6</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>24-Jul 9:35</t>
+          <t>28-Jul 9:29</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2013,12 +2005,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sotefin Bharat BSE SMEL@205.00 (9.63%)</t>
+          <t>Gulf Lloyds BSE SMEL@100.00 (0%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹2.5 (1.34%) 1 ↓ / 27 ↑</t>
+          <t>₹1 (1.00%) 1 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2028,60 +2020,60 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3.99x</t>
+          <t>10.85x</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>187</v>
+        <v>100</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹89.76 Cr</t>
+          <t>₹18.19 Cr</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 18</t>
+          <t>20-Jul GMP: 10</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20-Jul GMP: 1</t>
+          <t>22-Jul GMP: 1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>21-Jul</t>
+          <t>23-Jul</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 2.5</t>
+          <t>27-Jul GMP: 1</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>23-Jul 9:34</t>
+          <t>27-Jul 9:29</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SBI Funds Management IPOL@613.30 (6.85%)</t>
+          <t>Caliber Mining IPOL@500.25 (17.98%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹65 (11.32%) 65 ↓ / 140 ↑</t>
+          <t>₹60 (14.15%) 60 ↓ / 117 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2091,43 +2083,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>41.73x</t>
+          <t>154.66x</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>574</v>
+        <v>424</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹9812.91 Cr</t>
+          <t>₹450.00 Cr</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>14-Jul GMP: 88</t>
+          <t>17-Jul GMP: 116</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 97</t>
+          <t>21-Jul GMP: 71</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>17-Jul</t>
+          <t>22-Jul</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 65</t>
+          <t>24-Jul GMP: 60</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>21-Jul 9:35</t>
+          <t>24-Jul 9:35</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2139,12 +2131,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alpine Texworld IPOL@105.00 (0%)</t>
+          <t>Sotefin Bharat BSE SMEL@205.00 (9.63%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹1 (0.95%) 1 ↓ / 5 ↑</t>
+          <t>₹2.5 (1.34%) 1 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2154,48 +2146,48 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>3.99x</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹126.25 Cr</t>
+          <t>₹89.76 Cr</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>142</v>
+        <v>600</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>14-Jul GMP: 5</t>
+          <t>16-Jul GMP: 18</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 1</t>
+          <t>20-Jul GMP: 1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>17-Jul</t>
+          <t>21-Jul</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 1</t>
+          <t>23-Jul GMP: 2.5</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>21-Jul 9:35</t>
+          <t>23-Jul 9:34</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -2265,75 +2257,75 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Devson Catalyst BSE SMEL@196.15 (66.23%)</t>
+          <t>Alpine Texworld IPOL@105.00 (0%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹49 (41.53%) 8 ↓ / 51 ↑</t>
+          <t>₹1 (0.95%) 1 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>220.35x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹42.34 Cr</t>
+          <t>₹126.25 Cr</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1200</v>
+        <v>142</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>9-Jul GMP: 45</t>
+          <t>14-Jul GMP: 5</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>13-Jul GMP: 49</t>
+          <t>16-Jul GMP: 1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>14-Jul</t>
+          <t>17-Jul</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 49</t>
+          <t>21-Jul GMP: 1</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>16-Jul 9:37</t>
+          <t>21-Jul 9:35</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Happy Steels NSE SMEL@68.00 (3.03%)</t>
+          <t>SBI Funds Management IPOL@613.30 (6.85%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹10 (15.15%) 7 ↓ / 14 ↑</t>
+          <t>₹65 (11.32%) 65 ↓ / 140 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2343,43 +2335,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>77.81x</t>
+          <t>41.73x</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>66</v>
+        <v>574</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹25.00 Cr</t>
+          <t>₹9812.91 Cr</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2000</v>
+        <v>26</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>9-Jul GMP: 8</t>
+          <t>14-Jul GMP: 88</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>13-Jul GMP: 8</t>
+          <t>16-Jul GMP: 97</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>14-Jul</t>
+          <t>17-Jul</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 10</t>
+          <t>21-Jul GMP: 65</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>16-Jul 9:29</t>
+          <t>21-Jul 9:35</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>31-Jul 14:40</t>
+          <t>1-Aug 5:55</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>31-Jul 15:30</t>
+          <t>1-Aug 5:55</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -624,12 +624,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹7 (7.45%) 7 ↓ / 7 ↑</t>
+          <t>₹22 (23.40%) 22 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>31-Jul 16:36</t>
+          <t>1-Aug 10:28</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹10 (18.87%) 10 ↓ / 13 ↑</t>
+          <t>₹6.5 (12.26%) 6.50 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>31-Jul 16:28</t>
+          <t>1-Aug 10:30</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>31-Jul 16:29</t>
+          <t>1-Aug 10:29</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹65 (24.07%) 60 ↓ / 70 ↑</t>
+          <t>₹80 (29.63%) 60 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>31-Jul 16:31</t>
+          <t>1-Aug 10:33</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.2x</t>
+          <t>2.3x</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>31-Jul 16:30</t>
+          <t>1-Aug 10:29</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹7 (4.40%) 7 ↓ / 9 ↑</t>
+          <t>₹4 (2.52%) 4 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.76x</t>
+          <t>0.79x</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -965,7 +965,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 7</t>
+          <t>31-Jul GMP: 4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>31-Jul 16:34</t>
+          <t>1-Aug 10:35</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.33x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>31-Jul 16:31</t>
+          <t>1-Aug 10:32</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12.22x</t>
+          <t>12.79x</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>31-Jul 16:29</t>
+          <t>1-Aug 10:28</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹5.5 (2.44%) 5.50 ↓ / 17 ↑</t>
+          <t>₹2.5 (1.11%) 2.50 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>31-Jul 16:31</t>
+          <t>1-Aug 10:31</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>31-Jul 16:33</t>
+          <t>1-Aug 10:33</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1249,7 +1249,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H.R. Hygiene Products BSE SMECT</t>
+          <t>H.R. Hygiene Products BSE SMEC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6.61x</t>
+          <t>6.65x</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>31-Jul 16:37</t>
+          <t>1-Aug 10:30</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1312,12 +1312,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Manipal Health Enterprises IPOCT</t>
+          <t>Manipal Health Enterprises IPOC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹3 (0.51%) 3 ↓ / 35 ↑</t>
+          <t>₹-15 (-2.54%) -15 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5.11x</t>
+          <t>5.12x</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 3</t>
+          <t>31-Jul GMP: -15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>31-Jul 16:36</t>
+          <t>1-Aug 10:33</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1375,7 +1375,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Poojaa Precision Engg. BSE SMEC</t>
+          <t>Poojaa Precision Engg. BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>31-Jul 16:37</t>
+          <t>1-Aug 10:29</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>31-Jul 16:35</t>
+          <t>1-Aug 10:33</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹5 (5.26%) 3.50 ↓ / 9 ↑</t>
+          <t>₹3 (3.16%) 3 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹24.03 Cr</t>
+          <t>₹24.04 Cr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>31-Jul 16:29</t>
+          <t>1-Aug 10:29</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1564,12 +1564,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Silverstorm Parks &amp; Resorts BSE SMEL@132.90 (-0.08%)</t>
+          <t>Cube Highways Trust InvIT IPOCAllotted</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹5 (3.76%) 5 ↓ / 5 ↑</t>
+          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1579,28 +1579,28 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.91x</t>
+          <t>9.35x</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹82.43 Cr</t>
+          <t>₹5000.00 Cr</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 0</t>
+          <t>22-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 0</t>
+          <t>24-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 5</t>
+          <t>31-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>31-Jul 9:34</t>
+          <t>1-Aug 5:55</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1627,58 +1627,58 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Xtranet Technologies IPOL@136.00 (7.09%)</t>
+          <t>Silverstorm Parks &amp; Resorts BSE SMEL@132.90 (-0.08%)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹14.5 (11.42%) 7.50 ↓ / 26 ↑</t>
+          <t>₹5 (3.76%) 5 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>12.24x</t>
+          <t>1.91x</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹166.80 Cr</t>
+          <t>₹82.43 Cr</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 8</t>
+          <t>24-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 7.7</t>
+          <t>28-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>28-Jul</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 14.5</t>
+          <t>31-Jul GMP: 5</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>30-Jul 9:31</t>
+          <t>31-Jul 9:34</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1690,43 +1690,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lohia Corp IPOL@461.00 (8.47%)</t>
+          <t>Indo-MIM IPOL@700.00 (44.33%)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹17 (4.00%) 7 ↓ / 56 ↑</t>
+          <t>₹184 (37.94%) 168 ↓ / 213 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7.26x</t>
+          <t>72.37x</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>425</v>
+        <v>485</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹1101.28 Cr</t>
+          <t>₹3811.21 Cr</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 12</t>
+          <t>23-Jul GMP: 170</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 11.5</t>
+          <t>27-Jul GMP: 190</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1736,12 +1736,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 17</t>
+          <t>30-Jul GMP: 184</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>30-Jul 9:30</t>
+          <t>30-Jul 9:36</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1753,43 +1753,43 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Indo-MIM IPOL@700.00 (44.33%)</t>
+          <t>Lohia Corp IPOL@461.00 (8.47%)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹184 (37.94%) 168 ↓ / 213 ↑</t>
+          <t>₹17 (4.00%) 7 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>72.37x</t>
+          <t>7.26x</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>485</v>
+        <v>425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹3811.21 Cr</t>
+          <t>₹1101.28 Cr</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 170</t>
+          <t>23-Jul GMP: 12</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 190</t>
+          <t>27-Jul GMP: 11.5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 184</t>
+          <t>30-Jul GMP: 17</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>30-Jul 9:36</t>
+          <t>30-Jul 9:30</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1816,58 +1816,58 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Shree Balaji Mala BSE SMEL@133.00 (90%)</t>
+          <t>Xtranet Technologies IPOL@136.00 (7.09%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹56 (80.00%) 11 ↓ / 56 ↑</t>
+          <t>₹14.5 (11.42%) 7.50 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>200.34x</t>
+          <t>12.24x</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>70</v>
+        <v>127</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹18.90 Cr</t>
+          <t>₹166.80 Cr</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2000</v>
+        <v>110</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 16</t>
+          <t>23-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 13</t>
+          <t>27-Jul GMP: 7.7</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>27-Jul</t>
+          <t>28-Jul</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 56</t>
+          <t>30-Jul GMP: 14.5</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>29-Jul 9:29</t>
+          <t>30-Jul 9:31</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1879,58 +1879,58 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cube Highways Trust InvIT IPOLT</t>
+          <t>Shree Balaji Mala BSE SMEL@133.00 (90%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
+          <t>₹56 (80.00%) 11 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>9.35x</t>
+          <t>200.34x</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹5000.00 Cr</t>
+          <t>₹18.90 Cr</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>95</v>
+        <v>2000</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 0</t>
+          <t>22-Jul GMP: 16</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 1.75</t>
+          <t>24-Jul GMP: 13</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>27-Jul</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 1.75</t>
+          <t>29-Jul GMP: 56</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>31-Jul 9:31</t>
+          <t>29-Jul 9:29</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2257,43 +2257,43 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alpine Texworld IPOL@105.00 (0%)</t>
+          <t>SBI Funds Management IPOL@613.30 (6.85%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹1 (0.95%) 1 ↓ / 5 ↑</t>
+          <t>₹65 (11.32%) 65 ↓ / 140 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>41.73x</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>105</v>
+        <v>574</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹126.25 Cr</t>
+          <t>₹9812.91 Cr</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>142</v>
+        <v>26</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>14-Jul GMP: 5</t>
+          <t>14-Jul GMP: 88</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 1</t>
+          <t>16-Jul GMP: 97</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 1</t>
+          <t>21-Jul GMP: 65</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2313,50 +2313,50 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SBI Funds Management IPOL@613.30 (6.85%)</t>
+          <t>Alpine Texworld IPOL@105.00 (0%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹65 (11.32%) 65 ↓ / 140 ↑</t>
+          <t>₹1 (0.95%) 1 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>41.73x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>574</v>
+        <v>105</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹9812.91 Cr</t>
+          <t>₹126.25 Cr</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>26</v>
+        <v>142</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>14-Jul GMP: 88</t>
+          <t>14-Jul GMP: 5</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 97</t>
+          <t>16-Jul GMP: 1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 65</t>
+          <t>21-Jul GMP: 1</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -624,7 +624,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹22 (23.40%) 22 ↓ / 22 ↑</t>
+          <t>₹25 (26.60%) 22 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1-Aug 10:28</t>
+          <t>1-Aug 15:55</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹6.5 (12.26%) 6.50 ↓ / 13 ↑</t>
+          <t>₹6 (11.32%) 6 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1-Aug 10:30</t>
+          <t>1-Aug 16:00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1-Aug 10:29</t>
+          <t>1-Aug 15:55</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹80 (29.63%) 60 ↓ / 80 ↑</t>
+          <t>₹90 (33.33%) 60 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1-Aug 10:33</t>
+          <t>1-Aug 15:57</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹25 (19.23%) 18 ↓ / 25 ↑</t>
+          <t>₹26 (20.00%) 18 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1-Aug 10:29</t>
+          <t>1-Aug 15:53</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1-Aug 10:35</t>
+          <t>1-Aug 15:59</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1-Aug 10:32</t>
+          <t>1-Aug 15:55</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹133 (31.29%) 60 ↓ / 133 ↑</t>
+          <t>₹115 (27.06%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1-Aug 10:28</t>
+          <t>1-Aug 15:56</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹2.5 (1.11%) 2.50 ↓ / 17 ↑</t>
+          <t>₹2 (0.89%) 2 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1-Aug 10:31</t>
+          <t>1-Aug 15:54</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1-Aug 10:33</t>
+          <t>1-Aug 16:02</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1-Aug 10:30</t>
+          <t>1-Aug 15:58</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹-15 (-2.54%) -15 ↓ / 35 ↑</t>
+          <t>₹-8 (-1.36%) -15 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1-Aug 10:33</t>
+          <t>1-Aug 15:56</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹225 (74.75%) 195 ↓ / 300 ↑</t>
+          <t>₹215 (71.43%) 195 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1-Aug 10:29</t>
+          <t>1-Aug 15:55</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1-Aug 10:33</t>
+          <t>1-Aug 16:00</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1-Aug 10:29</t>
+          <t>1-Aug 15:56</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1-Aug 5:55</t>
+          <t>2-Aug 5:55</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1-Aug 5:55</t>
+          <t>2-Aug 5:55</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1-Aug 15:55</t>
+          <t>2-Aug 10:57</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹6 (11.32%) 6 ↓ / 13 ↑</t>
+          <t>₹7 (13.21%) 6.50 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1-Aug 16:00</t>
+          <t>2-Aug 10:53</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1-Aug 15:55</t>
+          <t>2-Aug 10:53</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1-Aug 15:57</t>
+          <t>2-Aug 10:53</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1-Aug 15:53</t>
+          <t>2-Aug 10:54</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1-Aug 15:59</t>
+          <t>2-Aug 10:53</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹12 (12.37%) 8 ↓ / 15 ↑</t>
+          <t>₹11 (11.34%) 8 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1-Aug 15:55</t>
+          <t>2-Aug 10:53</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹115 (27.06%) 60 ↓ / 133 ↑</t>
+          <t>₹110 (25.88%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1-Aug 15:56</t>
+          <t>2-Aug 11:00</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹2 (0.89%) 2 ↓ / 17 ↑</t>
+          <t>₹1.5 (0.67%) 1.50 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1-Aug 15:54</t>
+          <t>2-Aug 10:58</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1-Aug 16:02</t>
+          <t>2-Aug 10:58</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1-Aug 15:58</t>
+          <t>2-Aug 10:59</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹-8 (-1.36%) -15 ↓ / 35 ↑</t>
+          <t>₹-9 (-1.53%) -15 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1-Aug 15:56</t>
+          <t>2-Aug 11:00</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹215 (71.43%) 195 ↓ / 300 ↑</t>
+          <t>₹220 (73.09%) 195 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1-Aug 15:55</t>
+          <t>2-Aug 10:54</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1-Aug 16:00</t>
+          <t>2-Aug 10:58</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹3 (3.16%) 3 ↓ / 9 ↑</t>
+          <t>₹4 (4.21%) 3 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1-Aug 15:56</t>
+          <t>2-Aug 10:54</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1-Aug 5:55</t>
+          <t>2-Aug 5:55</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2-Aug 10:57</t>
+          <t>2-Aug 15:57</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹7 (13.21%) 6.50 ↓ / 13 ↑</t>
+          <t>₹6.75 (12.74%) 6.50 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2-Aug 10:53</t>
+          <t>2-Aug 16:01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2-Aug 10:53</t>
+          <t>2-Aug 15:56</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2-Aug 10:53</t>
+          <t>2-Aug 15:55</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2-Aug 10:54</t>
+          <t>2-Aug 15:58</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2-Aug 10:53</t>
+          <t>2-Aug 15:56</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2-Aug 10:53</t>
+          <t>2-Aug 15:58</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹110 (25.88%) 60 ↓ / 133 ↑</t>
+          <t>₹113 (26.59%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2-Aug 11:00</t>
+          <t>2-Aug 15:55</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2-Aug 10:58</t>
+          <t>2-Aug 16:02</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2-Aug 10:58</t>
+          <t>2-Aug 16:00</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2-Aug 10:59</t>
+          <t>2-Aug 16:00</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹-9 (-1.53%) -15 ↓ / 35 ↑</t>
+          <t>₹-7 (-1.19%) -15 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2-Aug 11:00</t>
+          <t>2-Aug 16:01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹220 (73.09%) 195 ↓ / 300 ↑</t>
+          <t>₹225 (74.75%) 195 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2-Aug 10:54</t>
+          <t>2-Aug 16:02</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2-Aug 10:58</t>
+          <t>2-Aug 15:57</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2-Aug 10:54</t>
+          <t>2-Aug 15:57</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,12 +506,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹16.5 (7.78%) 16.50 ↓ / 16.50 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -519,13 +519,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>212</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>₹251.88 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>70</v>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>7-Aug</t>
@@ -548,7 +552,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2-Aug 5:55</t>
+          <t>3-Aug 11:55</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -560,12 +564,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Optimystix Entertainment NSE SMEU</t>
+          <t>LEAP India IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹7 (4.40%) 7 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -578,13 +582,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>159</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>₹2480.00 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>94</v>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>7-Aug</t>
@@ -607,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2-Aug 5:55</t>
+          <t>3-Aug 11:56</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -619,17 +627,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LAPL Automotive BSE SMEU</t>
+          <t>Optimystix Entertainment NSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹25 (26.60%) 22 ↓ / 25 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -637,40 +645,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>94</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹32.40 Cr</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1200</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2-Aug 15:57</t>
+          <t>3-Aug 5:55</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -682,17 +686,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOU</t>
+          <t>LAPL Automotive BSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹6.75 (12.74%) 6.50 ↓ / 13 ↑</t>
+          <t>₹25 (26.60%) 22 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -701,39 +705,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
+          <t>₹32.40 Cr</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>281</v>
+        <v>1200</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2-Aug 16:01</t>
+          <t>3-Aug 11:58</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -745,17 +749,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aegeus Technologies BSE SMEU</t>
+          <t>Ardee Industries IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6.75 (12.74%) 6.50 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -764,39 +768,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹23.71 Cr</t>
+          <t>₹425.87 Cr</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1200</v>
+        <v>281</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2-Aug 15:56</t>
+          <t>3-Aug 11:56</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -808,17 +812,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Anawil Wire &amp; Engineering NSE SMEU</t>
+          <t>Aegeus Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹90 (33.33%) 60 ↓ / 90 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -827,39 +831,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>270</v>
+        <v>105</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹177.81 Cr</t>
+          <t>₹23.71 Cr</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2-Aug 15:55</t>
+          <t>3-Aug 11:58</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -871,12 +875,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEO</t>
+          <t>Anawil Wire &amp; Engineering NSE SMEO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹26 (20.00%) 18 ↓ / 26 ↑</t>
+          <t>₹80 (29.63%) 60 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -886,43 +890,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.3x</t>
+          <t>1.05x</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>130</v>
+        <v>270</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹177.81 Cr</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 25</t>
+          <t>3-Aug GMP: 80</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2-Aug 15:58</t>
+          <t>3-Aug 12:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -934,38 +938,38 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fusion Klassroom Edutech BSE SMEO</t>
+          <t>G.V. Electricals BSE SMEO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹4 (2.52%) 4 ↓ / 9 ↑</t>
+          <t>₹26 (20.00%) 18 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.79x</t>
+          <t>10.92x</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹39.04 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 4</t>
+          <t>31-Jul GMP: 25</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -985,7 +989,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2-Aug 15:56</t>
+          <t>3-Aug 12:02</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -997,58 +1001,58 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dhaval Packaging BSE SMEO</t>
+          <t>Fusion Klassroom Edutech BSE SMEO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹11 (11.34%) 8 ↓ / 15 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>0.87x</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹36.36 Cr</t>
+          <t>₹39.04 Cr</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 15</t>
+          <t>31-Jul GMP: 4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2-Aug 15:58</t>
+          <t>3-Aug 11:54</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1060,43 +1064,43 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MV Electrosystems IPOO</t>
+          <t>Juniper Green Energy IPOCT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹113 (26.59%) 60 ↓ / 133 ↑</t>
+          <t>₹1.5 (0.67%) 1.50 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12.79x</t>
+          <t>1.36x</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>425</v>
+        <v>225</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹290.00 Cr</t>
+          <t>₹1800.00 Cr</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 125</t>
+          <t>30-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>3-Aug GMP: 1.5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1111,7 +1115,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2-Aug 15:55</t>
+          <t>3-Aug 12:02</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1123,12 +1127,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Juniper Green Energy IPOO</t>
+          <t>Oneindig Technologies BSE SMECT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹1.5 (0.67%) 1.50 ↓ / 17 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1138,28 +1142,28 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.49x</t>
+          <t>1.05x</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>225</v>
+        <v>96</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹1800.00 Cr</t>
+          <t>₹27.65 Cr</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>66</v>
+        <v>1200</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 8</t>
+          <t>30-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>3-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1174,7 +1178,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2-Aug 16:02</t>
+          <t>3-Aug 11:58</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1186,43 +1190,43 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Oneindig Technologies BSE SMEO</t>
+          <t>MV Electrosystems IPOCT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹112 (26.35%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.79x</t>
+          <t>71.07x</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>96</v>
+        <v>425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹27.65 Cr</t>
+          <t>₹290.00 Cr</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1200</v>
+        <v>34</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 0</t>
+          <t>30-Jul GMP: 125</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>3-Aug GMP: 112</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1237,7 +1241,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2-Aug 16:00</t>
+          <t>3-Aug 11:59</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1249,58 +1253,58 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H.R. Hygiene Products BSE SMEC</t>
+          <t>Dhaval Packaging BSE SMECT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹2 (2.27%) 2 ↓ / 2 ↑</t>
+          <t>₹6 (6.19%) 6 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6.65x</t>
+          <t>7.57x</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹53.95 Cr</t>
+          <t>₹36.36 Cr</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 2</t>
+          <t>30-Jul GMP: 15</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 2</t>
+          <t>3-Aug GMP: 6</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2-Aug 16:00</t>
+          <t>3-Aug 11:54</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1312,12 +1316,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Manipal Health Enterprises IPOC</t>
+          <t>H.R. Hygiene Products BSE SMEC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹-7 (-1.19%) -15 ↓ / 35 ↑</t>
+          <t>₹2 (2.27%) 2 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1327,28 +1331,28 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5.12x</t>
+          <t>6.65x</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>590</v>
+        <v>88</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹9275.22 Cr</t>
+          <t>₹53.95 Cr</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>25</v>
+        <v>1600</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 9</t>
+          <t>29-Jul GMP: 2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>31-Jul GMP: -15</t>
+          <t>31-Jul GMP: 2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1363,7 +1367,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2-Aug 16:01</t>
+          <t>3-Aug 11:53</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1375,58 +1379,58 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Poojaa Precision Engg. BSE SMECAllotted</t>
+          <t>Manipal Health Enterprises IPOC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹225 (74.75%) 195 ↓ / 300 ↑</t>
+          <t>₹-10 (-1.69%) -15 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>278.83x</t>
+          <t>5.12x</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>301</v>
+        <v>590</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹159.83 Cr</t>
+          <t>₹9275.22 Cr</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>400</v>
+        <v>25</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 300</t>
+          <t>29-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 225</t>
+          <t>31-Jul GMP: -15</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2-Aug 16:02</t>
+          <t>3-Aug 11:56</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1438,75 +1442,75 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Propshop Events &amp; Exhibitions NSE SMECAllotted</t>
+          <t>Poojaa Precision Engg. BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹230 (76.41%) 195 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.53x</t>
+          <t>278.83x</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>69</v>
+        <v>301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>₹28.57 Cr</t>
+          <t>₹159.83 Cr</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 0</t>
+          <t>28-Jul GMP: 300</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 0</t>
+          <t>30-Jul GMP: 225</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>31-Jul</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2-Aug 15:57</t>
+          <t>3-Aug 11:58</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Advance Technoforge BSE SMEC</t>
+          <t>Cube Highways Trust InvIT IPOCAllotted</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹4 (4.21%) 3 ↓ / 9 ↑</t>
+          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1516,60 +1520,60 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.55x</t>
+          <t>9.35x</t>
         </is>
       </c>
       <c r="E19" t="n">
+        <v>152</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>₹5000.00 Cr</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
         <v>95</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>₹24.04 Cr</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>1200</v>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 9</t>
+          <t>22-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 8</t>
+          <t>24-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>31-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2-Aug 15:57</t>
+          <t>3-Aug 5:55</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cube Highways Trust InvIT IPOCAllotted</t>
+          <t>Propshop Events &amp; Exhibitions NSE SMEL@55.20 (-20%)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1579,60 +1583,60 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9.35x</t>
+          <t>1.53x</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹5000.00 Cr</t>
+          <t>₹28.57 Cr</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>95</v>
+        <v>2000</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 0</t>
+          <t>27-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 1.75</t>
+          <t>29-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 1.75</t>
+          <t>3-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2-Aug 5:55</t>
+          <t>3-Aug 9:35</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Silverstorm Parks &amp; Resorts BSE SMEL@132.90 (-0.08%)</t>
+          <t>Advance Technoforge BSE SMELT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹5 (3.76%) 5 ↓ / 5 ↑</t>
+          <t>₹4 (4.21%) 3 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1642,106 +1646,106 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.91x</t>
+          <t>1.55x</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹82.43 Cr</t>
+          <t>₹24.04 Cr</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 0</t>
+          <t>27-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 0</t>
+          <t>29-Jul GMP: 8</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 5</t>
+          <t>3-Aug GMP: 4</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>31-Jul 9:34</t>
+          <t>3-Aug 9:30</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Indo-MIM IPOL@700.00 (44.33%)</t>
+          <t>Silverstorm Parks &amp; Resorts BSE SMEL@132.90 (-0.08%)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹184 (37.94%) 168 ↓ / 213 ↑</t>
+          <t>₹5 (3.76%) 5 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>72.37x</t>
+          <t>1.91x</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>485</v>
+        <v>133</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹3811.21 Cr</t>
+          <t>₹82.43 Cr</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 170</t>
+          <t>24-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 190</t>
+          <t>28-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>28-Jul</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 184</t>
+          <t>31-Jul GMP: 5</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>30-Jul 9:36</t>
+          <t>31-Jul 9:34</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1879,58 +1883,58 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Shree Balaji Mala BSE SMEL@133.00 (90%)</t>
+          <t>Indo-MIM IPOL@700.00 (44.33%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹56 (80.00%) 11 ↓ / 56 ↑</t>
+          <t>₹184 (37.94%) 168 ↓ / 213 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>200.34x</t>
+          <t>72.37x</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>70</v>
+        <v>485</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹18.90 Cr</t>
+          <t>₹3811.21 Cr</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2000</v>
+        <v>30</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 16</t>
+          <t>23-Jul GMP: 170</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 13</t>
+          <t>27-Jul GMP: 190</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>27-Jul</t>
+          <t>28-Jul</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 56</t>
+          <t>30-Jul GMP: 184</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>29-Jul 9:29</t>
+          <t>30-Jul 9:36</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1942,58 +1946,58 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Metalic Technoforge NSE SMEL@87.00 (12.99%)</t>
+          <t>Shree Balaji Mala BSE SMEL@133.00 (90%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹6 (7.79%) 6 ↓ / 8.10 ↑</t>
+          <t>₹56 (80.00%) 11 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.47x</t>
+          <t>200.34x</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹49.96 Cr</t>
+          <t>₹18.90 Cr</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 0</t>
+          <t>22-Jul GMP: 16</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 6</t>
+          <t>24-Jul GMP: 13</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>24-Jul</t>
+          <t>27-Jul</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 6</t>
+          <t>29-Jul GMP: 56</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>28-Jul 9:29</t>
+          <t>29-Jul 9:29</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2005,184 +2009,184 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Gulf Lloyds BSE SMEL@100.00 (0%)</t>
+          <t>Metalic Technoforge NSE SMEL@87.00 (12.99%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹1 (1.00%) 1 ↓ / 25 ↑</t>
+          <t>₹6 (7.79%) 6 ↓ / 8.10 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10.85x</t>
+          <t>8.47x</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹18.19 Cr</t>
+          <t>₹49.96 Cr</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>20-Jul GMP: 10</t>
+          <t>21-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 1</t>
+          <t>23-Jul GMP: 6</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>23-Jul</t>
+          <t>24-Jul</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 1</t>
+          <t>28-Jul GMP: 6</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>27-Jul 9:29</t>
+          <t>28-Jul 9:29</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Caliber Mining IPOL@500.25 (17.98%)</t>
+          <t>Gulf Lloyds BSE SMEL@100.00 (0%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹60 (14.15%) 60 ↓ / 117 ↑</t>
+          <t>₹1 (1.00%) 1 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>154.66x</t>
+          <t>10.85x</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>424</v>
+        <v>100</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹450.00 Cr</t>
+          <t>₹18.19 Cr</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>35</v>
+        <v>1200</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>17-Jul GMP: 116</t>
+          <t>20-Jul GMP: 10</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 71</t>
+          <t>22-Jul GMP: 1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>22-Jul</t>
+          <t>23-Jul</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 60</t>
+          <t>27-Jul GMP: 1</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>24-Jul 9:35</t>
+          <t>27-Jul 9:29</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sotefin Bharat BSE SMEL@205.00 (9.63%)</t>
+          <t>Caliber Mining IPOL@500.25 (17.98%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹2.5 (1.34%) 1 ↓ / 27 ↑</t>
+          <t>₹60 (14.15%) 60 ↓ / 117 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3.99x</t>
+          <t>154.66x</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>187</v>
+        <v>424</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹89.76 Cr</t>
+          <t>₹450.00 Cr</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>600</v>
+        <v>35</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 18</t>
+          <t>17-Jul GMP: 116</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20-Jul GMP: 1</t>
+          <t>21-Jul GMP: 71</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>21-Jul</t>
+          <t>22-Jul</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 2.5</t>
+          <t>24-Jul GMP: 60</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>23-Jul 9:34</t>
+          <t>24-Jul 9:35</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2194,58 +2198,58 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Millworks Technologies BSE SMEL@628.90 (90%)</t>
+          <t>Sotefin Bharat BSE SMEL@205.00 (9.63%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹395 (119.34%) 300 ↓ / 400 ↑</t>
+          <t>₹2.5 (1.34%) 1 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>219.54x</t>
+          <t>3.99x</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>331</v>
+        <v>187</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹160.34 Cr</t>
+          <t>₹89.76 Cr</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>14-Jul GMP: 300</t>
+          <t>16-Jul GMP: 18</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 380</t>
+          <t>20-Jul GMP: 1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>17-Jul</t>
+          <t>21-Jul</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 395</t>
+          <t>23-Jul GMP: 2.5</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>21-Jul 9:32</t>
+          <t>23-Jul 9:34</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2257,43 +2261,43 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SBI Funds Management IPOL@613.30 (6.85%)</t>
+          <t>Alpine Texworld IPOL@105.00 (0%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹65 (11.32%) 65 ↓ / 140 ↑</t>
+          <t>₹1 (0.95%) 1 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>41.73x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>574</v>
+        <v>105</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹9812.91 Cr</t>
+          <t>₹126.25 Cr</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>26</v>
+        <v>142</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>14-Jul GMP: 88</t>
+          <t>14-Jul GMP: 5</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 97</t>
+          <t>16-Jul GMP: 1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2303,7 +2307,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 65</t>
+          <t>21-Jul GMP: 1</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2313,50 +2317,50 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alpine Texworld IPOL@105.00 (0%)</t>
+          <t>SBI Funds Management IPOL@613.30 (6.85%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹1 (0.95%) 1 ↓ / 5 ↑</t>
+          <t>₹65 (11.32%) 65 ↓ / 140 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>41.73x</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>105</v>
+        <v>574</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹126.25 Cr</t>
+          <t>₹9812.91 Cr</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>142</v>
+        <v>26</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>14-Jul GMP: 5</t>
+          <t>14-Jul GMP: 88</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 1</t>
+          <t>16-Jul GMP: 97</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2366,7 +2370,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 1</t>
+          <t>21-Jul GMP: 65</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2376,7 +2380,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,17 +501,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Technocraft Ventures IPOU</t>
+          <t>Dhoot Transmission IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹16.5 (7.78%) 16.50 ↓ / 16.50 ↑</t>
+          <t>₹-- (%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -519,40 +519,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>212</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹251.88 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>70</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>7-Aug</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>11-Aug</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>12-Aug</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>14-Aug</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>3-Aug 11:55</t>
+          <t>3-Aug 12:40</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -569,7 +545,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹7 (4.40%) 7 ↓ / 8 ↑</t>
+          <t>₹4 (2.52%) 4 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -615,7 +591,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>3-Aug 11:56</t>
+          <t>3-Aug 17:31</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -627,17 +603,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Optimystix Entertainment NSE SMEU</t>
+          <t>Technocraft Ventures IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹16 (7.55%) 16 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -645,13 +621,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>212</v>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>₹251.88 Cr</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>70</v>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>7-Aug</t>
@@ -674,7 +654,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3-Aug 5:55</t>
+          <t>3-Aug 17:29</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -686,17 +666,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LAPL Automotive BSE SMEU</t>
+          <t>Optimystix Entertainment NSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹25 (26.60%) 22 ↓ / 25 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -704,40 +684,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>94</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹32.40 Cr</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1200</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>3-Aug 11:58</t>
+          <t>3-Aug 5:55</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -749,17 +725,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOU</t>
+          <t>LAPL Automotive BSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹6.75 (12.74%) 6.50 ↓ / 13 ↑</t>
+          <t>₹25 (26.60%) 22 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -768,39 +744,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
+          <t>₹32.40 Cr</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>281</v>
+        <v>1200</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>3-Aug 11:56</t>
+          <t>3-Aug 17:31</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -812,17 +788,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aegeus Technologies BSE SMEU</t>
+          <t>Ardee Industries IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6.75 (12.74%) 6.50 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -831,39 +807,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹23.71 Cr</t>
+          <t>₹425.87 Cr</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1200</v>
+        <v>281</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3-Aug 11:58</t>
+          <t>3-Aug 17:34</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -875,58 +851,58 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Anawil Wire &amp; Engineering NSE SMEO</t>
+          <t>Aegeus Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹80 (29.63%) 60 ↓ / 90 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.05x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>270</v>
+        <v>105</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹177.81 Cr</t>
+          <t>₹23.71 Cr</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 80</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>3-Aug 12:02</t>
+          <t>3-Aug 17:32</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -938,12 +914,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEO</t>
+          <t>Anawil Wire &amp; Engineering NSE SMEO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹26 (20.00%) 18 ↓ / 26 ↑</t>
+          <t>₹80 (29.63%) 60 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -953,43 +929,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10.92x</t>
+          <t>4.77x</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>130</v>
+        <v>270</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹177.81 Cr</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 25</t>
+          <t>3-Aug GMP: 80</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3-Aug 12:02</t>
+          <t>3-Aug 17:33</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1001,38 +977,38 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fusion Klassroom Edutech BSE SMEO</t>
+          <t>G.V. Electricals BSE SMEO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
+          <t>₹26 (20.00%) 18 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.87x</t>
+          <t>22.13x</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹39.04 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 4</t>
+          <t>31-Jul GMP: 25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1052,7 +1028,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3-Aug 11:54</t>
+          <t>3-Aug 17:31</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1064,12 +1040,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Juniper Green Energy IPOCT</t>
+          <t>Fusion Klassroom Edutech BSE SMEO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹1.5 (0.67%) 1.50 ↓ / 17 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1079,43 +1055,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.36x</t>
+          <t>0.97x</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>225</v>
+        <v>159</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹1800.00 Cr</t>
+          <t>₹39.04 Cr</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>66</v>
+        <v>800</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 8</t>
+          <t>31-Jul GMP: 4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 1.5</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3-Aug 12:02</t>
+          <t>3-Aug 17:34</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1142,7 +1118,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.05x</t>
+          <t>1.73x</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1178,7 +1154,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3-Aug 11:58</t>
+          <t>3-Aug 17:34</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1190,43 +1166,43 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MV Electrosystems IPOCT</t>
+          <t>Juniper Green Energy IPOCT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹112 (26.35%) 60 ↓ / 133 ↑</t>
+          <t>₹3.75 (1.67%) 1.50 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>71.07x</t>
+          <t>8.38x</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>425</v>
+        <v>225</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹290.00 Cr</t>
+          <t>₹1800.00 Cr</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 125</t>
+          <t>30-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 112</t>
+          <t>3-Aug GMP: 3.75</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1241,7 +1217,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>3-Aug 11:59</t>
+          <t>3-Aug 17:32</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1253,43 +1229,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dhaval Packaging BSE SMECT</t>
+          <t>MV Electrosystems IPOCT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹6 (6.19%) 6 ↓ / 15 ↑</t>
+          <t>₹100 (23.53%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.57x</t>
+          <t>200.66x</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>97</v>
+        <v>425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹36.36 Cr</t>
+          <t>₹290.00 Cr</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1200</v>
+        <v>34</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 15</t>
+          <t>30-Jul GMP: 125</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 6</t>
+          <t>3-Aug GMP: 100</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1304,7 +1280,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>3-Aug 11:54</t>
+          <t>3-Aug 17:30</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1316,58 +1292,58 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H.R. Hygiene Products BSE SMEC</t>
+          <t>Dhaval Packaging BSE SMECT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹2 (2.27%) 2 ↓ / 2 ↑</t>
+          <t>₹5 (5.15%) 5 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6.65x</t>
+          <t>49.99x</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹53.95 Cr</t>
+          <t>₹36.36 Cr</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 2</t>
+          <t>30-Jul GMP: 15</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 2</t>
+          <t>3-Aug GMP: 5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>3-Aug 11:53</t>
+          <t>3-Aug 17:30</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1384,7 +1360,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹-10 (-1.69%) -15 ↓ / 35 ↑</t>
+          <t>₹-6 (-1.02%) -15 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1430,7 +1406,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>3-Aug 11:56</t>
+          <t>3-Aug 17:31</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1442,58 +1418,58 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Poojaa Precision Engg. BSE SMECAllotted</t>
+          <t>H.R. Hygiene Products BSE SMEC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹230 (76.41%) 195 ↓ / 300 ↑</t>
+          <t>₹2 (2.27%) 2 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>278.83x</t>
+          <t>6.65x</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>301</v>
+        <v>88</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>₹159.83 Cr</t>
+          <t>₹53.95 Cr</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>400</v>
+        <v>1600</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 300</t>
+          <t>29-Jul GMP: 2</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 225</t>
+          <t>31-Jul GMP: 2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>3-Aug 11:58</t>
+          <t>3-Aug 17:34</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1505,58 +1481,58 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cube Highways Trust InvIT IPOCAllotted</t>
+          <t>Poojaa Precision Engg. BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
+          <t>₹235 (78.07%) 195 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9.35x</t>
+          <t>278.83x</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>152</v>
+        <v>301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹5000.00 Cr</t>
+          <t>₹159.83 Cr</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>95</v>
+        <v>400</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 0</t>
+          <t>28-Jul GMP: 300</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 1.75</t>
+          <t>30-Jul GMP: 225</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>31-Jul</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 1.75</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>3-Aug 5:55</t>
+          <t>3-Aug 17:32</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1568,12 +1544,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Propshop Events &amp; Exhibitions NSE SMEL@55.20 (-20%)</t>
+          <t>Cube Highways Trust InvIT IPOCAllotted</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1583,55 +1559,55 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.53x</t>
+          <t>9.35x</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>69</v>
+        <v>152</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹28.57 Cr</t>
+          <t>₹5000.00 Cr</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2000</v>
+        <v>95</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 0</t>
+          <t>22-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 0</t>
+          <t>24-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 0</t>
+          <t>31-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>3-Aug 9:35</t>
+          <t>3-Aug 5:55</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Advance Technoforge BSE SMELT</t>
+          <t>Advance Technoforge BSE SMEL@94.00 (-1.05%)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1694,12 +1670,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Silverstorm Parks &amp; Resorts BSE SMEL@132.90 (-0.08%)</t>
+          <t>Propshop Events &amp; Exhibitions NSE SMEL@55.20 (-20%)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹5 (3.76%) 5 ↓ / 5 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1709,60 +1685,60 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.91x</t>
+          <t>1.53x</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹82.43 Cr</t>
+          <t>₹28.57 Cr</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 0</t>
+          <t>27-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 0</t>
+          <t>29-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 5</t>
+          <t>3-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>31-Jul 9:34</t>
+          <t>3-Aug 9:35</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lohia Corp IPOL@461.00 (8.47%)</t>
+          <t>Silverstorm Parks &amp; Resorts BSE SMEL@132.90 (-0.08%)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹17 (4.00%) 7 ↓ / 56 ↑</t>
+          <t>₹5 (3.76%) 5 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1772,43 +1748,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7.26x</t>
+          <t>1.91x</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>425</v>
+        <v>133</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹1101.28 Cr</t>
+          <t>₹82.43 Cr</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>35</v>
+        <v>1000</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 12</t>
+          <t>24-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 11.5</t>
+          <t>28-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>28-Jul</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 17</t>
+          <t>31-Jul GMP: 5</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>30-Jul 9:30</t>
+          <t>31-Jul 9:34</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1820,43 +1796,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Xtranet Technologies IPOL@136.00 (7.09%)</t>
+          <t>Lohia Corp IPOL@461.00 (8.47%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹14.5 (11.42%) 7.50 ↓ / 26 ↑</t>
+          <t>₹17 (4.00%) 7 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>12.24x</t>
+          <t>7.26x</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>127</v>
+        <v>425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹166.80 Cr</t>
+          <t>₹1101.28 Cr</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 8</t>
+          <t>23-Jul GMP: 12</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 7.7</t>
+          <t>27-Jul GMP: 11.5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1866,12 +1842,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 14.5</t>
+          <t>30-Jul GMP: 17</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>30-Jul 9:31</t>
+          <t>30-Jul 9:30</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1883,43 +1859,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indo-MIM IPOL@700.00 (44.33%)</t>
+          <t>Xtranet Technologies IPOL@136.00 (7.09%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹184 (37.94%) 168 ↓ / 213 ↑</t>
+          <t>₹14.5 (11.42%) 7.50 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>72.37x</t>
+          <t>12.24x</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>485</v>
+        <v>127</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹3811.21 Cr</t>
+          <t>₹166.80 Cr</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 170</t>
+          <t>23-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 190</t>
+          <t>27-Jul GMP: 7.7</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1929,12 +1905,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 184</t>
+          <t>30-Jul GMP: 14.5</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>30-Jul 9:36</t>
+          <t>30-Jul 9:31</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1946,58 +1922,58 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Shree Balaji Mala BSE SMEL@133.00 (90%)</t>
+          <t>Indo-MIM IPOL@700.00 (44.33%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹56 (80.00%) 11 ↓ / 56 ↑</t>
+          <t>₹184 (37.94%) 168 ↓ / 213 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>200.34x</t>
+          <t>72.37x</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>70</v>
+        <v>485</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹18.90 Cr</t>
+          <t>₹3811.21 Cr</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2000</v>
+        <v>30</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 16</t>
+          <t>23-Jul GMP: 170</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 13</t>
+          <t>27-Jul GMP: 190</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>27-Jul</t>
+          <t>28-Jul</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 56</t>
+          <t>30-Jul GMP: 184</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>29-Jul 9:29</t>
+          <t>30-Jul 9:36</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2009,58 +1985,58 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Metalic Technoforge NSE SMEL@87.00 (12.99%)</t>
+          <t>Shree Balaji Mala BSE SMEL@133.00 (90%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹6 (7.79%) 6 ↓ / 8.10 ↑</t>
+          <t>₹56 (80.00%) 11 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.47x</t>
+          <t>200.34x</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹49.96 Cr</t>
+          <t>₹18.90 Cr</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 0</t>
+          <t>22-Jul GMP: 16</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 6</t>
+          <t>24-Jul GMP: 13</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>24-Jul</t>
+          <t>27-Jul</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 6</t>
+          <t>29-Jul GMP: 56</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>28-Jul 9:29</t>
+          <t>29-Jul 9:29</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2072,184 +2048,184 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Gulf Lloyds BSE SMEL@100.00 (0%)</t>
+          <t>Metalic Technoforge NSE SMEL@87.00 (12.99%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹1 (1.00%) 1 ↓ / 25 ↑</t>
+          <t>₹6 (7.79%) 6 ↓ / 8.10 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>10.85x</t>
+          <t>8.47x</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹18.19 Cr</t>
+          <t>₹49.96 Cr</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>20-Jul GMP: 10</t>
+          <t>21-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 1</t>
+          <t>23-Jul GMP: 6</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>23-Jul</t>
+          <t>24-Jul</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 1</t>
+          <t>28-Jul GMP: 6</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>27-Jul 9:29</t>
+          <t>28-Jul 9:29</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caliber Mining IPOL@500.25 (17.98%)</t>
+          <t>Gulf Lloyds BSE SMEL@100.00 (0%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹60 (14.15%) 60 ↓ / 117 ↑</t>
+          <t>₹1 (1.00%) 1 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>154.66x</t>
+          <t>10.85x</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>424</v>
+        <v>100</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹450.00 Cr</t>
+          <t>₹18.19 Cr</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>35</v>
+        <v>1200</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>17-Jul GMP: 116</t>
+          <t>20-Jul GMP: 10</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 71</t>
+          <t>22-Jul GMP: 1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>22-Jul</t>
+          <t>23-Jul</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 60</t>
+          <t>27-Jul GMP: 1</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>24-Jul 9:35</t>
+          <t>27-Jul 9:29</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sotefin Bharat BSE SMEL@205.00 (9.63%)</t>
+          <t>Caliber Mining IPOL@500.25 (17.98%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹2.5 (1.34%) 1 ↓ / 27 ↑</t>
+          <t>₹60 (14.15%) 60 ↓ / 117 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3.99x</t>
+          <t>154.66x</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>187</v>
+        <v>424</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹89.76 Cr</t>
+          <t>₹450.00 Cr</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>600</v>
+        <v>35</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 18</t>
+          <t>17-Jul GMP: 116</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20-Jul GMP: 1</t>
+          <t>21-Jul GMP: 71</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>21-Jul</t>
+          <t>22-Jul</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 2.5</t>
+          <t>24-Jul GMP: 60</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>23-Jul 9:34</t>
+          <t>24-Jul 9:35</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2261,12 +2237,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alpine Texworld IPOL@105.00 (0%)</t>
+          <t>Sotefin Bharat BSE SMEL@205.00 (9.63%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹1 (0.95%) 1 ↓ / 5 ↑</t>
+          <t>₹2.5 (1.34%) 1 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2276,91 +2252,91 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>3.99x</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹126.25 Cr</t>
+          <t>₹89.76 Cr</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>142</v>
+        <v>600</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>14-Jul GMP: 5</t>
+          <t>16-Jul GMP: 18</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 1</t>
+          <t>20-Jul GMP: 1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>17-Jul</t>
+          <t>21-Jul</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 1</t>
+          <t>23-Jul GMP: 2.5</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>21-Jul 9:35</t>
+          <t>23-Jul 9:34</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SBI Funds Management IPOL@613.30 (6.85%)</t>
+          <t>Millworks Technologies BSE SMEL@628.90 (90%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹65 (11.32%) 65 ↓ / 140 ↑</t>
+          <t>₹395 (119.34%) 300 ↓ / 400 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>41.73x</t>
+          <t>219.54x</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>574</v>
+        <v>331</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹9812.91 Cr</t>
+          <t>₹160.34 Cr</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>26</v>
+        <v>400</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>14-Jul GMP: 88</t>
+          <t>14-Jul GMP: 300</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 97</t>
+          <t>16-Jul GMP: 380</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2370,12 +2346,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 65</t>
+          <t>21-Jul GMP: 395</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>21-Jul 9:35</t>
+          <t>21-Jul 9:32</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,12 +506,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (%) 0 ↓ / 0 ↑</t>
+          <t>₹200 (22.96%) 146 ↓ / 200 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -519,16 +519,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>871</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹3066.89 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>17</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>10-Aug</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12-Aug</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>13-Aug</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>17-Aug</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>3-Aug 12:40</t>
+          <t>4-Aug 10:57</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -591,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>3-Aug 17:31</t>
+          <t>4-Aug 11:01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -608,12 +632,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹16 (7.55%) 16 ↓ / 16 ↑</t>
+          <t>₹10 (4.72%) 10 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -654,7 +678,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3-Aug 17:29</t>
+          <t>4-Aug 10:55</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -684,13 +708,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>175</v>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>₹108.50 Cr</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>800</v>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>7-Aug</t>
@@ -713,7 +741,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>3-Aug 5:55</t>
+          <t>4-Aug 11:02</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -730,7 +758,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹25 (26.60%) 22 ↓ / 25 ↑</t>
+          <t>₹27 (28.72%) 22 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -776,7 +804,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>3-Aug 17:31</t>
+          <t>4-Aug 10:56</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -793,7 +821,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹6.75 (12.74%) 6.50 ↓ / 13 ↑</t>
+          <t>₹7.5 (14.15%) 6.50 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -839,7 +867,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3-Aug 17:34</t>
+          <t>4-Aug 10:55</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -851,7 +879,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Aegeus Technologies BSE SMEU</t>
+          <t>Aegeus Technologies BSE SMEO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -866,7 +894,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.11x</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -882,7 +910,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -902,7 +930,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>3-Aug 17:32</t>
+          <t>4-Aug 10:53</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -929,7 +957,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.77x</t>
+          <t>6.37x</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -965,7 +993,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3-Aug 17:33</t>
+          <t>4-Aug 10:55</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -977,7 +1005,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEO</t>
+          <t>G.V. Electricals BSE SMECT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -992,7 +1020,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>22.13x</t>
+          <t>37.95x</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1013,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>4-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1028,7 +1056,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3-Aug 17:31</t>
+          <t>4-Aug 11:02</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1040,7 +1068,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fusion Klassroom Edutech BSE SMEO</t>
+          <t>Fusion Klassroom Edutech BSE SMECT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1055,7 +1083,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.97x</t>
+          <t>1.07x</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1076,7 +1104,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1091,7 +1119,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3-Aug 17:34</t>
+          <t>4-Aug 10:58</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1103,30 +1131,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Oneindig Technologies BSE SMECT</t>
+          <t>Dhaval Packaging BSE SMEC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹8 (8.25%) 8 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.73x</t>
+          <t>49.99x</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹27.65 Cr</t>
+          <t>₹36.36 Cr</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1134,12 +1162,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 0</t>
+          <t>30-Jul GMP: 15</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 0</t>
+          <t>3-Aug GMP: 8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1154,7 +1182,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3-Aug 17:34</t>
+          <t>4-Aug 10:56</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1166,43 +1194,43 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Juniper Green Energy IPOCT</t>
+          <t>MV Electrosystems IPOC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹3.75 (1.67%) 1.50 ↓ / 17 ↑</t>
+          <t>₹100 (23.53%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.38x</t>
+          <t>200.66x</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>225</v>
+        <v>425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹1800.00 Cr</t>
+          <t>₹290.00 Cr</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 8</t>
+          <t>30-Jul GMP: 125</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 3.75</t>
+          <t>3-Aug GMP: 100</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,7 +1245,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>3-Aug 17:32</t>
+          <t>4-Aug 11:01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1229,43 +1257,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MV Electrosystems IPOCT</t>
+          <t>Juniper Green Energy IPOC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹100 (23.53%) 60 ↓ / 133 ↑</t>
+          <t>₹10.75 (4.78%) 1.50 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>200.66x</t>
+          <t>8.38x</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>425</v>
+        <v>225</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹290.00 Cr</t>
+          <t>₹1800.00 Cr</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 125</t>
+          <t>30-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 100</t>
+          <t>3-Aug GMP: 9.5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1280,7 +1308,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>3-Aug 17:30</t>
+          <t>4-Aug 11:01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1292,30 +1320,30 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dhaval Packaging BSE SMECT</t>
+          <t>Oneindig Technologies BSE SMEC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹5 (5.15%) 5 ↓ / 15 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>49.99x</t>
+          <t>1.73x</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹36.36 Cr</t>
+          <t>₹27.65 Cr</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1323,12 +1351,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 15</t>
+          <t>30-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 5</t>
+          <t>3-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1343,7 +1371,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>3-Aug 17:30</t>
+          <t>4-Aug 11:02</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1355,12 +1383,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Manipal Health Enterprises IPOC</t>
+          <t>H.R. Hygiene Products BSE SMEC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹-6 (-1.02%) -15 ↓ / 35 ↑</t>
+          <t>₹2 (2.27%) 2 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1370,28 +1398,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5.12x</t>
+          <t>6.65x</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>590</v>
+        <v>88</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹9275.22 Cr</t>
+          <t>₹53.95 Cr</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>25</v>
+        <v>1600</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 9</t>
+          <t>29-Jul GMP: 2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>31-Jul GMP: -15</t>
+          <t>31-Jul GMP: 2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1406,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>3-Aug 17:31</t>
+          <t>4-Aug 11:02</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1418,12 +1446,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H.R. Hygiene Products BSE SMEC</t>
+          <t>Manipal Health Enterprises IPOCAllotted</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹2 (2.27%) 2 ↓ / 2 ↑</t>
+          <t>₹-2 (-0.34%) -15 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1433,28 +1461,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6.65x</t>
+          <t>5.12x</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>88</v>
+        <v>590</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>₹53.95 Cr</t>
+          <t>₹9275.22 Cr</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1600</v>
+        <v>25</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 2</t>
+          <t>29-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 2</t>
+          <t>31-Jul GMP: -15</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1469,7 +1497,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>3-Aug 17:34</t>
+          <t>4-Aug 10:54</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1481,58 +1509,58 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Poojaa Precision Engg. BSE SMECAllotted</t>
+          <t>Cube Highways Trust InvIT IPOCAllotted</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹235 (78.07%) 195 ↓ / 300 ↑</t>
+          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>278.83x</t>
+          <t>9.35x</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>301</v>
+        <v>152</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹159.83 Cr</t>
+          <t>₹5000.00 Cr</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>400</v>
+        <v>95</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 300</t>
+          <t>22-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 225</t>
+          <t>24-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>31-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>3-Aug 17:32</t>
+          <t>4-Aug 5:55</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1544,58 +1572,58 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cube Highways Trust InvIT IPOCAllotted</t>
+          <t>Poojaa Precision Engg. BSE SMEL@470.00 (56.15%)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
+          <t>₹200 (66.45%) 195 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9.35x</t>
+          <t>278.83x</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>152</v>
+        <v>301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹5000.00 Cr</t>
+          <t>₹159.83 Cr</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>95</v>
+        <v>400</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 0</t>
+          <t>28-Jul GMP: 300</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 1.75</t>
+          <t>30-Jul GMP: 225</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>31-Jul</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 1.75</t>
+          <t>4-Aug GMP: 200</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>3-Aug 5:55</t>
+          <t>4-Aug 9:33</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1607,12 +1635,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Advance Technoforge BSE SMEL@94.00 (-1.05%)</t>
+          <t>Propshop Events &amp; Exhibitions NSE SMEL@55.20 (-20%)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹4 (4.21%) 3 ↓ / 9 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1622,28 +1650,28 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.55x</t>
+          <t>1.53x</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹24.04 Cr</t>
+          <t>₹28.57 Cr</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 9</t>
+          <t>27-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 8</t>
+          <t>29-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1653,12 +1681,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 4</t>
+          <t>3-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>3-Aug 9:30</t>
+          <t>3-Aug 9:35</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1670,12 +1698,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Propshop Events &amp; Exhibitions NSE SMEL@55.20 (-20%)</t>
+          <t>Advance Technoforge BSE SMEL@94.00 (-1.05%)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹4 (4.21%) 3 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1685,28 +1713,28 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.53x</t>
+          <t>1.55x</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹28.57 Cr</t>
+          <t>₹24.04 Cr</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 0</t>
+          <t>27-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 0</t>
+          <t>29-Jul GMP: 8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1716,12 +1744,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 0</t>
+          <t>3-Aug GMP: 4</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>3-Aug 9:35</t>
+          <t>3-Aug 9:30</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1859,43 +1887,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Xtranet Technologies IPOL@136.00 (7.09%)</t>
+          <t>Indo-MIM IPOL@700.00 (44.33%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹14.5 (11.42%) 7.50 ↓ / 26 ↑</t>
+          <t>₹184 (37.94%) 168 ↓ / 213 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>12.24x</t>
+          <t>72.37x</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>127</v>
+        <v>485</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹166.80 Cr</t>
+          <t>₹3811.21 Cr</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 8</t>
+          <t>23-Jul GMP: 170</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 7.7</t>
+          <t>27-Jul GMP: 190</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1905,12 +1933,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 14.5</t>
+          <t>30-Jul GMP: 184</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>30-Jul 9:31</t>
+          <t>30-Jul 9:36</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1922,43 +1950,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Indo-MIM IPOL@700.00 (44.33%)</t>
+          <t>Xtranet Technologies IPOL@136.00 (7.09%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹184 (37.94%) 168 ↓ / 213 ↑</t>
+          <t>₹14.5 (11.42%) 7.50 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>72.37x</t>
+          <t>12.24x</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>485</v>
+        <v>127</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹3811.21 Cr</t>
+          <t>₹166.80 Cr</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 170</t>
+          <t>23-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 190</t>
+          <t>27-Jul GMP: 7.7</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1968,12 +1996,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 184</t>
+          <t>30-Jul GMP: 14.5</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>30-Jul 9:36</t>
+          <t>30-Jul 9:31</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2300,43 +2328,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Millworks Technologies BSE SMEL@628.90 (90%)</t>
+          <t>SBI Funds Management IPOL@613.30 (6.85%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹395 (119.34%) 300 ↓ / 400 ↑</t>
+          <t>₹65 (11.32%) 65 ↓ / 140 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>219.54x</t>
+          <t>41.73x</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>331</v>
+        <v>574</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹160.34 Cr</t>
+          <t>₹9812.91 Cr</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>400</v>
+        <v>26</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>14-Jul GMP: 300</t>
+          <t>14-Jul GMP: 88</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 380</t>
+          <t>16-Jul GMP: 97</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2346,12 +2374,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 395</t>
+          <t>21-Jul GMP: 65</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>21-Jul 9:32</t>
+          <t>21-Jul 9:35</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,17 +501,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOU</t>
+          <t>Molbio Diagnostics IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹200 (22.96%) 146 ↓ / 200 ↑</t>
+          <t>₹-- (%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -519,17 +519,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>871</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹3066.89 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>17</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>10-Aug</t>
@@ -552,7 +544,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4-Aug 10:57</t>
+          <t>4-Aug 12:00</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -564,17 +556,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LEAP India IPOU</t>
+          <t>Dhoot Transmission IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹4 (2.52%) 4 ↓ / 8 ↑</t>
+          <t>₹246 (28.24%) 146 ↓ / 246 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -583,39 +575,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>159</v>
+        <v>871</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹2480.00 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4-Aug 11:01</t>
+          <t>4-Aug 16:31</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -627,12 +619,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Technocraft Ventures IPOU</t>
+          <t>LEAP India IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹10 (4.72%) 10 ↓ / 10 ↑</t>
+          <t>₹3 (1.89%) 3 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -646,15 +638,15 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹251.88 Cr</t>
+          <t>₹2480.00 Cr</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -678,7 +670,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>4-Aug 10:55</t>
+          <t>4-Aug 16:32</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -690,12 +682,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Optimystix Entertainment NSE SMEU</t>
+          <t>Technocraft Ventures IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹10 (4.72%) 10 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -709,15 +701,15 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹108.50 Cr</t>
+          <t>₹251.88 Cr</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>800</v>
+        <v>70</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -741,7 +733,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>4-Aug 11:02</t>
+          <t>4-Aug 16:30</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -753,17 +745,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LAPL Automotive BSE SMEU</t>
+          <t>Optimystix Entertainment NSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹27 (28.72%) 22 ↓ / 27 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -772,39 +764,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>94</v>
+        <v>175</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹32.40 Cr</t>
+          <t>₹108.50 Cr</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>4-Aug 10:56</t>
+          <t>4-Aug 16:36</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -816,17 +808,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOU</t>
+          <t>LAPL Automotive BSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹7.5 (14.15%) 6.50 ↓ / 13 ↑</t>
+          <t>₹27 (28.72%) 22 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -835,39 +827,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
+          <t>₹32.40 Cr</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>281</v>
+        <v>1200</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>4-Aug 10:55</t>
+          <t>4-Aug 16:28</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -879,58 +871,58 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Aegeus Technologies BSE SMEO</t>
+          <t>Ardee Industries IPOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹7.5 (14.15%) 6.50 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.11x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹23.71 Cr</t>
+          <t>₹425.87 Cr</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1200</v>
+        <v>281</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>4-Aug 10:53</t>
+          <t>4-Aug 16:30</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -942,58 +934,58 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anawil Wire &amp; Engineering NSE SMEO</t>
+          <t>Aegeus Technologies BSE SMEO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹80 (29.63%) 60 ↓ / 90 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6.37x</t>
+          <t>0.37x</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>270</v>
+        <v>105</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹177.81 Cr</t>
+          <t>₹23.71 Cr</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 80</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4-Aug 10:55</t>
+          <t>4-Aug 16:29</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1005,12 +997,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMECT</t>
+          <t>Anawil Wire &amp; Engineering NSE SMEO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹26 (20.00%) 18 ↓ / 26 ↑</t>
+          <t>₹80 (29.63%) 60 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1020,43 +1012,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>37.95x</t>
+          <t>10.95x</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>130</v>
+        <v>270</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹177.81 Cr</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 25</t>
+          <t>3-Aug GMP: 80</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 26</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4-Aug 11:02</t>
+          <t>4-Aug 16:35</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1068,43 +1060,43 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fusion Klassroom Edutech BSE SMECT</t>
+          <t>G.V. Electricals BSE SMECT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
+          <t>₹24 (18.46%) 18 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.07x</t>
+          <t>146.11x</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹39.04 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 4</t>
+          <t>31-Jul GMP: 25</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>4-Aug GMP: 24</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1119,7 +1111,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>4-Aug 10:58</t>
+          <t>4-Aug 16:28</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1131,58 +1123,58 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dhaval Packaging BSE SMEC</t>
+          <t>Fusion Klassroom Edutech BSE SMECT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹8 (8.25%) 8 ↓ / 15 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>49.99x</t>
+          <t>1.5x</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹36.36 Cr</t>
+          <t>₹39.04 Cr</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 15</t>
+          <t>31-Jul GMP: 4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 8</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4-Aug 10:56</t>
+          <t>4-Aug 16:29</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1199,7 +1191,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹100 (23.53%) 60 ↓ / 133 ↑</t>
+          <t>₹98 (23.06%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1245,7 +1237,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>4-Aug 11:01</t>
+          <t>4-Aug 16:37</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1262,12 +1254,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹10.75 (4.78%) 1.50 ↓ / 17 ↑</t>
+          <t>₹13.5 (6.00%) 1.50 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1308,7 +1300,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>4-Aug 11:01</t>
+          <t>4-Aug 16:36</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1371,7 +1363,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>4-Aug 11:02</t>
+          <t>4-Aug 16:32</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1383,58 +1375,58 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H.R. Hygiene Products BSE SMEC</t>
+          <t>Dhaval Packaging BSE SMEC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹2 (2.27%) 2 ↓ / 2 ↑</t>
+          <t>₹8 (8.25%) 8 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6.65x</t>
+          <t>49.99x</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹53.95 Cr</t>
+          <t>₹36.36 Cr</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 2</t>
+          <t>30-Jul GMP: 15</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 2</t>
+          <t>3-Aug GMP: 8</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>4-Aug 11:02</t>
+          <t>4-Aug 16:29</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1446,12 +1438,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Manipal Health Enterprises IPOCAllotted</t>
+          <t>H.R. Hygiene Products BSE SMEC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹-2 (-0.34%) -15 ↓ / 35 ↑</t>
+          <t>₹2 (2.27%) 2 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1461,28 +1453,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5.12x</t>
+          <t>6.65x</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>590</v>
+        <v>88</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>₹9275.22 Cr</t>
+          <t>₹53.95 Cr</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>25</v>
+        <v>1600</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 9</t>
+          <t>29-Jul GMP: 2</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>31-Jul GMP: -15</t>
+          <t>31-Jul GMP: 2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1497,7 +1489,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>4-Aug 10:54</t>
+          <t>4-Aug 16:28</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1509,12 +1501,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cube Highways Trust InvIT IPOCAllotted</t>
+          <t>Manipal Health Enterprises IPOCAllotted</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
+          <t>₹2 (0.34%) -15 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1524,43 +1516,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9.35x</t>
+          <t>5.12x</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>152</v>
+        <v>590</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹5000.00 Cr</t>
+          <t>₹9275.22 Cr</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 0</t>
+          <t>29-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 1.75</t>
+          <t>31-Jul GMP: -15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 1.75</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>4-Aug 5:55</t>
+          <t>4-Aug 16:36</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1572,58 +1564,58 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Poojaa Precision Engg. BSE SMEL@470.00 (56.15%)</t>
+          <t>Cube Highways Trust InvIT IPOCAllotted</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹200 (66.45%) 195 ↓ / 300 ↑</t>
+          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>278.83x</t>
+          <t>9.35x</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>301</v>
+        <v>152</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹159.83 Cr</t>
+          <t>₹5000.00 Cr</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>400</v>
+        <v>95</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 300</t>
+          <t>22-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 225</t>
+          <t>24-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 200</t>
+          <t>31-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>4-Aug 9:33</t>
+          <t>4-Aug 5:55</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1635,63 +1627,63 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Propshop Events &amp; Exhibitions NSE SMEL@55.20 (-20%)</t>
+          <t>Poojaa Precision Engg. BSE SMEL@470.00 (56.15%)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹200 (66.45%) 195 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.53x</t>
+          <t>278.83x</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>69</v>
+        <v>301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹28.57 Cr</t>
+          <t>₹159.83 Cr</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 0</t>
+          <t>28-Jul GMP: 300</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 0</t>
+          <t>30-Jul GMP: 225</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>31-Jul</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 0</t>
+          <t>4-Aug GMP: 200</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>3-Aug 9:35</t>
+          <t>4-Aug 9:33</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1753,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Silverstorm Parks &amp; Resorts BSE SMEL@132.90 (-0.08%)</t>
+          <t>Propshop Events &amp; Exhibitions NSE SMEL@55.20 (-20%)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹5 (3.76%) 5 ↓ / 5 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1776,60 +1768,60 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.91x</t>
+          <t>1.53x</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹82.43 Cr</t>
+          <t>₹28.57 Cr</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 0</t>
+          <t>27-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 0</t>
+          <t>29-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 5</t>
+          <t>3-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>31-Jul 9:34</t>
+          <t>3-Aug 9:35</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lohia Corp IPOL@461.00 (8.47%)</t>
+          <t>Silverstorm Parks &amp; Resorts BSE SMEL@132.90 (-0.08%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹17 (4.00%) 7 ↓ / 56 ↑</t>
+          <t>₹5 (3.76%) 5 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1839,43 +1831,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.26x</t>
+          <t>1.91x</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>425</v>
+        <v>133</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹1101.28 Cr</t>
+          <t>₹82.43 Cr</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>35</v>
+        <v>1000</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 12</t>
+          <t>24-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 11.5</t>
+          <t>28-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>28-Jul</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 17</t>
+          <t>31-Jul GMP: 5</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>30-Jul 9:30</t>
+          <t>31-Jul 9:34</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1887,43 +1879,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indo-MIM IPOL@700.00 (44.33%)</t>
+          <t>Xtranet Technologies IPOL@136.00 (7.09%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹184 (37.94%) 168 ↓ / 213 ↑</t>
+          <t>₹14.5 (11.42%) 7.50 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>72.37x</t>
+          <t>12.24x</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>485</v>
+        <v>127</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹3811.21 Cr</t>
+          <t>₹166.80 Cr</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 170</t>
+          <t>23-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 190</t>
+          <t>27-Jul GMP: 7.7</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1933,12 +1925,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 184</t>
+          <t>30-Jul GMP: 14.5</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>30-Jul 9:36</t>
+          <t>30-Jul 9:31</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1950,43 +1942,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Xtranet Technologies IPOL@136.00 (7.09%)</t>
+          <t>Lohia Corp IPOL@461.00 (8.47%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹14.5 (11.42%) 7.50 ↓ / 26 ↑</t>
+          <t>₹17 (4.00%) 7 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>12.24x</t>
+          <t>7.26x</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>127</v>
+        <v>425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹166.80 Cr</t>
+          <t>₹1101.28 Cr</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 8</t>
+          <t>23-Jul GMP: 12</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 7.7</t>
+          <t>27-Jul GMP: 11.5</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1996,12 +1988,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 14.5</t>
+          <t>30-Jul GMP: 17</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>30-Jul 9:31</t>
+          <t>30-Jul 9:30</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2013,58 +2005,58 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Shree Balaji Mala BSE SMEL@133.00 (90%)</t>
+          <t>Indo-MIM IPOL@700.00 (44.33%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹56 (80.00%) 11 ↓ / 56 ↑</t>
+          <t>₹184 (37.94%) 168 ↓ / 213 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>200.34x</t>
+          <t>72.37x</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>70</v>
+        <v>485</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹18.90 Cr</t>
+          <t>₹3811.21 Cr</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2000</v>
+        <v>30</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 16</t>
+          <t>23-Jul GMP: 170</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 13</t>
+          <t>27-Jul GMP: 190</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>27-Jul</t>
+          <t>28-Jul</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 56</t>
+          <t>30-Jul GMP: 184</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>29-Jul 9:29</t>
+          <t>30-Jul 9:36</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2076,58 +2068,58 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Metalic Technoforge NSE SMEL@87.00 (12.99%)</t>
+          <t>Shree Balaji Mala BSE SMEL@133.00 (90%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹6 (7.79%) 6 ↓ / 8.10 ↑</t>
+          <t>₹56 (80.00%) 11 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.47x</t>
+          <t>200.34x</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹49.96 Cr</t>
+          <t>₹18.90 Cr</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 0</t>
+          <t>22-Jul GMP: 16</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 6</t>
+          <t>24-Jul GMP: 13</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>24-Jul</t>
+          <t>27-Jul</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 6</t>
+          <t>29-Jul GMP: 56</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>28-Jul 9:29</t>
+          <t>29-Jul 9:29</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2139,184 +2131,184 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gulf Lloyds BSE SMEL@100.00 (0%)</t>
+          <t>Metalic Technoforge NSE SMEL@87.00 (12.99%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹1 (1.00%) 1 ↓ / 25 ↑</t>
+          <t>₹6 (7.79%) 6 ↓ / 8.10 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10.85x</t>
+          <t>8.47x</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹18.19 Cr</t>
+          <t>₹49.96 Cr</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>20-Jul GMP: 10</t>
+          <t>21-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 1</t>
+          <t>23-Jul GMP: 6</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>23-Jul</t>
+          <t>24-Jul</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 1</t>
+          <t>28-Jul GMP: 6</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>27-Jul 9:29</t>
+          <t>28-Jul 9:29</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caliber Mining IPOL@500.25 (17.98%)</t>
+          <t>Gulf Lloyds BSE SMEL@100.00 (0%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹60 (14.15%) 60 ↓ / 117 ↑</t>
+          <t>₹1 (1.00%) 1 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>154.66x</t>
+          <t>10.85x</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>424</v>
+        <v>100</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹450.00 Cr</t>
+          <t>₹18.19 Cr</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>35</v>
+        <v>1200</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>17-Jul GMP: 116</t>
+          <t>20-Jul GMP: 10</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 71</t>
+          <t>22-Jul GMP: 1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>22-Jul</t>
+          <t>23-Jul</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 60</t>
+          <t>27-Jul GMP: 1</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>24-Jul 9:35</t>
+          <t>27-Jul 9:29</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sotefin Bharat BSE SMEL@205.00 (9.63%)</t>
+          <t>Caliber Mining IPOL@500.25 (17.98%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹2.5 (1.34%) 1 ↓ / 27 ↑</t>
+          <t>₹60 (14.15%) 60 ↓ / 117 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3.99x</t>
+          <t>154.66x</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>187</v>
+        <v>424</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹89.76 Cr</t>
+          <t>₹450.00 Cr</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>600</v>
+        <v>35</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 18</t>
+          <t>17-Jul GMP: 116</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20-Jul GMP: 1</t>
+          <t>21-Jul GMP: 71</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>21-Jul</t>
+          <t>22-Jul</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 2.5</t>
+          <t>24-Jul GMP: 60</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>23-Jul 9:34</t>
+          <t>24-Jul 9:35</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2328,58 +2320,58 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SBI Funds Management IPOL@613.30 (6.85%)</t>
+          <t>Sotefin Bharat BSE SMEL@205.00 (9.63%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹65 (11.32%) 65 ↓ / 140 ↑</t>
+          <t>₹2.5 (1.34%) 1 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>41.73x</t>
+          <t>3.99x</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>574</v>
+        <v>187</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹9812.91 Cr</t>
+          <t>₹89.76 Cr</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>26</v>
+        <v>600</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>14-Jul GMP: 88</t>
+          <t>16-Jul GMP: 18</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 97</t>
+          <t>20-Jul GMP: 1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>17-Jul</t>
+          <t>21-Jul</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 65</t>
+          <t>23-Jul GMP: 2.5</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>21-Jul 9:35</t>
+          <t>23-Jul 9:34</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,12 +501,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOU</t>
+          <t>Pramodini Medicare NSE SMEU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -519,32 +519,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>118</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹69.04 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1200</v>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4-Aug 12:00</t>
+          <t>5-Aug 10:53</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -556,17 +564,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOU</t>
+          <t>Milky Mist Dairy Food IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹246 (28.24%) 146 ↓ / 246 ↑</t>
+          <t>₹-- (%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -574,40 +582,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>871</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>17</v>
-      </c>
+          <t>₹1553.00 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4-Aug 16:31</t>
+          <t>5-Aug 9:20</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -619,17 +623,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LEAP India IPOU</t>
+          <t>Dhoot Transmission IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹3 (1.89%) 3 ↓ / 8 ↑</t>
+          <t>₹253 (29.05%) 146 ↓ / 253 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -638,39 +642,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>159</v>
+        <v>871</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹2480.00 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>4-Aug 16:32</t>
+          <t>5-Aug 11:00</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -682,12 +686,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Technocraft Ventures IPOU</t>
+          <t>Molbio Diagnostics IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹10 (4.72%) 10 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -701,39 +705,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>212</v>
+        <v>807</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹251.88 Cr</t>
+          <t>₹939.70 Cr</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>4-Aug 16:30</t>
+          <t>5-Aug 11:01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -745,12 +749,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Optimystix Entertainment NSE SMEU</t>
+          <t>Technocraft Ventures IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹10 (4.72%) 10 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -764,15 +768,15 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹108.50 Cr</t>
+          <t>₹251.88 Cr</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>800</v>
+        <v>70</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -796,7 +800,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>4-Aug 16:36</t>
+          <t>5-Aug 11:00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -808,17 +812,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LAPL Automotive BSE SMEU</t>
+          <t>Optimystix Entertainment NSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹27 (28.72%) 22 ↓ / 27 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -827,39 +831,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>94</v>
+        <v>175</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹32.40 Cr</t>
+          <t>₹108.50 Cr</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>4-Aug 16:28</t>
+          <t>5-Aug 10:58</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -871,17 +875,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOU</t>
+          <t>LEAP India IPOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹7.5 (14.15%) 6.50 ↓ / 13 ↑</t>
+          <t>₹3 (1.89%) 3 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -890,39 +894,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>159</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
+          <t>₹2480.00 Cr</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>281</v>
+        <v>94</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>4-Aug 16:30</t>
+          <t>5-Aug 11:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -934,30 +938,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aegeus Technologies BSE SMEO</t>
+          <t>LAPL Automotive BSE SMEU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹27 (28.72%) 22 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.37x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹23.71 Cr</t>
+          <t>₹32.40 Cr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -965,27 +969,27 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4-Aug 16:29</t>
+          <t>5-Aug 11:01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -997,58 +1001,58 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anawil Wire &amp; Engineering NSE SMEO</t>
+          <t>Ardee Industries IPOO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹80 (29.63%) 60 ↓ / 90 ↑</t>
+          <t>₹8 (15.09%) 6.50 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10.95x</t>
+          <t>0.52x</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>270</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹177.81 Cr</t>
+          <t>₹425.87 Cr</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>400</v>
+        <v>281</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 80</t>
+          <t>5-Aug GMP: 8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4-Aug 16:35</t>
+          <t>5-Aug 10:57</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1060,58 +1064,58 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMECT</t>
+          <t>Aegeus Technologies BSE SMEO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹24 (18.46%) 18 ↓ / 26 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>146.11x</t>
+          <t>0.62x</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹23.71 Cr</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 25</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 24</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>4-Aug 16:28</t>
+          <t>5-Aug 10:57</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1123,58 +1127,58 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fusion Klassroom Edutech BSE SMECT</t>
+          <t>Anawil Wire &amp; Engineering NSE SMECT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
+          <t>₹80 (29.63%) 60 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.5x</t>
+          <t>25.02x</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>159</v>
+        <v>270</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹39.04 Cr</t>
+          <t>₹177.81 Cr</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 4</t>
+          <t>3-Aug GMP: 80</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>5-Aug GMP: 80</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4-Aug 16:29</t>
+          <t>5-Aug 10:56</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1186,58 +1190,58 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MV Electrosystems IPOC</t>
+          <t>Fusion Klassroom Edutech BSE SMEC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹98 (23.06%) 60 ↓ / 133 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>200.66x</t>
+          <t>1.5x</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>425</v>
+        <v>159</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹290.00 Cr</t>
+          <t>₹39.04 Cr</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>34</v>
+        <v>800</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 125</t>
+          <t>31-Jul GMP: 4</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 100</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>4-Aug 16:37</t>
+          <t>5-Aug 11:01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1249,58 +1253,58 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Juniper Green Energy IPOC</t>
+          <t>G.V. Electricals BSE SMEC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹13.5 (6.00%) 1.50 ↓ / 17 ↑</t>
+          <t>₹24 (18.46%) 18 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.38x</t>
+          <t>146.76x</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>225</v>
+        <v>130</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹1800.00 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>66</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 8</t>
+          <t>31-Jul GMP: 25</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 9.5</t>
+          <t>4-Aug GMP: 24</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>4-Aug 16:36</t>
+          <t>5-Aug 10:54</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1312,43 +1316,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Oneindig Technologies BSE SMEC</t>
+          <t>MV Electrosystems IPOCAllotted</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹102 (24.00%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.73x</t>
+          <t>200.66x</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>96</v>
+        <v>425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹27.65 Cr</t>
+          <t>₹290.00 Cr</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1200</v>
+        <v>34</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 0</t>
+          <t>30-Jul GMP: 125</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 0</t>
+          <t>3-Aug GMP: 100</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1363,7 +1367,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>4-Aug 16:32</t>
+          <t>5-Aug 10:59</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1375,12 +1379,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dhaval Packaging BSE SMEC</t>
+          <t>Oneindig Technologies BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹8 (8.25%) 8 ↓ / 15 ↑</t>
+          <t>₹7 (7.29%) 7 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1390,15 +1394,15 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>49.99x</t>
+          <t>1.73x</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹36.36 Cr</t>
+          <t>₹27.65 Cr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1406,12 +1410,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 15</t>
+          <t>30-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 8</t>
+          <t>3-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1426,7 +1430,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>4-Aug 16:29</t>
+          <t>5-Aug 10:59</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1438,58 +1442,58 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H.R. Hygiene Products BSE SMEC</t>
+          <t>Juniper Green Energy IPOCAllotted</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹2 (2.27%) 2 ↓ / 2 ↑</t>
+          <t>₹16 (7.11%) 1.50 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6.65x</t>
+          <t>8.38x</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>88</v>
+        <v>225</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>₹53.95 Cr</t>
+          <t>₹1800.00 Cr</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1600</v>
+        <v>66</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 2</t>
+          <t>30-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 2</t>
+          <t>3-Aug GMP: 9.5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>4-Aug 16:28</t>
+          <t>5-Aug 10:55</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1501,58 +1505,58 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Manipal Health Enterprises IPOCAllotted</t>
+          <t>Dhaval Packaging BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹2 (0.34%) -15 ↓ / 35 ↑</t>
+          <t>₹10 (10.31%) 8 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5.12x</t>
+          <t>49.99x</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>590</v>
+        <v>97</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹9275.22 Cr</t>
+          <t>₹36.36 Cr</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>25</v>
+        <v>1200</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 9</t>
+          <t>30-Jul GMP: 15</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>31-Jul GMP: -15</t>
+          <t>3-Aug GMP: 8</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>4-Aug 16:36</t>
+          <t>5-Aug 10:57</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1615,7 +1619,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>4-Aug 5:55</t>
+          <t>5-Aug 5:55</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1627,58 +1631,58 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Poojaa Precision Engg. BSE SMEL@470.00 (56.15%)</t>
+          <t>Manipal Health Enterprises IPOL@652.00 (10.51%)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹200 (66.45%) 195 ↓ / 300 ↑</t>
+          <t>₹7 (1.19%) -15 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>278.83x</t>
+          <t>5.12x</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>301</v>
+        <v>590</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹159.83 Cr</t>
+          <t>₹9275.22 Cr</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>400</v>
+        <v>25</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 300</t>
+          <t>29-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 225</t>
+          <t>31-Jul GMP: -15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 200</t>
+          <t>5-Aug GMP: 7</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>4-Aug 9:33</t>
+          <t>5-Aug 9:30</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1690,12 +1694,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Advance Technoforge BSE SMEL@94.00 (-1.05%)</t>
+          <t>H.R. Hygiene Products BSE SMEL@90.00 (2.27%)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹4 (4.21%) 3 ↓ / 9 ↑</t>
+          <t>₹1 (1.14%) 1 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1705,123 +1709,123 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.55x</t>
+          <t>6.65x</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹24.04 Cr</t>
+          <t>₹53.95 Cr</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 9</t>
+          <t>29-Jul GMP: 2</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 8</t>
+          <t>31-Jul GMP: 2</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 4</t>
+          <t>5-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>3-Aug 9:30</t>
+          <t>5-Aug 9:37</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Propshop Events &amp; Exhibitions NSE SMEL@55.20 (-20%)</t>
+          <t>Poojaa Precision Engg. BSE SMEL@470.00 (56.15%)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹200 (66.45%) 195 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.53x</t>
+          <t>278.83x</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>69</v>
+        <v>301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹28.57 Cr</t>
+          <t>₹159.83 Cr</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 0</t>
+          <t>28-Jul GMP: 300</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 0</t>
+          <t>30-Jul GMP: 225</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>31-Jul</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 0</t>
+          <t>4-Aug GMP: 200</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3-Aug 9:35</t>
+          <t>4-Aug 9:33</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Silverstorm Parks &amp; Resorts BSE SMEL@132.90 (-0.08%)</t>
+          <t>Advance Technoforge BSE SMEL@94.00 (-1.05%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹5 (3.76%) 5 ↓ / 5 ↑</t>
+          <t>₹4 (4.21%) 3 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1831,123 +1835,123 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.91x</t>
+          <t>1.55x</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹82.43 Cr</t>
+          <t>₹24.04 Cr</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 0</t>
+          <t>27-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 0</t>
+          <t>29-Jul GMP: 8</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 5</t>
+          <t>3-Aug GMP: 4</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>31-Jul 9:34</t>
+          <t>3-Aug 9:30</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Xtranet Technologies IPOL@136.00 (7.09%)</t>
+          <t>Propshop Events &amp; Exhibitions NSE SMEL@55.20 (-20%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹14.5 (11.42%) 7.50 ↓ / 26 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>12.24x</t>
+          <t>1.53x</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>127</v>
+        <v>69</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹166.80 Cr</t>
+          <t>₹28.57 Cr</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>110</v>
+        <v>2000</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 8</t>
+          <t>27-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 7.7</t>
+          <t>29-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>28-Jul</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 14.5</t>
+          <t>3-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>30-Jul 9:31</t>
+          <t>3-Aug 9:35</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lohia Corp IPOL@461.00 (8.47%)</t>
+          <t>Silverstorm Parks &amp; Resorts BSE SMEL@132.90 (-0.08%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹17 (4.00%) 7 ↓ / 56 ↑</t>
+          <t>₹5 (3.76%) 5 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1957,43 +1961,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7.26x</t>
+          <t>1.91x</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>425</v>
+        <v>133</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹1101.28 Cr</t>
+          <t>₹82.43 Cr</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>35</v>
+        <v>1000</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 12</t>
+          <t>24-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 11.5</t>
+          <t>28-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>28-Jul</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 17</t>
+          <t>31-Jul GMP: 5</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>30-Jul 9:30</t>
+          <t>31-Jul 9:34</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2005,43 +2009,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Indo-MIM IPOL@700.00 (44.33%)</t>
+          <t>Lohia Corp IPOL@461.00 (8.47%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹184 (37.94%) 168 ↓ / 213 ↑</t>
+          <t>₹17 (4.00%) 7 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>72.37x</t>
+          <t>7.26x</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>485</v>
+        <v>425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹3811.21 Cr</t>
+          <t>₹1101.28 Cr</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 170</t>
+          <t>23-Jul GMP: 12</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 190</t>
+          <t>27-Jul GMP: 11.5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2051,12 +2055,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 184</t>
+          <t>30-Jul GMP: 17</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>30-Jul 9:36</t>
+          <t>30-Jul 9:30</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2068,58 +2072,58 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Shree Balaji Mala BSE SMEL@133.00 (90%)</t>
+          <t>Indo-MIM IPOL@700.00 (44.33%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹56 (80.00%) 11 ↓ / 56 ↑</t>
+          <t>₹184 (37.94%) 168 ↓ / 213 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>200.34x</t>
+          <t>72.37x</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>70</v>
+        <v>485</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹18.90 Cr</t>
+          <t>₹3811.21 Cr</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2000</v>
+        <v>30</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 16</t>
+          <t>23-Jul GMP: 170</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 13</t>
+          <t>27-Jul GMP: 190</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>27-Jul</t>
+          <t>28-Jul</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 56</t>
+          <t>30-Jul GMP: 184</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>29-Jul 9:29</t>
+          <t>30-Jul 9:36</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2131,58 +2135,58 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Metalic Technoforge NSE SMEL@87.00 (12.99%)</t>
+          <t>Xtranet Technologies IPOL@136.00 (7.09%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹6 (7.79%) 6 ↓ / 8.10 ↑</t>
+          <t>₹14.5 (11.42%) 7.50 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.47x</t>
+          <t>12.24x</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹49.96 Cr</t>
+          <t>₹166.80 Cr</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1600</v>
+        <v>110</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 0</t>
+          <t>23-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 6</t>
+          <t>27-Jul GMP: 7.7</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>24-Jul</t>
+          <t>28-Jul</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 6</t>
+          <t>30-Jul GMP: 14.5</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>28-Jul 9:29</t>
+          <t>30-Jul 9:31</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2194,121 +2198,121 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gulf Lloyds BSE SMEL@100.00 (0%)</t>
+          <t>Shree Balaji Mala BSE SMEL@133.00 (90%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹1 (1.00%) 1 ↓ / 25 ↑</t>
+          <t>₹56 (80.00%) 11 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10.85x</t>
+          <t>200.34x</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹18.19 Cr</t>
+          <t>₹18.90 Cr</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>20-Jul GMP: 10</t>
+          <t>22-Jul GMP: 16</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 1</t>
+          <t>24-Jul GMP: 13</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>23-Jul</t>
+          <t>27-Jul</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 1</t>
+          <t>29-Jul GMP: 56</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>27-Jul 9:29</t>
+          <t>29-Jul 9:29</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caliber Mining IPOL@500.25 (17.98%)</t>
+          <t>Metalic Technoforge NSE SMEL@87.00 (12.99%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹60 (14.15%) 60 ↓ / 117 ↑</t>
+          <t>₹6 (7.79%) 6 ↓ / 8.10 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>154.66x</t>
+          <t>8.47x</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>424</v>
+        <v>77</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹450.00 Cr</t>
+          <t>₹49.96 Cr</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>35</v>
+        <v>1600</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>17-Jul GMP: 116</t>
+          <t>21-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 71</t>
+          <t>23-Jul GMP: 6</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>22-Jul</t>
+          <t>24-Jul</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 60</t>
+          <t>28-Jul GMP: 6</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>24-Jul 9:35</t>
+          <t>28-Jul 9:29</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2320,12 +2324,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sotefin Bharat BSE SMEL@205.00 (9.63%)</t>
+          <t>Gulf Lloyds BSE SMEL@100.00 (0%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹2.5 (1.34%) 1 ↓ / 27 ↑</t>
+          <t>₹1 (1.00%) 1 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2335,48 +2339,48 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3.99x</t>
+          <t>10.85x</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>187</v>
+        <v>100</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹89.76 Cr</t>
+          <t>₹18.19 Cr</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>16-Jul GMP: 18</t>
+          <t>20-Jul GMP: 10</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20-Jul GMP: 1</t>
+          <t>22-Jul GMP: 1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>21-Jul</t>
+          <t>23-Jul</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 2.5</t>
+          <t>27-Jul GMP: 1</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>23-Jul 9:34</t>
+          <t>27-Jul 9:29</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5-Aug 10:53</t>
+          <t>5-Aug 16:29</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹253 (29.05%) 146 ↓ / 253 ↑</t>
+          <t>₹255 (29.28%) 146 ↓ / 255 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5-Aug 11:00</t>
+          <t>5-Aug 16:31</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>5-Aug 11:01</t>
+          <t>5-Aug 16:33</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹10 (4.72%) 10 ↓ / 10 ↑</t>
+          <t>₹12 (5.66%) 10 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>5-Aug 11:00</t>
+          <t>5-Aug 16:29</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>5-Aug 10:58</t>
+          <t>5-Aug 16:29</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5-Aug 11:02</t>
+          <t>5-Aug 16:31</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹27 (28.72%) 22 ↓ / 27 ↑</t>
+          <t>₹26 (27.66%) 22 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5-Aug 11:01</t>
+          <t>5-Aug 16:34</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1001,12 +1001,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOO</t>
+          <t>G.V. Electricals BSE SMEO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹8 (15.09%) 6.50 ↓ / 13 ↑</t>
+          <t>₹24 (18.46%) 18 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1016,23 +1016,23 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.52x</t>
+          <t>146.76x</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>281</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 8</t>
+          <t>31-Jul GMP: 25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>5-Aug 10:57</t>
+          <t>5-Aug 16:35</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1064,58 +1064,58 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aegeus Technologies BSE SMEO</t>
+          <t>Ardee Industries IPOO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹14 (26.42%) 6.50 ↓ / 14 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.62x</t>
+          <t>3.03x</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹23.71 Cr</t>
+          <t>₹425.87 Cr</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1200</v>
+        <v>281</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>5-Aug GMP: 14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>5-Aug 10:57</t>
+          <t>5-Aug 16:32</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1127,58 +1127,58 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Anawil Wire &amp; Engineering NSE SMECT</t>
+          <t>Aegeus Technologies BSE SMEO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹80 (29.63%) 60 ↓ / 90 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>25.02x</t>
+          <t>1.87x</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>270</v>
+        <v>105</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹177.81 Cr</t>
+          <t>₹23.71 Cr</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 80</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 80</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5-Aug 10:56</t>
+          <t>5-Aug 16:32</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1190,58 +1190,58 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fusion Klassroom Edutech BSE SMEC</t>
+          <t>Anawil Wire &amp; Engineering NSE SMECT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
+          <t>₹80 (29.63%) 60 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.5x</t>
+          <t>148.89x</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>159</v>
+        <v>270</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹39.04 Cr</t>
+          <t>₹177.81 Cr</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 4</t>
+          <t>3-Aug GMP: 80</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>5-Aug GMP: 80</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>5-Aug 11:01</t>
+          <t>5-Aug 16:28</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1253,58 +1253,58 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEC</t>
+          <t>Fusion Klassroom Edutech BSE SMEC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹24 (18.46%) 18 ↓ / 26 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>146.76x</t>
+          <t>1.5x</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹39.04 Cr</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 25</t>
+          <t>31-Jul GMP: 4</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 24</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>5-Aug 10:54</t>
+          <t>5-Aug 16:30</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹102 (24.00%) 60 ↓ / 133 ↑</t>
+          <t>₹103 (24.24%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5-Aug 10:59</t>
+          <t>5-Aug 16:28</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>5-Aug 10:59</t>
+          <t>5-Aug 16:30</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹16 (7.11%) 1.50 ↓ / 17 ↑</t>
+          <t>₹17.5 (7.78%) 1.50 ↓ / 17.50 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>5-Aug 10:55</t>
+          <t>5-Aug 16:37</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>5-Aug 10:57</t>
+          <t>5-Aug 16:37</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5-Aug 16:29</t>
+          <t>6-Aug 11:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -564,12 +564,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food IPOU</t>
+          <t>Shiprocket IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -582,36 +582,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>97</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹1553.00 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>₹1617.48 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>154</v>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5-Aug 9:20</t>
+          <t>6-Aug 10:53</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -623,17 +627,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOU</t>
+          <t>Fascinate Textiles NSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹255 (29.28%) 146 ↓ / 255 ↑</t>
+          <t>₹-- (%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -642,39 +646,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>871</v>
+        <v>156</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
+          <t>₹66.99 Cr</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>17</v>
+        <v>800</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5-Aug 16:31</t>
+          <t>6-Aug 9:10</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -686,7 +690,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOU</t>
+          <t>Milky Mist Dairy Food IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -705,39 +709,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>807</v>
+        <v>140</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹939.70 Cr</t>
+          <t>₹1553.00 Cr</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>5-Aug 16:33</t>
+          <t>6-Aug 10:54</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -749,17 +753,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Technocraft Ventures IPOU</t>
+          <t>Dhoot Transmission IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹12 (5.66%) 10 ↓ / 12 ↑</t>
+          <t>₹250 (28.70%) 146 ↓ / 253 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -768,39 +772,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>212</v>
+        <v>871</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹251.88 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>5-Aug 16:29</t>
+          <t>6-Aug 11:01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -812,17 +816,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Optimystix Entertainment NSE SMEU</t>
+          <t>Molbio Diagnostics IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹185 (22.92%) 170 ↓ / 185 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -831,39 +835,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>175</v>
+        <v>807</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹108.50 Cr</t>
+          <t>₹939.70 Cr</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>800</v>
+        <v>18</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>5-Aug 16:29</t>
+          <t>6-Aug 10:59</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -875,12 +879,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LEAP India IPOU</t>
+          <t>Optimystix Entertainment NSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹3 (1.89%) 3 ↓ / 8 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -894,15 +898,15 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹2480.00 Cr</t>
+          <t>₹108.50 Cr</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>94</v>
+        <v>800</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -926,7 +930,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5-Aug 16:31</t>
+          <t>6-Aug 10:56</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -938,17 +942,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LAPL Automotive BSE SMEU</t>
+          <t>Technocraft Ventures IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹26 (27.66%) 22 ↓ / 27 ↑</t>
+          <t>₹13 (6.13%) 10 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -957,39 +961,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>94</v>
+        <v>212</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹32.40 Cr</t>
+          <t>₹251.88 Cr</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1200</v>
+        <v>70</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5-Aug 16:34</t>
+          <t>6-Aug 11:01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1001,58 +1005,58 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEO</t>
+          <t>LEAP India IPOU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹24 (18.46%) 18 ↓ / 26 ↑</t>
+          <t>₹3 (1.89%) 3 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>146.76x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹2480.00 Cr</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>94</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 25</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>5-Aug 16:35</t>
+          <t>6-Aug 10:59</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1064,12 +1068,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOO</t>
+          <t>LAPL Automotive BSE SMEO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹14 (26.42%) 6.50 ↓ / 14 ↑</t>
+          <t>₹30 (31.91%) 22 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1079,43 +1083,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.03x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
+          <t>₹32.40 Cr</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>281</v>
+        <v>1200</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 14</t>
+          <t>6-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>5-Aug 16:32</t>
+          <t>6-Aug 10:56</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1127,58 +1131,58 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aegeus Technologies BSE SMEO</t>
+          <t>G.V. Electricals BSE SMEO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹26 (20.00%) 18 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.87x</t>
+          <t>146.76x</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹23.71 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>31-Jul GMP: 25</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5-Aug 16:32</t>
+          <t>6-Aug 11:02</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1190,12 +1194,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Anawil Wire &amp; Engineering NSE SMECT</t>
+          <t>Ardee Industries IPOO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹80 (29.63%) 60 ↓ / 90 ↑</t>
+          <t>₹14 (26.42%) 6.50 ↓ / 15.25 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1205,43 +1209,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>148.89x</t>
+          <t>6.4x</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>270</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹177.81 Cr</t>
+          <t>₹425.87 Cr</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>400</v>
+        <v>281</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 80</t>
+          <t>5-Aug GMP: 15.25</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 80</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>5-Aug 16:28</t>
+          <t>6-Aug 10:54</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1253,12 +1257,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fusion Klassroom Edutech BSE SMEC</t>
+          <t>Aegeus Technologies BSE SMECT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1268,43 +1272,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.5x</t>
+          <t>3.38x</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>159</v>
+        <v>105</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹39.04 Cr</t>
+          <t>₹23.71 Cr</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 4</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>6-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>5-Aug 16:30</t>
+          <t>6-Aug 10:56</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1316,12 +1320,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MV Electrosystems IPOCAllotted</t>
+          <t>Anawil Wire &amp; Engineering NSE SMEC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹103 (24.24%) 60 ↓ / 133 ↑</t>
+          <t>₹78 (28.89%) 60 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1331,43 +1335,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>200.66x</t>
+          <t>149.13x</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>425</v>
+        <v>270</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹290.00 Cr</t>
+          <t>₹177.81 Cr</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>34</v>
+        <v>400</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 125</t>
+          <t>3-Aug GMP: 80</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 100</t>
+          <t>5-Aug GMP: 78</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5-Aug 16:28</t>
+          <t>6-Aug 10:57</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1379,58 +1383,58 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Oneindig Technologies BSE SMECAllotted</t>
+          <t>Fusion Klassroom Edutech BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹7 (7.29%) 7 ↓ / 7 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.73x</t>
+          <t>1.5x</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>96</v>
+        <v>159</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹27.65 Cr</t>
+          <t>₹39.04 Cr</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 0</t>
+          <t>31-Jul GMP: 4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 0</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>5-Aug 16:30</t>
+          <t>6-Aug 10:56</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1442,58 +1446,58 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Juniper Green Energy IPOCAllotted</t>
+          <t>Cube Highways Trust InvIT IPOCAllotted</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹17.5 (7.78%) 1.50 ↓ / 17.50 ↑</t>
+          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.38x</t>
+          <t>9.35x</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>225</v>
+        <v>152</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>₹1800.00 Cr</t>
+          <t>₹5000.00 Cr</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 8</t>
+          <t>22-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 9.5</t>
+          <t>24-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>31-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>5-Aug 16:37</t>
+          <t>6-Aug 5:55</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1505,12 +1509,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dhaval Packaging BSE SMECAllotted</t>
+          <t>Dhaval Packaging BSE SMEL@110.00 (13.4%)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹10 (10.31%) 8 ↓ / 15 ↑</t>
+          <t>₹12 (12.37%) 8 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1551,12 +1555,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>6-Aug GMP: 12</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>5-Aug 16:37</t>
+          <t>6-Aug 9:33</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1568,58 +1572,58 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cube Highways Trust InvIT IPOCAllotted</t>
+          <t>Oneindig Technologies BSE SMEL@120.00 (25%)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
+          <t>₹7 (7.29%) 7 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9.35x</t>
+          <t>1.73x</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹5000.00 Cr</t>
+          <t>₹27.65 Cr</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>95</v>
+        <v>1200</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 0</t>
+          <t>30-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 1.75</t>
+          <t>3-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 1.75</t>
+          <t>6-Aug GMP: 7</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>5-Aug 5:55</t>
+          <t>6-Aug 9:28</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1631,58 +1635,58 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Manipal Health Enterprises IPOL@652.00 (10.51%)</t>
+          <t>MV Electrosystems IPOL@520.00 (22.35%)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹7 (1.19%) -15 ↓ / 35 ↑</t>
+          <t>₹109 (25.65%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5.12x</t>
+          <t>200.66x</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>590</v>
+        <v>425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹9275.22 Cr</t>
+          <t>₹290.00 Cr</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 9</t>
+          <t>30-Jul GMP: 125</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>31-Jul GMP: -15</t>
+          <t>3-Aug GMP: 100</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 7</t>
+          <t>6-Aug GMP: 109</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>5-Aug 9:30</t>
+          <t>6-Aug 9:35</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1694,58 +1698,58 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H.R. Hygiene Products BSE SMEL@90.00 (2.27%)</t>
+          <t>Juniper Green Energy IPOL@245.00 (8.89%)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹1 (1.14%) 1 ↓ / 2 ↑</t>
+          <t>₹23 (10.22%) 1.50 ↓ / 23 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>6.65x</t>
+          <t>8.38x</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>88</v>
+        <v>225</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹53.95 Cr</t>
+          <t>₹1800.00 Cr</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1600</v>
+        <v>66</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 2</t>
+          <t>30-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 2</t>
+          <t>3-Aug GMP: 9.5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 1</t>
+          <t>6-Aug GMP: 23</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>5-Aug 9:37</t>
+          <t>6-Aug 9:37</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1757,58 +1761,58 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Poojaa Precision Engg. BSE SMEL@470.00 (56.15%)</t>
+          <t>Manipal Health Enterprises IPOL@652.00 (10.51%)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹200 (66.45%) 195 ↓ / 300 ↑</t>
+          <t>₹7 (1.19%) -15 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>278.83x</t>
+          <t>5.12x</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>301</v>
+        <v>590</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹159.83 Cr</t>
+          <t>₹9275.22 Cr</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>400</v>
+        <v>25</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 300</t>
+          <t>29-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 225</t>
+          <t>31-Jul GMP: -15</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 200</t>
+          <t>5-Aug GMP: 7</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>4-Aug 9:33</t>
+          <t>5-Aug 9:30</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1820,12 +1824,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Advance Technoforge BSE SMEL@94.00 (-1.05%)</t>
+          <t>H.R. Hygiene Products BSE SMEL@90.00 (2.27%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹4 (4.21%) 3 ↓ / 9 ↑</t>
+          <t>₹1 (1.14%) 1 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1835,123 +1839,123 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.55x</t>
+          <t>6.65x</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹24.04 Cr</t>
+          <t>₹53.95 Cr</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 9</t>
+          <t>29-Jul GMP: 2</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 8</t>
+          <t>31-Jul GMP: 2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 4</t>
+          <t>5-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3-Aug 9:30</t>
+          <t>5-Aug 9:37</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Propshop Events &amp; Exhibitions NSE SMEL@55.20 (-20%)</t>
+          <t>Poojaa Precision Engg. BSE SMEL@470.00 (56.15%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹200 (66.45%) 195 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.53x</t>
+          <t>278.83x</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>69</v>
+        <v>301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹28.57 Cr</t>
+          <t>₹159.83 Cr</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 0</t>
+          <t>28-Jul GMP: 300</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 0</t>
+          <t>30-Jul GMP: 225</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>31-Jul</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 0</t>
+          <t>4-Aug GMP: 200</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>3-Aug 9:35</t>
+          <t>4-Aug 9:33</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Silverstorm Parks &amp; Resorts BSE SMEL@132.90 (-0.08%)</t>
+          <t>Propshop Events &amp; Exhibitions NSE SMEL@55.20 (-20%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹5 (3.76%) 5 ↓ / 5 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1961,60 +1965,60 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.91x</t>
+          <t>1.53x</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹82.43 Cr</t>
+          <t>₹28.57 Cr</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 0</t>
+          <t>27-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 0</t>
+          <t>29-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 5</t>
+          <t>3-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>31-Jul 9:34</t>
+          <t>3-Aug 9:35</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lohia Corp IPOL@461.00 (8.47%)</t>
+          <t>Advance Technoforge BSE SMEL@94.00 (-1.05%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹17 (4.00%) 7 ↓ / 56 ↑</t>
+          <t>₹4 (4.21%) 3 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2024,106 +2028,106 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7.26x</t>
+          <t>1.55x</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>425</v>
+        <v>95</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹1101.28 Cr</t>
+          <t>₹24.04 Cr</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>35</v>
+        <v>1200</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 12</t>
+          <t>27-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 11.5</t>
+          <t>29-Jul GMP: 8</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>28-Jul</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 17</t>
+          <t>3-Aug GMP: 4</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>30-Jul 9:30</t>
+          <t>3-Aug 9:30</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Indo-MIM IPOL@700.00 (44.33%)</t>
+          <t>Silverstorm Parks &amp; Resorts BSE SMEL@132.90 (-0.08%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹184 (37.94%) 168 ↓ / 213 ↑</t>
+          <t>₹5 (3.76%) 5 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>72.37x</t>
+          <t>1.91x</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>485</v>
+        <v>133</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹3811.21 Cr</t>
+          <t>₹82.43 Cr</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 170</t>
+          <t>24-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 190</t>
+          <t>28-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>28-Jul</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 184</t>
+          <t>31-Jul GMP: 5</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>30-Jul 9:36</t>
+          <t>31-Jul 9:34</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2198,58 +2202,58 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Shree Balaji Mala BSE SMEL@133.00 (90%)</t>
+          <t>Lohia Corp IPOL@461.00 (8.47%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹56 (80.00%) 11 ↓ / 56 ↑</t>
+          <t>₹17 (4.00%) 7 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>200.34x</t>
+          <t>7.26x</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>70</v>
+        <v>425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹18.90 Cr</t>
+          <t>₹1101.28 Cr</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2000</v>
+        <v>35</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 16</t>
+          <t>23-Jul GMP: 12</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 13</t>
+          <t>27-Jul GMP: 11.5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>27-Jul</t>
+          <t>28-Jul</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 56</t>
+          <t>30-Jul GMP: 17</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>29-Jul 9:29</t>
+          <t>30-Jul 9:30</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2261,58 +2265,58 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Metalic Technoforge NSE SMEL@87.00 (12.99%)</t>
+          <t>Indo-MIM IPOL@700.00 (44.33%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹6 (7.79%) 6 ↓ / 8.10 ↑</t>
+          <t>₹184 (37.94%) 168 ↓ / 213 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.47x</t>
+          <t>72.37x</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>77</v>
+        <v>485</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹49.96 Cr</t>
+          <t>₹3811.21 Cr</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1600</v>
+        <v>30</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>21-Jul GMP: 0</t>
+          <t>23-Jul GMP: 170</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 6</t>
+          <t>27-Jul GMP: 190</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>24-Jul</t>
+          <t>28-Jul</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 6</t>
+          <t>30-Jul GMP: 184</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>28-Jul 9:29</t>
+          <t>30-Jul 9:36</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2324,63 +2328,63 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gulf Lloyds BSE SMEL@100.00 (0%)</t>
+          <t>Shree Balaji Mala BSE SMEL@133.00 (90%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹1 (1.00%) 1 ↓ / 25 ↑</t>
+          <t>₹56 (80.00%) 11 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>10.85x</t>
+          <t>200.34x</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹18.19 Cr</t>
+          <t>₹18.90 Cr</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>20-Jul GMP: 10</t>
+          <t>22-Jul GMP: 16</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 1</t>
+          <t>24-Jul GMP: 13</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>23-Jul</t>
+          <t>27-Jul</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 1</t>
+          <t>29-Jul GMP: 56</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>27-Jul 9:29</t>
+          <t>29-Jul 9:29</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6-Aug 11:02</t>
+          <t>6-Aug 16:33</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>6-Aug 10:53</t>
+          <t>6-Aug 16:32</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹-- (%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>6-Aug 9:10</t>
+          <t>6-Aug 16:36</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>6-Aug 10:54</t>
+          <t>6-Aug 16:31</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹250 (28.70%) 146 ↓ / 253 ↑</t>
+          <t>₹258 (29.62%) 146 ↓ / 258 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>6-Aug 11:01</t>
+          <t>6-Aug 16:31</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹185 (22.92%) 170 ↓ / 185 ↑</t>
+          <t>₹210 (26.02%) 170 ↓ / 210 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6-Aug 10:59</t>
+          <t>6-Aug 16:30</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹5 (2.86%) 5 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>6-Aug 10:56</t>
+          <t>6-Aug 16:28</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹13 (6.13%) 10 ↓ / 13 ↑</t>
+          <t>₹15 (7.08%) 10 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>6-Aug 11:01</t>
+          <t>6-Aug 16:28</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹3 (1.89%) 3 ↓ / 8 ↑</t>
+          <t>₹11 (6.92%) 3 ↓ / 11 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>6-Aug 10:59</t>
+          <t>6-Aug 16:31</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.27x</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6-Aug 10:56</t>
+          <t>6-Aug 16:31</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>6-Aug 11:02</t>
+          <t>6-Aug 16:29</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹14 (26.42%) 6.50 ↓ / 15.25 ↑</t>
+          <t>₹15.5 (29.25%) 6.50 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6.4x</t>
+          <t>14.4x</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>6-Aug 10:54</t>
+          <t>6-Aug 16:33</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1262,17 +1262,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹12 (11.43%) 12 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.38x</t>
+          <t>29.4x</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 0</t>
+          <t>6-Aug GMP: 12</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>6-Aug 10:56</t>
+          <t>6-Aug 16:35</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>6-Aug 10:57</t>
+          <t>6-Aug 16:35</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>6-Aug 10:56</t>
+          <t>6-Aug 16:35</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6-Aug 16:33</t>
+          <t>7-Aug 10:00</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -569,12 +569,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹16 (16.49%) 14 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>6-Aug 16:32</t>
+          <t>7-Aug 9:54</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMEU</t>
+          <t>Behari Lal Engineering IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,39 +646,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>156</v>
+        <v>285</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹66.99 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>800</v>
+        <v>52</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>6-Aug 16:36</t>
+          <t>7-Aug 9:53</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -695,12 +695,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹25 (17.86%) 25 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>6-Aug 16:31</t>
+          <t>7-Aug 9:57</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -753,17 +753,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOU</t>
+          <t>Fascinate Textiles NSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹258 (29.62%) 146 ↓ / 258 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -772,39 +772,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>871</v>
+        <v>156</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
+          <t>₹66.98 Cr</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>17</v>
+        <v>800</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>6-Aug 16:31</t>
+          <t>7-Aug 9:57</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -816,17 +816,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOU</t>
+          <t>Sham Foam BSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹210 (26.02%) 170 ↓ / 210 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -835,61 +835,61 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>807</v>
+        <v>130</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹939.70 Cr</t>
+          <t>₹40.48 Cr</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6-Aug 16:30</t>
+          <t>7-Aug 9:55</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Optimystix Entertainment NSE SMEU</t>
+          <t>Molbio Diagnostics IPOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹5 (2.86%) 5 ↓ / 5 ↑</t>
+          <t>₹205 (25.40%) 170 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -898,39 +898,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>175</v>
+        <v>807</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹108.50 Cr</t>
+          <t>₹939.70 Cr</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>800</v>
+        <v>18</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>6-Aug 16:28</t>
+          <t>7-Aug 10:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -942,17 +942,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Technocraft Ventures IPOU</t>
+          <t>Dhoot Transmission IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹15 (7.08%) 10 ↓ / 15 ↑</t>
+          <t>₹255 (29.28%) 146 ↓ / 259 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -961,39 +961,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>212</v>
+        <v>871</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹251.88 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>6-Aug 16:28</t>
+          <t>7-Aug 10:01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1005,12 +1005,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LEAP India IPOU</t>
+          <t>Technocraft Ventures IPOO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹11 (6.92%) 3 ↓ / 11 ↑</t>
+          <t>₹17 (8.02%) 10 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1020,23 +1020,23 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.05x</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹2480.00 Cr</t>
+          <t>₹251.88 Cr</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>7-Aug GMP: 17</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>6-Aug 16:31</t>
+          <t>7-Aug 9:53</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1068,58 +1068,58 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LAPL Automotive BSE SMEO</t>
+          <t>LEAP India IPOO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹30 (31.91%) 22 ↓ / 30 ↑</t>
+          <t>₹19 (11.95%) 3 ↓ / 19.50 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.27x</t>
+          <t>0x</t>
         </is>
       </c>
       <c r="E12" t="n">
+        <v>159</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>₹2480.00 Cr</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
         <v>94</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>₹32.40 Cr</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>1200</v>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 30</t>
+          <t>7-Aug GMP: 19</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6-Aug 16:31</t>
+          <t>7-Aug 9:58</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1131,58 +1131,58 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEO</t>
+          <t>Optimystix Entertainment NSE SMEO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹26 (20.00%) 18 ↓ / 26 ↑</t>
+          <t>₹5 (2.86%) 5 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>146.76x</t>
+          <t>0.01x</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹108.50 Cr</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 25</t>
+          <t>7-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>6-Aug 16:29</t>
+          <t>7-Aug 9:54</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1194,12 +1194,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOO</t>
+          <t>LAPL Automotive BSE SMEO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹15.5 (29.25%) 6.50 ↓ / 15.50 ↑</t>
+          <t>₹32 (34.04%) 22 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1209,43 +1209,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>14.4x</t>
+          <t>5.99x</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
+          <t>₹32.40 Cr</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>281</v>
+        <v>1200</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 15.25</t>
+          <t>6-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>6-Aug 16:33</t>
+          <t>7-Aug 9:56</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1257,58 +1257,58 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Aegeus Technologies BSE SMECT</t>
+          <t>G.V. Electricals BSE SMECT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹12 (11.43%) 12 ↓ / 12 ↑</t>
+          <t>₹26 (20.00%) 18 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>29.4x</t>
+          <t>146.76x</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹23.71 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>31-Jul GMP: 25</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 12</t>
+          <t>7-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>6-Aug 16:35</t>
+          <t>7-Aug 9:57</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1320,12 +1320,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Anawil Wire &amp; Engineering NSE SMEC</t>
+          <t>Ardee Industries IPOCT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹78 (28.89%) 60 ↓ / 90 ↑</t>
+          <t>₹13 (24.53%) 6.50 ↓ / 15.25 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1335,43 +1335,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>149.13x</t>
+          <t>17.5x</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>270</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹177.81 Cr</t>
+          <t>₹425.87 Cr</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>400</v>
+        <v>281</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 80</t>
+          <t>5-Aug GMP: 15.25</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 78</t>
+          <t>7-Aug GMP: 13</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>6-Aug 16:35</t>
+          <t>7-Aug 9:58</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1383,58 +1383,58 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Fusion Klassroom Edutech BSE SMECAllotted</t>
+          <t>Aegeus Technologies BSE SMEC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
+          <t>₹12 (11.43%) 12 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.5x</t>
+          <t>29.91x</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>159</v>
+        <v>105</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹39.04 Cr</t>
+          <t>₹23.71 Cr</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 4</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>6-Aug GMP: 12</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>6-Aug 16:35</t>
+          <t>7-Aug 9:55</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1446,58 +1446,58 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cube Highways Trust InvIT IPOCAllotted</t>
+          <t>Anawil Wire &amp; Engineering NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
+          <t>₹67 (24.81%) 60 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9.35x</t>
+          <t>149.13x</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>152</v>
+        <v>270</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>₹5000.00 Cr</t>
+          <t>₹177.81 Cr</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>95</v>
+        <v>400</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 0</t>
+          <t>3-Aug GMP: 80</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 1.75</t>
+          <t>5-Aug GMP: 78</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 1.75</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>6-Aug 5:55</t>
+          <t>7-Aug 10:02</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1509,58 +1509,58 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dhaval Packaging BSE SMEL@110.00 (13.4%)</t>
+          <t>Cube Highways Trust InvIT IPOCAllotted</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹12 (12.37%) 8 ↓ / 15 ↑</t>
+          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>49.99x</t>
+          <t>9.35x</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹36.36 Cr</t>
+          <t>₹5000.00 Cr</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1200</v>
+        <v>95</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 15</t>
+          <t>22-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 8</t>
+          <t>24-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 12</t>
+          <t>31-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>6-Aug 9:33</t>
+          <t>7-Aug 5:55</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1572,58 +1572,58 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Oneindig Technologies BSE SMEL@120.00 (25%)</t>
+          <t>Fusion Klassroom Edutech BSE SMEL@170.00 (6.92%)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹7 (7.29%) 7 ↓ / 7 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.73x</t>
+          <t>1.5x</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>96</v>
+        <v>159</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹27.65 Cr</t>
+          <t>₹39.04 Cr</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 0</t>
+          <t>31-Jul GMP: 4</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 0</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 7</t>
+          <t>7-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>6-Aug 9:28</t>
+          <t>7-Aug 9:35</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1635,43 +1635,43 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MV Electrosystems IPOL@520.00 (22.35%)</t>
+          <t>Oneindig Technologies BSE SMEL@120.00 (25%)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹109 (25.65%) 60 ↓ / 133 ↑</t>
+          <t>₹7 (7.29%) 7 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>200.66x</t>
+          <t>1.73x</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>425</v>
+        <v>96</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹290.00 Cr</t>
+          <t>₹27.65 Cr</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>34</v>
+        <v>1200</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 125</t>
+          <t>30-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 100</t>
+          <t>3-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 109</t>
+          <t>6-Aug GMP: 7</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>6-Aug 9:35</t>
+          <t>6-Aug 9:28</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1698,43 +1698,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Juniper Green Energy IPOL@245.00 (8.89%)</t>
+          <t>MV Electrosystems IPOL@520.00 (22.35%)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹23 (10.22%) 1.50 ↓ / 23 ↑</t>
+          <t>₹109 (25.65%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.38x</t>
+          <t>200.66x</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>225</v>
+        <v>425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹1800.00 Cr</t>
+          <t>₹290.00 Cr</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 8</t>
+          <t>30-Jul GMP: 125</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 9.5</t>
+          <t>3-Aug GMP: 100</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 23</t>
+          <t>6-Aug GMP: 109</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>6-Aug 9:37</t>
+          <t>6-Aug 9:35</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1761,58 +1761,58 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Manipal Health Enterprises IPOL@652.00 (10.51%)</t>
+          <t>Juniper Green Energy IPOL@245.00 (8.89%)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹7 (1.19%) -15 ↓ / 35 ↑</t>
+          <t>₹23 (10.22%) 1.50 ↓ / 23 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5.12x</t>
+          <t>8.38x</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>590</v>
+        <v>225</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹9275.22 Cr</t>
+          <t>₹1800.00 Cr</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 9</t>
+          <t>30-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>31-Jul GMP: -15</t>
+          <t>3-Aug GMP: 9.5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 7</t>
+          <t>6-Aug GMP: 23</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>5-Aug 9:30</t>
+          <t>6-Aug 9:37</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1824,58 +1824,58 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>H.R. Hygiene Products BSE SMEL@90.00 (2.27%)</t>
+          <t>Dhaval Packaging BSE SMEL@110.00 (13.4%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹1 (1.14%) 1 ↓ / 2 ↑</t>
+          <t>₹12 (12.37%) 8 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6.65x</t>
+          <t>49.99x</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹53.95 Cr</t>
+          <t>₹36.36 Cr</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 2</t>
+          <t>30-Jul GMP: 15</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 2</t>
+          <t>3-Aug GMP: 8</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 1</t>
+          <t>6-Aug GMP: 12</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>5-Aug 9:37</t>
+          <t>6-Aug 9:33</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1887,58 +1887,58 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Poojaa Precision Engg. BSE SMEL@470.00 (56.15%)</t>
+          <t>H.R. Hygiene Products BSE SMEL@90.00 (2.27%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹200 (66.45%) 195 ↓ / 300 ↑</t>
+          <t>₹1 (1.14%) 1 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>278.83x</t>
+          <t>6.65x</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>301</v>
+        <v>88</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹159.83 Cr</t>
+          <t>₹53.95 Cr</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>400</v>
+        <v>1600</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 300</t>
+          <t>29-Jul GMP: 2</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 225</t>
+          <t>31-Jul GMP: 2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 200</t>
+          <t>5-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>4-Aug 9:33</t>
+          <t>5-Aug 9:37</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1950,12 +1950,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Propshop Events &amp; Exhibitions NSE SMEL@55.20 (-20%)</t>
+          <t>Manipal Health Enterprises IPOL@652.00 (10.51%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹7 (1.19%) -15 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1965,123 +1965,123 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.53x</t>
+          <t>5.12x</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>69</v>
+        <v>590</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹28.57 Cr</t>
+          <t>₹9275.22 Cr</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2000</v>
+        <v>25</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 0</t>
+          <t>29-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 0</t>
+          <t>31-Jul GMP: -15</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 0</t>
+          <t>5-Aug GMP: 7</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>3-Aug 9:35</t>
+          <t>5-Aug 9:30</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Advance Technoforge BSE SMEL@94.00 (-1.05%)</t>
+          <t>Poojaa Precision Engg. BSE SMEL@470.00 (56.15%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹4 (4.21%) 3 ↓ / 9 ↑</t>
+          <t>₹200 (66.45%) 195 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.55x</t>
+          <t>278.83x</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>95</v>
+        <v>301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹24.04 Cr</t>
+          <t>₹159.83 Cr</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 9</t>
+          <t>28-Jul GMP: 300</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 8</t>
+          <t>30-Jul GMP: 225</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>31-Jul</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 4</t>
+          <t>4-Aug GMP: 200</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>3-Aug 9:30</t>
+          <t>4-Aug 9:33</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Silverstorm Parks &amp; Resorts BSE SMEL@132.90 (-0.08%)</t>
+          <t>Propshop Events &amp; Exhibitions NSE SMEL@55.20 (-20%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹5 (3.76%) 5 ↓ / 5 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2091,123 +2091,123 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.91x</t>
+          <t>1.53x</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹82.43 Cr</t>
+          <t>₹28.57 Cr</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 0</t>
+          <t>27-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 0</t>
+          <t>29-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 5</t>
+          <t>3-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>31-Jul 9:34</t>
+          <t>3-Aug 9:35</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Xtranet Technologies IPOL@136.00 (7.09%)</t>
+          <t>Advance Technoforge BSE SMEL@94.00 (-1.05%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹14.5 (11.42%) 7.50 ↓ / 26 ↑</t>
+          <t>₹4 (4.21%) 3 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>12.24x</t>
+          <t>1.55x</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹166.80 Cr</t>
+          <t>₹24.04 Cr</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>110</v>
+        <v>1200</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 8</t>
+          <t>27-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 7.7</t>
+          <t>29-Jul GMP: 8</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>28-Jul</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 14.5</t>
+          <t>3-Aug GMP: 4</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>30-Jul 9:31</t>
+          <t>3-Aug 9:30</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lohia Corp IPOL@461.00 (8.47%)</t>
+          <t>Silverstorm Parks &amp; Resorts BSE SMEL@132.90 (-0.08%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹17 (4.00%) 7 ↓ / 56 ↑</t>
+          <t>₹5 (3.76%) 5 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,43 +2217,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7.26x</t>
+          <t>1.91x</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>425</v>
+        <v>133</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹1101.28 Cr</t>
+          <t>₹82.43 Cr</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>35</v>
+        <v>1000</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 12</t>
+          <t>24-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 11.5</t>
+          <t>28-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>28-Jul</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 17</t>
+          <t>31-Jul GMP: 5</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>30-Jul 9:30</t>
+          <t>31-Jul 9:34</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2265,43 +2265,43 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Indo-MIM IPOL@700.00 (44.33%)</t>
+          <t>Xtranet Technologies IPOL@136.00 (7.09%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹184 (37.94%) 168 ↓ / 213 ↑</t>
+          <t>₹14.5 (11.42%) 7.50 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>72.37x</t>
+          <t>12.24x</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>485</v>
+        <v>127</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹3811.21 Cr</t>
+          <t>₹166.80 Cr</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 170</t>
+          <t>23-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 190</t>
+          <t>27-Jul GMP: 7.7</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 184</t>
+          <t>30-Jul GMP: 14.5</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>30-Jul 9:36</t>
+          <t>30-Jul 9:31</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2328,58 +2328,58 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Shree Balaji Mala BSE SMEL@133.00 (90%)</t>
+          <t>Lohia Corp IPOL@461.00 (8.47%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹56 (80.00%) 11 ↓ / 56 ↑</t>
+          <t>₹17 (4.00%) 7 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>200.34x</t>
+          <t>7.26x</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>70</v>
+        <v>425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹18.90 Cr</t>
+          <t>₹1101.28 Cr</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2000</v>
+        <v>35</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 16</t>
+          <t>23-Jul GMP: 12</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 13</t>
+          <t>27-Jul GMP: 11.5</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>27-Jul</t>
+          <t>28-Jul</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 56</t>
+          <t>30-Jul GMP: 17</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>29-Jul 9:29</t>
+          <t>30-Jul 9:30</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>7-Aug 10:00</t>
+          <t>7-Aug 15:31</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹16 (16.49%) 14 ↓ / 16 ↑</t>
+          <t>₹15 (15.46%) 14 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>7-Aug 9:54</t>
+          <t>7-Aug 15:30</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -632,12 +632,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹30 (10.53%) 30 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>7-Aug 9:53</t>
+          <t>7-Aug 15:30</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹25 (17.86%) 25 ↓ / 26 ↑</t>
+          <t>₹24 (17.14%) 24 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>7-Aug 9:57</t>
+          <t>7-Aug 15:33</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>7-Aug 9:57</t>
+          <t>7-Aug 15:33</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>7-Aug 9:55</t>
+          <t>7-Aug 15:30</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹205 (25.40%) 170 ↓ / 220 ↑</t>
+          <t>₹125 (15.49%) 125 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>7-Aug 10:02</t>
+          <t>7-Aug 15:36</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹255 (29.28%) 146 ↓ / 259 ↑</t>
+          <t>₹250 (28.70%) 146 ↓ / 259 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>7-Aug 10:01</t>
+          <t>7-Aug 15:36</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹17 (8.02%) 10 ↓ / 17 ↑</t>
+          <t>₹18 (8.49%) 10 ↓ / 18 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.05x</t>
+          <t>2.07x</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 17</t>
+          <t>7-Aug GMP: 18</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>7-Aug 9:53</t>
+          <t>7-Aug 15:37</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1073,17 +1073,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹19 (11.95%) 3 ↓ / 19.50 ↑</t>
+          <t>₹14.5 (9.12%) 3 ↓ / 19.50 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0x</t>
+          <t>0.26x</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 19</t>
+          <t>7-Aug GMP: 14.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>7-Aug 9:58</t>
+          <t>7-Aug 15:33</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.01x</t>
+          <t>0.46x</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7-Aug 9:54</t>
+          <t>7-Aug 15:37</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5.99x</t>
+          <t>25.88x</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>7-Aug 9:56</t>
+          <t>7-Aug 15:34</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>146.76x</t>
+          <t>165.62x</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>7-Aug 9:57</t>
+          <t>7-Aug 15:32</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>17.5x</t>
+          <t>134.55x</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>7-Aug 9:58</t>
+          <t>7-Aug 15:37</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7-Aug 9:55</t>
+          <t>7-Aug 15:29</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹67 (24.81%) 60 ↓ / 90 ↑</t>
+          <t>₹64 (23.70%) 60 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>7-Aug 10:02</t>
+          <t>7-Aug 15:29</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,17 +501,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMEU</t>
+          <t>Q&amp;T Foods BSE SMEU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6 (5.22%) 6 ↓ / 6 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -520,11 +520,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
+          <t>₹26.25 Cr</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -552,29 +552,29 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>7-Aug 15:31</t>
+          <t>8-Aug 9:34</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shiprocket IPOU</t>
+          <t>Pramodini Medicare NSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹15 (15.46%) 14 ↓ / 15 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -583,15 +583,15 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹69.04 Cr</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>154</v>
+        <v>1200</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>7-Aug 15:30</t>
+          <t>8-Aug 9:28</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -627,12 +627,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOU</t>
+          <t>Shiprocket IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹30 (10.53%) 30 ↓ / 30 ↑</t>
+          <t>₹14 (14.43%) 14 ↓ / 14 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -646,15 +646,15 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>285</v>
+        <v>97</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹1617.48 Cr</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>52</v>
+        <v>154</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>7-Aug 15:30</t>
+          <t>8-Aug 9:33</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -690,12 +690,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food IPOU</t>
+          <t>Behari Lal Engineering IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹24 (17.14%) 24 ↓ / 26 ↑</t>
+          <t>₹30 (10.53%) 30 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -709,39 +709,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>140</v>
+        <v>285</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹1553.00 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>7-Aug 15:33</t>
+          <t>8-Aug 9:37</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -753,17 +753,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMEU</t>
+          <t>Milky Mist Dairy Food IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹24 (17.14%) 24 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -772,15 +772,15 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹66.98 Cr</t>
+          <t>₹1553.00 Cr</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>800</v>
+        <v>107</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>7-Aug 15:33</t>
+          <t>8-Aug 9:30</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sham Foam BSE SMEU</t>
+          <t>Fascinate Textiles NSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -835,15 +835,15 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹40.48 Cr</t>
+          <t>₹66.98 Cr</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -867,29 +867,29 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>7-Aug 15:30</t>
+          <t>8-Aug 9:31</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOU</t>
+          <t>Sham Foam BSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹125 (15.49%) 125 ↓ / 220 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -898,61 +898,61 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>807</v>
+        <v>130</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹939.70 Cr</t>
+          <t>₹40.48 Cr</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>7-Aug 15:36</t>
+          <t>8-Aug 9:31</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOU</t>
+          <t>Molbio Diagnostics IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹250 (28.70%) 146 ↓ / 259 ↑</t>
+          <t>₹130 (16.11%) 130 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>871</v>
+        <v>807</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
+          <t>₹939.70 Cr</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>7-Aug 15:36</t>
+          <t>8-Aug 9:30</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1005,58 +1005,58 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Technocraft Ventures IPOO</t>
+          <t>Dhoot Transmission IPOU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹18 (8.49%) 10 ↓ / 18 ↑</t>
+          <t>₹247 (28.36%) 146 ↓ / 259 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.07x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>212</v>
+        <v>871</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹251.88 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 18</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>7-Aug 15:37</t>
+          <t>8-Aug 9:29</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1068,12 +1068,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LEAP India IPOO</t>
+          <t>Technocraft Ventures IPOO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹14.5 (9.12%) 3 ↓ / 19.50 ↑</t>
+          <t>₹15 (7.08%) 10 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1083,23 +1083,23 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.26x</t>
+          <t>2.59x</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹2480.00 Cr</t>
+          <t>₹251.88 Cr</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 14.5</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>7-Aug 15:33</t>
+          <t>8-Aug 9:33</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1131,38 +1131,38 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Optimystix Entertainment NSE SMEO</t>
+          <t>LEAP India IPOO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹5 (2.86%) 5 ↓ / 5 ↑</t>
+          <t>₹15 (9.43%) 3 ↓ / 19.50 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.46x</t>
+          <t>0.28x</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹108.50 Cr</t>
+          <t>₹2480.00 Cr</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>800</v>
+        <v>94</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 5</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7-Aug 15:37</t>
+          <t>8-Aug 9:30</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1194,58 +1194,58 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LAPL Automotive BSE SMEO</t>
+          <t>Optimystix Entertainment NSE SMEO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹32 (34.04%) 22 ↓ / 32 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>25.88x</t>
+          <t>0.73x</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>94</v>
+        <v>175</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹32.40 Cr</t>
+          <t>₹108.50 Cr</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 32</t>
+          <t>7-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>7-Aug 15:34</t>
+          <t>8-Aug 9:28</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1257,12 +1257,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMECT</t>
+          <t>LAPL Automotive BSE SMEO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹26 (20.00%) 18 ↓ / 26 ↑</t>
+          <t>₹32 (34.04%) 22 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1272,43 +1272,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>165.62x</t>
+          <t>31.41x</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹32.40 Cr</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 25</t>
+          <t>6-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 26</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>7-Aug 15:32</t>
+          <t>8-Aug 9:29</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1320,12 +1320,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOCT</t>
+          <t>G.V. Electricals BSE SMEC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹13 (24.53%) 6.50 ↓ / 15.25 ↑</t>
+          <t>₹26 (20.00%) 18 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1335,28 +1335,28 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>134.55x</t>
+          <t>169.26x</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>281</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 15.25</t>
+          <t>31-Jul GMP: 25</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 13</t>
+          <t>7-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>7-Aug 15:37</t>
+          <t>8-Aug 9:36</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1383,58 +1383,58 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Aegeus Technologies BSE SMEC</t>
+          <t>Ardee Industries IPOC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹12 (11.43%) 12 ↓ / 12 ↑</t>
+          <t>₹15 (28.30%) 6.50 ↓ / 15.25 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>29.91x</t>
+          <t>138.83x</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹23.71 Cr</t>
+          <t>₹425.87 Cr</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1200</v>
+        <v>281</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>5-Aug GMP: 15.25</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 12</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7-Aug 15:29</t>
+          <t>8-Aug 9:37</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1446,58 +1446,58 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Anawil Wire &amp; Engineering NSE SMECAllotted</t>
+          <t>Aegeus Technologies BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹64 (23.70%) 60 ↓ / 90 ↑</t>
+          <t>₹12 (11.43%) 12 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>149.13x</t>
+          <t>29.91x</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>270</v>
+        <v>105</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>₹177.81 Cr</t>
+          <t>₹23.71 Cr</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 80</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 78</t>
+          <t>6-Aug GMP: 12</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>7-Aug 15:29</t>
+          <t>8-Aug 9:30</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1509,58 +1509,58 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cube Highways Trust InvIT IPOCAllotted</t>
+          <t>Anawil Wire &amp; Engineering NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
+          <t>₹64 (23.70%) 60 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9.35x</t>
+          <t>149.13x</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>152</v>
+        <v>270</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹5000.00 Cr</t>
+          <t>₹177.81 Cr</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>95</v>
+        <v>400</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 0</t>
+          <t>3-Aug GMP: 80</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 1.75</t>
+          <t>5-Aug GMP: 78</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 1.75</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>7-Aug 5:55</t>
+          <t>8-Aug 9:35</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1572,12 +1572,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Fusion Klassroom Edutech BSE SMEL@170.00 (6.92%)</t>
+          <t>Cube Highways Trust InvIT IPOCAllotted</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
+          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1587,43 +1587,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.5x</t>
+          <t>9.35x</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹39.04 Cr</t>
+          <t>₹5000.00 Cr</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>800</v>
+        <v>95</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 4</t>
+          <t>22-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>24-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 0</t>
+          <t>31-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>7-Aug 9:35</t>
+          <t>8-Aug 5:55</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1635,58 +1635,58 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Oneindig Technologies BSE SMEL@120.00 (25%)</t>
+          <t>Fusion Klassroom Edutech BSE SMEL@170.00 (6.92%)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹7 (7.29%) 7 ↓ / 7 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.73x</t>
+          <t>1.5x</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>96</v>
+        <v>159</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹27.65 Cr</t>
+          <t>₹39.04 Cr</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 0</t>
+          <t>31-Jul GMP: 4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 0</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 7</t>
+          <t>7-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>6-Aug 9:28</t>
+          <t>7-Aug 9:35</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1698,43 +1698,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MV Electrosystems IPOL@520.00 (22.35%)</t>
+          <t>Oneindig Technologies BSE SMEL@120.00 (25%)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹109 (25.65%) 60 ↓ / 133 ↑</t>
+          <t>₹7 (7.29%) 7 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>200.66x</t>
+          <t>1.73x</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>425</v>
+        <v>96</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹290.00 Cr</t>
+          <t>₹27.65 Cr</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>34</v>
+        <v>1200</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 125</t>
+          <t>30-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 100</t>
+          <t>3-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 109</t>
+          <t>6-Aug GMP: 7</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>6-Aug 9:35</t>
+          <t>6-Aug 9:28</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1761,43 +1761,43 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Juniper Green Energy IPOL@245.00 (8.89%)</t>
+          <t>MV Electrosystems IPOL@520.00 (22.35%)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹23 (10.22%) 1.50 ↓ / 23 ↑</t>
+          <t>₹109 (25.65%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.38x</t>
+          <t>200.66x</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>225</v>
+        <v>425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹1800.00 Cr</t>
+          <t>₹290.00 Cr</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 8</t>
+          <t>30-Jul GMP: 125</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 9.5</t>
+          <t>3-Aug GMP: 100</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 23</t>
+          <t>6-Aug GMP: 109</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>6-Aug 9:37</t>
+          <t>6-Aug 9:35</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1824,12 +1824,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dhaval Packaging BSE SMEL@110.00 (13.4%)</t>
+          <t>Juniper Green Energy IPOL@245.00 (8.89%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹12 (12.37%) 8 ↓ / 15 ↑</t>
+          <t>₹23 (10.22%) 1.50 ↓ / 23 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1839,28 +1839,28 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>49.99x</t>
+          <t>8.38x</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹36.36 Cr</t>
+          <t>₹1800.00 Cr</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1200</v>
+        <v>66</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 15</t>
+          <t>30-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 8</t>
+          <t>3-Aug GMP: 9.5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 12</t>
+          <t>6-Aug GMP: 23</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>6-Aug 9:33</t>
+          <t>6-Aug 9:37</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1887,58 +1887,58 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>H.R. Hygiene Products BSE SMEL@90.00 (2.27%)</t>
+          <t>Dhaval Packaging BSE SMEL@110.00 (13.4%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹1 (1.14%) 1 ↓ / 2 ↑</t>
+          <t>₹12 (12.37%) 8 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6.65x</t>
+          <t>49.99x</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹53.95 Cr</t>
+          <t>₹36.36 Cr</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 2</t>
+          <t>30-Jul GMP: 15</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 2</t>
+          <t>3-Aug GMP: 8</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 1</t>
+          <t>6-Aug GMP: 12</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>5-Aug 9:37</t>
+          <t>6-Aug 9:33</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1950,12 +1950,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Manipal Health Enterprises IPOL@652.00 (10.51%)</t>
+          <t>H.R. Hygiene Products BSE SMEL@90.00 (2.27%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹7 (1.19%) -15 ↓ / 35 ↑</t>
+          <t>₹1 (1.14%) 1 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1965,28 +1965,28 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5.12x</t>
+          <t>6.65x</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>590</v>
+        <v>88</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹9275.22 Cr</t>
+          <t>₹53.95 Cr</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>25</v>
+        <v>1600</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 9</t>
+          <t>29-Jul GMP: 2</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>31-Jul GMP: -15</t>
+          <t>31-Jul GMP: 2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 7</t>
+          <t>5-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>5-Aug 9:30</t>
+          <t>5-Aug 9:37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2013,58 +2013,58 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Poojaa Precision Engg. BSE SMEL@470.00 (56.15%)</t>
+          <t>Manipal Health Enterprises IPOL@652.00 (10.51%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹200 (66.45%) 195 ↓ / 300 ↑</t>
+          <t>₹7 (1.19%) -15 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>278.83x</t>
+          <t>5.12x</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>301</v>
+        <v>590</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹159.83 Cr</t>
+          <t>₹9275.22 Cr</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>400</v>
+        <v>25</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 300</t>
+          <t>29-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 225</t>
+          <t>31-Jul GMP: -15</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 200</t>
+          <t>5-Aug GMP: 7</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>4-Aug 9:33</t>
+          <t>5-Aug 9:30</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2076,75 +2076,75 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Propshop Events &amp; Exhibitions NSE SMEL@55.20 (-20%)</t>
+          <t>Poojaa Precision Engg. BSE SMEL@470.00 (56.15%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹200 (66.45%) 195 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.53x</t>
+          <t>278.83x</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>69</v>
+        <v>301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹28.57 Cr</t>
+          <t>₹159.83 Cr</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 0</t>
+          <t>28-Jul GMP: 300</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 0</t>
+          <t>30-Jul GMP: 225</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>31-Jul</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 0</t>
+          <t>4-Aug GMP: 200</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>3-Aug 9:35</t>
+          <t>4-Aug 9:33</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Advance Technoforge BSE SMEL@94.00 (-1.05%)</t>
+          <t>Propshop Events &amp; Exhibitions NSE SMEL@55.20 (-20%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹4 (4.21%) 3 ↓ / 9 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2154,28 +2154,28 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.55x</t>
+          <t>1.53x</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹24.04 Cr</t>
+          <t>₹28.57 Cr</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 9</t>
+          <t>27-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 8</t>
+          <t>29-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 4</t>
+          <t>3-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3-Aug 9:30</t>
+          <t>3-Aug 9:35</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2202,12 +2202,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Silverstorm Parks &amp; Resorts BSE SMEL@132.90 (-0.08%)</t>
+          <t>Advance Technoforge BSE SMEL@94.00 (-1.05%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹5 (3.76%) 5 ↓ / 5 ↑</t>
+          <t>₹4 (4.21%) 3 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,106 +2217,106 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.91x</t>
+          <t>1.55x</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹82.43 Cr</t>
+          <t>₹24.04 Cr</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 0</t>
+          <t>27-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 0</t>
+          <t>29-Jul GMP: 8</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 5</t>
+          <t>3-Aug GMP: 4</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>31-Jul 9:34</t>
+          <t>3-Aug 9:30</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Xtranet Technologies IPOL@136.00 (7.09%)</t>
+          <t>Silverstorm Parks &amp; Resorts BSE SMEL@132.90 (-0.08%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹14.5 (11.42%) 7.50 ↓ / 26 ↑</t>
+          <t>₹5 (3.76%) 5 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>12.24x</t>
+          <t>1.91x</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹166.80 Cr</t>
+          <t>₹82.43 Cr</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 8</t>
+          <t>24-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 7.7</t>
+          <t>28-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>28-Jul</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 14.5</t>
+          <t>31-Jul GMP: 5</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>30-Jul 9:31</t>
+          <t>31-Jul 9:34</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2328,43 +2328,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Lohia Corp IPOL@461.00 (8.47%)</t>
+          <t>Xtranet Technologies IPOL@136.00 (7.09%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹17 (4.00%) 7 ↓ / 56 ↑</t>
+          <t>₹14.5 (11.42%) 7.50 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7.26x</t>
+          <t>12.24x</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>425</v>
+        <v>127</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹1101.28 Cr</t>
+          <t>₹166.80 Cr</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 12</t>
+          <t>23-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 11.5</t>
+          <t>27-Jul GMP: 7.7</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 17</t>
+          <t>30-Jul GMP: 14.5</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>30-Jul 9:30</t>
+          <t>30-Jul 9:31</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8-Aug 9:34</t>
+          <t>8-Aug 14:58</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>8-Aug 9:28</t>
+          <t>8-Aug 14:58</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>8-Aug 9:33</t>
+          <t>8-Aug 14:55</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8-Aug 9:37</t>
+          <t>8-Aug 14:59</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹24 (17.14%) 24 ↓ / 26 ↑</t>
+          <t>₹23 (16.43%) 23 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8-Aug 9:30</t>
+          <t>8-Aug 15:00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMEU</t>
+          <t>Sham Foam BSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -835,15 +835,15 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹66.98 Cr</t>
+          <t>₹40.48 Cr</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -867,19 +867,19 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8-Aug 9:31</t>
+          <t>8-Aug 14:54</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sham Foam BSE SMEU</t>
+          <t>Fascinate Textiles NSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -898,15 +898,15 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹40.48 Cr</t>
+          <t>₹66.98 Cr</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -930,12 +930,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>8-Aug 9:31</t>
+          <t>8-Aug 14:56</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>8-Aug 9:30</t>
+          <t>8-Aug 14:53</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹247 (28.36%) 146 ↓ / 259 ↑</t>
+          <t>₹250 (28.70%) 146 ↓ / 259 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>8-Aug 9:29</t>
+          <t>8-Aug 14:54</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹15 (7.08%) 10 ↓ / 16 ↑</t>
+          <t>₹19 (8.96%) 10 ↓ / 19 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>8-Aug 9:33</t>
+          <t>8-Aug 15:01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>8-Aug 9:30</t>
+          <t>8-Aug 14:58</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 5 ↑</t>
+          <t>₹5 (2.86%) 5 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>8-Aug 9:28</t>
+          <t>8-Aug 14:54</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹32 (34.04%) 22 ↓ / 32 ↑</t>
+          <t>₹35 (37.23%) 22 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>8-Aug 9:29</t>
+          <t>8-Aug 14:58</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>8-Aug 9:36</t>
+          <t>8-Aug 14:56</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>8-Aug 9:37</t>
+          <t>8-Aug 14:54</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>8-Aug 9:30</t>
+          <t>8-Aug 14:58</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>8-Aug 9:35</t>
+          <t>8-Aug 15:01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8-Aug 14:58</t>
+          <t>9-Aug 9:36</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>8-Aug 14:58</t>
+          <t>9-Aug 9:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹14 (14.43%) 14 ↓ / 14 ↑</t>
+          <t>₹16 (16.49%) 14 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>8-Aug 14:55</t>
+          <t>9-Aug 9:31</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -695,12 +695,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹30 (10.53%) 30 ↓ / 30 ↑</t>
+          <t>₹25 (8.77%) 25 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8-Aug 14:59</t>
+          <t>9-Aug 9:29</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹23 (16.43%) 23 ↓ / 26 ↑</t>
+          <t>₹27 (19.29%) 24 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8-Aug 15:00</t>
+          <t>9-Aug 9:34</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8-Aug 14:54</t>
+          <t>9-Aug 9:32</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>8-Aug 14:56</t>
+          <t>9-Aug 9:34</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>8-Aug 14:53</t>
+          <t>9-Aug 9:35</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹250 (28.70%) 146 ↓ / 259 ↑</t>
+          <t>₹259 (29.74%) 146 ↓ / 259 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>8-Aug 14:54</t>
+          <t>9-Aug 9:28</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹19 (8.96%) 10 ↓ / 19 ↑</t>
+          <t>₹21.5 (10.14%) 10 ↓ / 21.50 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>8-Aug 15:01</t>
+          <t>9-Aug 9:31</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹15 (9.43%) 3 ↓ / 19.50 ↑</t>
+          <t>₹16 (10.06%) 3 ↓ / 19.50 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>8-Aug 14:58</t>
+          <t>9-Aug 9:34</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>8-Aug 14:54</t>
+          <t>9-Aug 9:28</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>8-Aug 14:58</t>
+          <t>9-Aug 9:28</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>8-Aug 14:56</t>
+          <t>9-Aug 9:28</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹15 (28.30%) 6.50 ↓ / 15.25 ↑</t>
+          <t>₹16 (30.19%) 6.50 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>8-Aug 14:54</t>
+          <t>9-Aug 9:31</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>8-Aug 14:58</t>
+          <t>9-Aug 9:28</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹64 (23.70%) 60 ↓ / 90 ↑</t>
+          <t>₹62 (22.96%) 60 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>8-Aug 15:01</t>
+          <t>9-Aug 9:28</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>8-Aug 5:55</t>
+          <t>9-Aug 5:55</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>9-Aug 9:36</t>
+          <t>9-Aug 14:58</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>9-Aug 9:37</t>
+          <t>9-Aug 14:58</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -632,12 +632,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹16 (16.49%) 14 ↓ / 16 ↑</t>
+          <t>₹21 (21.65%) 14 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>9-Aug 9:31</t>
+          <t>9-Aug 14:58</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>9-Aug 9:29</t>
+          <t>9-Aug 14:55</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>9-Aug 9:34</t>
+          <t>9-Aug 14:56</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>9-Aug 9:32</t>
+          <t>9-Aug 14:55</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>9-Aug 9:34</t>
+          <t>9-Aug 15:01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>9-Aug 9:35</t>
+          <t>9-Aug 14:53</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>9-Aug 9:28</t>
+          <t>9-Aug 15:02</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹21.5 (10.14%) 10 ↓ / 21.50 ↑</t>
+          <t>₹22 (10.38%) 10 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>9-Aug 9:31</t>
+          <t>9-Aug 15:02</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>9-Aug 9:34</t>
+          <t>9-Aug 14:54</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>9-Aug 9:28</t>
+          <t>9-Aug 14:55</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>9-Aug 9:28</t>
+          <t>9-Aug 14:53</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>9-Aug 9:28</t>
+          <t>9-Aug 14:53</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>9-Aug 9:31</t>
+          <t>9-Aug 14:56</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>9-Aug 9:28</t>
+          <t>9-Aug 15:00</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>9-Aug 9:28</t>
+          <t>9-Aug 14:58</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,17 +501,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods BSE SMEU</t>
+          <t>Credent Connect NSE SMEU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹6 (5.22%) 6 ↓ / 6 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -520,61 +520,61 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹26.25 Cr</t>
+          <t>₹93.90 Cr</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>9-Aug 14:58</t>
+          <t>10-Aug 10:00</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMEU</t>
+          <t>Q&amp;T Foods BSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6 (5.22%) 6 ↓ / 6 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -583,11 +583,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
+          <t>₹26.25 Cr</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -615,29 +615,29 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>9-Aug 14:58</t>
+          <t>10-Aug 10:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shiprocket IPOU</t>
+          <t>Pramodini Medicare NSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹21 (21.65%) 14 ↓ / 21 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -646,15 +646,15 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹69.04 Cr</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>154</v>
+        <v>1200</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>9-Aug 14:58</t>
+          <t>10-Aug 9:55</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>9-Aug 14:55</t>
+          <t>10-Aug 9:54</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -753,17 +753,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food IPOU</t>
+          <t>Shiprocket IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹27 (19.29%) 24 ↓ / 27 ↑</t>
+          <t>₹22 (22.68%) 14 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -772,39 +772,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹1553.00 Cr</t>
+          <t>₹1617.48 Cr</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>9-Aug 14:56</t>
+          <t>10-Aug 9:53</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>9-Aug 14:55</t>
+          <t>10-Aug 9:55</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>9-Aug 15:01</t>
+          <t>10-Aug 9:53</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -942,12 +942,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOU</t>
+          <t>Milky Mist Dairy Food IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹130 (16.11%) 130 ↓ / 220 ↑</t>
+          <t>₹26 (18.57%) 24 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -961,39 +961,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>807</v>
+        <v>140</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹939.70 Cr</t>
+          <t>₹1553.00 Cr</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>9-Aug 14:53</t>
+          <t>10-Aug 9:59</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1005,38 +1005,38 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOU</t>
+          <t>Molbio Diagnostics IPOO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹259 (29.74%) 146 ↓ / 259 ↑</t>
+          <t>₹132 (16.36%) 130 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.03x</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>871</v>
+        <v>807</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
+          <t>₹939.70 Cr</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>10-Aug GMP: 132</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>9-Aug 15:02</t>
+          <t>10-Aug 9:56</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1068,58 +1068,58 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Technocraft Ventures IPOO</t>
+          <t>Dhoot Transmission IPOO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹22 (10.38%) 10 ↓ / 22 ↑</t>
+          <t>₹259 (29.74%) 146 ↓ / 259 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.59x</t>
+          <t>0.03x</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>212</v>
+        <v>871</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹251.88 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>10-Aug GMP: 259</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>9-Aug 15:02</t>
+          <t>10-Aug 9:58</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1131,12 +1131,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LEAP India IPOO</t>
+          <t>Technocraft Ventures IPOO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹16 (10.06%) 3 ↓ / 19.50 ↑</t>
+          <t>₹23 (10.85%) 10 ↓ / 23 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1146,19 +1146,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.28x</t>
+          <t>2.85x</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹2480.00 Cr</t>
+          <t>₹251.88 Cr</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>9-Aug 14:54</t>
+          <t>10-Aug 10:01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>9-Aug 14:55</t>
+          <t>10-Aug 10:00</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1257,58 +1257,58 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LAPL Automotive BSE SMEO</t>
+          <t>LEAP India IPOO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹35 (37.23%) 22 ↓ / 35 ↑</t>
+          <t>₹16 (10.06%) 3 ↓ / 19.50 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>31.41x</t>
+          <t>0.31x</t>
         </is>
       </c>
       <c r="E15" t="n">
+        <v>159</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>₹2480.00 Cr</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
         <v>94</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>₹32.40 Cr</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>1200</v>
-      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 32</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>9-Aug 14:53</t>
+          <t>10-Aug 9:55</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1320,12 +1320,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEC</t>
+          <t>LAPL Automotive BSE SMECT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹26 (20.00%) 18 ↓ / 26 ↑</t>
+          <t>₹37 (39.36%) 22 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1335,43 +1335,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>169.26x</t>
+          <t>42.89x</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹32.40 Cr</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 25</t>
+          <t>6-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 26</t>
+          <t>10-Aug GMP: 37</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>9-Aug 14:53</t>
+          <t>10-Aug 9:55</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1383,12 +1383,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOC</t>
+          <t>G.V. Electricals BSE SMEC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹16 (30.19%) 6.50 ↓ / 16 ↑</t>
+          <t>₹26 (20.00%) 18 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1398,28 +1398,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>138.83x</t>
+          <t>169.26x</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>281</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 15.25</t>
+          <t>31-Jul GMP: 25</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>7-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>9-Aug 14:56</t>
+          <t>10-Aug 9:58</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1446,58 +1446,58 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aegeus Technologies BSE SMECAllotted</t>
+          <t>Ardee Industries IPOC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹12 (11.43%) 12 ↓ / 12 ↑</t>
+          <t>₹16 (30.19%) 6.50 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>29.91x</t>
+          <t>138.83x</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>₹23.71 Cr</t>
+          <t>₹425.87 Cr</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1200</v>
+        <v>281</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>5-Aug GMP: 15.25</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 12</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>9-Aug 15:00</t>
+          <t>10-Aug 9:59</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1509,58 +1509,58 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Anawil Wire &amp; Engineering NSE SMECAllotted</t>
+          <t>Aegeus Technologies BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹62 (22.96%) 60 ↓ / 90 ↑</t>
+          <t>₹12 (11.43%) 12 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>149.13x</t>
+          <t>29.91x</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>270</v>
+        <v>105</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹177.81 Cr</t>
+          <t>₹23.71 Cr</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 80</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 78</t>
+          <t>6-Aug GMP: 12</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>9-Aug 14:58</t>
+          <t>10-Aug 10:00</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>9-Aug 5:55</t>
+          <t>10-Aug 5:55</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1635,58 +1635,58 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Fusion Klassroom Edutech BSE SMEL@170.00 (6.92%)</t>
+          <t>Anawil Wire &amp; Engineering NSE SMEL@329.65 (22.09%)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
+          <t>₹58 (21.48%) 58 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.5x</t>
+          <t>149.13x</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>159</v>
+        <v>270</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹39.04 Cr</t>
+          <t>₹177.81 Cr</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 4</t>
+          <t>3-Aug GMP: 80</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>5-Aug GMP: 78</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 0</t>
+          <t>10-Aug GMP: 58</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>7-Aug 9:35</t>
+          <t>10-Aug 9:32</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1698,58 +1698,58 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Oneindig Technologies BSE SMEL@120.00 (25%)</t>
+          <t>Fusion Klassroom Edutech BSE SMEL@170.00 (6.92%)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹7 (7.29%) 7 ↓ / 7 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.73x</t>
+          <t>1.5x</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>96</v>
+        <v>159</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹27.65 Cr</t>
+          <t>₹39.04 Cr</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 0</t>
+          <t>31-Jul GMP: 4</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 0</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 7</t>
+          <t>7-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>6-Aug 9:28</t>
+          <t>7-Aug 9:35</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1761,43 +1761,43 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MV Electrosystems IPOL@520.00 (22.35%)</t>
+          <t>Oneindig Technologies BSE SMEL@120.00 (25%)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹109 (25.65%) 60 ↓ / 133 ↑</t>
+          <t>₹7 (7.29%) 7 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>200.66x</t>
+          <t>1.73x</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>425</v>
+        <v>96</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹290.00 Cr</t>
+          <t>₹27.65 Cr</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>34</v>
+        <v>1200</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 125</t>
+          <t>30-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 100</t>
+          <t>3-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 109</t>
+          <t>6-Aug GMP: 7</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>6-Aug 9:35</t>
+          <t>6-Aug 9:28</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1887,43 +1887,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dhaval Packaging BSE SMEL@110.00 (13.4%)</t>
+          <t>MV Electrosystems IPOL@520.00 (22.35%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹12 (12.37%) 8 ↓ / 15 ↑</t>
+          <t>₹109 (25.65%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>49.99x</t>
+          <t>200.66x</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>97</v>
+        <v>425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹36.36 Cr</t>
+          <t>₹290.00 Cr</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1200</v>
+        <v>34</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 15</t>
+          <t>30-Jul GMP: 125</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 8</t>
+          <t>3-Aug GMP: 100</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 12</t>
+          <t>6-Aug GMP: 109</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>6-Aug 9:33</t>
+          <t>6-Aug 9:35</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1950,58 +1950,58 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>H.R. Hygiene Products BSE SMEL@90.00 (2.27%)</t>
+          <t>Dhaval Packaging BSE SMEL@110.00 (13.4%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹1 (1.14%) 1 ↓ / 2 ↑</t>
+          <t>₹12 (12.37%) 8 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6.65x</t>
+          <t>49.99x</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹53.95 Cr</t>
+          <t>₹36.36 Cr</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 2</t>
+          <t>30-Jul GMP: 15</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 2</t>
+          <t>3-Aug GMP: 8</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 1</t>
+          <t>6-Aug GMP: 12</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>5-Aug 9:37</t>
+          <t>6-Aug 9:33</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2013,12 +2013,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Manipal Health Enterprises IPOL@652.00 (10.51%)</t>
+          <t>H.R. Hygiene Products BSE SMEL@90.00 (2.27%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹7 (1.19%) -15 ↓ / 35 ↑</t>
+          <t>₹1 (1.14%) 1 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2028,28 +2028,28 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5.12x</t>
+          <t>6.65x</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>590</v>
+        <v>88</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹9275.22 Cr</t>
+          <t>₹53.95 Cr</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>25</v>
+        <v>1600</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 9</t>
+          <t>29-Jul GMP: 2</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>31-Jul GMP: -15</t>
+          <t>31-Jul GMP: 2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 7</t>
+          <t>5-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>5-Aug 9:30</t>
+          <t>5-Aug 9:37</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2076,58 +2076,58 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Poojaa Precision Engg. BSE SMEL@470.00 (56.15%)</t>
+          <t>Manipal Health Enterprises IPOL@652.00 (10.51%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹200 (66.45%) 195 ↓ / 300 ↑</t>
+          <t>₹7 (1.19%) -15 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>278.83x</t>
+          <t>5.12x</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>301</v>
+        <v>590</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹159.83 Cr</t>
+          <t>₹9275.22 Cr</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>400</v>
+        <v>25</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 300</t>
+          <t>29-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 225</t>
+          <t>31-Jul GMP: -15</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 200</t>
+          <t>5-Aug GMP: 7</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>4-Aug 9:33</t>
+          <t>5-Aug 9:30</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2139,75 +2139,75 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Propshop Events &amp; Exhibitions NSE SMEL@55.20 (-20%)</t>
+          <t>Poojaa Precision Engg. BSE SMEL@470.00 (56.15%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹200 (66.45%) 195 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.53x</t>
+          <t>278.83x</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>69</v>
+        <v>301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹28.57 Cr</t>
+          <t>₹159.83 Cr</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 0</t>
+          <t>28-Jul GMP: 300</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 0</t>
+          <t>30-Jul GMP: 225</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>31-Jul</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 0</t>
+          <t>4-Aug GMP: 200</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3-Aug 9:35</t>
+          <t>4-Aug 9:33</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Advance Technoforge BSE SMEL@94.00 (-1.05%)</t>
+          <t>Propshop Events &amp; Exhibitions NSE SMEL@55.20 (-20%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹4 (4.21%) 3 ↓ / 9 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,28 +2217,28 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.55x</t>
+          <t>1.53x</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹24.04 Cr</t>
+          <t>₹28.57 Cr</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 9</t>
+          <t>27-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 8</t>
+          <t>29-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 4</t>
+          <t>3-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>3-Aug 9:30</t>
+          <t>3-Aug 9:35</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2265,12 +2265,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Silverstorm Parks &amp; Resorts BSE SMEL@132.90 (-0.08%)</t>
+          <t>Advance Technoforge BSE SMEL@94.00 (-1.05%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹5 (3.76%) 5 ↓ / 5 ↑</t>
+          <t>₹4 (4.21%) 3 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2280,106 +2280,106 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.91x</t>
+          <t>1.55x</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹82.43 Cr</t>
+          <t>₹24.04 Cr</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 0</t>
+          <t>27-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 0</t>
+          <t>29-Jul GMP: 8</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 5</t>
+          <t>3-Aug GMP: 4</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>31-Jul 9:34</t>
+          <t>3-Aug 9:30</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Xtranet Technologies IPOL@136.00 (7.09%)</t>
+          <t>Silverstorm Parks &amp; Resorts BSE SMEL@132.90 (-0.08%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹14.5 (11.42%) 7.50 ↓ / 26 ↑</t>
+          <t>₹5 (3.76%) 5 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>12.24x</t>
+          <t>1.91x</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹166.80 Cr</t>
+          <t>₹82.43 Cr</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>23-Jul GMP: 8</t>
+          <t>24-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 7.7</t>
+          <t>28-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>28-Jul</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 14.5</t>
+          <t>31-Jul GMP: 5</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>30-Jul 9:31</t>
+          <t>31-Jul 9:34</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,12 +501,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Credent Connect NSE SMEU</t>
+          <t>Lalithaa Jewellery Mart IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -519,40 +519,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>189</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹93.90 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>600</v>
-      </c>
+          <t>₹1700.00 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10-Aug 10:00</t>
+          <t>10-Aug 13:50</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -564,17 +560,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods BSE SMEU</t>
+          <t>Credent Connect NSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹6 (5.22%) 6 ↓ / 6 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -583,61 +579,61 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹26.25 Cr</t>
+          <t>₹93.90 Cr</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>10-Aug 10:00</t>
+          <t>10-Aug 15:35</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMEU</t>
+          <t>Q&amp;T Foods BSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹15 (13.04%) 6 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -646,11 +642,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
+          <t>₹26.25 Cr</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -678,29 +674,29 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>10-Aug 9:55</t>
+          <t>10-Aug 15:32</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOU</t>
+          <t>Pramodini Medicare NSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹25 (8.77%) 25 ↓ / 30 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -709,15 +705,15 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>285</v>
+        <v>118</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹69.04 Cr</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>52</v>
+        <v>1200</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -741,7 +737,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>10-Aug 9:54</t>
+          <t>10-Aug 15:33</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -758,7 +754,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹22 (22.68%) 14 ↓ / 22 ↑</t>
+          <t>₹26.5 (27.32%) 14 ↓ / 26.50 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -804,7 +800,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>10-Aug 9:53</t>
+          <t>10-Aug 15:36</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -816,17 +812,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sham Foam BSE SMEU</t>
+          <t>Behari Lal Engineering IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹53 (18.60%) 25 ↓ / 53 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -835,61 +831,61 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>130</v>
+        <v>285</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹40.48 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>52</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>10-Aug 9:55</t>
+          <t>10-Aug 15:35</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMEU</t>
+          <t>Milky Mist Dairy Food IPOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹25 (17.86%) 24 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -898,15 +894,15 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹66.98 Cr</t>
+          <t>₹1553.00 Cr</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>800</v>
+        <v>107</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -930,7 +926,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>10-Aug 9:53</t>
+          <t>10-Aug 15:28</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -942,17 +938,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food IPOU</t>
+          <t>Sham Foam BSE SMEU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹26 (18.57%) 24 ↓ / 27 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -961,15 +957,15 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹1553.00 Cr</t>
+          <t>₹40.48 Cr</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>107</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -993,70 +989,70 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>10-Aug 9:59</t>
+          <t>10-Aug 15:32</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOO</t>
+          <t>Fascinate Textiles NSE SMEU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹132 (16.36%) 130 ↓ / 220 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.03x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>807</v>
+        <v>156</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹939.70 Cr</t>
+          <t>₹66.98 Cr</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>18</v>
+        <v>800</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 132</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>10-Aug 9:56</t>
+          <t>10-Aug 15:34</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1073,7 +1069,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹259 (29.74%) 146 ↓ / 259 ↑</t>
+          <t>₹270 (31.00%) 146 ↓ / 270 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1083,7 +1079,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.03x</t>
+          <t>0.5x</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1099,7 +1095,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 259</t>
+          <t>10-Aug GMP: 270</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1119,7 +1115,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>10-Aug 9:58</t>
+          <t>10-Aug 15:35</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1131,12 +1127,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Technocraft Ventures IPOO</t>
+          <t>Molbio Diagnostics IPOO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹23 (10.85%) 10 ↓ / 23 ↑</t>
+          <t>₹138 (17.10%) 130 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1146,43 +1142,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.85x</t>
+          <t>0.74x</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>212</v>
+        <v>807</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹251.88 Cr</t>
+          <t>₹939.70 Cr</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>10-Aug GMP: 138</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>10-Aug 10:01</t>
+          <t>10-Aug 15:36</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1194,38 +1190,38 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Optimystix Entertainment NSE SMEO</t>
+          <t>LEAP India IPOO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹5 (2.86%) 5 ↓ / 5 ↑</t>
+          <t>₹12 (7.55%) 3 ↓ / 19.50 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.73x</t>
+          <t>0.46x</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹108.50 Cr</t>
+          <t>₹2480.00 Cr</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>800</v>
+        <v>94</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 0</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1245,7 +1241,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>10-Aug 10:00</t>
+          <t>10-Aug 15:34</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1257,12 +1253,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LEAP India IPOO</t>
+          <t>Technocraft Ventures IPOO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹16 (10.06%) 3 ↓ / 19.50 ↑</t>
+          <t>₹27.5 (12.97%) 10 ↓ / 27.50 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1272,19 +1268,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.31x</t>
+          <t>4.32x</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹2480.00 Cr</t>
+          <t>₹251.88 Cr</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1308,7 +1304,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>10-Aug 9:55</t>
+          <t>10-Aug 15:34</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1320,58 +1316,58 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LAPL Automotive BSE SMECT</t>
+          <t>Optimystix Entertainment NSE SMEO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹37 (39.36%) 22 ↓ / 37 ↑</t>
+          <t>₹5 (2.86%) 5 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>42.89x</t>
+          <t>0.73x</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>94</v>
+        <v>175</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹32.40 Cr</t>
+          <t>₹108.50 Cr</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 32</t>
+          <t>7-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 37</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>10-Aug 9:55</t>
+          <t>10-Aug 15:29</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1383,12 +1379,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEC</t>
+          <t>LAPL Automotive BSE SMECT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹26 (20.00%) 18 ↓ / 26 ↑</t>
+          <t>₹39 (41.49%) 22 ↓ / 39 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1398,43 +1394,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>169.26x</t>
+          <t>332.33x</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹32.40 Cr</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 25</t>
+          <t>6-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 26</t>
+          <t>10-Aug GMP: 39</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>10-Aug 9:58</t>
+          <t>10-Aug 15:35</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1446,12 +1442,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOC</t>
+          <t>G.V. Electricals BSE SMEC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹16 (30.19%) 6.50 ↓ / 16 ↑</t>
+          <t>₹26 (20.00%) 18 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1461,28 +1457,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>138.83x</t>
+          <t>169.26x</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>281</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 15.25</t>
+          <t>31-Jul GMP: 25</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>7-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1497,7 +1493,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>10-Aug 9:59</t>
+          <t>10-Aug 15:32</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1509,58 +1505,58 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aegeus Technologies BSE SMECAllotted</t>
+          <t>Ardee Industries IPOC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹12 (11.43%) 12 ↓ / 12 ↑</t>
+          <t>₹15 (28.30%) 6.50 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>29.91x</t>
+          <t>138.83x</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹23.71 Cr</t>
+          <t>₹425.87 Cr</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1200</v>
+        <v>281</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>5-Aug GMP: 15.25</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 12</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>10-Aug 10:00</t>
+          <t>10-Aug 15:37</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1572,58 +1568,58 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cube Highways Trust InvIT IPOCAllotted</t>
+          <t>Aegeus Technologies BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
+          <t>₹12 (11.43%) 12 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9.35x</t>
+          <t>29.91x</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>152</v>
+        <v>105</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹5000.00 Cr</t>
+          <t>₹23.71 Cr</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>95</v>
+        <v>1200</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 0</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 1.75</t>
+          <t>6-Aug GMP: 12</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 1.75</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>10-Aug 5:55</t>
+          <t>10-Aug 15:34</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1635,58 +1631,58 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Anawil Wire &amp; Engineering NSE SMEL@329.65 (22.09%)</t>
+          <t>Cube Highways Trust InvIT IPOCAllotted</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹58 (21.48%) 58 ↓ / 90 ↑</t>
+          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>149.13x</t>
+          <t>9.35x</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>270</v>
+        <v>152</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹177.81 Cr</t>
+          <t>₹5000.00 Cr</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>400</v>
+        <v>95</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 80</t>
+          <t>22-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 78</t>
+          <t>24-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 58</t>
+          <t>31-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>10-Aug 9:32</t>
+          <t>10-Aug 5:55</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1698,58 +1694,58 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fusion Klassroom Edutech BSE SMEL@170.00 (6.92%)</t>
+          <t>Anawil Wire &amp; Engineering NSE SMEL@329.65 (22.09%)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
+          <t>₹58 (21.48%) 58 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.5x</t>
+          <t>149.13x</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>159</v>
+        <v>270</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹39.04 Cr</t>
+          <t>₹177.81 Cr</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 4</t>
+          <t>3-Aug GMP: 80</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>5-Aug GMP: 78</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 0</t>
+          <t>10-Aug GMP: 58</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>7-Aug 9:35</t>
+          <t>10-Aug 9:32</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1761,58 +1757,58 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Oneindig Technologies BSE SMEL@120.00 (25%)</t>
+          <t>Fusion Klassroom Edutech BSE SMEL@170.00 (6.92%)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹7 (7.29%) 7 ↓ / 7 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.73x</t>
+          <t>1.5x</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>96</v>
+        <v>159</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹27.65 Cr</t>
+          <t>₹39.04 Cr</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 0</t>
+          <t>31-Jul GMP: 4</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 0</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 7</t>
+          <t>7-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>6-Aug 9:28</t>
+          <t>7-Aug 9:35</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1887,43 +1883,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MV Electrosystems IPOL@520.00 (22.35%)</t>
+          <t>Oneindig Technologies BSE SMEL@120.00 (25%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹109 (25.65%) 60 ↓ / 133 ↑</t>
+          <t>₹7 (7.29%) 7 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>200.66x</t>
+          <t>1.73x</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>425</v>
+        <v>96</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹290.00 Cr</t>
+          <t>₹27.65 Cr</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>34</v>
+        <v>1200</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 125</t>
+          <t>30-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 100</t>
+          <t>3-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1933,12 +1929,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 109</t>
+          <t>6-Aug GMP: 7</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>6-Aug 9:35</t>
+          <t>6-Aug 9:28</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2013,58 +2009,58 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>H.R. Hygiene Products BSE SMEL@90.00 (2.27%)</t>
+          <t>MV Electrosystems IPOL@520.00 (22.35%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹1 (1.14%) 1 ↓ / 2 ↑</t>
+          <t>₹109 (25.65%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6.65x</t>
+          <t>200.66x</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>88</v>
+        <v>425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹53.95 Cr</t>
+          <t>₹290.00 Cr</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1600</v>
+        <v>34</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 2</t>
+          <t>30-Jul GMP: 125</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 2</t>
+          <t>3-Aug GMP: 100</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 1</t>
+          <t>6-Aug GMP: 109</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>5-Aug 9:37</t>
+          <t>6-Aug 9:35</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2076,12 +2072,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Manipal Health Enterprises IPOL@652.00 (10.51%)</t>
+          <t>H.R. Hygiene Products BSE SMEL@90.00 (2.27%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹7 (1.19%) -15 ↓ / 35 ↑</t>
+          <t>₹1 (1.14%) 1 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2091,28 +2087,28 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5.12x</t>
+          <t>6.65x</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>590</v>
+        <v>88</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹9275.22 Cr</t>
+          <t>₹53.95 Cr</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>25</v>
+        <v>1600</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 9</t>
+          <t>29-Jul GMP: 2</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>31-Jul GMP: -15</t>
+          <t>31-Jul GMP: 2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2122,12 +2118,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 7</t>
+          <t>5-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>5-Aug 9:30</t>
+          <t>5-Aug 9:37</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2139,58 +2135,58 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Poojaa Precision Engg. BSE SMEL@470.00 (56.15%)</t>
+          <t>Manipal Health Enterprises IPOL@652.00 (10.51%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹200 (66.45%) 195 ↓ / 300 ↑</t>
+          <t>₹7 (1.19%) -15 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>278.83x</t>
+          <t>5.12x</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>301</v>
+        <v>590</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹159.83 Cr</t>
+          <t>₹9275.22 Cr</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>400</v>
+        <v>25</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 300</t>
+          <t>29-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 225</t>
+          <t>31-Jul GMP: -15</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 200</t>
+          <t>5-Aug GMP: 7</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>4-Aug 9:33</t>
+          <t>5-Aug 9:30</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2202,75 +2198,75 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Propshop Events &amp; Exhibitions NSE SMEL@55.20 (-20%)</t>
+          <t>Poojaa Precision Engg. BSE SMEL@470.00 (56.15%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹200 (66.45%) 195 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.53x</t>
+          <t>278.83x</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>69</v>
+        <v>301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹28.57 Cr</t>
+          <t>₹159.83 Cr</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 0</t>
+          <t>28-Jul GMP: 300</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 0</t>
+          <t>30-Jul GMP: 225</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>31-Jul</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 0</t>
+          <t>4-Aug GMP: 200</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>3-Aug 9:35</t>
+          <t>4-Aug 9:33</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Advance Technoforge BSE SMEL@94.00 (-1.05%)</t>
+          <t>Propshop Events &amp; Exhibitions NSE SMEL@55.20 (-20%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹4 (4.21%) 3 ↓ / 9 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2280,28 +2276,28 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.55x</t>
+          <t>1.53x</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹24.04 Cr</t>
+          <t>₹28.57 Cr</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 9</t>
+          <t>27-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 8</t>
+          <t>29-Jul GMP: 0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2311,12 +2307,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 4</t>
+          <t>3-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>3-Aug 9:30</t>
+          <t>3-Aug 9:35</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2328,12 +2324,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Silverstorm Parks &amp; Resorts BSE SMEL@132.90 (-0.08%)</t>
+          <t>Advance Technoforge BSE SMEL@94.00 (-1.05%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹5 (3.76%) 5 ↓ / 5 ↑</t>
+          <t>₹4 (4.21%) 3 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2343,48 +2339,48 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.91x</t>
+          <t>1.55x</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹82.43 Cr</t>
+          <t>₹24.04 Cr</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 0</t>
+          <t>27-Jul GMP: 9</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 0</t>
+          <t>29-Jul GMP: 8</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>30-Jul</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 5</t>
+          <t>3-Aug GMP: 4</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>31-Jul 9:34</t>
+          <t>3-Aug 9:30</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOU</t>
+          <t>ENS Enterprises BSE SMEU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -519,36 +519,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>92</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>₹33.14 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1200</v>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>18-Aug</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>19-Aug</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>20-Aug</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10-Aug 13:50</t>
+          <t>11-Aug 8:40</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -560,17 +564,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Credent Connect NSE SMEU</t>
+          <t>Technocrats Plasma Systems BSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹30 (22.73%) 30 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -579,39 +583,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>189</v>
+        <v>132</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹93.90 Cr</t>
+          <t>₹60.98 Cr</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>10-Aug 15:35</t>
+          <t>11-Aug 9:28</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -623,17 +627,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods BSE SMEU</t>
+          <t>Sunshine Pictures IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹15 (13.04%) 6 ↓ / 15 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -642,51 +646,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>115</v>
+        <v>360</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹26.25 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1200</v>
+        <v>41</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>10-Aug 15:32</t>
+          <t>11-Aug 9:31</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMEU</t>
+          <t>Shankesh Jewellers IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -705,39 +709,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1200</v>
+        <v>160</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>10-Aug 15:33</t>
+          <t>11-Aug 9:30</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -749,17 +753,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Shiprocket IPOU</t>
+          <t>Lalithaa Jewellery Mart IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹26.5 (27.32%) 14 ↓ / 26.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -768,39 +772,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>97</v>
+        <v>201</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹1700.00 Cr</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>154</v>
+        <v>74</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>10-Aug 15:36</t>
+          <t>11-Aug 9:37</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -812,17 +816,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOU</t>
+          <t>Skytech Infinite Platform NSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹53 (18.60%) 25 ↓ / 53 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -831,61 +835,61 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>285</v>
+        <v>77</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹22.68 Cr</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>52</v>
+        <v>1600</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>10-Aug 15:35</t>
+          <t>11-Aug 9:33</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food IPOU</t>
+          <t>Credent Connect NSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹25 (17.86%) 24 ↓ / 27 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -894,39 +898,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>140</v>
+        <v>189</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹1553.00 Cr</t>
+          <t>₹93.90 Cr</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>107</v>
+        <v>600</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>10-Aug 15:28</t>
+          <t>11-Aug 9:37</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -938,17 +942,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sham Foam BSE SMEU</t>
+          <t>Q&amp;T Foods BSE SMEU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹15 (13.04%) 6 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -957,39 +961,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹40.48 Cr</t>
+          <t>₹26.25 Cr</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>10-Aug 15:32</t>
+          <t>11-Aug 9:33</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1001,7 +1005,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMEU</t>
+          <t>Pramodini Medicare NSE SMEU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1020,39 +1024,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹66.98 Cr</t>
+          <t>₹69.04 Cr</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>10-Aug 15:34</t>
+          <t>11-Aug 9:32</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1064,58 +1068,58 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOO</t>
+          <t>Behari Lal Engineering IPOU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹270 (31.00%) 146 ↓ / 270 ↑</t>
+          <t>₹53 (18.60%) 25 ↓ / 53 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.5x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>871</v>
+        <v>285</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 270</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>10-Aug 15:35</t>
+          <t>11-Aug 9:36</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1127,58 +1131,58 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOO</t>
+          <t>Shiprocket IPOU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹138 (17.10%) 130 ↓ / 220 ↑</t>
+          <t>₹27 (27.84%) 14 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.74x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>807</v>
+        <v>97</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹939.70 Cr</t>
+          <t>₹1617.48 Cr</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 138</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>10-Aug 15:36</t>
+          <t>11-Aug 9:29</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1190,121 +1194,121 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LEAP India IPOO</t>
+          <t>Sham Foam BSE SMEO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹12 (7.55%) 3 ↓ / 19.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.46x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹2480.00 Cr</t>
+          <t>₹40.48 Cr</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>94</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>10-Aug 15:34</t>
+          <t>11-Aug 9:33</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Technocraft Ventures IPOO</t>
+          <t>Fascinate Textiles NSE SMEO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹27.5 (12.97%) 10 ↓ / 27.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.32x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>212</v>
+        <v>156</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹251.88 Cr</t>
+          <t>₹66.98 Cr</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>70</v>
+        <v>800</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>10-Aug 15:34</t>
+          <t>11-Aug 9:34</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1316,58 +1320,58 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Optimystix Entertainment NSE SMEO</t>
+          <t>Milky Mist Dairy Food IPOO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹5 (2.86%) 5 ↓ / 5 ↑</t>
+          <t>₹20.5 (14.64%) 20.50 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.73x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹108.50 Cr</t>
+          <t>₹1553.00 Cr</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>800</v>
+        <v>107</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 0</t>
+          <t>11-Aug GMP: 20.5</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>10-Aug 15:29</t>
+          <t>11-Aug 9:31</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1379,12 +1383,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LAPL Automotive BSE SMECT</t>
+          <t>Dhoot Transmission IPOO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹39 (41.49%) 22 ↓ / 39 ↑</t>
+          <t>₹250 (28.70%) 146 ↓ / 259 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1394,43 +1398,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>332.33x</t>
+          <t>0.62x</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>94</v>
+        <v>871</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹32.40 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1200</v>
+        <v>17</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 32</t>
+          <t>10-Aug GMP: 250</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 39</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>10-Aug 15:35</t>
+          <t>11-Aug 9:31</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1442,58 +1446,58 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEC</t>
+          <t>Molbio Diagnostics IPOO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹26 (20.00%) 18 ↓ / 26 ↑</t>
+          <t>₹127 (15.74%) 127 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>169.26x</t>
+          <t>0.83x</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>130</v>
+        <v>807</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹939.70 Cr</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 25</t>
+          <t>10-Aug GMP: 127</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 26</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>10-Aug 15:32</t>
+          <t>11-Aug 9:31</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1505,58 +1509,58 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOC</t>
+          <t>Optimystix Entertainment NSE SMECT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹15 (28.30%) 6.50 ↓ / 16 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>138.83x</t>
+          <t>0.77x</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
+          <t>₹108.50 Cr</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>281</v>
+        <v>800</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 15.25</t>
+          <t>7-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>10-Aug 15:37</t>
+          <t>11-Aug 9:35</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1568,12 +1572,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Aegeus Technologies BSE SMECAllotted</t>
+          <t>Technocraft Ventures IPOCT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹12 (11.43%) 12 ↓ / 12 ↑</t>
+          <t>₹30 (14.15%) 10 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1583,43 +1587,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>29.91x</t>
+          <t>4.74x</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105</v>
+        <v>212</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹23.71 Cr</t>
+          <t>₹251.88 Cr</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1200</v>
+        <v>70</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 12</t>
+          <t>11-Aug GMP: 30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>10-Aug 15:34</t>
+          <t>11-Aug 9:36</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1631,58 +1635,58 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cube Highways Trust InvIT IPOCAllotted</t>
+          <t>LEAP India IPOCT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
+          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9.35x</t>
+          <t>0.52x</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹5000.00 Cr</t>
+          <t>₹2480.00 Cr</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 0</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 1.75</t>
+          <t>11-Aug GMP: 13</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 1.75</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>10-Aug 5:55</t>
+          <t>11-Aug 9:37</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1694,12 +1698,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Anawil Wire &amp; Engineering NSE SMEL@329.65 (22.09%)</t>
+          <t>LAPL Automotive BSE SMEC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹58 (21.48%) 58 ↓ / 90 ↑</t>
+          <t>₹39 (41.49%) 22 ↓ / 39 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1709,43 +1713,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>149.13x</t>
+          <t>344.31x</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>270</v>
+        <v>94</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹177.81 Cr</t>
+          <t>₹32.40 Cr</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 80</t>
+          <t>6-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 78</t>
+          <t>10-Aug GMP: 39</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 58</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>10-Aug 9:32</t>
+          <t>11-Aug 9:36</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1757,58 +1761,58 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Fusion Klassroom Edutech BSE SMEL@170.00 (6.92%)</t>
+          <t>G.V. Electricals BSE SMEC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
+          <t>₹25 (19.23%) 18 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.5x</t>
+          <t>169.26x</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹39.04 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 4</t>
+          <t>31-Jul GMP: 25</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>7-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 0</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>7-Aug 9:35</t>
+          <t>11-Aug 9:28</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1820,58 +1824,58 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Juniper Green Energy IPOL@245.00 (8.89%)</t>
+          <t>Ardee Industries IPOCAllotted</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹23 (10.22%) 1.50 ↓ / 23 ↑</t>
+          <t>₹14.5 (27.36%) 6.50 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.38x</t>
+          <t>138.83x</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>225</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹1800.00 Cr</t>
+          <t>₹425.87 Cr</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>66</v>
+        <v>281</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 8</t>
+          <t>5-Aug GMP: 15.25</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 9.5</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 23</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>6-Aug 9:37</t>
+          <t>11-Aug 9:32</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1883,58 +1887,58 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Oneindig Technologies BSE SMEL@120.00 (25%)</t>
+          <t>Cube Highways Trust InvIT IPOCAllotted</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹7 (7.29%) 7 ↓ / 7 ↑</t>
+          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.73x</t>
+          <t>9.35x</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹27.65 Cr</t>
+          <t>₹5000.00 Cr</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1200</v>
+        <v>95</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 0</t>
+          <t>22-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 0</t>
+          <t>24-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>29-Jul</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 7</t>
+          <t>31-Jul GMP: 1.75</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>6-Aug 9:28</t>
+          <t>11-Aug 5:55</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1946,12 +1950,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dhaval Packaging BSE SMEL@110.00 (13.4%)</t>
+          <t>Aegeus Technologies BSE SMELT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹12 (12.37%) 8 ↓ / 15 ↑</t>
+          <t>₹12 (11.43%) 12 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1961,15 +1965,15 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>49.99x</t>
+          <t>29.91x</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹36.36 Cr</t>
+          <t>₹23.71 Cr</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1977,27 +1981,27 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 15</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 8</t>
+          <t>6-Aug GMP: 12</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 12</t>
+          <t>11-Aug GMP: 12</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>6-Aug 9:33</t>
+          <t>11-Aug 9:30</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2009,12 +2013,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MV Electrosystems IPOL@520.00 (22.35%)</t>
+          <t>Anawil Wire &amp; Engineering NSE SMEL@329.65 (22.09%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹109 (25.65%) 60 ↓ / 133 ↑</t>
+          <t>₹58 (21.48%) 58 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2024,43 +2028,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>200.66x</t>
+          <t>149.13x</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>425</v>
+        <v>270</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹290.00 Cr</t>
+          <t>₹177.81 Cr</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>34</v>
+        <v>400</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 125</t>
+          <t>3-Aug GMP: 80</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 100</t>
+          <t>5-Aug GMP: 78</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 109</t>
+          <t>10-Aug GMP: 58</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>6-Aug 9:35</t>
+          <t>10-Aug 9:32</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2072,12 +2076,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>H.R. Hygiene Products BSE SMEL@90.00 (2.27%)</t>
+          <t>Fusion Klassroom Edutech BSE SMEL@170.00 (6.92%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹1 (1.14%) 1 ↓ / 2 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2087,43 +2091,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6.65x</t>
+          <t>1.5x</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹53.95 Cr</t>
+          <t>₹39.04 Cr</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1600</v>
+        <v>800</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 2</t>
+          <t>31-Jul GMP: 4</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 2</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 1</t>
+          <t>7-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>5-Aug 9:37</t>
+          <t>7-Aug 9:35</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2135,58 +2139,58 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Manipal Health Enterprises IPOL@652.00 (10.51%)</t>
+          <t>Oneindig Technologies BSE SMEL@120.00 (25%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹7 (1.19%) -15 ↓ / 35 ↑</t>
+          <t>₹7 (7.29%) 7 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5.12x</t>
+          <t>1.73x</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>590</v>
+        <v>96</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹9275.22 Cr</t>
+          <t>₹27.65 Cr</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>25</v>
+        <v>1200</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 9</t>
+          <t>30-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>31-Jul GMP: -15</t>
+          <t>3-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 7</t>
+          <t>6-Aug GMP: 7</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>5-Aug 9:30</t>
+          <t>6-Aug 9:28</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2198,58 +2202,58 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Poojaa Precision Engg. BSE SMEL@470.00 (56.15%)</t>
+          <t>Juniper Green Energy IPOL@245.00 (8.89%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹200 (66.45%) 195 ↓ / 300 ↑</t>
+          <t>₹23 (10.22%) 1.50 ↓ / 23 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>278.83x</t>
+          <t>8.38x</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>301</v>
+        <v>225</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹159.83 Cr</t>
+          <t>₹1800.00 Cr</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>400</v>
+        <v>66</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 300</t>
+          <t>30-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 225</t>
+          <t>3-Aug GMP: 9.5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 200</t>
+          <t>6-Aug GMP: 23</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>4-Aug 9:33</t>
+          <t>6-Aug 9:37</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2261,93 +2265,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Propshop Events &amp; Exhibitions NSE SMEL@55.20 (-20%)</t>
+          <t>MV Electrosystems IPOL@520.00 (22.35%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹109 (25.65%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.53x</t>
+          <t>200.66x</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>69</v>
+        <v>425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹28.57 Cr</t>
+          <t>₹290.00 Cr</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2000</v>
+        <v>34</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 0</t>
+          <t>30-Jul GMP: 125</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 0</t>
+          <t>3-Aug GMP: 100</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 0</t>
+          <t>6-Aug GMP: 109</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>3-Aug 9:35</t>
+          <t>6-Aug 9:35</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Advance Technoforge BSE SMEL@94.00 (-1.05%)</t>
+          <t>Dhaval Packaging BSE SMEL@110.00 (13.4%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹4 (4.21%) 3 ↓ / 9 ↑</t>
+          <t>₹12 (12.37%) 8 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.55x</t>
+          <t>49.99x</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹24.04 Cr</t>
+          <t>₹36.36 Cr</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2355,32 +2359,32 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>27-Jul GMP: 9</t>
+          <t>30-Jul GMP: 15</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>29-Jul GMP: 8</t>
+          <t>3-Aug GMP: 8</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>4-Aug</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 4</t>
+          <t>6-Aug GMP: 12</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>3-Aug 9:30</t>
+          <t>6-Aug 9:33</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,12 +501,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMEU</t>
+          <t>Shankesh Jewellers IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -520,39 +520,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹33.14 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1200</v>
+        <v>160</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>11-Aug 8:40</t>
+          <t>11-Aug 15:32</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -564,17 +564,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems BSE SMEU</t>
+          <t>Sunshine Pictures IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹30 (22.73%) 30 ↓ / 30 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -583,39 +583,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>132</v>
+        <v>360</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹60.98 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>41</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>11-Aug 9:28</t>
+          <t>11-Aug 15:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOU</t>
+          <t>Lalithaa Jewellery Mart IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,39 +646,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>360</v>
+        <v>201</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹1700.00 Cr</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>19-Aug</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>20-Aug</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>21-Aug</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>11-Aug 9:31</t>
+          <t>11-Aug 15:36</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOU</t>
+          <t>ENS Enterprises BSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -709,39 +709,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹367.18 Cr</t>
+          <t>₹33.14 Cr</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>160</v>
+        <v>1200</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>14-Aug</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>18-Aug</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20-Aug</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>19-Aug</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>21-Aug</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>25-Aug</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>11-Aug 9:30</t>
+          <t>11-Aug 15:34</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOU</t>
+          <t>Skytech Infinite Platform NSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -772,61 +772,61 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹22.68 Cr</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>74</v>
+        <v>1600</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>18-Aug</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>19-Aug</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>20-Aug</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>11-Aug 9:37</t>
+          <t>11-Aug 15:32</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Skytech Infinite Platform NSE SMEU</t>
+          <t>Technocrats Plasma Systems BSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹26 (19.70%) 26 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -835,15 +835,15 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹22.68 Cr</t>
+          <t>₹60.98 Cr</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1600</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -867,12 +867,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>11-Aug 9:33</t>
+          <t>11-Aug 15:30</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>11-Aug 9:37</t>
+          <t>11-Aug 15:32</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>11-Aug 9:33</t>
+          <t>11-Aug 15:32</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>11-Aug 9:32</t>
+          <t>11-Aug 15:35</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹53 (18.60%) 25 ↓ / 53 ↑</t>
+          <t>₹45 (15.79%) 25 ↓ / 53 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>11-Aug 9:36</t>
+          <t>11-Aug 15:29</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>11-Aug 9:29</t>
+          <t>11-Aug 15:37</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sham Foam BSE SMEO</t>
+          <t>Fascinate Textiles NSE SMEO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1209,19 +1209,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.05x</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹40.48 Cr</t>
+          <t>₹66.98 Cr</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>11-Aug 9:33</t>
+          <t>11-Aug 15:33</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1257,38 +1257,38 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMEO</t>
+          <t>Milky Mist Dairy Food IPOO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹21 (15.00%) 20.50 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.7x</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹66.98 Cr</t>
+          <t>₹1553.00 Cr</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>800</v>
+        <v>107</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>11-Aug GMP: 21</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>11-Aug 9:34</t>
+          <t>11-Aug 15:32</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1320,38 +1320,38 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food IPOO</t>
+          <t>Sham Foam BSE SMEO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹20.5 (14.64%) 20.50 ↓ / 27 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.02x</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹1553.00 Cr</t>
+          <t>₹40.48 Cr</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>107</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 20.5</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1371,50 +1371,50 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>11-Aug 9:31</t>
+          <t>11-Aug 15:37</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOO</t>
+          <t>Molbio Diagnostics IPOO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹250 (28.70%) 146 ↓ / 259 ↑</t>
+          <t>₹122 (15.12%) 122 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.62x</t>
+          <t>2.78x</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>871</v>
+        <v>807</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
+          <t>₹939.70 Cr</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 250</t>
+          <t>10-Aug GMP: 127</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>11-Aug 9:31</t>
+          <t>11-Aug 15:36</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1446,38 +1446,38 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOO</t>
+          <t>Dhoot Transmission IPOO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹127 (15.74%) 127 ↓ / 220 ↑</t>
+          <t>₹246 (28.24%) 146 ↓ / 259 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.83x</t>
+          <t>3.41x</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>807</v>
+        <v>871</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>₹939.70 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 127</t>
+          <t>10-Aug GMP: 250</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>11-Aug 9:31</t>
+          <t>11-Aug 15:34</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.77x</t>
+          <t>1.94x</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>11-Aug 9:35</t>
+          <t>11-Aug 15:33</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1572,34 +1572,34 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Technocraft Ventures IPOCT</t>
+          <t>LEAP India IPOCT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹30 (14.15%) 10 ↓ / 30 ↑</t>
+          <t>₹10.5 (6.60%) 3 ↓ / 19.50 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4.74x</t>
+          <t>7.02x</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹251.88 Cr</t>
+          <t>₹2480.00 Cr</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 30</t>
+          <t>11-Aug GMP: 10.5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>11-Aug 9:36</t>
+          <t>11-Aug 15:29</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1635,34 +1635,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LEAP India IPOCT</t>
+          <t>Technocraft Ventures IPOCT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
+          <t>₹26 (12.26%) 10 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.52x</t>
+          <t>36.39x</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹2480.00 Cr</t>
+          <t>₹251.88 Cr</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 13</t>
+          <t>11-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>11-Aug 9:37</t>
+          <t>11-Aug 15:32</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>11-Aug 9:36</t>
+          <t>11-Aug 15:31</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>11-Aug 9:28</t>
+          <t>11-Aug 15:32</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹14.5 (27.36%) 6.50 ↓ / 16 ↑</t>
+          <t>₹12.5 (23.58%) 6.50 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>11-Aug 9:32</t>
+          <t>11-Aug 15:29</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1950,7 +1950,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aegeus Technologies BSE SMELT</t>
+          <t>Aegeus Technologies BSE SMEL@124.50 (18.57%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2139,30 +2139,30 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Oneindig Technologies BSE SMEL@120.00 (25%)</t>
+          <t>Dhaval Packaging BSE SMEL@110.00 (13.4%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹7 (7.29%) 7 ↓ / 7 ↑</t>
+          <t>₹12 (12.37%) 8 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.73x</t>
+          <t>49.99x</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹27.65 Cr</t>
+          <t>₹36.36 Cr</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 0</t>
+          <t>30-Jul GMP: 15</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 0</t>
+          <t>3-Aug GMP: 8</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 7</t>
+          <t>6-Aug GMP: 12</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>6-Aug 9:28</t>
+          <t>6-Aug 9:33</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2202,43 +2202,43 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Juniper Green Energy IPOL@245.00 (8.89%)</t>
+          <t>MV Electrosystems IPOL@520.00 (22.35%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹23 (10.22%) 1.50 ↓ / 23 ↑</t>
+          <t>₹109 (25.65%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.38x</t>
+          <t>200.66x</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>225</v>
+        <v>425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹1800.00 Cr</t>
+          <t>₹290.00 Cr</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 8</t>
+          <t>30-Jul GMP: 125</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 9.5</t>
+          <t>3-Aug GMP: 100</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 23</t>
+          <t>6-Aug GMP: 109</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6-Aug 9:37</t>
+          <t>6-Aug 9:35</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2265,43 +2265,43 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MV Electrosystems IPOL@520.00 (22.35%)</t>
+          <t>Juniper Green Energy IPOL@245.00 (8.89%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹109 (25.65%) 60 ↓ / 133 ↑</t>
+          <t>₹23 (10.22%) 1.50 ↓ / 23 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>200.66x</t>
+          <t>8.38x</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>425</v>
+        <v>225</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹290.00 Cr</t>
+          <t>₹1800.00 Cr</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 125</t>
+          <t>30-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 100</t>
+          <t>3-Aug GMP: 9.5</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 109</t>
+          <t>6-Aug GMP: 23</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>6-Aug 9:35</t>
+          <t>6-Aug 9:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2328,30 +2328,30 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dhaval Packaging BSE SMEL@110.00 (13.4%)</t>
+          <t>Oneindig Technologies BSE SMEL@120.00 (25%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹12 (12.37%) 8 ↓ / 15 ↑</t>
+          <t>₹7 (7.29%) 7 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>49.99x</t>
+          <t>1.73x</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹36.36 Cr</t>
+          <t>₹27.65 Cr</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 15</t>
+          <t>30-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 8</t>
+          <t>3-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 12</t>
+          <t>6-Aug GMP: 7</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>6-Aug 9:33</t>
+          <t>6-Aug 9:28</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>11-Aug 15:32</t>
+          <t>12-Aug 10:16</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>11-Aug 15:37</t>
+          <t>12-Aug 10:15</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOU</t>
+          <t>Horizon Industrial Parks IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,15 +646,15 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>201</v>
+        <v>60</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹2600.00 Cr</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>74</v>
+        <v>250</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>11-Aug 15:36</t>
+          <t>12-Aug 10:15</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -690,17 +690,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMEU</t>
+          <t>Lalithaa Jewellery Mart IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹21 (10.45%) 17 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -709,39 +709,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>92</v>
+        <v>201</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹33.14 Cr</t>
+          <t>₹1700.00 Cr</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1200</v>
+        <v>74</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>11-Aug 15:34</t>
+          <t>12-Aug 10:22</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Skytech Infinite Platform NSE SMEU</t>
+          <t>ENS Enterprises BSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -772,15 +772,15 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹22.68 Cr</t>
+          <t>₹33.14 Cr</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -804,29 +804,29 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>11-Aug 15:32</t>
+          <t>12-Aug 10:19</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems BSE SMEU</t>
+          <t>Skytech Infinite Platform NSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹26 (19.70%) 26 ↓ / 26 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -835,15 +835,15 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹60.98 Cr</t>
+          <t>₹22.68 Cr</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -867,24 +867,24 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>11-Aug 15:30</t>
+          <t>12-Aug 10:24</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Credent Connect NSE SMEU</t>
+          <t>Technocrats Plasma Systems BSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -898,39 +898,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>189</v>
+        <v>132</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹93.90 Cr</t>
+          <t>₹60.98 Cr</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>11-Aug 15:32</t>
+          <t>12-Aug 10:17</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -942,12 +942,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods BSE SMEU</t>
+          <t>Credent Connect NSE SMEU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹15 (13.04%) 6 ↓ / 15 ↑</t>
+          <t>₹35 (18.52%) 35 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -961,74 +961,74 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹26.25 Cr</t>
+          <t>₹93.90 Cr</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>11-Aug 15:32</t>
+          <t>12-Aug 10:20</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMEU</t>
+          <t>Q&amp;T Foods BSE SMEO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹21 (18.26%) 6 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.04x</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
+          <t>₹26.25 Cr</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>12-Aug GMP: 21</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1056,50 +1056,50 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>11-Aug 15:35</t>
+          <t>12-Aug 10:23</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOU</t>
+          <t>Pramodini Medicare NSE SMEO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹45 (15.79%) 25 ↓ / 53 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.02x</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>285</v>
+        <v>118</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹69.04 Cr</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>52</v>
+        <v>1200</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>12-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>11-Aug 15:29</t>
+          <t>12-Aug 10:16</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1131,12 +1131,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shiprocket IPOU</t>
+          <t>Behari Lal Engineering IPOO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹27 (27.84%) 14 ↓ / 27 ↑</t>
+          <t>₹67 (23.51%) 25 ↓ / 67 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1146,23 +1146,23 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.16x</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>97</v>
+        <v>285</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>154</v>
+        <v>52</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>12-Aug GMP: 67</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>11-Aug 15:37</t>
+          <t>12-Aug 10:18</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1194,101 +1194,101 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMEO</t>
+          <t>Shiprocket IPOO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹31 (31.96%) 14 ↓ / 31 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.05x</t>
+          <t>0.08x</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹66.98 Cr</t>
+          <t>₹1617.48 Cr</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>800</v>
+        <v>154</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>12-Aug GMP: 31</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>11-Aug 15:33</t>
+          <t>12-Aug 10:20</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food IPOO</t>
+          <t>Fascinate Textiles NSE SMEO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹21 (15.00%) 20.50 ↓ / 27 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.7x</t>
+          <t>0.07x</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹1553.00 Cr</t>
+          <t>₹66.98 Cr</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>107</v>
+        <v>800</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 21</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1308,50 +1308,50 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>11-Aug 15:32</t>
+          <t>12-Aug 10:21</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sham Foam BSE SMEO</t>
+          <t>Milky Mist Dairy Food IPOO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹22.5 (16.07%) 20.50 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.02x</t>
+          <t>1.03x</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹40.48 Cr</t>
+          <t>₹1553.00 Cr</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>107</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>11-Aug GMP: 22.5</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1371,118 +1371,118 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>11-Aug 15:37</t>
+          <t>12-Aug 10:18</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOO</t>
+          <t>Sham Foam BSE SMEO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹122 (15.12%) 122 ↓ / 220 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.78x</t>
+          <t>0.03x</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>807</v>
+        <v>130</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹939.70 Cr</t>
+          <t>₹40.48 Cr</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 127</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>11-Aug 15:36</t>
+          <t>12-Aug 10:20</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOO</t>
+          <t>Molbio Diagnostics IPOCT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹246 (28.24%) 146 ↓ / 259 ↑</t>
+          <t>₹139 (17.22%) 127 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3.41x</t>
+          <t>4.19x</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>871</v>
+        <v>807</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
+          <t>₹939.70 Cr</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 250</t>
+          <t>10-Aug GMP: 127</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>12-Aug GMP: 139</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>11-Aug 15:34</t>
+          <t>12-Aug 10:19</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1509,58 +1509,58 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Optimystix Entertainment NSE SMECT</t>
+          <t>Dhoot Transmission IPOCT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 5 ↑</t>
+          <t>₹258 (29.62%) 146 ↓ / 259 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.94x</t>
+          <t>5.06x</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>175</v>
+        <v>871</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹108.50 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>800</v>
+        <v>17</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 0</t>
+          <t>10-Aug GMP: 250</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>12-Aug GMP: 258</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>11-Aug 15:33</t>
+          <t>12-Aug 10:15</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1572,43 +1572,43 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LEAP India IPOCT</t>
+          <t>Optimystix Entertainment NSE SMEC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹10.5 (6.60%) 3 ↓ / 19.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.02x</t>
+          <t>2.05x</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹2480.00 Cr</t>
+          <t>₹108.50 Cr</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>94</v>
+        <v>800</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>7-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 10.5</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>11-Aug 15:29</t>
+          <t>12-Aug 10:21</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1635,34 +1635,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Technocraft Ventures IPOCT</t>
+          <t>LEAP India IPOC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹26 (12.26%) 10 ↓ / 30 ↑</t>
+          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>36.39x</t>
+          <t>8.82x</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹251.88 Cr</t>
+          <t>₹2480.00 Cr</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 26</t>
+          <t>11-Aug GMP: 13</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>11-Aug 15:32</t>
+          <t>12-Aug 10:20</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1698,58 +1698,58 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LAPL Automotive BSE SMEC</t>
+          <t>Technocraft Ventures IPOC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹39 (41.49%) 22 ↓ / 39 ↑</t>
+          <t>₹27 (12.74%) 10 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>344.31x</t>
+          <t>38.69x</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>94</v>
+        <v>212</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹32.40 Cr</t>
+          <t>₹251.88 Cr</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1200</v>
+        <v>70</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 32</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 39</t>
+          <t>11-Aug GMP: 29</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>11-Aug 15:31</t>
+          <t>12-Aug 10:17</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1761,58 +1761,58 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEC</t>
+          <t>LAPL Automotive BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹25 (19.23%) 18 ↓ / 26 ↑</t>
+          <t>₹47 (50.00%) 22 ↓ / 47 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>169.26x</t>
+          <t>344.31x</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹32.40 Cr</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 25</t>
+          <t>6-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 26</t>
+          <t>10-Aug GMP: 39</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>11-Aug 15:32</t>
+          <t>12-Aug 10:24</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1824,43 +1824,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOCAllotted</t>
+          <t>G.V. Electricals BSE SMEL@158.00 (21.54%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹12.5 (23.58%) 6.50 ↓ / 16 ↑</t>
+          <t>₹25 (19.23%) 18 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>138.83x</t>
+          <t>169.26x</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>281</v>
+        <v>1000</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 15.25</t>
+          <t>31-Jul GMP: 25</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>7-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>12-Aug GMP: 25</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>11-Aug 15:29</t>
+          <t>12-Aug 9:32</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1887,58 +1887,58 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cube Highways Trust InvIT IPOCAllotted</t>
+          <t>Ardee Industries IPOL@72.00 (35.85%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹1.75 (1.15%) 1.75 ↓ / 1.75 ↑</t>
+          <t>₹17 (32.08%) 6.50 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>9.35x</t>
+          <t>138.83x</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>152</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹5000.00 Cr</t>
+          <t>₹425.87 Cr</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>95</v>
+        <v>281</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>22-Jul GMP: 0</t>
+          <t>5-Aug GMP: 15.25</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>24-Jul GMP: 1.75</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>29-Jul</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 1.75</t>
+          <t>12-Aug GMP: 17</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>11-Aug 5:55</t>
+          <t>12-Aug 9:35</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2139,43 +2139,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dhaval Packaging BSE SMEL@110.00 (13.4%)</t>
+          <t>MV Electrosystems IPOL@520.00 (22.35%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹12 (12.37%) 8 ↓ / 15 ↑</t>
+          <t>₹109 (25.65%) 60 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>49.99x</t>
+          <t>200.66x</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>97</v>
+        <v>425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹36.36 Cr</t>
+          <t>₹290.00 Cr</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1200</v>
+        <v>34</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 15</t>
+          <t>30-Jul GMP: 125</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 8</t>
+          <t>3-Aug GMP: 100</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 12</t>
+          <t>6-Aug GMP: 109</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>6-Aug 9:33</t>
+          <t>6-Aug 9:35</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2202,43 +2202,43 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MV Electrosystems IPOL@520.00 (22.35%)</t>
+          <t>Juniper Green Energy IPOL@245.00 (8.89%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹109 (25.65%) 60 ↓ / 133 ↑</t>
+          <t>₹23 (10.22%) 1.50 ↓ / 23 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>200.66x</t>
+          <t>8.38x</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>425</v>
+        <v>225</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹290.00 Cr</t>
+          <t>₹1800.00 Cr</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 125</t>
+          <t>30-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 100</t>
+          <t>3-Aug GMP: 9.5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 109</t>
+          <t>6-Aug GMP: 23</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6-Aug 9:35</t>
+          <t>6-Aug 9:37</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2265,12 +2265,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Juniper Green Energy IPOL@245.00 (8.89%)</t>
+          <t>Dhaval Packaging BSE SMEL@110.00 (13.4%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹23 (10.22%) 1.50 ↓ / 23 ↑</t>
+          <t>₹12 (12.37%) 8 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2280,28 +2280,28 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.38x</t>
+          <t>49.99x</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>225</v>
+        <v>97</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹1800.00 Cr</t>
+          <t>₹36.36 Cr</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>66</v>
+        <v>1200</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 8</t>
+          <t>30-Jul GMP: 15</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 9.5</t>
+          <t>3-Aug GMP: 8</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 23</t>
+          <t>6-Aug GMP: 12</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>6-Aug 9:37</t>
+          <t>6-Aug 9:33</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>12-Aug 10:16</t>
+          <t>12-Aug 15:33</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>12-Aug 10:15</t>
+          <t>12-Aug 15:31</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>12-Aug 10:15</t>
+          <t>12-Aug 15:31</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹21 (10.45%) 17 ↓ / 21 ↑</t>
+          <t>₹35 (17.41%) 17 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>12-Aug 10:22</t>
+          <t>12-Aug 15:37</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>12-Aug 10:19</t>
+          <t>12-Aug 15:33</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>12-Aug 10:24</t>
+          <t>12-Aug 15:35</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>12-Aug 10:17</t>
+          <t>12-Aug 15:28</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹35 (18.52%) 35 ↓ / 35 ↑</t>
+          <t>₹50 (26.46%) 35 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>12-Aug 10:20</t>
+          <t>12-Aug 15:32</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹21 (18.26%) 6 ↓ / 21 ↑</t>
+          <t>₹17 (14.78%) 6 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.04x</t>
+          <t>0.48x</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 21</t>
+          <t>12-Aug GMP: 17</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>12-Aug 10:23</t>
+          <t>12-Aug 15:36</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.02x</t>
+          <t>0.68x</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>12-Aug 10:16</t>
+          <t>12-Aug 15:28</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹67 (23.51%) 25 ↓ / 67 ↑</t>
+          <t>₹70 (24.56%) 25 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.16x</t>
+          <t>1.82x</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 67</t>
+          <t>12-Aug GMP: 70</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>12-Aug 10:18</t>
+          <t>12-Aug 15:31</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹31 (31.96%) 14 ↓ / 31 ↑</t>
+          <t>₹32 (32.99%) 14 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.08x</t>
+          <t>0.79x</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 31</t>
+          <t>12-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>12-Aug 10:20</t>
+          <t>12-Aug 15:35</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.07x</t>
+          <t>0.11x</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>12-Aug 10:21</t>
+          <t>12-Aug 15:34</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹22.5 (16.07%) 20.50 ↓ / 27 ↑</t>
+          <t>₹18 (12.86%) 18 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.03x</t>
+          <t>2.01x</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>12-Aug 10:18</t>
+          <t>12-Aug 15:34</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹9 (6.92%) 9 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.03x</t>
+          <t>0.08x</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>12-Aug 10:20</t>
+          <t>12-Aug 15:35</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹139 (17.22%) 127 ↓ / 220 ↑</t>
+          <t>₹136 (16.85%) 127 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4.19x</t>
+          <t>64.19x</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 139</t>
+          <t>12-Aug GMP: 136</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>12-Aug 10:19</t>
+          <t>12-Aug 15:32</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹258 (29.62%) 146 ↓ / 259 ↑</t>
+          <t>₹250 (28.70%) 146 ↓ / 259 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5.06x</t>
+          <t>68.68x</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 258</t>
+          <t>12-Aug GMP: 250</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>12-Aug 10:15</t>
+          <t>12-Aug 15:31</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>12-Aug 10:21</t>
+          <t>12-Aug 15:35</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
+          <t>₹12 (7.55%) 3 ↓ / 19.50 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>12-Aug 10:20</t>
+          <t>12-Aug 15:35</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹27 (12.74%) 10 ↓ / 30 ↑</t>
+          <t>₹35 (16.51%) 10 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>12-Aug 10:17</t>
+          <t>12-Aug 15:32</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>12-Aug 10:24</t>
+          <t>12-Aug 15:33</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOU</t>
+          <t>Gaja Alternative Asset Management IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -520,39 +520,39 @@
         </is>
       </c>
       <c r="E3" t="n">
+        <v>160</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹550.00 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>93</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹367.18 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>160</v>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>12-Aug 15:33</t>
+          <t>13-Aug 9:53</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -564,17 +564,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOU</t>
+          <t>Shankesh Jewellers IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹7 (7.53%) 7 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -583,15 +583,15 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>360</v>
+        <v>93</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>41</v>
+        <v>160</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>12-Aug 15:31</t>
+          <t>13-Aug 9:57</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -627,17 +627,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks IPOU</t>
+          <t>Sunshine Pictures IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹19 (5.28%) 17 ↓ / 19 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -646,39 +646,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>360</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹2600.00 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>250</v>
+        <v>41</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>12-Aug 15:31</t>
+          <t>13-Aug 9:57</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -690,17 +690,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOU</t>
+          <t>Horizon Industrial Parks IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹35 (17.41%) 17 ↓ / 35 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -709,15 +709,15 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>201</v>
+        <v>60</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹2600.00 Cr</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>74</v>
+        <v>250</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>12-Aug 15:37</t>
+          <t>13-Aug 10:00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -753,17 +753,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMEU</t>
+          <t>Lalithaa Jewellery Mart IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹41 (20.40%) 17 ↓ / 41 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -772,39 +772,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>92</v>
+        <v>201</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹33.14 Cr</t>
+          <t>₹1700.00 Cr</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1200</v>
+        <v>74</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>12-Aug 15:33</t>
+          <t>13-Aug 9:58</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>12-Aug 15:35</t>
+          <t>13-Aug 9:53</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 29 ↑</t>
+          <t>₹18 (13.64%) 12 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>12-Aug 15:28</t>
+          <t>13-Aug 10:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -942,17 +942,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Credent Connect NSE SMEU</t>
+          <t>ENS Enterprises BSE SMEU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹50 (26.46%) 35 ↓ / 50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -961,39 +961,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>189</v>
+        <v>92</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹93.90 Cr</t>
+          <t>₹33.14 Cr</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>12-Aug 15:32</t>
+          <t>13-Aug 9:59</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1005,101 +1005,101 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods BSE SMEO</t>
+          <t>Credent Connect NSE SMEO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹17 (14.78%) 6 ↓ / 21 ↑</t>
+          <t>₹50 (26.46%) 35 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.48x</t>
+          <t>0.05x</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹26.25 Cr</t>
+          <t>₹93.90 Cr</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 17</t>
+          <t>13-Aug GMP: 50</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>12-Aug 15:36</t>
+          <t>13-Aug 9:55</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMEO</t>
+          <t>Shiprocket IPOO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹34 (35.05%) 14 ↓ / 34 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.68x</t>
+          <t>1.2x</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
+          <t>₹1617.48 Cr</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1200</v>
+        <v>154</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 0</t>
+          <t>12-Aug GMP: 34</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>12-Aug 15:28</t>
+          <t>13-Aug 9:54</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1131,38 +1131,38 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOO</t>
+          <t>Q&amp;T Foods BSE SMEO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹70 (24.56%) 25 ↓ / 70 ↑</t>
+          <t>₹10 (8.70%) 6 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.82x</t>
+          <t>0.68x</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>285</v>
+        <v>115</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹26.25 Cr</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>52</v>
+        <v>1200</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 70</t>
+          <t>12-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1182,24 +1182,24 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>12-Aug 15:31</t>
+          <t>13-Aug 9:57</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shiprocket IPOO</t>
+          <t>Behari Lal Engineering IPOO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹32 (32.99%) 14 ↓ / 32 ↑</t>
+          <t>₹74 (25.96%) 25 ↓ / 74 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1209,23 +1209,23 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.79x</t>
+          <t>2.98x</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>97</v>
+        <v>285</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>154</v>
+        <v>52</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 32</t>
+          <t>12-Aug GMP: 74</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>12-Aug 15:35</t>
+          <t>13-Aug 9:54</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1257,7 +1257,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMEO</t>
+          <t>Pramodini Medicare NSE SMEO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1272,91 +1272,91 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.11x</t>
+          <t>0.78x</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹66.98 Cr</t>
+          <t>₹69.04 Cr</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>12-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>12-Aug 15:34</t>
+          <t>13-Aug 9:57</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food IPOO</t>
+          <t>Fascinate Textiles NSE SMECT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹18 (12.86%) 18 ↓ / 27 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.01x</t>
+          <t>0.13x</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹1553.00 Cr</t>
+          <t>₹66.98 Cr</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>107</v>
+        <v>800</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 22.5</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>13-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1371,19 +1371,19 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>12-Aug 15:34</t>
+          <t>13-Aug 10:01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sham Foam BSE SMEO</t>
+          <t>Sham Foam BSE SMECT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.08x</t>
+          <t>0.15x</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>13-Aug GMP: 9</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>12-Aug 15:35</t>
+          <t>13-Aug 10:02</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1446,12 +1446,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOCT</t>
+          <t>Milky Mist Dairy Food IPOCT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹136 (16.85%) 127 ↓ / 220 ↑</t>
+          <t>₹23 (16.43%) 20.50 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1461,43 +1461,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>64.19x</t>
+          <t>2.65x</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>807</v>
+        <v>140</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>₹939.70 Cr</t>
+          <t>₹1553.00 Cr</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 127</t>
+          <t>11-Aug GMP: 22.5</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 136</t>
+          <t>13-Aug GMP: 23</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>12-Aug 15:32</t>
+          <t>13-Aug 10:00</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1509,43 +1509,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOCT</t>
+          <t>Molbio Diagnostics IPOC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹250 (28.70%) 146 ↓ / 259 ↑</t>
+          <t>₹154 (19.08%) 127 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>68.68x</t>
+          <t>70.27x</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>871</v>
+        <v>807</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
+          <t>₹939.70 Cr</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 250</t>
+          <t>10-Aug GMP: 127</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 250</t>
+          <t>12-Aug GMP: 154</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>12-Aug 15:31</t>
+          <t>13-Aug 9:54</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1572,58 +1572,58 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Optimystix Entertainment NSE SMEC</t>
+          <t>Dhoot Transmission IPOC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 5 ↑</t>
+          <t>₹276 (31.69%) 146 ↓ / 276 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.05x</t>
+          <t>75.06x</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>175</v>
+        <v>871</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹108.50 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>800</v>
+        <v>17</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 0</t>
+          <t>10-Aug GMP: 250</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>12-Aug GMP: 276</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>12-Aug 15:35</t>
+          <t>13-Aug 9:54</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1635,7 +1635,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LEAP India IPOC</t>
+          <t>LEAP India IPOCAllotted</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>12-Aug 15:35</t>
+          <t>13-Aug 10:00</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1698,43 +1698,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Technocraft Ventures IPOC</t>
+          <t>Optimystix Entertainment NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹35 (16.51%) 10 ↓ / 35 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>38.69x</t>
+          <t>2.05x</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>212</v>
+        <v>175</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹251.88 Cr</t>
+          <t>₹108.50 Cr</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>70</v>
+        <v>800</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>7-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 29</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>12-Aug 15:32</t>
+          <t>13-Aug 9:58</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1761,58 +1761,58 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LAPL Automotive BSE SMECAllotted</t>
+          <t>Technocraft Ventures IPOCAllotted</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹47 (50.00%) 22 ↓ / 47 ↑</t>
+          <t>₹37 (17.45%) 10 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>344.31x</t>
+          <t>38.69x</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>94</v>
+        <v>212</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹32.40 Cr</t>
+          <t>₹251.88 Cr</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1200</v>
+        <v>70</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 32</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 39</t>
+          <t>11-Aug GMP: 29</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>12-Aug 15:33</t>
+          <t>13-Aug 9:59</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1824,58 +1824,58 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEL@158.00 (21.54%)</t>
+          <t>LAPL Automotive BSE SMELT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹25 (19.23%) 18 ↓ / 26 ↑</t>
+          <t>₹50 (53.19%) 22 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>169.26x</t>
+          <t>344.31x</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹32.40 Cr</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 25</t>
+          <t>6-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 26</t>
+          <t>10-Aug GMP: 39</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 25</t>
+          <t>13-Aug GMP: 50</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>12-Aug 9:32</t>
+          <t>13-Aug 9:36</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1887,43 +1887,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOL@72.00 (35.85%)</t>
+          <t>G.V. Electricals BSE SMEL@158.00 (21.54%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹17 (32.08%) 6.50 ↓ / 17 ↑</t>
+          <t>₹25 (19.23%) 18 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>138.83x</t>
+          <t>169.26x</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>281</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 15.25</t>
+          <t>31-Jul GMP: 25</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>7-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 17</t>
+          <t>12-Aug GMP: 25</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>12-Aug 9:35</t>
+          <t>12-Aug 9:32</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1950,58 +1950,58 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aegeus Technologies BSE SMEL@124.50 (18.57%)</t>
+          <t>Ardee Industries IPOL@72.00 (35.85%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹12 (11.43%) 12 ↓ / 12 ↑</t>
+          <t>₹17 (32.08%) 6.50 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>29.91x</t>
+          <t>138.83x</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹23.71 Cr</t>
+          <t>₹425.87 Cr</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1200</v>
+        <v>281</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>5-Aug GMP: 15.25</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 12</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 12</t>
+          <t>12-Aug GMP: 17</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>11-Aug 9:30</t>
+          <t>12-Aug 9:35</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2013,58 +2013,58 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Anawil Wire &amp; Engineering NSE SMEL@329.65 (22.09%)</t>
+          <t>Aegeus Technologies BSE SMEL@124.50 (18.57%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹58 (21.48%) 58 ↓ / 90 ↑</t>
+          <t>₹12 (11.43%) 12 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>149.13x</t>
+          <t>29.91x</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>270</v>
+        <v>105</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹177.81 Cr</t>
+          <t>₹23.71 Cr</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 80</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 78</t>
+          <t>6-Aug GMP: 12</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 58</t>
+          <t>11-Aug GMP: 12</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>10-Aug 9:32</t>
+          <t>11-Aug 9:30</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2076,58 +2076,58 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Fusion Klassroom Edutech BSE SMEL@170.00 (6.92%)</t>
+          <t>Anawil Wire &amp; Engineering NSE SMEL@329.65 (22.09%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
+          <t>₹58 (21.48%) 58 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.5x</t>
+          <t>149.13x</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>159</v>
+        <v>270</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹39.04 Cr</t>
+          <t>₹177.81 Cr</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 4</t>
+          <t>3-Aug GMP: 80</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>5-Aug GMP: 78</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 0</t>
+          <t>10-Aug GMP: 58</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>7-Aug 9:35</t>
+          <t>10-Aug 9:32</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2139,58 +2139,58 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MV Electrosystems IPOL@520.00 (22.35%)</t>
+          <t>Fusion Klassroom Edutech BSE SMEL@170.00 (6.92%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹109 (25.65%) 60 ↓ / 133 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>200.66x</t>
+          <t>1.5x</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>425</v>
+        <v>159</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹290.00 Cr</t>
+          <t>₹39.04 Cr</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>34</v>
+        <v>800</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 125</t>
+          <t>31-Jul GMP: 4</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 100</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 109</t>
+          <t>7-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>6-Aug 9:35</t>
+          <t>7-Aug 9:35</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2202,43 +2202,43 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Juniper Green Energy IPOL@245.00 (8.89%)</t>
+          <t>Oneindig Technologies BSE SMEL@120.00 (25%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹23 (10.22%) 1.50 ↓ / 23 ↑</t>
+          <t>₹7 (7.29%) 7 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.38x</t>
+          <t>1.73x</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>225</v>
+        <v>96</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹1800.00 Cr</t>
+          <t>₹27.65 Cr</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>66</v>
+        <v>1200</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 8</t>
+          <t>30-Jul GMP: 0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 9.5</t>
+          <t>3-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 23</t>
+          <t>6-Aug GMP: 7</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6-Aug 9:37</t>
+          <t>6-Aug 9:28</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2265,12 +2265,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dhaval Packaging BSE SMEL@110.00 (13.4%)</t>
+          <t>Juniper Green Energy IPOL@245.00 (8.89%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹12 (12.37%) 8 ↓ / 15 ↑</t>
+          <t>₹23 (10.22%) 1.50 ↓ / 23 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2280,28 +2280,28 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>49.99x</t>
+          <t>8.38x</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹36.36 Cr</t>
+          <t>₹1800.00 Cr</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1200</v>
+        <v>66</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 15</t>
+          <t>30-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 8</t>
+          <t>3-Aug GMP: 9.5</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 12</t>
+          <t>6-Aug GMP: 23</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>6-Aug 9:33</t>
+          <t>6-Aug 9:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2328,30 +2328,30 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Oneindig Technologies BSE SMEL@120.00 (25%)</t>
+          <t>Dhaval Packaging BSE SMEL@110.00 (13.4%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹7 (7.29%) 7 ↓ / 7 ↑</t>
+          <t>₹12 (12.37%) 8 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.73x</t>
+          <t>49.99x</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹27.65 Cr</t>
+          <t>₹36.36 Cr</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 0</t>
+          <t>30-Jul GMP: 15</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 0</t>
+          <t>3-Aug GMP: 8</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 7</t>
+          <t>6-Aug GMP: 12</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>6-Aug 9:28</t>
+          <t>6-Aug 9:33</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,12 +501,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOU</t>
+          <t>Skyways Air IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹19 (0.00%) 19 ↓ / 19 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -520,39 +520,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹550.00 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>93</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>13-Aug 9:53</t>
+          <t>13-Aug 15:32</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -564,17 +562,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOU</t>
+          <t>Gaja Alternative Asset Management IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹7 (7.53%) 7 ↓ / 7 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -583,39 +581,39 @@
         </is>
       </c>
       <c r="E4" t="n">
+        <v>160</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>₹550.00 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>93</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>₹367.18 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>160</v>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>13-Aug 9:57</t>
+          <t>13-Aug 15:30</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -632,7 +630,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹19 (5.28%) 17 ↓ / 19 ↑</t>
+          <t>₹25 (6.94%) 17 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -678,7 +676,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>13-Aug 9:57</t>
+          <t>13-Aug 15:28</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -690,17 +688,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks IPOU</t>
+          <t>Shankesh Jewellers IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹7 (7.53%) 7 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -709,39 +707,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹2600.00 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>13-Aug 10:00</t>
+          <t>13-Aug 15:33</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -753,17 +751,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOU</t>
+          <t>Horizon Industrial Parks IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹41 (20.40%) 17 ↓ / 41 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -772,15 +770,15 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>201</v>
+        <v>60</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹2600.00 Cr</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>74</v>
+        <v>250</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -804,7 +802,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>13-Aug 9:58</t>
+          <t>13-Aug 15:28</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -816,17 +814,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Skytech Infinite Platform NSE SMEU</t>
+          <t>Lalithaa Jewellery Mart IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹15 (7.46%) 15 ↓ / 41 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -835,44 +833,44 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹22.68 Cr</t>
+          <t>₹1700.00 Cr</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1600</v>
+        <v>74</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>13-Aug 9:53</t>
+          <t>13-Aug 15:34</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -884,7 +882,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹18 (13.64%) 12 ↓ / 29 ↑</t>
+          <t>₹22 (16.67%) 12 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -930,7 +928,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>13-Aug 10:02</t>
+          <t>13-Aug 15:32</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -942,7 +940,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMEU</t>
+          <t>Skytech Infinite Platform NSE SMEU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -961,15 +959,15 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹33.14 Cr</t>
+          <t>₹22.68 Cr</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -993,70 +991,70 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>13-Aug 9:59</t>
+          <t>13-Aug 15:36</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Credent Connect NSE SMEO</t>
+          <t>ENS Enterprises BSE SMEU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹50 (26.46%) 35 ↓ / 50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.05x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>189</v>
+        <v>92</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹93.90 Cr</t>
+          <t>₹33.14 Cr</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 50</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>13-Aug 9:55</t>
+          <t>13-Aug 15:37</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1068,12 +1066,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shiprocket IPOO</t>
+          <t>Credent Connect NSE SMEO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹34 (35.05%) 14 ↓ / 34 ↑</t>
+          <t>₹62 (32.80%) 35 ↓ / 62 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1083,43 +1081,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.2x</t>
+          <t>1.76x</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>97</v>
+        <v>189</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹93.90 Cr</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>154</v>
+        <v>600</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 34</t>
+          <t>13-Aug GMP: 62</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>13-Aug 9:54</t>
+          <t>13-Aug 15:28</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1136,7 +1134,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹10 (8.70%) 6 ↓ / 21 ↑</t>
+          <t>₹6 (5.22%) 6 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1146,7 +1144,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.68x</t>
+          <t>0.89x</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1182,7 +1180,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>13-Aug 9:57</t>
+          <t>13-Aug 15:31</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1194,38 +1192,38 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOO</t>
+          <t>Pramodini Medicare NSE SMEO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹74 (25.96%) 25 ↓ / 74 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.98x</t>
+          <t>0.88x</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>285</v>
+        <v>118</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹69.04 Cr</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>52</v>
+        <v>1200</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 74</t>
+          <t>12-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1245,7 +1243,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>13-Aug 9:54</t>
+          <t>13-Aug 15:36</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1257,38 +1255,38 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMEO</t>
+          <t>Shiprocket IPOO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹34 (35.05%) 14 ↓ / 34 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.78x</t>
+          <t>2.92x</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
+          <t>₹1617.48 Cr</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1200</v>
+        <v>154</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 0</t>
+          <t>12-Aug GMP: 34</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1308,7 +1306,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>13-Aug 9:57</t>
+          <t>13-Aug 15:37</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1320,106 +1318,106 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMECT</t>
+          <t>Behari Lal Engineering IPOO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹78 (27.37%) 25 ↓ / 78 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.13x</t>
+          <t>6.97x</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>156</v>
+        <v>285</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹66.98 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>800</v>
+        <v>52</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>12-Aug GMP: 74</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 0</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>13-Aug 10:01</t>
+          <t>13-Aug 15:35</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sham Foam BSE SMECT</t>
+          <t>Milky Mist Dairy Food IPOCT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹9 (6.92%) 9 ↓ / 9 ↑</t>
+          <t>₹30 (21.43%) 20.50 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.15x</t>
+          <t>58.51x</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹40.48 Cr</t>
+          <t>₹1553.00 Cr</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>107</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>11-Aug GMP: 22.5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 9</t>
+          <t>13-Aug GMP: 30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1434,55 +1432,55 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>13-Aug 10:02</t>
+          <t>13-Aug 15:35</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food IPOCT</t>
+          <t>Sham Foam BSE SMECT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹23 (16.43%) 20.50 ↓ / 27 ↑</t>
+          <t>₹4 (3.08%) 4 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.65x</t>
+          <t>2.19x</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>₹1553.00 Cr</t>
+          <t>₹40.48 Cr</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>107</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 22.5</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 23</t>
+          <t>13-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1497,118 +1495,118 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>13-Aug 10:00</t>
+          <t>13-Aug 15:28</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOC</t>
+          <t>Fascinate Textiles NSE SMECT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹154 (19.08%) 127 ↓ / 220 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>70.27x</t>
+          <t>0.4x</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>807</v>
+        <v>156</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹939.70 Cr</t>
+          <t>₹66.98 Cr</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>18</v>
+        <v>800</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 127</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 154</t>
+          <t>13-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>13-Aug 9:54</t>
+          <t>13-Aug 15:30</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOC</t>
+          <t>Molbio Diagnostics IPOC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹276 (31.69%) 146 ↓ / 276 ↑</t>
+          <t>₹156 (19.33%) 127 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>75.06x</t>
+          <t>70.27x</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>871</v>
+        <v>807</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
+          <t>₹939.70 Cr</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 250</t>
+          <t>10-Aug GMP: 127</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 276</t>
+          <t>12-Aug GMP: 154</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1623,7 +1621,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>13-Aug 9:54</t>
+          <t>13-Aug 15:30</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1635,58 +1633,58 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LEAP India IPOCAllotted</t>
+          <t>Dhoot Transmission IPOC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹12 (7.55%) 3 ↓ / 19.50 ↑</t>
+          <t>₹279 (32.03%) 146 ↓ / 279 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.82x</t>
+          <t>75.06x</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>159</v>
+        <v>871</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹2480.00 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>10-Aug GMP: 250</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 13</t>
+          <t>12-Aug GMP: 276</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>13-Aug 10:00</t>
+          <t>13-Aug 15:28</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1749,7 +1747,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>13-Aug 9:58</t>
+          <t>13-Aug 15:30</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1761,34 +1759,34 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Technocraft Ventures IPOCAllotted</t>
+          <t>LEAP India IPOCAllotted</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹37 (17.45%) 10 ↓ / 37 ↑</t>
+          <t>₹14 (8.81%) 3 ↓ / 19.50 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>38.69x</t>
+          <t>8.82x</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹251.88 Cr</t>
+          <t>₹2480.00 Cr</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1797,7 +1795,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 29</t>
+          <t>11-Aug GMP: 13</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1812,7 +1810,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>13-Aug 9:59</t>
+          <t>13-Aug 15:29</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1824,58 +1822,58 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LAPL Automotive BSE SMELT</t>
+          <t>Technocraft Ventures IPOCAllotted</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹50 (53.19%) 22 ↓ / 50 ↑</t>
+          <t>₹37 (17.45%) 10 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>344.31x</t>
+          <t>38.69x</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>94</v>
+        <v>212</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹32.40 Cr</t>
+          <t>₹251.88 Cr</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1200</v>
+        <v>70</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 32</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 39</t>
+          <t>11-Aug GMP: 29</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 50</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>13-Aug 9:36</t>
+          <t>13-Aug 15:29</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1887,58 +1885,58 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEL@158.00 (21.54%)</t>
+          <t>LAPL Automotive BSE SMEL@135.00 (43.62%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹25 (19.23%) 18 ↓ / 26 ↑</t>
+          <t>₹50 (53.19%) 22 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>169.26x</t>
+          <t>344.31x</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹32.40 Cr</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 25</t>
+          <t>6-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 26</t>
+          <t>10-Aug GMP: 39</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 25</t>
+          <t>13-Aug GMP: 50</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>12-Aug 9:32</t>
+          <t>13-Aug 9:36</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2013,12 +2011,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aegeus Technologies BSE SMEL@124.50 (18.57%)</t>
+          <t>G.V. Electricals BSE SMEL@158.00 (21.54%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹12 (11.43%) 12 ↓ / 12 ↑</t>
+          <t>₹25 (19.23%) 18 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2028,43 +2026,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>29.91x</t>
+          <t>169.26x</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹23.71 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>31-Jul GMP: 25</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 12</t>
+          <t>7-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 12</t>
+          <t>12-Aug GMP: 25</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>11-Aug 9:30</t>
+          <t>12-Aug 9:32</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2076,58 +2074,58 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Anawil Wire &amp; Engineering NSE SMEL@329.65 (22.09%)</t>
+          <t>Aegeus Technologies BSE SMEL@124.50 (18.57%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹58 (21.48%) 58 ↓ / 90 ↑</t>
+          <t>₹12 (11.43%) 12 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>149.13x</t>
+          <t>29.91x</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>270</v>
+        <v>105</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹177.81 Cr</t>
+          <t>₹23.71 Cr</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 80</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 78</t>
+          <t>6-Aug GMP: 12</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 58</t>
+          <t>11-Aug GMP: 12</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>10-Aug 9:32</t>
+          <t>11-Aug 9:30</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2139,58 +2137,58 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Fusion Klassroom Edutech BSE SMEL@170.00 (6.92%)</t>
+          <t>Anawil Wire &amp; Engineering NSE SMEL@329.65 (22.09%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
+          <t>₹58 (21.48%) 58 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.5x</t>
+          <t>149.13x</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>159</v>
+        <v>270</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹39.04 Cr</t>
+          <t>₹177.81 Cr</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 4</t>
+          <t>3-Aug GMP: 80</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>5-Aug GMP: 78</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 0</t>
+          <t>10-Aug GMP: 58</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>7-Aug 9:35</t>
+          <t>10-Aug 9:32</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2202,58 +2200,58 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Oneindig Technologies BSE SMEL@120.00 (25%)</t>
+          <t>Fusion Klassroom Edutech BSE SMEL@170.00 (6.92%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹7 (7.29%) 7 ↓ / 7 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.73x</t>
+          <t>1.5x</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>96</v>
+        <v>159</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹27.65 Cr</t>
+          <t>₹39.04 Cr</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 0</t>
+          <t>31-Jul GMP: 4</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 0</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 7</t>
+          <t>7-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6-Aug 9:28</t>
+          <t>7-Aug 9:35</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2265,12 +2263,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Juniper Green Energy IPOL@245.00 (8.89%)</t>
+          <t>Dhaval Packaging BSE SMEL@110.00 (13.4%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹23 (10.22%) 1.50 ↓ / 23 ↑</t>
+          <t>₹12 (12.37%) 8 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2280,28 +2278,28 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.38x</t>
+          <t>49.99x</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>225</v>
+        <v>97</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹1800.00 Cr</t>
+          <t>₹36.36 Cr</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>66</v>
+        <v>1200</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 8</t>
+          <t>30-Jul GMP: 15</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 9.5</t>
+          <t>3-Aug GMP: 8</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2311,12 +2309,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 23</t>
+          <t>6-Aug GMP: 12</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>6-Aug 9:37</t>
+          <t>6-Aug 9:33</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2328,12 +2326,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dhaval Packaging BSE SMEL@110.00 (13.4%)</t>
+          <t>Juniper Green Energy IPOL@245.00 (8.89%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹12 (12.37%) 8 ↓ / 15 ↑</t>
+          <t>₹23 (10.22%) 1.50 ↓ / 23 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2343,28 +2341,28 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>49.99x</t>
+          <t>8.38x</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹36.36 Cr</t>
+          <t>₹1800.00 Cr</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1200</v>
+        <v>66</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 15</t>
+          <t>30-Jul GMP: 8</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 8</t>
+          <t>3-Aug GMP: 9.5</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2374,12 +2372,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 12</t>
+          <t>6-Aug GMP: 23</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>6-Aug 9:33</t>
+          <t>6-Aug 9:37</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,12 +501,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Skyways Air IPOU</t>
+          <t>Dhanwel Hybrid Seeds BSE SMEU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹19 (0.00%) 19 ↓ / 19 ↑</t>
+          <t>₹-- (%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -520,49 +520,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>₹26.73 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1200</v>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>19-Aug</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>21-Aug</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>24-Aug</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>27-Aug</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>28-Aug</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>13-Aug 15:32</t>
+          <t>14-Aug 8:30</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOU</t>
+          <t>Mopshop Distribution BSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -581,15 +583,15 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹550.00 Cr</t>
+          <t>₹27.26 Cr</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>93</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -613,29 +615,29 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>13-Aug 15:30</t>
+          <t>14-Aug 9:33</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOU</t>
+          <t>Skyways Air IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹25 (6.94%) 17 ↓ / 25 ↑</t>
+          <t>₹19 (13.77%) 19 ↓ / 19 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -644,39 +646,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>360</v>
+        <v>138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹582.80 Cr</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>13-Aug 15:28</t>
+          <t>14-Aug 9:31</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -688,17 +690,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOU</t>
+          <t>Gaja Alternative Asset Management IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹7 (7.53%) 7 ↓ / 7 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -707,39 +709,39 @@
         </is>
       </c>
       <c r="E6" t="n">
+        <v>160</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>₹550.00 Cr</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>93</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>₹367.18 Cr</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>160</v>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>13-Aug 15:33</t>
+          <t>14-Aug 9:33</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -751,17 +753,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks IPOU</t>
+          <t>Sunshine Pictures IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹33 (9.17%) 17 ↓ / 33 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -770,39 +772,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>360</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹2600.00 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>250</v>
+        <v>41</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>13-Aug 15:28</t>
+          <t>14-Aug 9:37</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -814,12 +816,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOU</t>
+          <t>Shankesh Jewellers IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹15 (7.46%) 15 ↓ / 41 ↑</t>
+          <t>₹8 (8.60%) 7 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -833,39 +835,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>201</v>
+        <v>93</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>13-Aug 15:34</t>
+          <t>14-Aug 9:33</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -877,17 +879,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems BSE SMEU</t>
+          <t>Horizon Industrial Parks IPOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹22 (16.67%) 12 ↓ / 29 ↑</t>
+          <t>₹4.5 (7.50%) 4.50 ↓ / 4.50 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -896,39 +898,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹60.98 Cr</t>
+          <t>₹2600.00 Cr</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>13-Aug 15:32</t>
+          <t>14-Aug 9:35</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -940,17 +942,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Skytech Infinite Platform NSE SMEU</t>
+          <t>Lalithaa Jewellery Mart IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹38 (18.91%) 17 ↓ / 41 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -959,51 +961,51 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹22.68 Cr</t>
+          <t>₹1700.00 Cr</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1600</v>
+        <v>74</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>13-Aug 15:36</t>
+          <t>14-Aug 9:32</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMEU</t>
+          <t>Fascinate Textiles NSE SMEO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1018,106 +1020,98 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.41x</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹33.14 Cr</t>
+          <t>₹64.83 Cr</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>18-Aug</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
           <t>19-Aug</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>21-Aug</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>13-Aug 15:37</t>
+          <t>14-Aug 9:36</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Credent Connect NSE SMEO</t>
+          <t>ENS Enterprises BSE SMEO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹62 (32.80%) 35 ↓ / 62 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.76x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>189</v>
+        <v>92</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹93.90 Cr</t>
+          <t>₹33.14 Cr</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 62</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>13-Aug 15:28</t>
+          <t>14-Aug 9:34</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1129,58 +1123,58 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods BSE SMEO</t>
+          <t>Skytech Infinite Platform NSE SMEO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹6 (5.22%) 6 ↓ / 21 ↑</t>
+          <t>₹13 (16.88%) 13 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.89x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹26.25 Cr</t>
+          <t>₹22.68 Cr</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 10</t>
+          <t>14-Aug GMP: 13</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>13-Aug 15:31</t>
+          <t>14-Aug 9:34</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1192,58 +1186,58 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMEO</t>
+          <t>Technocrats Plasma Systems BSE SMEO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹22 (16.67%) 12 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.88x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
+          <t>₹60.98 Cr</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 0</t>
+          <t>14-Aug GMP: 22</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>13-Aug 15:36</t>
+          <t>14-Aug 9:35</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1255,12 +1249,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Shiprocket IPOO</t>
+          <t>Credent Connect NSE SMEO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹34 (35.05%) 14 ↓ / 34 ↑</t>
+          <t>₹75 (39.68%) 35 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1270,43 +1264,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.92x</t>
+          <t>2.18x</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>97</v>
+        <v>189</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹93.90 Cr</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>154</v>
+        <v>600</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 34</t>
+          <t>13-Aug GMP: 75</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>13-Aug 15:37</t>
+          <t>14-Aug 9:31</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1318,43 +1312,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOO</t>
+          <t>Q&amp;T Foods BSE SMECT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹78 (27.37%) 25 ↓ / 78 ↑</t>
+          <t>₹3 (2.61%) 3 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6.97x</t>
+          <t>0.94x</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>285</v>
+        <v>115</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹26.25 Cr</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>52</v>
+        <v>1200</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 74</t>
+          <t>12-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>14-Aug GMP: 3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1369,70 +1363,70 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>13-Aug 15:35</t>
+          <t>14-Aug 9:32</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food IPOCT</t>
+          <t>Pramodini Medicare NSE SMECT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹30 (21.43%) 20.50 ↓ / 30 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>58.51x</t>
+          <t>0.91x</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹1553.00 Cr</t>
+          <t>₹69.04 Cr</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>107</v>
+        <v>1200</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 22.5</t>
+          <t>12-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 30</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>13-Aug 15:35</t>
+          <t>14-Aug 9:35</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1444,138 +1438,138 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sham Foam BSE SMECT</t>
+          <t>Behari Lal Engineering IPOCT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹4 (3.08%) 4 ↓ / 9 ↑</t>
+          <t>₹80 (28.07%) 25 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.19x</t>
+          <t>8.47x</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>130</v>
+        <v>285</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>₹40.48 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>52</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>12-Aug GMP: 74</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 4</t>
+          <t>14-Aug GMP: 80</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>13-Aug 15:28</t>
+          <t>14-Aug 9:31</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMECT</t>
+          <t>Shiprocket IPOCT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹36.5 (37.63%) 14 ↓ / 36.50 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.4x</t>
+          <t>3.26x</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹66.98 Cr</t>
+          <t>₹1617.48 Cr</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>800</v>
+        <v>154</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>12-Aug GMP: 34</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 0</t>
+          <t>14-Aug GMP: 36.5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>13-Aug 15:30</t>
+          <t>14-Aug 9:34</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOC</t>
+          <t>Milky Mist Dairy Food IPOC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹156 (19.33%) 127 ↓ / 220 ↑</t>
+          <t>₹26 (18.57%) 20.50 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1585,43 +1579,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>70.27x</t>
+          <t>59.08x</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>807</v>
+        <v>140</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹939.70 Cr</t>
+          <t>₹1553.00 Cr</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 127</t>
+          <t>11-Aug GMP: 22.5</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 154</t>
+          <t>13-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>13-Aug 15:30</t>
+          <t>14-Aug 9:33</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1633,121 +1627,121 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOC</t>
+          <t>Sham Foam BSE SMEC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹279 (32.03%) 146 ↓ / 279 ↑</t>
+          <t>₹4 (3.08%) 4 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>75.06x</t>
+          <t>2.4x</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>871</v>
+        <v>130</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
+          <t>₹40.48 Cr</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 250</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 276</t>
+          <t>13-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>13-Aug 15:28</t>
+          <t>14-Aug 9:32</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Optimystix Entertainment NSE SMECAllotted</t>
+          <t>Molbio Diagnostics IPOCAllotted</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 5 ↑</t>
+          <t>₹156 (19.33%) 127 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.05x</t>
+          <t>70.27x</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>175</v>
+        <v>807</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹108.50 Cr</t>
+          <t>₹939.70 Cr</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>800</v>
+        <v>18</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 0</t>
+          <t>10-Aug GMP: 127</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>12-Aug GMP: 154</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>13-Aug 15:30</t>
+          <t>14-Aug 9:34</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1759,58 +1753,58 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LEAP India IPOCAllotted</t>
+          <t>Dhoot Transmission IPOCAllotted</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹14 (8.81%) 3 ↓ / 19.50 ↑</t>
+          <t>₹275 (31.57%) 146 ↓ / 276 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.82x</t>
+          <t>75.06x</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>159</v>
+        <v>871</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹2480.00 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>10-Aug GMP: 250</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 13</t>
+          <t>12-Aug GMP: 276</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>13-Aug 15:29</t>
+          <t>14-Aug 9:33</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1822,43 +1816,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Technocraft Ventures IPOCAllotted</t>
+          <t>Optimystix Entertainment NSE SMELT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹37 (17.45%) 10 ↓ / 37 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>38.69x</t>
+          <t>2.05x</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>212</v>
+        <v>175</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹251.88 Cr</t>
+          <t>₹108.50 Cr</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>70</v>
+        <v>800</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>7-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 29</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1868,12 +1862,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>13-Aug 15:29</t>
+          <t>14-Aug 9:35</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1885,58 +1879,58 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LAPL Automotive BSE SMEL@135.00 (43.62%)</t>
+          <t>Technocraft Ventures IPOLT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹50 (53.19%) 22 ↓ / 50 ↑</t>
+          <t>₹42 (19.81%) 10 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>344.31x</t>
+          <t>38.69x</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>94</v>
+        <v>212</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹32.40 Cr</t>
+          <t>₹251.88 Cr</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1200</v>
+        <v>70</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 32</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 39</t>
+          <t>11-Aug GMP: 29</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 50</t>
+          <t>14-Aug GMP: 42</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>13-Aug 9:36</t>
+          <t>14-Aug 9:28</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1948,58 +1942,58 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOL@72.00 (35.85%)</t>
+          <t>LEAP India IPOLT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹17 (32.08%) 6.50 ↓ / 17 ↑</t>
+          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>138.83x</t>
+          <t>8.82x</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>159</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
+          <t>₹2480.00 Cr</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>281</v>
+        <v>94</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 15.25</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>11-Aug GMP: 13</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 17</t>
+          <t>14-Aug GMP: 13</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>12-Aug 9:35</t>
+          <t>14-Aug 9:28</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2011,58 +2005,58 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEL@158.00 (21.54%)</t>
+          <t>LAPL Automotive BSE SMEL@135.00 (43.62%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹25 (19.23%) 18 ↓ / 26 ↑</t>
+          <t>₹50 (53.19%) 22 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>169.26x</t>
+          <t>344.31x</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹32.40 Cr</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 25</t>
+          <t>6-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 26</t>
+          <t>10-Aug GMP: 39</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 25</t>
+          <t>13-Aug GMP: 50</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>12-Aug 9:32</t>
+          <t>13-Aug 9:36</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2074,58 +2068,58 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aegeus Technologies BSE SMEL@124.50 (18.57%)</t>
+          <t>Ardee Industries IPOL@72.00 (35.85%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹12 (11.43%) 12 ↓ / 12 ↑</t>
+          <t>₹17 (32.08%) 6.50 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>29.91x</t>
+          <t>138.83x</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹23.71 Cr</t>
+          <t>₹425.87 Cr</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1200</v>
+        <v>281</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>5-Aug GMP: 15.25</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 12</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 12</t>
+          <t>12-Aug GMP: 17</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>11-Aug 9:30</t>
+          <t>12-Aug 9:35</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2137,58 +2131,58 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Anawil Wire &amp; Engineering NSE SMEL@329.65 (22.09%)</t>
+          <t>G.V. Electricals BSE SMEL@158.00 (21.54%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹58 (21.48%) 58 ↓ / 90 ↑</t>
+          <t>₹25 (19.23%) 18 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>149.13x</t>
+          <t>169.26x</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>270</v>
+        <v>130</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹177.81 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 80</t>
+          <t>31-Jul GMP: 25</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 78</t>
+          <t>7-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 58</t>
+          <t>12-Aug GMP: 25</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>10-Aug 9:32</t>
+          <t>12-Aug 9:32</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2200,58 +2194,58 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Fusion Klassroom Edutech BSE SMEL@170.00 (6.92%)</t>
+          <t>Aegeus Technologies BSE SMEL@124.50 (18.57%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
+          <t>₹12 (11.43%) 12 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.5x</t>
+          <t>29.91x</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>159</v>
+        <v>105</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹39.04 Cr</t>
+          <t>₹23.71 Cr</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 4</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>6-Aug GMP: 12</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 0</t>
+          <t>11-Aug GMP: 12</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>7-Aug 9:35</t>
+          <t>11-Aug 9:30</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2263,58 +2257,58 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dhaval Packaging BSE SMEL@110.00 (13.4%)</t>
+          <t>Anawil Wire &amp; Engineering NSE SMEL@329.65 (22.09%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹12 (12.37%) 8 ↓ / 15 ↑</t>
+          <t>₹58 (21.48%) 58 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>49.99x</t>
+          <t>149.13x</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>97</v>
+        <v>270</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹36.36 Cr</t>
+          <t>₹177.81 Cr</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 15</t>
+          <t>3-Aug GMP: 80</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 8</t>
+          <t>5-Aug GMP: 78</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 12</t>
+          <t>10-Aug GMP: 58</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>6-Aug 9:33</t>
+          <t>10-Aug 9:32</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2326,58 +2320,58 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Juniper Green Energy IPOL@245.00 (8.89%)</t>
+          <t>Fusion Klassroom Edutech BSE SMEL@170.00 (6.92%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹23 (10.22%) 1.50 ↓ / 23 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.38x</t>
+          <t>1.5x</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>225</v>
+        <v>159</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹1800.00 Cr</t>
+          <t>₹39.04 Cr</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>66</v>
+        <v>800</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>30-Jul GMP: 8</t>
+          <t>31-Jul GMP: 4</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 9.5</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 23</t>
+          <t>7-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>6-Aug 9:37</t>
+          <t>7-Aug 9:35</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,17 +501,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMEU</t>
+          <t>Skyways Air IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (%) 0 ↓ / 0 ↑</t>
+          <t>₹20 (14.49%) 19 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -520,51 +520,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹26.73 Cr</t>
+          <t>₹582.80 Cr</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1200</v>
+        <v>100</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>14-Aug 8:30</t>
+          <t>14-Aug 15:35</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mopshop Distribution BSE SMEU</t>
+          <t>Gaja Alternative Asset Management IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -583,15 +583,15 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹27.26 Cr</t>
+          <t>₹550.00 Cr</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>93</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -615,29 +615,29 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>14-Aug 9:33</t>
+          <t>14-Aug 15:28</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Skyways Air IPOU</t>
+          <t>Dhanwel Hybrid Seeds BSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹19 (13.77%) 19 ↓ / 19 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -646,61 +646,61 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹26.73 Cr</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>19-Aug</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>21-Aug</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>24-Aug</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>27-Aug</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>28-Aug</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>14-Aug 9:31</t>
+          <t>14-Aug 15:36</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOU</t>
+          <t>Mopshop Distribution BSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹10 (7.25%) 10 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -709,15 +709,15 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹550.00 Cr</t>
+          <t>₹27.26 Cr</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>93</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -741,24 +741,24 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>14-Aug 9:33</t>
+          <t>14-Aug 15:30</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOU</t>
+          <t>Shankesh Jewellers IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹33 (9.17%) 17 ↓ / 33 ↑</t>
+          <t>₹6 (6.45%) 6 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -772,15 +772,15 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>360</v>
+        <v>93</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>41</v>
+        <v>160</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>14-Aug 9:37</t>
+          <t>14-Aug 15:33</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -816,17 +816,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOU</t>
+          <t>Sunshine Pictures IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹8 (8.60%) 7 ↓ / 8 ↑</t>
+          <t>₹48 (13.33%) 17 ↓ / 48 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -835,15 +835,15 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>93</v>
+        <v>360</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹367.18 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>14-Aug 9:33</t>
+          <t>14-Aug 15:29</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>14-Aug 9:35</t>
+          <t>14-Aug 15:37</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹38 (18.91%) 17 ↓ / 41 ↑</t>
+          <t>₹35 (17.41%) 17 ↓ / 41 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>14-Aug 9:32</t>
+          <t>14-Aug 15:32</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.41x</t>
+          <t>0.44x</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1048,7 +1048,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>14-Aug 9:36</t>
+          <t>14-Aug 15:35</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.41x</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>14-Aug 9:34</t>
+          <t>14-Aug 15:29</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1123,12 +1123,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Skytech Infinite Platform NSE SMEO</t>
+          <t>Technocrats Plasma Systems BSE SMEO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹13 (16.88%) 13 ↓ / 13 ↑</t>
+          <t>₹20 (15.15%) 12 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1138,23 +1138,23 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.3x</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹22.68 Cr</t>
+          <t>₹60.98 Cr</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1600</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 13</t>
+          <t>14-Aug GMP: 20</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1174,24 +1174,24 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>14-Aug 9:34</t>
+          <t>14-Aug 15:29</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems BSE SMEO</t>
+          <t>Skytech Infinite Platform NSE SMEO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹22 (16.67%) 12 ↓ / 29 ↑</t>
+          <t>₹13 (16.88%) 13 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1201,23 +1201,23 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.39x</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹60.98 Cr</t>
+          <t>₹22.68 Cr</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 22</t>
+          <t>14-Aug GMP: 13</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>14-Aug 9:35</t>
+          <t>14-Aug 15:28</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.18x</t>
+          <t>10.3x</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>14-Aug 9:31</t>
+          <t>14-Aug 15:36</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1312,43 +1312,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods BSE SMECT</t>
+          <t>Shiprocket IPOCT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹3 (2.61%) 3 ↓ / 21 ↑</t>
+          <t>₹37 (38.14%) 14 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.94x</t>
+          <t>89.78x</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹26.25 Cr</t>
+          <t>₹1617.48 Cr</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1200</v>
+        <v>154</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 10</t>
+          <t>12-Aug GMP: 34</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 3</t>
+          <t>14-Aug GMP: 37</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1363,55 +1363,55 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>14-Aug 9:32</t>
+          <t>14-Aug 15:33</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMECT</t>
+          <t>Behari Lal Engineering IPOCT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹83 (29.12%) 25 ↓ / 83 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.91x</t>
+          <t>103.8x</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>118</v>
+        <v>285</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1200</v>
+        <v>52</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 0</t>
+          <t>12-Aug GMP: 74</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 83</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>14-Aug 9:35</t>
+          <t>14-Aug 15:30</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1438,43 +1438,43 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOCT</t>
+          <t>Pramodini Medicare NSE SMECT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹80 (28.07%) 25 ↓ / 80 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.47x</t>
+          <t>3.37x</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>285</v>
+        <v>118</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹69.04 Cr</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>52</v>
+        <v>1200</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 74</t>
+          <t>12-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 80</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>14-Aug 9:31</t>
+          <t>14-Aug 15:30</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1501,43 +1501,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Shiprocket IPOCT</t>
+          <t>Q&amp;T Foods BSE SMECT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹36.5 (37.63%) 14 ↓ / 36.50 ↑</t>
+          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3.26x</t>
+          <t>1.33x</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹26.25 Cr</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>154</v>
+        <v>1200</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 34</t>
+          <t>12-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 36.5</t>
+          <t>14-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1552,12 +1552,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>14-Aug 9:34</t>
+          <t>14-Aug 15:35</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹26 (18.57%) 20.50 ↓ / 27 ↑</t>
+          <t>₹24 (17.14%) 20.50 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>14-Aug 9:33</t>
+          <t>14-Aug 15:28</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>14-Aug 9:32</t>
+          <t>14-Aug 15:34</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1690,43 +1690,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOCAllotted</t>
+          <t>Dhoot Transmission IPOCAllotted</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹156 (19.33%) 127 ↓ / 220 ↑</t>
+          <t>₹266 (30.54%) 146 ↓ / 276 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>70.27x</t>
+          <t>75.06x</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>807</v>
+        <v>871</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹939.70 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 127</t>
+          <t>10-Aug GMP: 250</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 154</t>
+          <t>12-Aug GMP: 276</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>14-Aug 9:34</t>
+          <t>14-Aug 15:36</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1753,43 +1753,43 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOCAllotted</t>
+          <t>Molbio Diagnostics IPOCAllotted</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹275 (31.57%) 146 ↓ / 276 ↑</t>
+          <t>₹136 (16.85%) 127 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>75.06x</t>
+          <t>70.27x</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>871</v>
+        <v>807</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
+          <t>₹939.70 Cr</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 250</t>
+          <t>10-Aug GMP: 127</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 276</t>
+          <t>12-Aug GMP: 154</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>14-Aug 9:33</t>
+          <t>14-Aug 15:31</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1816,43 +1816,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Optimystix Entertainment NSE SMELT</t>
+          <t>Technocraft Ventures IPOL@284.00 (33.96%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 5 ↑</t>
+          <t>₹42 (19.81%) 10 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.05x</t>
+          <t>38.69x</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹108.50 Cr</t>
+          <t>₹251.88 Cr</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>800</v>
+        <v>70</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 0</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>11-Aug GMP: 29</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 42</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>14-Aug 9:35</t>
+          <t>14-Aug 9:28</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1879,34 +1879,34 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Technocraft Ventures IPOLT</t>
+          <t>LEAP India IPOL@165.90 (4.34%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹42 (19.81%) 10 ↓ / 42 ↑</t>
+          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>38.69x</t>
+          <t>8.82x</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹251.88 Cr</t>
+          <t>₹2480.00 Cr</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 29</t>
+          <t>11-Aug GMP: 13</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 42</t>
+          <t>14-Aug GMP: 13</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1942,43 +1942,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LEAP India IPOLT</t>
+          <t>Optimystix Entertainment NSE SMEL@180 (2.86%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.82x</t>
+          <t>2.05x</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹2480.00 Cr</t>
+          <t>₹108.50 Cr</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>94</v>
+        <v>800</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>7-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 13</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 13</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>14-Aug 9:28</t>
+          <t>14-Aug 9:35</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,17 +501,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Skyways Air IPOU</t>
+          <t>Tempsens Instruments (India) IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹20 (14.49%) 19 ↓ / 20 ↑</t>
+          <t>₹40 (0.00%) 40 ↓ / 40 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -519,40 +519,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>138</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹582.80 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>100</v>
-      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
+          <t>20-Aug</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>24-Aug</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>25-Aug</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>27-Aug</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>28-Aug</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>1-Sep</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>14-Aug 15:35</t>
+          <t>15-Aug 8:56</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -564,17 +560,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOU</t>
+          <t>Skyways Air IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹28 (20.29%) 19 ↓ / 28 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -582,40 +578,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>160</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹550.00 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>93</v>
+          <t>₹582.80 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>14-Aug 15:28</t>
+          <t>15-Aug 8:56</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMEU</t>
+          <t>Gaja Alternative Asset Management IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -645,16 +645,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>99</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹26.73 Cr</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1200</v>
+          <t>₹550.00 Cr</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -678,29 +682,29 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>14-Aug 15:36</t>
+          <t>15-Aug 9:01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mopshop Distribution BSE SMEU</t>
+          <t>Dhanwel Hybrid Seeds BSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹10 (7.25%) 10 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -708,16 +712,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>138</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹27.26 Cr</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1000</v>
+          <t>₹26.73 Cr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -741,7 +749,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>14-Aug 15:30</t>
+          <t>15-Aug 8:57</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -753,12 +761,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOU</t>
+          <t>Mopshop Distribution BSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹6 (6.45%) 6 ↓ / 8 ↑</t>
+          <t>₹10 (7.25%) 10 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -771,62 +779,66 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>93</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹367.18 Cr</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>160</v>
+          <t>₹27.26 Cr</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>14-Aug 15:33</t>
+          <t>15-Aug 9:01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOU</t>
+          <t>Shankesh Jewellers IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹48 (13.33%) 17 ↓ / 48 ↑</t>
+          <t>₹6 (6.45%) 6 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -834,16 +846,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>360</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>41</v>
+          <t>₹367.18 Cr</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -867,7 +883,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>14-Aug 15:29</t>
+          <t>15-Aug 8:54</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -879,17 +895,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks IPOU</t>
+          <t>Sunshine Pictures IPOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹4.5 (7.50%) 4.50 ↓ / 4.50 ↑</t>
+          <t>₹50 (13.89%) 17 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -897,40 +913,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>60</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹2600.00 Cr</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>250</v>
+          <t>₹282.14 Cr</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>14-Aug 15:37</t>
+          <t>15-Aug 8:53</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -942,17 +962,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOU</t>
+          <t>Horizon Industrial Parks IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹35 (17.41%) 17 ↓ / 41 ↑</t>
+          <t>₹4 (6.67%) 4 ↓ / 4.50 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -960,16 +980,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>201</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>74</v>
+          <t>₹2600.00 Cr</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -993,7 +1017,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>14-Aug 15:32</t>
+          <t>15-Aug 8:54</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1005,38 +1029,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMEO</t>
+          <t>Lalithaa Jewellery Mart IPOU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹24 (11.94%) 17 ↓ / 41 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.44x</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>151</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹64.83 Cr</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>800</v>
+          <t>₹1700.00 Cr</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1044,23 +1072,31 @@
           <t>19-Aug</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>20-Aug</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>24-Aug</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>14-Aug 15:35</t>
+          <t>15-Aug 8:56</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMEO</t>
+          <t>Fascinate Textiles NSE SMEO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1075,86 +1111,94 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.41x</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>92</v>
+          <t>0.51x</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹33.14 Cr</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>1200</v>
+          <t>₹64.83 Cr</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>14-Aug 15:29</t>
+          <t>15-Aug 8:53</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems BSE SMEO</t>
+          <t>ENS Enterprises BSE SMEO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹20 (15.15%) 12 ↓ / 29 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.3x</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>132</v>
+          <t>0.63x</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹60.98 Cr</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>1000</v>
+          <t>₹33.14 Cr</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 20</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1174,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>14-Aug 15:29</t>
+          <t>15-Aug 9:02</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1186,38 +1230,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Skytech Infinite Platform NSE SMEO</t>
+          <t>Technocrats Plasma Systems BSE SMEO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹13 (16.88%) 13 ↓ / 13 ↑</t>
+          <t>₹30 (22.73%) 12 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.39x</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>77</v>
+          <t>0.42x</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹22.68 Cr</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>1600</v>
+          <t>₹60.98 Cr</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 13</t>
+          <t>14-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1237,87 +1285,91 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>14-Aug 15:28</t>
+          <t>15-Aug 9:02</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Credent Connect NSE SMEO</t>
+          <t>Skytech Infinite Platform NSE SMEO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹75 (39.68%) 35 ↓ / 75 ↑</t>
+          <t>₹10 (12.99%) 10 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>10.3x</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>189</v>
+          <t>0.46x</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹93.90 Cr</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>600</v>
+          <t>₹22.68 Cr</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 75</t>
+          <t>14-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>14-Aug 15:36</t>
+          <t>15-Aug 8:57</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Shiprocket IPOCT</t>
+          <t>Credent Connect NSE SMEO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹37 (38.14%) 14 ↓ / 37 ↑</t>
+          <t>₹65 (34.39%) 35 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1327,43 +1379,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>89.78x</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>97</v>
+          <t>12.14x</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>154</v>
+          <t>₹93.90 Cr</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 34</t>
+          <t>13-Aug GMP: 75</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 37</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>14-Aug 15:33</t>
+          <t>15-Aug 9:02</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1375,12 +1431,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOCT</t>
+          <t>Shiprocket IPOC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹83 (29.12%) 25 ↓ / 83 ↑</t>
+          <t>₹34 (35.05%) 14 ↓ / 36.50 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1390,28 +1446,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>103.8x</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>285</v>
+          <t>102.28x</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>52</v>
+          <t>₹1617.48 Cr</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 74</t>
+          <t>12-Aug GMP: 34</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 83</t>
+          <t>14-Aug GMP: 34</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1426,7 +1486,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>14-Aug 15:30</t>
+          <t>15-Aug 8:57</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1438,106 +1498,114 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMECT</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>GMP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>Rating</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3.37x</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>118</v>
+          <t>Sub</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Price (₹)</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>1200</v>
+          <t>IPO Size</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 0</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>BoA Dt</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>14-Aug 15:30</t>
+          <t>Updated-On</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Anchor</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods BSE SMECT</t>
+          <t>Behari Lal Engineering IPOC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
+          <t>₹83 (29.12%) 25 ↓ / 83 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.33x</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>115</v>
+          <t>118.07x</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹26.25 Cr</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>1200</v>
+          <t>₹301.62 Cr</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 10</t>
+          <t>12-Aug GMP: 74</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 1</t>
+          <t>14-Aug GMP: 83</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1552,70 +1620,74 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>14-Aug 15:35</t>
+          <t>15-Aug 8:57</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food IPOC</t>
+          <t>Pramodini Medicare NSE SMEC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹24 (17.14%) 20.50 ↓ / 27 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>59.08x</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>140</v>
+          <t>3.87x</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹1553.00 Cr</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>107</v>
+          <t>₹69.04 Cr</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 22.5</t>
+          <t>12-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 26</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>14-Aug 15:28</t>
+          <t>15-Aug 9:01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1627,12 +1699,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sham Foam BSE SMEC</t>
+          <t>Q&amp;T Foods BSE SMEC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹4 (3.08%) 4 ↓ / 9 ↑</t>
+          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1642,43 +1714,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.4x</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>130</v>
+          <t>1.42x</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹40.48 Cr</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>1000</v>
+          <t>₹26.25 Cr</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>12-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 4</t>
+          <t>14-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>14-Aug 15:34</t>
+          <t>15-Aug 8:58</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1690,58 +1766,62 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOCAllotted</t>
+          <t>Milky Mist Dairy Food IPOCAllotted</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹266 (30.54%) 146 ↓ / 276 ↑</t>
+          <t>₹20.5 (14.64%) 20 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>75.06x</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>871</v>
+          <t>59.08x</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>17</v>
+          <t>₹1553.00 Cr</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 250</t>
+          <t>11-Aug GMP: 22.5</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 276</t>
+          <t>13-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>14-Aug 15:36</t>
+          <t>15-Aug 8:55</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1753,121 +1833,129 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOCAllotted</t>
+          <t>Sham Foam BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹136 (16.85%) 127 ↓ / 220 ↑</t>
+          <t>₹4 (3.08%) 4 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>70.27x</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>807</v>
+          <t>2.4x</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹939.70 Cr</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>18</v>
+          <t>₹40.48 Cr</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 127</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 154</t>
+          <t>13-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>14-Aug 15:31</t>
+          <t>15-Aug 8:59</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Technocraft Ventures IPOL@284.00 (33.96%)</t>
+          <t>Dhoot Transmission IPOCAllotted</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹42 (19.81%) 10 ↓ / 42 ↑</t>
+          <t>₹262 (30.08%) 146 ↓ / 276 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>38.69x</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>212</v>
+          <t>75.06x</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹251.88 Cr</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>70</v>
+          <t>₹3066.89 Cr</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>10-Aug GMP: 250</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 29</t>
+          <t>12-Aug GMP: 276</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 42</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>14-Aug 9:28</t>
+          <t>15-Aug 8:57</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1879,58 +1967,62 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LEAP India IPOL@165.90 (4.34%)</t>
+          <t>Molbio Diagnostics IPOCAllotted</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
+          <t>₹115 (14.25%) 115 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.82x</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>159</v>
+          <t>70.27x</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>807</t>
+        </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹2480.00 Cr</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>94</v>
+          <t>₹939.70 Cr</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>10-Aug GMP: 127</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 13</t>
+          <t>12-Aug GMP: 154</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 13</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>14-Aug 9:28</t>
+          <t>15-Aug 8:57</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1942,43 +2034,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Optimystix Entertainment NSE SMEL@180 (2.86%)</t>
+          <t>Technocraft Ventures IPOL@284.00 (33.96%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 5 ↑</t>
+          <t>₹42 (19.81%) 10 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.05x</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>175</v>
+          <t>38.69x</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹108.50 Cr</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>800</v>
+          <t>₹251.88 Cr</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 0</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>11-Aug GMP: 29</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1988,12 +2084,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 42</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>14-Aug 9:35</t>
+          <t>14-Aug 9:28</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2005,58 +2101,62 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LAPL Automotive BSE SMEL@135.00 (43.62%)</t>
+          <t>LEAP India IPOL@165.90 (4.34%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹50 (53.19%) 22 ↓ / 50 ↑</t>
+          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>344.31x</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>94</v>
+          <t>8.82x</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹32.40 Cr</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>1200</v>
+          <t>₹2480.00 Cr</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 32</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 39</t>
+          <t>11-Aug GMP: 13</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 50</t>
+          <t>14-Aug GMP: 13</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>13-Aug 9:36</t>
+          <t>14-Aug 9:28</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2068,58 +2168,62 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOL@72.00 (35.85%)</t>
+          <t>Optimystix Entertainment NSE SMEL@180 (2.86%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹17 (32.08%) 6.50 ↓ / 17 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>138.83x</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>53</v>
+          <t>2.05x</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>281</v>
+          <t>₹108.50 Cr</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 15.25</t>
+          <t>7-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 17</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>12-Aug 9:35</t>
+          <t>14-Aug 9:35</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2131,58 +2235,62 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEL@158.00 (21.54%)</t>
+          <t>LAPL Automotive BSE SMEL@135.00 (43.62%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹25 (19.23%) 18 ↓ / 26 ↑</t>
+          <t>₹50 (53.19%) 22 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>169.26x</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>130</v>
+          <t>344.31x</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>1000</v>
+          <t>₹32.40 Cr</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 25</t>
+          <t>6-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 26</t>
+          <t>10-Aug GMP: 39</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 25</t>
+          <t>13-Aug GMP: 50</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>12-Aug 9:32</t>
+          <t>13-Aug 9:36</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2194,58 +2302,62 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aegeus Technologies BSE SMEL@124.50 (18.57%)</t>
+          <t>Ardee Industries IPOL@72.00 (35.85%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹12 (11.43%) 12 ↓ / 12 ↑</t>
+          <t>₹17 (32.08%) 6.50 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>29.91x</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>105</v>
+          <t>138.83x</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹23.71 Cr</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>1200</v>
+          <t>₹425.87 Cr</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>5-Aug GMP: 15.25</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 12</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 12</t>
+          <t>12-Aug GMP: 17</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>11-Aug 9:30</t>
+          <t>12-Aug 9:35</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2257,58 +2369,62 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Anawil Wire &amp; Engineering NSE SMEL@329.65 (22.09%)</t>
+          <t>G.V. Electricals BSE SMEL@158.00 (21.54%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹58 (21.48%) 58 ↓ / 90 ↑</t>
+          <t>₹25 (19.23%) 18 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>149.13x</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>270</v>
+          <t>169.26x</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹177.81 Cr</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>400</v>
+          <t>₹42.25 Cr</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 80</t>
+          <t>31-Jul GMP: 25</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 78</t>
+          <t>7-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 58</t>
+          <t>12-Aug GMP: 25</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>10-Aug 9:32</t>
+          <t>12-Aug 9:32</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2320,61 +2436,132 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Fusion Klassroom Edutech BSE SMEL@170.00 (6.92%)</t>
+          <t>Aegeus Technologies BSE SMEL@124.50 (18.57%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
+          <t>₹12 (11.43%) 12 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.5x</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>159</v>
+          <t>29.91x</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹39.04 Cr</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>800</v>
+          <t>₹23.71 Cr</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 4</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>6-Aug GMP: 12</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 0</t>
+          <t>11-Aug GMP: 12</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>7-Aug 9:35</t>
+          <t>11-Aug 9:30</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Anawil Wire &amp; Engineering NSE SMEL@329.65 (22.09%)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>₹58 (21.48%) 58 ↓ / 90 ↑</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>149.13x</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>₹177.81 Cr</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>3-Aug GMP: 80</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5-Aug GMP: 78</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>6-Aug</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>10-Aug GMP: 58</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>10-Aug 9:32</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,17 +501,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOU</t>
+          <t>Skyways Air IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹40 (0.00%) 40 ↓ / 40 ↑</t>
+          <t>₹28 (20.29%) 19 ↓ / 28 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -521,34 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹582.80 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>15-Aug 8:56</t>
+          <t>15-Aug 14:58</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -560,17 +568,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Skyways Air IPOU</t>
+          <t>Tempsens Instruments (India) IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹28 (20.29%) 19 ↓ / 28 ↑</t>
+          <t>₹85 (0.00%) 85 ↓ / 85 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -580,42 +588,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>₹582.80 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
+          <t>20-Aug</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>24-Aug</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>25-Aug</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>27-Aug</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>28-Aug</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>1-Sep</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>15-Aug 8:56</t>
+          <t>15-Aug 14:53</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>15-Aug 9:01</t>
+          <t>15-Aug 14:59</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>15-Aug 8:57</t>
+          <t>15-Aug 14:57</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>15-Aug 9:01</t>
+          <t>15-Aug 14:56</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -828,17 +828,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOU</t>
+          <t>Sunshine Pictures IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹6 (6.45%) 6 ↓ / 8 ↑</t>
+          <t>₹50 (13.89%) 17 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹367.18 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>15-Aug 8:54</t>
+          <t>15-Aug 14:53</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -895,17 +895,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOU</t>
+          <t>Shankesh Jewellers IPOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹50 (13.89%) 17 ↓ / 50 ↑</t>
+          <t>₹6 (6.45%) 6 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -915,17 +915,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>15-Aug 8:53</t>
+          <t>15-Aug 14:55</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>15-Aug 8:54</t>
+          <t>15-Aug 14:53</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>15-Aug 8:56</t>
+          <t>15-Aug 14:56</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>15-Aug 8:53</t>
+          <t>15-Aug 14:56</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1163,42 +1163,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMEO</t>
+          <t>Technocrats Plasma Systems BSE SMEO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹32 (24.24%) 12 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.63x</t>
+          <t>0.42x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹33.14 Cr</t>
+          <t>₹60.98 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>15-Aug 9:02</t>
+          <t>15-Aug 14:55</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1230,42 +1230,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems BSE SMEO</t>
+          <t>ENS Enterprises BSE SMEO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹30 (22.73%) 12 ↓ / 30 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.42x</t>
+          <t>0.63x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹60.98 Cr</t>
+          <t>₹33.14 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 30</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>15-Aug 9:02</t>
+          <t>15-Aug 14:58</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>15-Aug 8:57</t>
+          <t>15-Aug 14:59</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹65 (34.39%) 35 ↓ / 75 ↑</t>
+          <t>₹55 (29.10%) 35 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>15-Aug 9:02</t>
+          <t>15-Aug 15:02</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1431,12 +1431,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Shiprocket IPOC</t>
+          <t>Behari Lal Engineering IPOC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹34 (35.05%) 14 ↓ / 36.50 ↑</t>
+          <t>₹83 (29.12%) 25 ↓ / 83 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>102.28x</t>
+          <t>118.07x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>285</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 34</t>
+          <t>12-Aug GMP: 74</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 34</t>
+          <t>14-Aug GMP: 83</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>15-Aug 8:57</t>
+          <t>15-Aug 15:00</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1565,12 +1565,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOC</t>
+          <t>Shiprocket IPOC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹83 (29.12%) 25 ↓ / 83 ↑</t>
+          <t>₹31 (31.96%) 14 ↓ / 36.50 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1580,32 +1580,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>118.07x</t>
+          <t>102.28x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹1617.48 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 74</t>
+          <t>12-Aug GMP: 34</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 83</t>
+          <t>14-Aug GMP: 34</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>15-Aug 8:57</t>
+          <t>15-Aug 14:59</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1632,12 +1632,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMEC</t>
+          <t>Q&amp;T Foods BSE SMEC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1647,17 +1647,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.87x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
+          <t>₹26.25 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 0</t>
+          <t>12-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1687,24 +1687,24 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>15-Aug 9:01</t>
+          <t>15-Aug 14:57</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods BSE SMEC</t>
+          <t>Pramodini Medicare NSE SMEC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1714,17 +1714,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>3.87x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹26.25 Cr</t>
+          <t>₹69.04 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1734,12 +1734,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 10</t>
+          <t>12-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 1</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1754,59 +1754,59 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>15-Aug 8:58</t>
+          <t>15-Aug 14:59</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food IPOCAllotted</t>
+          <t>Sham Foam BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹20.5 (14.64%) 20 ↓ / 27 ↑</t>
+          <t>₹6.5 (5.00%) 4 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>59.08x</t>
+          <t>2.4x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹1553.00 Cr</t>
+          <t>₹40.48 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 22.5</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 26</t>
+          <t>13-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1821,59 +1821,59 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>15-Aug 8:55</t>
+          <t>15-Aug 14:57</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sham Foam BSE SMECAllotted</t>
+          <t>Milky Mist Dairy Food IPOCAllotted</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹4 (3.08%) 4 ↓ / 9 ↑</t>
+          <t>₹16 (11.43%) 16 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.4x</t>
+          <t>59.08x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹40.48 Cr</t>
+          <t>₹1553.00 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>11-Aug GMP: 22.5</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 4</t>
+          <t>13-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>15-Aug 8:59</t>
+          <t>15-Aug 14:58</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹262 (30.08%) 146 ↓ / 276 ↑</t>
+          <t>₹260 (29.85%) 146 ↓ / 276 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>15-Aug 8:57</t>
+          <t>15-Aug 14:56</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>15-Aug 8:57</t>
+          <t>15-Aug 14:54</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2034,37 +2034,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Technocraft Ventures IPOL@284.00 (33.96%)</t>
+          <t>LEAP India IPOL@165.90 (4.34%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹42 (19.81%) 10 ↓ / 42 ↑</t>
+          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>38.69x</t>
+          <t>8.82x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>159</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹251.88 Cr</t>
+          <t>₹2480.00 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 29</t>
+          <t>11-Aug GMP: 13</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 42</t>
+          <t>14-Aug GMP: 13</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2101,37 +2101,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LEAP India IPOL@165.90 (4.34%)</t>
+          <t>Technocraft Ventures IPOL@284.00 (33.96%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
+          <t>₹42 (19.81%) 10 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.82x</t>
+          <t>38.69x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>212</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹2480.00 Cr</t>
+          <t>₹251.88 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 13</t>
+          <t>11-Aug GMP: 29</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 13</t>
+          <t>14-Aug GMP: 42</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2302,47 +2302,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOL@72.00 (35.85%)</t>
+          <t>G.V. Electricals BSE SMEL@158.00 (21.54%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹17 (32.08%) 6.50 ↓ / 17 ↑</t>
+          <t>₹25 (19.23%) 18 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>138.83x</t>
+          <t>169.26x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 15.25</t>
+          <t>31-Jul GMP: 25</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>7-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 17</t>
+          <t>12-Aug GMP: 25</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>12-Aug 9:35</t>
+          <t>12-Aug 9:32</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2369,47 +2369,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEL@158.00 (21.54%)</t>
+          <t>Ardee Industries IPOL@72.00 (35.85%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹25 (19.23%) 18 ↓ / 26 ↑</t>
+          <t>₹17 (32.08%) 6.50 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>169.26x</t>
+          <t>138.83x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹425.87 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>281</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 25</t>
+          <t>5-Aug GMP: 15.25</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 26</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 25</t>
+          <t>12-Aug GMP: 17</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>12-Aug 9:32</t>
+          <t>12-Aug 9:35</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>15-Aug 14:58</t>
+          <t>16-Aug 8:53</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>15-Aug 14:53</t>
+          <t>16-Aug 9:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>15-Aug 14:59</t>
+          <t>16-Aug 8:55</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>15-Aug 14:57</t>
+          <t>16-Aug 8:57</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>15-Aug 14:56</t>
+          <t>16-Aug 8:55</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹50 (13.89%) 17 ↓ / 50 ↑</t>
+          <t>₹53 (14.72%) 17 ↓ / 53 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>15-Aug 14:53</t>
+          <t>16-Aug 9:02</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>15-Aug 14:55</t>
+          <t>16-Aug 8:58</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>15-Aug 14:53</t>
+          <t>16-Aug 8:54</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹24 (11.94%) 17 ↓ / 41 ↑</t>
+          <t>₹26 (12.94%) 17 ↓ / 41 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>15-Aug 14:56</t>
+          <t>16-Aug 8:59</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>15-Aug 14:56</t>
+          <t>16-Aug 8:53</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>15-Aug 14:55</t>
+          <t>16-Aug 8:54</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>15-Aug 14:58</t>
+          <t>16-Aug 8:54</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>15-Aug 14:59</t>
+          <t>16-Aug 8:56</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>15-Aug 15:02</t>
+          <t>16-Aug 9:00</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>15-Aug 15:00</t>
+          <t>16-Aug 8:59</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹31 (31.96%) 14 ↓ / 36.50 ↑</t>
+          <t>₹32 (32.99%) 14 ↓ / 36.50 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>15-Aug 14:59</t>
+          <t>16-Aug 8:54</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>15-Aug 14:57</t>
+          <t>16-Aug 8:53</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>15-Aug 14:59</t>
+          <t>16-Aug 8:55</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹6.5 (5.00%) 4 ↓ / 9 ↑</t>
+          <t>₹9 (6.92%) 4 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>15-Aug 14:57</t>
+          <t>16-Aug 9:01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹16 (11.43%) 16 ↓ / 27 ↑</t>
+          <t>₹18.5 (13.21%) 18.50 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>15-Aug 14:58</t>
+          <t>16-Aug 9:01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹260 (29.85%) 146 ↓ / 276 ↑</t>
+          <t>₹255 (29.28%) 146 ↓ / 276 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>15-Aug 14:56</t>
+          <t>16-Aug 9:01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹115 (14.25%) 115 ↓ / 220 ↑</t>
+          <t>₹125 (15.49%) 115 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>15-Aug 14:54</t>
+          <t>16-Aug 9:01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16-Aug 8:53</t>
+          <t>16-Aug 15:01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>16-Aug 9:00</t>
+          <t>16-Aug 15:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>16-Aug 8:55</t>
+          <t>16-Aug 14:56</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>16-Aug 8:57</t>
+          <t>16-Aug 14:55</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>16-Aug 8:55</t>
+          <t>16-Aug 14:58</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>16-Aug 9:02</t>
+          <t>16-Aug 14:53</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹6 (6.45%) 6 ↓ / 8 ↑</t>
+          <t>₹5 (5.38%) 5 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>16-Aug 8:58</t>
+          <t>16-Aug 14:59</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>16-Aug 8:54</t>
+          <t>16-Aug 14:53</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>16-Aug 8:59</t>
+          <t>16-Aug 14:59</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>16-Aug 8:53</t>
+          <t>16-Aug 15:01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>16-Aug 8:54</t>
+          <t>16-Aug 14:59</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>16-Aug 8:54</t>
+          <t>16-Aug 14:54</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>16-Aug 8:56</t>
+          <t>16-Aug 14:55</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>16-Aug 9:00</t>
+          <t>16-Aug 14:56</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>16-Aug 8:59</t>
+          <t>16-Aug 15:00</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>16-Aug 8:54</t>
+          <t>16-Aug 15:00</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>16-Aug 8:53</t>
+          <t>16-Aug 15:02</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>16-Aug 8:55</t>
+          <t>16-Aug 14:55</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>16-Aug 9:01</t>
+          <t>16-Aug 15:01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹18.5 (13.21%) 18.50 ↓ / 27 ↑</t>
+          <t>₹18 (12.86%) 18 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>16-Aug 9:01</t>
+          <t>16-Aug 14:53</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹255 (29.28%) 146 ↓ / 276 ↑</t>
+          <t>₹252 (28.93%) 146 ↓ / 276 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>16-Aug 9:01</t>
+          <t>16-Aug 14:56</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>16-Aug 9:01</t>
+          <t>16-Aug 14:56</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,17 +501,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Skyways Air IPOU</t>
+          <t>ABH Healthcare NSE SMEU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹28 (20.29%) 19 ↓ / 28 ↑</t>
+          <t>₹-- (%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹34.98 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -541,22 +541,22 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>26-Aug</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>27-Aug</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>28-Aug</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16-Aug 15:01</t>
+          <t>17-Aug 8:30</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -568,17 +568,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOU</t>
+          <t>Skyways Air IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹85 (0.00%) 85 ↓ / 85 ↑</t>
+          <t>₹28 (20.29%) 19 ↓ / 28 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -588,34 +588,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>₹582.80 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>16-Aug 15:00</t>
+          <t>17-Aug 8:54</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -627,17 +635,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOU</t>
+          <t>Tempsens Instruments (India) IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹65 (21.67%) 65 ↓ / 85 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -647,42 +655,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹550.00 Cr</t>
+          <t>₹650.00 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>16-Aug 14:56</t>
+          <t>17-Aug 8:56</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -694,7 +702,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMEU</t>
+          <t>Gaja Alternative Asset Management IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -714,17 +722,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹26.73 Cr</t>
+          <t>₹550.00 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -749,29 +757,29 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>16-Aug 14:55</t>
+          <t>17-Aug 8:54</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mopshop Distribution BSE SMEU</t>
+          <t>Dhanwel Hybrid Seeds BSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹10 (7.25%) 10 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -781,17 +789,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹27.26 Cr</t>
+          <t>₹26.73 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -816,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>16-Aug 14:58</t>
+          <t>17-Aug 8:59</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -828,17 +836,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOU</t>
+          <t>Mopshop Distribution BSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹53 (14.72%) 17 ↓ / 53 ↑</t>
+          <t>₹10 (7.25%) 10 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -848,64 +856,64 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹27.26 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>16-Aug 14:53</t>
+          <t>17-Aug 9:00</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOU</t>
+          <t>Sunshine Pictures IPOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹5 (5.38%) 5 ↓ / 8 ↑</t>
+          <t>₹54 (15.00%) 17 ↓ / 54 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -915,17 +923,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹367.18 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -950,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>16-Aug 14:59</t>
+          <t>17-Aug 9:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -962,12 +970,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks IPOU</t>
+          <t>Shankesh Jewellers IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹4 (6.67%) 4 ↓ / 4.50 ↑</t>
+          <t>₹5 (5.38%) 5 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -982,42 +990,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹2600.00 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>16-Aug 14:53</t>
+          <t>17-Aug 8:59</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1029,17 +1037,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOU</t>
+          <t>Horizon Industrial Parks IPOO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹26 (12.94%) 17 ↓ / 41 ↑</t>
+          <t>₹3.5 (5.83%) 3.50 ↓ / 4.50 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1049,22 +1057,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹2600.00 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>17-Aug GMP: 3.5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1084,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>16-Aug 14:59</t>
+          <t>17-Aug 8:56</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1151,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>16-Aug 15:01</t>
+          <t>17-Aug 9:01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1163,62 +1171,62 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems BSE SMEO</t>
+          <t>Lalithaa Jewellery Mart IPOO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹32 (24.24%) 12 ↓ / 32 ↑</t>
+          <t>₹29.5 (14.68%) 17 ↓ / 41 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.42x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹60.98 Cr</t>
+          <t>₹1700.00 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 30</t>
+          <t>17-Aug GMP: 29.5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>16-Aug 14:59</t>
+          <t>17-Aug 8:57</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1230,42 +1238,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMEO</t>
+          <t>Technocrats Plasma Systems BSE SMEO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹32 (24.24%) 12 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.63x</t>
+          <t>0.42x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹33.14 Cr</t>
+          <t>₹60.98 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1285,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>16-Aug 14:54</t>
+          <t>17-Aug 9:00</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1297,42 +1305,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Skytech Infinite Platform NSE SMEO</t>
+          <t>ENS Enterprises BSE SMEO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹10 (12.99%) 10 ↓ / 13 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.46x</t>
+          <t>0.63x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹22.68 Cr</t>
+          <t>₹33.14 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 10</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1352,91 +1360,91 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>16-Aug 14:55</t>
+          <t>17-Aug 8:59</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Credent Connect NSE SMEO</t>
+          <t>Skytech Infinite Platform NSE SMEO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹55 (29.10%) 35 ↓ / 75 ↑</t>
+          <t>₹7 (9.09%) 7 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>12.14x</t>
+          <t>0.46x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹93.90 Cr</t>
+          <t>₹22.68 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 75</t>
+          <t>14-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>16-Aug 14:56</t>
+          <t>17-Aug 8:55</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOC</t>
+          <t>Credent Connect NSE SMECT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹83 (29.12%) 25 ↓ / 83 ↑</t>
+          <t>₹55 (29.10%) 35 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1446,47 +1454,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>118.07x</t>
+          <t>12.14x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹93.90 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 74</t>
+          <t>13-Aug GMP: 75</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 83</t>
+          <t>17-Aug GMP: 55</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>16-Aug 15:00</t>
+          <t>17-Aug 8:54</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1565,12 +1573,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Shiprocket IPOC</t>
+          <t>Behari Lal Engineering IPOC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹32 (32.99%) 14 ↓ / 36.50 ↑</t>
+          <t>₹84 (29.47%) 25 ↓ / 84 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1580,32 +1588,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>102.28x</t>
+          <t>118.07x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>285</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 34</t>
+          <t>12-Aug GMP: 74</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 34</t>
+          <t>14-Aug GMP: 83</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1620,7 +1628,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>16-Aug 15:00</t>
+          <t>17-Aug 8:56</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1632,47 +1640,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods BSE SMEC</t>
+          <t>Shiprocket IPOC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
+          <t>₹32 (32.99%) 14 ↓ / 36.50 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>102.28x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹26.25 Cr</t>
+          <t>₹1617.48 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 10</t>
+          <t>12-Aug GMP: 34</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 1</t>
+          <t>14-Aug GMP: 34</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1687,24 +1695,24 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>16-Aug 15:02</t>
+          <t>17-Aug 8:53</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMEC</t>
+          <t>Q&amp;T Foods BSE SMEC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1714,17 +1722,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.87x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
+          <t>₹26.25 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1734,12 +1742,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 0</t>
+          <t>12-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1754,126 +1762,126 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>16-Aug 14:55</t>
+          <t>17-Aug 8:54</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sham Foam BSE SMECAllotted</t>
+          <t>Pramodini Medicare NSE SMEC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹9 (6.92%) 4 ↓ / 9 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.4x</t>
+          <t>3.87x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹40.48 Cr</t>
+          <t>₹69.04 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>12-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 4</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>16-Aug 15:01</t>
+          <t>17-Aug 8:54</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food IPOCAllotted</t>
+          <t>Sham Foam BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹18 (12.86%) 18 ↓ / 27 ↑</t>
+          <t>₹6 (4.62%) 4 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>59.08x</t>
+          <t>2.4x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹1553.00 Cr</t>
+          <t>₹40.48 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 22.5</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 26</t>
+          <t>13-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1888,74 +1896,74 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>16-Aug 14:53</t>
+          <t>17-Aug 8:57</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOCAllotted</t>
+          <t>Milky Mist Dairy Food IPOCAllotted</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹252 (28.93%) 146 ↓ / 276 ↑</t>
+          <t>₹18 (12.86%) 18 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>75.06x</t>
+          <t>59.08x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
+          <t>₹1553.00 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 250</t>
+          <t>11-Aug GMP: 22.5</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 276</t>
+          <t>13-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>16-Aug 14:56</t>
+          <t>17-Aug 8:55</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1967,47 +1975,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOCAllotted</t>
+          <t>Dhoot Transmission IPOLT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹125 (15.49%) 115 ↓ / 220 ↑</t>
+          <t>₹262 (30.08%) 146 ↓ / 276 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>70.27x</t>
+          <t>75.06x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>871</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹939.70 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 127</t>
+          <t>10-Aug GMP: 250</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 154</t>
+          <t>12-Aug GMP: 276</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2017,12 +2025,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>17-Aug GMP: 262</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>16-Aug 14:56</t>
+          <t>17-Aug 8:54</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2034,62 +2042,62 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LEAP India IPOL@165.90 (4.34%)</t>
+          <t>Molbio Diagnostics IPOLT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
+          <t>₹116 (14.37%) 115 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.82x</t>
+          <t>70.27x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>807</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹2480.00 Cr</t>
+          <t>₹939.70 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>10-Aug GMP: 127</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 13</t>
+          <t>12-Aug GMP: 154</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 13</t>
+          <t>17-Aug GMP: 116</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>14-Aug 9:28</t>
+          <t>17-Aug 8:53</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2101,37 +2109,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Technocraft Ventures IPOL@284.00 (33.96%)</t>
+          <t>LEAP India IPOL@165.90 (4.34%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹42 (19.81%) 10 ↓ / 42 ↑</t>
+          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>38.69x</t>
+          <t>8.82x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>159</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹251.88 Cr</t>
+          <t>₹2480.00 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2141,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 29</t>
+          <t>11-Aug GMP: 13</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2151,7 +2159,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 42</t>
+          <t>14-Aug GMP: 13</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2168,47 +2176,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Optimystix Entertainment NSE SMEL@180 (2.86%)</t>
+          <t>Technocraft Ventures IPOL@284.00 (33.96%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 5 ↑</t>
+          <t>₹42 (19.81%) 10 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.05x</t>
+          <t>38.69x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>212</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹108.50 Cr</t>
+          <t>₹251.88 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 0</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>11-Aug GMP: 29</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2218,12 +2226,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 42</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>14-Aug 9:35</t>
+          <t>14-Aug 9:28</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2235,62 +2243,62 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LAPL Automotive BSE SMEL@135.00 (43.62%)</t>
+          <t>Optimystix Entertainment NSE SMEL@180 (2.86%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹50 (53.19%) 22 ↓ / 50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>344.31x</t>
+          <t>2.05x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>175</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹32.40 Cr</t>
+          <t>₹108.50 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 32</t>
+          <t>7-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 39</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 50</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>13-Aug 9:36</t>
+          <t>14-Aug 9:35</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2302,62 +2310,62 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEL@158.00 (21.54%)</t>
+          <t>LAPL Automotive BSE SMEL@135.00 (43.62%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹25 (19.23%) 18 ↓ / 26 ↑</t>
+          <t>₹50 (53.19%) 22 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>169.26x</t>
+          <t>344.31x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹32.40 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 25</t>
+          <t>6-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 26</t>
+          <t>10-Aug GMP: 39</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 25</t>
+          <t>13-Aug GMP: 50</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>12-Aug 9:32</t>
+          <t>13-Aug 9:36</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2369,47 +2377,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOL@72.00 (35.85%)</t>
+          <t>G.V. Electricals BSE SMEL@158.00 (21.54%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹17 (32.08%) 6.50 ↓ / 17 ↑</t>
+          <t>₹25 (19.23%) 18 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>138.83x</t>
+          <t>169.26x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 15.25</t>
+          <t>31-Jul GMP: 25</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>7-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2419,12 +2427,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 17</t>
+          <t>12-Aug GMP: 25</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>12-Aug 9:35</t>
+          <t>12-Aug 9:32</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2436,62 +2444,62 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Aegeus Technologies BSE SMEL@124.50 (18.57%)</t>
+          <t>Ardee Industries IPOL@72.00 (35.85%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹12 (11.43%) 12 ↓ / 12 ↑</t>
+          <t>₹17 (32.08%) 6.50 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>29.91x</t>
+          <t>138.83x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹23.71 Cr</t>
+          <t>₹425.87 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>281</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>5-Aug GMP: 15.25</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 12</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 12</t>
+          <t>12-Aug GMP: 17</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>11-Aug 9:30</t>
+          <t>12-Aug 9:35</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2503,62 +2511,62 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Anawil Wire &amp; Engineering NSE SMEL@329.65 (22.09%)</t>
+          <t>Aegeus Technologies BSE SMEL@124.50 (18.57%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹58 (21.48%) 58 ↓ / 90 ↑</t>
+          <t>₹12 (11.43%) 12 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>149.13x</t>
+          <t>29.91x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>105</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹177.81 Cr</t>
+          <t>₹23.71 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 80</t>
+          <t>4-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 78</t>
+          <t>6-Aug GMP: 12</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 58</t>
+          <t>11-Aug GMP: 12</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>10-Aug 9:32</t>
+          <t>11-Aug 9:30</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,17 +501,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ABH Healthcare NSE SMEU</t>
+          <t>Skyways Air IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (%) 0 ↓ / 0 ↑</t>
+          <t>₹30 (21.74%) 19 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹34.98 Cr</t>
+          <t>₹582.80 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -541,22 +541,22 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>17-Aug 8:30</t>
+          <t>17-Aug 15:00</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -568,17 +568,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Skyways Air IPOU</t>
+          <t>ABH Healthcare NSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹28 (20.29%) 19 ↓ / 28 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -588,17 +588,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹34.98 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,22 +608,22 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>26-Aug</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>27-Aug</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>28-Aug</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>17-Aug 8:54</t>
+          <t>17-Aug 14:58</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹65 (21.67%) 65 ↓ / 85 ↑</t>
+          <t>₹130 (43.33%) 65 ↓ / 130 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>17-Aug 8:56</t>
+          <t>17-Aug 14:59</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹9.1 (5.69%) 9.10 ↓ / 9.10 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>17-Aug 8:54</t>
+          <t>17-Aug 14:55</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>17-Aug 8:59</t>
+          <t>17-Aug 15:00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹10 (7.25%) 10 ↓ / 10 ↑</t>
+          <t>₹12 (8.70%) 10 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>17-Aug 9:00</t>
+          <t>17-Aug 14:56</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -903,17 +903,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOU</t>
+          <t>Shankesh Jewellers IPOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹54 (15.00%) 17 ↓ / 54 ↑</t>
+          <t>₹3 (3.23%) 3 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>17-Aug 9:02</t>
+          <t>17-Aug 14:56</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -970,17 +970,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOU</t>
+          <t>Sunshine Pictures IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹5 (5.38%) 5 ↓ / 8 ↑</t>
+          <t>₹62 (17.22%) 17 ↓ / 62 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -990,17 +990,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹367.18 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>17-Aug 8:59</t>
+          <t>17-Aug 15:01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1037,42 +1037,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks IPOO</t>
+          <t>Fascinate Textiles NSE SMEO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹3.5 (5.83%) 3.50 ↓ / 4.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.81x</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹2600.00 Cr</t>
+          <t>₹64.83 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 3.5</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1092,24 +1092,24 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>17-Aug 8:56</t>
+          <t>17-Aug 14:53</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMEO</t>
+          <t>Horizon Industrial Parks IPOO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1.5 (2.50%) 1.50 ↓ / 4.50 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,27 +1119,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.51x</t>
+          <t>0.14x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹64.83 Cr</t>
+          <t>₹2600.04 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>17-Aug GMP: 1.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>17-Aug 9:01</t>
+          <t>17-Aug 15:02</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹29.5 (14.68%) 17 ↓ / 41 ↑</t>
+          <t>₹35 (17.41%) 17 ↓ / 41 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.45x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 29.5</t>
+          <t>17-Aug GMP: 35</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>17-Aug 8:57</t>
+          <t>17-Aug 15:01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1238,42 +1238,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems BSE SMEO</t>
+          <t>Skytech Infinite Platform NSE SMEO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹32 (24.24%) 12 ↓ / 32 ↑</t>
+          <t>₹4 (5.19%) 4 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.42x</t>
+          <t>0.84x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹60.98 Cr</t>
+          <t>₹22.68 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 30</t>
+          <t>14-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>17-Aug 9:00</t>
+          <t>17-Aug 14:55</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.63x</t>
+          <t>1.12x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>17-Aug 8:59</t>
+          <t>17-Aug 15:00</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1372,42 +1372,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Skytech Infinite Platform NSE SMEO</t>
+          <t>Technocrats Plasma Systems BSE SMEO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹7 (9.09%) 7 ↓ / 13 ↑</t>
+          <t>₹30 (22.73%) 12 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.46x</t>
+          <t>3.95x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹22.68 Cr</t>
+          <t>₹60.98 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 10</t>
+          <t>14-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>17-Aug 8:55</t>
+          <t>17-Aug 14:56</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12.14x</t>
+          <t>130.04x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>17-Aug 8:54</t>
+          <t>17-Aug 14:58</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1573,47 +1573,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOC</t>
+          <t>Q&amp;T Foods BSE SMEC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹84 (29.47%) 25 ↓ / 84 ↑</t>
+          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>118.07x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹26.25 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 74</t>
+          <t>12-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 83</t>
+          <t>14-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1628,59 +1628,59 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>17-Aug 8:56</t>
+          <t>17-Aug 14:54</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shiprocket IPOC</t>
+          <t>Pramodini Medicare NSE SMEC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹32 (32.99%) 14 ↓ / 36.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>102.28x</t>
+          <t>3.87x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹69.04 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 34</t>
+          <t>12-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 34</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>17-Aug 8:53</t>
+          <t>17-Aug 14:58</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1707,47 +1707,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods BSE SMEC</t>
+          <t>Shiprocket IPOC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
+          <t>₹33.5 (34.54%) 14 ↓ / 36.50 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>102.28x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹26.25 Cr</t>
+          <t>₹1617.48 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 10</t>
+          <t>12-Aug GMP: 34</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 1</t>
+          <t>14-Aug GMP: 34</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1762,59 +1762,59 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>17-Aug 8:54</t>
+          <t>17-Aug 14:53</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMEC</t>
+          <t>Behari Lal Engineering IPOC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹95 (33.33%) 25 ↓ / 95 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3.87x</t>
+          <t>118.07x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>285</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 0</t>
+          <t>12-Aug GMP: 74</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 83</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>17-Aug 8:54</t>
+          <t>17-Aug 14:56</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹6 (4.62%) 4 ↓ / 9 ↑</t>
+          <t>₹4 (3.08%) 4 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>17-Aug 8:57</t>
+          <t>17-Aug 15:00</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹18 (12.86%) 18 ↓ / 27 ↑</t>
+          <t>₹19.25 (13.75%) 18 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>17-Aug 8:55</t>
+          <t>17-Aug 15:01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1975,47 +1975,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOLT</t>
+          <t>Molbio Diagnostics IPOL@980.00 (21.44%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹262 (30.08%) 146 ↓ / 276 ↑</t>
+          <t>₹116 (14.37%) 115 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>75.06x</t>
+          <t>70.27x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>807</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
+          <t>₹939.70 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 250</t>
+          <t>10-Aug GMP: 127</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 276</t>
+          <t>12-Aug GMP: 154</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 262</t>
+          <t>17-Aug GMP: 116</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>17-Aug 8:54</t>
+          <t>17-Aug 8:53</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2042,47 +2042,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOLT</t>
+          <t>Dhoot Transmission IPOL@1200.00 (37.77%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹116 (14.37%) 115 ↓ / 220 ↑</t>
+          <t>₹262 (30.08%) 146 ↓ / 276 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>70.27x</t>
+          <t>75.06x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>871</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹939.70 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 127</t>
+          <t>10-Aug GMP: 250</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 154</t>
+          <t>12-Aug GMP: 276</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 116</t>
+          <t>17-Aug GMP: 262</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>17-Aug 8:53</t>
+          <t>17-Aug 8:54</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2109,37 +2109,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LEAP India IPOL@165.90 (4.34%)</t>
+          <t>Technocraft Ventures IPOL@284.00 (33.96%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
+          <t>₹42 (19.81%) 10 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.82x</t>
+          <t>38.69x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>212</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹2480.00 Cr</t>
+          <t>₹251.88 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 13</t>
+          <t>11-Aug GMP: 29</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 13</t>
+          <t>14-Aug GMP: 42</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2176,47 +2176,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Technocraft Ventures IPOL@284.00 (33.96%)</t>
+          <t>Optimystix Entertainment NSE SMEL@180 (2.86%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹42 (19.81%) 10 ↓ / 42 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>38.69x</t>
+          <t>2.05x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>175</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹251.88 Cr</t>
+          <t>₹108.50 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>7-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 29</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 42</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>14-Aug 9:28</t>
+          <t>14-Aug 9:35</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2243,47 +2243,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Optimystix Entertainment NSE SMEL@180 (2.86%)</t>
+          <t>LEAP India IPOL@165.90 (4.34%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 5 ↑</t>
+          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.05x</t>
+          <t>8.82x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>159</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹108.50 Cr</t>
+          <t>₹2480.00 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 0</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>11-Aug GMP: 13</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 13</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>14-Aug 9:35</t>
+          <t>14-Aug 9:28</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2377,47 +2377,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEL@158.00 (21.54%)</t>
+          <t>Ardee Industries IPOL@72.00 (35.85%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹25 (19.23%) 18 ↓ / 26 ↑</t>
+          <t>₹17 (32.08%) 6.50 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>169.26x</t>
+          <t>138.83x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹425.87 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>281</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 25</t>
+          <t>5-Aug GMP: 15.25</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 26</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 25</t>
+          <t>12-Aug GMP: 17</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>12-Aug 9:32</t>
+          <t>12-Aug 9:35</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2444,47 +2444,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOL@72.00 (35.85%)</t>
+          <t>G.V. Electricals BSE SMEL@158.00 (21.54%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹17 (32.08%) 6.50 ↓ / 17 ↑</t>
+          <t>₹25 (19.23%) 18 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>138.83x</t>
+          <t>169.26x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 15.25</t>
+          <t>31-Jul GMP: 25</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>7-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 17</t>
+          <t>12-Aug GMP: 25</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>12-Aug 9:35</t>
+          <t>12-Aug 9:32</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,17 +501,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Skyways Air IPOU</t>
+          <t>Madhur Knit NSE SMEU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹30 (21.74%) 19 ↓ / 30 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹27.00 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>17-Aug 15:00</t>
+          <t>18-Aug 9:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -568,12 +568,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ABH Healthcare NSE SMEU</t>
+          <t>Sumax Engineering NSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -588,12 +588,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹34.98 Cr</t>
+          <t>₹53.40 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -603,27 +603,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>17-Aug 14:58</t>
+          <t>18-Aug 7:20</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -635,12 +635,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOU</t>
+          <t>Skyways Air IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹130 (43.33%) 65 ↓ / 130 ↑</t>
+          <t>₹31 (22.46%) 19 ↓ / 31 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -655,42 +655,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹582.80 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>17-Aug 14:59</t>
+          <t>18-Aug 8:55</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -702,17 +702,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOU</t>
+          <t>ABH Healthcare NSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹9.1 (5.69%) 9.10 ↓ / 9.10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -722,54 +722,54 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹550.00 Cr</t>
+          <t>₹34.98 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>17-Aug 14:55</t>
+          <t>18-Aug 8:54</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMEU</t>
+          <t>Augmont Enterprises IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -789,64 +789,64 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹26.73 Cr</t>
+          <t>₹825.00 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>17-Aug 15:00</t>
+          <t>18-Aug 8:56</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mopshop Distribution BSE SMEU</t>
+          <t>Tempsens Instruments (India) IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹12 (8.70%) 10 ↓ / 12 ↑</t>
+          <t>₹154 (51.33%) 65 ↓ / 154 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -856,59 +856,59 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹27.26 Cr</t>
+          <t>₹650.00 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>17-Aug 14:56</t>
+          <t>18-Aug 8:57</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOU</t>
+          <t>Dhanwel Hybrid Seeds BSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹3 (3.23%) 3 ↓ / 8 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -923,59 +923,59 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹367.18 Cr</t>
+          <t>₹26.73 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>17-Aug 14:56</t>
+          <t>18-Aug 8:57</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOU</t>
+          <t>Mopshop Distribution BSE SMEU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹62 (17.22%) 17 ↓ / 62 ↑</t>
+          <t>₹18 (13.04%) 10 ↓ / 18 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -990,59 +990,59 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹27.26 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>17-Aug 15:01</t>
+          <t>18-Aug 8:58</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMEO</t>
+          <t>Gaja Alternative Asset Management IPOU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹7 (4.38%) 7 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1052,114 +1052,114 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.81x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹64.83 Cr</t>
+          <t>₹550.00 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>17-Aug 14:53</t>
+          <t>18-Aug 8:53</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks IPOO</t>
+          <t>Sunshine Pictures IPOO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹1.5 (2.50%) 1.50 ↓ / 4.50 ↑</t>
+          <t>₹75 (20.83%) 17 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.14x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹2600.04 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 1.5</t>
+          <t>18-Aug GMP: 75</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>17-Aug 15:02</t>
+          <t>18-Aug 8:53</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1171,62 +1171,62 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOO</t>
+          <t>Shankesh Jewellers IPOO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹35 (17.41%) 17 ↓ / 41 ↑</t>
+          <t>₹2 (2.15%) 2 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.45x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 35</t>
+          <t>18-Aug GMP: 2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>17-Aug 15:01</t>
+          <t>18-Aug 8:56</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1238,62 +1238,62 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Skytech Infinite Platform NSE SMEO</t>
+          <t>Fascinate Textiles NSE SMEO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹4 (5.19%) 4 ↓ / 13 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.84x</t>
+          <t>0.86x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹22.68 Cr</t>
+          <t>₹64.83 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 10</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>17-Aug 14:55</t>
+          <t>18-Aug 8:57</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1305,12 +1305,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMEO</t>
+          <t>Horizon Industrial Parks IPOO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1.7 (2.83%) 1.70 ↓ / 4.50 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1320,47 +1320,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.12x</t>
+          <t>0.15x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹33.14 Cr</t>
+          <t>₹2600.04 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>17-Aug GMP: 1.7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>17-Aug 15:00</t>
+          <t>18-Aug 9:00</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1372,62 +1372,62 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems BSE SMEO</t>
+          <t>Lalithaa Jewellery Mart IPOO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹30 (22.73%) 12 ↓ / 32 ↑</t>
+          <t>₹30 (14.93%) 17 ↓ / 41 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3.95x</t>
+          <t>0.75x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹60.98 Cr</t>
+          <t>₹1700.00 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 30</t>
+          <t>17-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>17-Aug 14:56</t>
+          <t>18-Aug 9:02</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1439,62 +1439,62 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Credent Connect NSE SMECT</t>
+          <t>ENS Enterprises BSE SMECT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹55 (29.10%) 35 ↓ / 75 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>130.04x</t>
+          <t>1.43x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹93.90 Cr</t>
+          <t>₹33.14 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 75</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 55</t>
+          <t>18-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>17-Aug 14:58</t>
+          <t>18-Aug 8:56</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1573,79 +1573,79 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods BSE SMEC</t>
+          <t>Technocrats Plasma Systems BSE SMECT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
+          <t>₹30 (22.73%) 12 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>5.71x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹26.25 Cr</t>
+          <t>₹60.98 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 10</t>
+          <t>14-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 1</t>
+          <t>18-Aug GMP: 30</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>17-Aug 14:54</t>
+          <t>18-Aug 9:00</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMEC</t>
+          <t>Skytech Infinite Platform NSE SMECT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1 (1.30%) 1 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1655,64 +1655,64 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.87x</t>
+          <t>0.94x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
+          <t>₹22.68 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 0</t>
+          <t>14-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>18-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>17-Aug 14:58</t>
+          <t>18-Aug 8:54</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shiprocket IPOC</t>
+          <t>Credent Connect NSE SMEC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹33.5 (34.54%) 14 ↓ / 36.50 ↑</t>
+          <t>₹45 (23.81%) 35 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1722,47 +1722,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>102.28x</t>
+          <t>153.13x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹93.90 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 34</t>
+          <t>13-Aug GMP: 75</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 34</t>
+          <t>17-Aug GMP: 45</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>17-Aug 14:53</t>
+          <t>18-Aug 8:56</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1774,47 +1774,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOC</t>
+          <t>Pramodini Medicare NSE SMEC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹95 (33.33%) 25 ↓ / 95 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>118.07x</t>
+          <t>3.87x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹69.04 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 74</t>
+          <t>12-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 83</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>17-Aug 14:56</t>
+          <t>18-Aug 8:54</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1841,12 +1841,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sham Foam BSE SMECAllotted</t>
+          <t>Q&amp;T Foods BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹4 (3.08%) 4 ↓ / 9 ↑</t>
+          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1856,47 +1856,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.4x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹40.48 Cr</t>
+          <t>₹26.25 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>12-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 4</t>
+          <t>14-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>17-Aug 15:00</t>
+          <t>18-Aug 9:02</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1908,62 +1908,62 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food IPOCAllotted</t>
+          <t>Shiprocket IPOCAllotted</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹19.25 (13.75%) 18 ↓ / 27 ↑</t>
+          <t>₹33.5 (34.54%) 14 ↓ / 36.50 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>59.08x</t>
+          <t>102.28x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹1553.00 Cr</t>
+          <t>₹1617.48 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 22.5</t>
+          <t>12-Aug GMP: 34</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 26</t>
+          <t>14-Aug GMP: 34</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>17-Aug 15:01</t>
+          <t>18-Aug 8:55</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1975,62 +1975,62 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOL@980.00 (21.44%)</t>
+          <t>Behari Lal Engineering IPOCAllotted</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹116 (14.37%) 115 ↓ / 220 ↑</t>
+          <t>₹105 (36.84%) 25 ↓ / 105 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>70.27x</t>
+          <t>118.07x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>285</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹939.70 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 127</t>
+          <t>12-Aug GMP: 74</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 154</t>
+          <t>14-Aug GMP: 83</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 116</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>17-Aug 8:53</t>
+          <t>18-Aug 8:57</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2042,79 +2042,79 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOL@1200.00 (37.77%)</t>
+          <t>Sham Foam BSE SMELT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹262 (30.08%) 146 ↓ / 276 ↑</t>
+          <t>₹1.5 (1.15%) 1.50 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>75.06x</t>
+          <t>2.4x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
+          <t>₹40.48 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 250</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 276</t>
+          <t>13-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 262</t>
+          <t>18-Aug GMP: 1.5</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>17-Aug 8:54</t>
+          <t>18-Aug 8:54</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Technocraft Ventures IPOL@284.00 (33.96%)</t>
+          <t>Milky Mist Dairy Food IPOLT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹42 (19.81%) 10 ↓ / 42 ↑</t>
+          <t>₹19.7 (14.07%) 18 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2124,47 +2124,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>38.69x</t>
+          <t>59.08x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹251.88 Cr</t>
+          <t>₹1553.00 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>11-Aug GMP: 22.5</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 29</t>
+          <t>13-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 42</t>
+          <t>18-Aug GMP: 19.7</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>14-Aug 9:28</t>
+          <t>18-Aug 9:02</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2176,62 +2176,62 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Optimystix Entertainment NSE SMEL@180 (2.86%)</t>
+          <t>Dhoot Transmission IPOL@1200.00 (37.77%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 5 ↑</t>
+          <t>₹262 (30.08%) 146 ↓ / 276 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.05x</t>
+          <t>75.06x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>871</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹108.50 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 0</t>
+          <t>10-Aug GMP: 250</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>12-Aug GMP: 276</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>17-Aug GMP: 262</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>14-Aug 9:35</t>
+          <t>17-Aug 8:54</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2243,62 +2243,62 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LEAP India IPOL@165.90 (4.34%)</t>
+          <t>Molbio Diagnostics IPOL@980.00 (21.44%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
+          <t>₹116 (14.37%) 115 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.82x</t>
+          <t>70.27x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>807</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹2480.00 Cr</t>
+          <t>₹939.70 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>10-Aug GMP: 127</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 13</t>
+          <t>12-Aug GMP: 154</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 13</t>
+          <t>17-Aug GMP: 116</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>14-Aug 9:28</t>
+          <t>17-Aug 8:53</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2310,62 +2310,62 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LAPL Automotive BSE SMEL@135.00 (43.62%)</t>
+          <t>LEAP India IPOL@165.90 (4.34%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹50 (53.19%) 22 ↓ / 50 ↑</t>
+          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>344.31x</t>
+          <t>8.82x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>₹2480.00 Cr</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>₹32.40 Cr</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 32</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 39</t>
+          <t>11-Aug GMP: 13</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 50</t>
+          <t>14-Aug GMP: 13</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>13-Aug 9:36</t>
+          <t>14-Aug 9:28</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2377,62 +2377,62 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ardee Industries IPOL@72.00 (35.85%)</t>
+          <t>Technocraft Ventures IPOL@284.00 (33.96%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹17 (32.08%) 6.50 ↓ / 17 ↑</t>
+          <t>₹42 (19.81%) 10 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>138.83x</t>
+          <t>38.69x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>212</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹425.87 Cr</t>
+          <t>₹251.88 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 15.25</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>11-Aug GMP: 29</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 17</t>
+          <t>14-Aug GMP: 42</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>12-Aug 9:35</t>
+          <t>14-Aug 9:28</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2444,62 +2444,62 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEL@158.00 (21.54%)</t>
+          <t>Optimystix Entertainment NSE SMEL@180 (2.86%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹25 (19.23%) 18 ↓ / 26 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>169.26x</t>
+          <t>2.05x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>175</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹42.25 Cr</t>
+          <t>₹108.50 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>31-Jul GMP: 25</t>
+          <t>7-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 26</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 25</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>12-Aug 9:32</t>
+          <t>14-Aug 9:35</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2511,32 +2511,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Aegeus Technologies BSE SMEL@124.50 (18.57%)</t>
+          <t>LAPL Automotive BSE SMEL@135.00 (43.62%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹12 (11.43%) 12 ↓ / 12 ↑</t>
+          <t>₹50 (53.19%) 22 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>29.91x</t>
+          <t>344.31x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹23.71 Cr</t>
+          <t>₹32.40 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2546,27 +2546,27 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4-Aug GMP: 0</t>
+          <t>6-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 12</t>
+          <t>10-Aug GMP: 39</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>11-Aug</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 12</t>
+          <t>13-Aug GMP: 50</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>11-Aug 9:30</t>
+          <t>13-Aug 9:36</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,12 +501,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Madhur Knit NSE SMEU</t>
+          <t>Kwick Forensic Solutions BSE SMEU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -519,44 +519,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹27.00 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>18-Aug 9:02</t>
+          <t>18-Aug 13:00</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -573,12 +565,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (%) 0 ↓ / 0 ↑</t>
+          <t>₹10 (9.90%) 10 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -623,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>18-Aug 7:20</t>
+          <t>18-Aug 15:01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -635,17 +627,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Skyways Air IPOU</t>
+          <t>Madhur Knit NSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹31 (22.46%) 19 ↓ / 31 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -655,17 +647,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹27.00 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -690,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>18-Aug 8:55</t>
+          <t>18-Aug 14:54</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -702,17 +694,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ABH Healthcare NSE SMEU</t>
+          <t>Skyways Air IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹31 (22.46%) 19 ↓ / 31 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -722,17 +714,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹34.98 Cr</t>
+          <t>₹582.80 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -742,34 +734,34 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>18-Aug 8:54</t>
+          <t>18-Aug 14:58</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOU</t>
+          <t>ABH Healthcare NSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -789,32 +781,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹825.00 Cr</t>
+          <t>₹34.98 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -824,29 +816,29 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>18-Aug 8:56</t>
+          <t>18-Aug 15:00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOU</t>
+          <t>Augmont Enterprises IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹154 (51.33%) 65 ↓ / 154 ↑</t>
+          <t>₹165 (20.94%) 165 ↓ / 165 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -856,42 +848,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹825.00 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>18-Aug 8:57</t>
+          <t>18-Aug 15:01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -903,17 +895,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMEU</t>
+          <t>Tempsens Instruments (India) IPOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹158 (52.67%) 65 ↓ / 158 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -923,47 +915,47 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹26.73 Cr</t>
+          <t>₹650.00 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>18-Aug 8:57</t>
+          <t>18-Aug 15:00</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1017,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>18-Aug 8:58</t>
+          <t>18-Aug 14:59</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1037,12 +1029,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOU</t>
+          <t>Dhanwel Hybrid Seeds BSE SMEU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹7 (4.38%) 7 ↓ / 7 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1057,17 +1049,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹550.00 Cr</t>
+          <t>₹26.73 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1092,29 +1084,29 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>18-Aug 8:53</t>
+          <t>18-Aug 14:58</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOO</t>
+          <t>Gaja Alternative Asset Management IPOU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹75 (20.83%) 17 ↓ / 75 ↑</t>
+          <t>₹5 (3.12%) 5 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1124,42 +1116,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹550.00 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 75</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>18-Aug 8:53</t>
+          <t>18-Aug 14:56</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1171,42 +1163,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOO</t>
+          <t>Sunshine Pictures IPOO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹2 (2.15%) 2 ↓ / 8 ↑</t>
+          <t>₹75 (20.83%) 17 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.24x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹367.18 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 2</t>
+          <t>18-Aug GMP: 75</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>18-Aug 8:56</t>
+          <t>18-Aug 14:56</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1238,12 +1230,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMEO</t>
+          <t>Shankesh Jewellers IPOO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹4 (4.30%) 2 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1253,64 +1245,64 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.86x</t>
+          <t>0.25x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹64.83 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>18-Aug GMP: 4</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>18-Aug 8:57</t>
+          <t>18-Aug 15:02</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks IPOO</t>
+          <t>Fascinate Textiles NSE SMEO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹1.7 (2.83%) 1.70 ↓ / 4.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1320,27 +1312,27 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.15x</t>
+          <t>0.92x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹2600.04 Cr</t>
+          <t>₹64.83 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 1.7</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1360,12 +1352,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>18-Aug 9:00</t>
+          <t>18-Aug 15:01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1369,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹30 (14.93%) 17 ↓ / 41 ↑</t>
+          <t>₹33 (16.42%) 17 ↓ / 41 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1387,7 +1379,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.75x</t>
+          <t>2.71x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1427,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>18-Aug 9:02</t>
+          <t>18-Aug 14:59</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1439,12 +1431,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMECT</t>
+          <t>Horizon Industrial Parks IPOO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1.25 (2.08%) 1.25 ↓ / 4.50 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1454,47 +1446,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.43x</t>
+          <t>0.2x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹33.14 Cr</t>
+          <t>₹2600.04 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>17-Aug GMP: 1.7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 0</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>18-Aug 8:56</t>
+          <t>18-Aug 15:02</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1578,7 +1570,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹30 (22.73%) 12 ↓ / 32 ↑</t>
+          <t>₹43 (32.58%) 12 ↓ / 43 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1588,7 +1580,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5.71x</t>
+          <t>152.88x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1613,7 +1605,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 30</t>
+          <t>18-Aug GMP: 43</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1628,7 +1620,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>18-Aug 9:00</t>
+          <t>18-Aug 14:55</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1655,7 +1647,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.94x</t>
+          <t>1.85x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1695,7 +1687,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>18-Aug 8:54</t>
+          <t>18-Aug 14:59</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1707,62 +1699,62 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Credent Connect NSE SMEC</t>
+          <t>ENS Enterprises BSE SMECT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹45 (23.81%) 35 ↓ / 75 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>153.13x</t>
+          <t>8.41x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹93.90 Cr</t>
+          <t>₹33.14 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 75</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 45</t>
+          <t>18-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>18-Aug 8:56</t>
+          <t>18-Aug 14:53</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1774,62 +1766,62 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMEC</t>
+          <t>Credent Connect NSE SMEC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹45 (23.81%) 35 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3.87x</t>
+          <t>153.13x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
+          <t>₹93.90 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 0</t>
+          <t>13-Aug GMP: 75</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>17-Aug GMP: 45</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>18-Aug 8:54</t>
+          <t>18-Aug 15:01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1841,12 +1833,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods BSE SMECAllotted</t>
+          <t>Pramodini Medicare NSE SMEC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1856,17 +1848,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>3.87x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹26.25 Cr</t>
+          <t>₹69.04 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1876,12 +1868,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 10</t>
+          <t>12-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 1</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1896,12 +1888,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>18-Aug 9:02</t>
+          <t>18-Aug 14:58</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1905,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹33.5 (34.54%) 14 ↓ / 36.50 ↑</t>
+          <t>₹34.75 (35.82%) 14 ↓ / 36.50 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1963,7 +1955,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>18-Aug 8:55</t>
+          <t>18-Aug 14:58</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1980,7 +1972,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹105 (36.84%) 25 ↓ / 105 ↑</t>
+          <t>₹121 (42.46%) 25 ↓ / 121 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2030,7 +2022,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>18-Aug 8:57</t>
+          <t>18-Aug 14:57</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2042,12 +2034,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sham Foam BSE SMELT</t>
+          <t>Q&amp;T Foods BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹1.5 (1.15%) 1.50 ↓ / 9 ↑</t>
+          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2057,47 +2049,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.4x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹40.48 Cr</t>
+          <t>₹26.25 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>12-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 4</t>
+          <t>14-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 1.5</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>18-Aug 8:54</t>
+          <t>18-Aug 14:53</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2109,7 +2101,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food IPOLT</t>
+          <t>Milky Mist Dairy Food IPOL@165.00 (17.86%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2164,7 +2156,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>18-Aug 9:02</t>
+          <t>18-Aug 9:34</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2176,67 +2168,67 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOL@1200.00 (37.77%)</t>
+          <t>Sham Foam BSE SMEL@104.00 (-20%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹262 (30.08%) 146 ↓ / 276 ↑</t>
+          <t>₹1.5 (1.15%) 1.50 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>75.06x</t>
+          <t>2.4x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
+          <t>₹40.48 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 250</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 276</t>
+          <t>13-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 262</t>
+          <t>18-Aug GMP: 1.5</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>17-Aug 8:54</t>
+          <t>18-Aug 9:28</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -2310,62 +2302,62 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LEAP India IPOL@165.90 (4.34%)</t>
+          <t>Dhoot Transmission IPOL@1200.00 (37.77%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
+          <t>₹262 (30.08%) 146 ↓ / 276 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.82x</t>
+          <t>75.06x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>871</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹2480.00 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>10-Aug GMP: 250</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 13</t>
+          <t>12-Aug GMP: 276</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 13</t>
+          <t>17-Aug GMP: 262</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>14-Aug 9:28</t>
+          <t>17-Aug 8:54</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2377,37 +2369,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Technocraft Ventures IPOL@284.00 (33.96%)</t>
+          <t>LEAP India IPOL@165.90 (4.34%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹42 (19.81%) 10 ↓ / 42 ↑</t>
+          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>38.69x</t>
+          <t>8.82x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>159</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹251.88 Cr</t>
+          <t>₹2480.00 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2417,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 29</t>
+          <t>11-Aug GMP: 13</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2427,7 +2419,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 42</t>
+          <t>14-Aug GMP: 13</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2511,62 +2503,62 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LAPL Automotive BSE SMEL@135.00 (43.62%)</t>
+          <t>Technocraft Ventures IPOL@284.00 (33.96%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹50 (53.19%) 22 ↓ / 50 ↑</t>
+          <t>₹42 (19.81%) 10 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>344.31x</t>
+          <t>38.69x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>212</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹32.40 Cr</t>
+          <t>₹251.88 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 32</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 39</t>
+          <t>11-Aug GMP: 29</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 50</t>
+          <t>14-Aug GMP: 42</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>13-Aug 9:36</t>
+          <t>14-Aug 9:28</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,12 +501,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kwick Forensic Solutions BSE SMEU</t>
+          <t>Symbiotec Pharmalab IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -519,36 +519,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>₹1757.00 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>24-Aug</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>27-Aug</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>31-Aug</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>28-Aug</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>1-Sep</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>3-Sep</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>18-Aug 13:00</t>
+          <t>19-Aug 8:54</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -560,17 +568,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sumax Engineering NSE SMEU</t>
+          <t>Kwick Forensic Solutions BSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹10 (9.90%) 10 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -578,44 +586,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹53.40 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>18-Aug 15:01</t>
+          <t>19-Aug 5:55</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -627,17 +627,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Madhur Knit NSE SMEU</t>
+          <t>Sumax Engineering NSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹20 (19.80%) 20 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -647,12 +647,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹27.00 Cr</t>
+          <t>₹53.40 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -662,27 +662,27 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>18-Aug 14:54</t>
+          <t>19-Aug 9:01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -694,17 +694,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Skyways Air IPOU</t>
+          <t>Madhur Knit NSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹31 (22.46%) 19 ↓ / 31 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹27.00 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>18-Aug 14:58</t>
+          <t>19-Aug 8:58</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -761,17 +761,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ABH Healthcare NSE SMEU</t>
+          <t>Skyways Air IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹40 (28.99%) 19 ↓ / 40 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -781,17 +781,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹34.98 Cr</t>
+          <t>₹582.80 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,44 +801,44 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>18-Aug 15:00</t>
+          <t>19-Aug 9:00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOU</t>
+          <t>ABH Healthcare NSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹165 (20.94%) 165 ↓ / 165 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -848,32 +848,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹825.00 Cr</t>
+          <t>₹34.98 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -883,29 +883,29 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>18-Aug 15:01</t>
+          <t>19-Aug 9:01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOU</t>
+          <t>Augmont Enterprises IPOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹158 (52.67%) 65 ↓ / 158 ↑</t>
+          <t>₹190 (24.11%) 190 ↓ / 190 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -915,42 +915,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹825.00 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>18-Aug 15:00</t>
+          <t>19-Aug 8:56</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -962,17 +962,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mopshop Distribution BSE SMEU</t>
+          <t>Tempsens Instruments (India) IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹18 (13.04%) 10 ↓ / 18 ↑</t>
+          <t>₹172 (57.33%) 65 ↓ / 172 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -982,64 +982,64 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹27.26 Cr</t>
+          <t>₹650.00 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>18-Aug 14:59</t>
+          <t>19-Aug 9:01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMEU</t>
+          <t>Mopshop Distribution BSE SMEO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹22 (15.94%) 10 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1049,22 +1049,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹26.73 Cr</t>
+          <t>₹27.26 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>19-Aug GMP: 22</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>18-Aug 14:58</t>
+          <t>19-Aug 8:55</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1096,12 +1096,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOU</t>
+          <t>Dhanwel Hybrid Seeds BSE SMEO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹5 (3.12%) 5 ↓ / 7 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1116,22 +1116,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹550.00 Cr</t>
+          <t>₹26.73 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>19-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1151,74 +1151,74 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>18-Aug 14:56</t>
+          <t>19-Aug 8:58</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOO</t>
+          <t>Gaja Alternative Asset Management IPOO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹75 (20.83%) 17 ↓ / 75 ↑</t>
+          <t>₹30 (18.75%) 7 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3.24x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹550.00 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 75</t>
+          <t>19-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>18-Aug 14:56</t>
+          <t>19-Aug 8:54</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1230,42 +1230,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOO</t>
+          <t>Sunshine Pictures IPOO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹4 (4.30%) 2 ↓ / 8 ↑</t>
+          <t>₹77 (21.39%) 17 ↓ / 77 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.25x</t>
+          <t>4.34x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹367.18 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 4</t>
+          <t>18-Aug GMP: 77</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>18-Aug 15:02</t>
+          <t>19-Aug 8:56</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1297,114 +1297,114 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMEO</t>
+          <t>Shankesh Jewellers IPOO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹5 (5.38%) 2 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.92x</t>
+          <t>0.36x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹64.83 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>18-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>18-Aug 15:01</t>
+          <t>19-Aug 8:55</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOO</t>
+          <t>Fascinate Textiles NSE SMECT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹33 (16.42%) 17 ↓ / 41 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.71x</t>
+          <t>0.95x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹64.83 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 30</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>19-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1419,59 +1419,59 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>18-Aug 14:59</t>
+          <t>19-Aug 8:54</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks IPOO</t>
+          <t>Lalithaa Jewellery Mart IPOCT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹1.25 (2.08%) 1.25 ↓ / 4.50 ↑</t>
+          <t>₹40 (19.90%) 17 ↓ / 41 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.2x</t>
+          <t>3.25x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹2600.04 Cr</t>
+          <t>₹1700.00 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 1.7</t>
+          <t>17-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>19-Aug GMP: 40</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>18-Aug 15:02</t>
+          <t>19-Aug 9:02</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1565,62 +1565,62 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems BSE SMECT</t>
+          <t>Horizon Industrial Parks IPOCT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹43 (32.58%) 12 ↓ / 43 ↑</t>
+          <t>₹1 (1.67%) 1 ↓ / 4.50 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>152.88x</t>
+          <t>0.25x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹60.98 Cr</t>
+          <t>₹2600.04 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 30</t>
+          <t>17-Aug GMP: 1.7</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 43</t>
+          <t>19-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>18-Aug 14:55</t>
+          <t>19-Aug 9:01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1632,47 +1632,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Skytech Infinite Platform NSE SMECT</t>
+          <t>Technocrats Plasma Systems BSE SMEC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹1 (1.30%) 1 ↓ / 13 ↑</t>
+          <t>₹43 (32.58%) 12 ↓ / 43 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.85x</t>
+          <t>203.36x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹22.68 Cr</t>
+          <t>₹60.98 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 10</t>
+          <t>14-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 1</t>
+          <t>18-Aug GMP: 43</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1687,24 +1687,24 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>18-Aug 14:59</t>
+          <t>19-Aug 8:58</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMECT</t>
+          <t>Skytech Infinite Platform NSE SMEC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1 (1.30%) 1 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1714,32 +1714,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.41x</t>
+          <t>2.04x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹33.14 Cr</t>
+          <t>₹22.68 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 0</t>
+          <t>18-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1754,74 +1754,74 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>18-Aug 14:53</t>
+          <t>19-Aug 9:02</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Credent Connect NSE SMEC</t>
+          <t>ENS Enterprises BSE SMEC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹45 (23.81%) 35 ↓ / 75 ↑</t>
+          <t>₹4 (4.35%) 4 ↓ / 4 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>153.13x</t>
+          <t>13.11x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹93.90 Cr</t>
+          <t>₹33.14 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 75</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 45</t>
+          <t>18-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>18-Aug 15:01</t>
+          <t>19-Aug 9:02</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1833,62 +1833,62 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMEC</t>
+          <t>Credent Connect NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹63 (33.33%) 35 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3.87x</t>
+          <t>153.13x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
+          <t>₹93.90 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 0</t>
+          <t>13-Aug GMP: 75</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>17-Aug GMP: 45</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>18-Aug 14:58</t>
+          <t>19-Aug 8:58</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1900,47 +1900,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Shiprocket IPOCAllotted</t>
+          <t>Pramodini Medicare NSE SMELT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹34.75 (35.82%) 14 ↓ / 36.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>102.28x</t>
+          <t>3.87x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹69.04 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 34</t>
+          <t>12-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 34</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>19-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>18-Aug 14:58</t>
+          <t>19-Aug 8:57</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1967,12 +1967,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOCAllotted</t>
+          <t>Shiprocket IPOLT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹121 (42.46%) 25 ↓ / 121 ↑</t>
+          <t>₹35 (36.08%) 14 ↓ / 36.50 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1982,32 +1982,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>118.07x</t>
+          <t>102.28x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹1617.48 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 74</t>
+          <t>12-Aug GMP: 34</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 83</t>
+          <t>14-Aug GMP: 34</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>19-Aug GMP: 35</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>18-Aug 14:57</t>
+          <t>19-Aug 9:02</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2034,47 +2034,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods BSE SMECAllotted</t>
+          <t>Behari Lal Engineering IPOLT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
+          <t>₹133 (46.67%) 25 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>118.07x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>285</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹26.25 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 10</t>
+          <t>12-Aug GMP: 74</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 1</t>
+          <t>14-Aug GMP: 83</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2084,131 +2084,131 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>19-Aug GMP: 133</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>18-Aug 14:53</t>
+          <t>19-Aug 8:54</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food IPOL@165.00 (17.86%)</t>
+          <t>Q&amp;T Foods BSE SMELT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹19.7 (14.07%) 18 ↓ / 27 ↑</t>
+          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>59.08x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹1553.00 Cr</t>
+          <t>₹26.25 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 22.5</t>
+          <t>12-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 26</t>
+          <t>14-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 19.7</t>
+          <t>19-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>18-Aug 9:34</t>
+          <t>19-Aug 8:59</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sham Foam BSE SMEL@104.00 (-20%)</t>
+          <t>Milky Mist Dairy Food IPOL@165.00 (17.86%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹1.5 (1.15%) 1.50 ↓ / 9 ↑</t>
+          <t>₹19.7 (14.07%) 18 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.4x</t>
+          <t>59.08x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹40.48 Cr</t>
+          <t>₹1553.00 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>11-Aug GMP: 22.5</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 4</t>
+          <t>13-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2218,131 +2218,131 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 1.5</t>
+          <t>18-Aug GMP: 19.7</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>18-Aug 9:28</t>
+          <t>18-Aug 9:34</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOL@980.00 (21.44%)</t>
+          <t>Sham Foam BSE SMEL@104.00 (-20%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹116 (14.37%) 115 ↓ / 220 ↑</t>
+          <t>₹1.5 (1.15%) 1.50 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>70.27x</t>
+          <t>2.4x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹939.70 Cr</t>
+          <t>₹40.48 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 127</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 154</t>
+          <t>13-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 116</t>
+          <t>18-Aug GMP: 1.5</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>17-Aug 8:53</t>
+          <t>18-Aug 9:28</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOL@1200.00 (37.77%)</t>
+          <t>Molbio Diagnostics IPOL@980.00 (21.44%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹262 (30.08%) 146 ↓ / 276 ↑</t>
+          <t>₹116 (14.37%) 115 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>75.06x</t>
+          <t>70.27x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>807</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
+          <t>₹939.70 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 250</t>
+          <t>10-Aug GMP: 127</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 276</t>
+          <t>12-Aug GMP: 154</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 262</t>
+          <t>17-Aug GMP: 116</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>17-Aug 8:54</t>
+          <t>17-Aug 8:53</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2369,62 +2369,62 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LEAP India IPOL@165.90 (4.34%)</t>
+          <t>Dhoot Transmission IPOL@1200.00 (37.77%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
+          <t>₹262 (30.08%) 146 ↓ / 276 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.82x</t>
+          <t>75.06x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>871</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹2480.00 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>10-Aug GMP: 250</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 13</t>
+          <t>12-Aug GMP: 276</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 13</t>
+          <t>17-Aug GMP: 262</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>14-Aug 9:28</t>
+          <t>17-Aug 8:54</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2436,47 +2436,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Optimystix Entertainment NSE SMEL@180 (2.86%)</t>
+          <t>LEAP India IPOL@165.90 (4.34%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 5 ↑</t>
+          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.05x</t>
+          <t>8.82x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>159</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹108.50 Cr</t>
+          <t>₹2480.00 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 0</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>11-Aug GMP: 13</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 13</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>14-Aug 9:35</t>
+          <t>14-Aug 9:28</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2503,47 +2503,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Technocraft Ventures IPOL@284.00 (33.96%)</t>
+          <t>Optimystix Entertainment NSE SMEL@180 (2.86%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹42 (19.81%) 10 ↓ / 42 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>38.69x</t>
+          <t>2.05x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>175</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹251.88 Cr</t>
+          <t>₹108.50 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>7-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 29</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 42</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>14-Aug 9:28</t>
+          <t>14-Aug 9:35</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOU</t>
+          <t>Kwick Forensic Solutions BSE SMEU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -519,44 +519,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>988</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹1757.00 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>19-Aug 8:54</t>
+          <t>19-Aug 5:55</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -568,17 +560,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kwick Forensic Solutions BSE SMEU</t>
+          <t>Sumax Engineering NSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹20 (19.80%) 20 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -586,36 +578,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>₹53.40 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>28-Aug</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>31-Aug</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>1-Sep</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>19-Aug 5:55</t>
+          <t>19-Aug 14:59</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -627,17 +627,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sumax Engineering NSE SMEU</t>
+          <t>Hy-Tech Engineers IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹20 (19.80%) 20 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -647,42 +647,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹53.40 Cr</t>
+          <t>₹135.73 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>27-Aug</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>28-Aug</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>31-Aug</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>19-Aug 9:01</t>
+          <t>19-Aug 15:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -694,17 +694,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Madhur Knit NSE SMEU</t>
+          <t>Skyways Air IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹40 (28.99%) 19 ↓ / 40 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -714,19 +714,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>₹582.80 Cr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>₹27.00 Cr</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>24-Aug</t>
@@ -749,7 +749,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>19-Aug 8:58</t>
+          <t>19-Aug 14:53</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -761,17 +761,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Skyways Air IPOU</t>
+          <t>Symbiotec Pharmalab IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹40 (28.99%) 19 ↓ / 40 ↑</t>
+          <t>₹150 (15.18%) 150 ↓ / 150 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -781,17 +781,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹1757.00 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>19-Aug 9:00</t>
+          <t>19-Aug 14:55</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -828,7 +828,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ABH Healthcare NSE SMEU</t>
+          <t>Madhur Knit NSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹34.98 Cr</t>
+          <t>₹53.27 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -868,44 +868,44 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>19-Aug 9:01</t>
+          <t>19-Aug 14:56</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOU</t>
+          <t>ABH Healthcare NSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹190 (24.11%) 190 ↓ / 190 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -915,32 +915,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹825.00 Cr</t>
+          <t>₹34.98 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -950,29 +950,29 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>19-Aug 8:56</t>
+          <t>19-Aug 15:01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOU</t>
+          <t>Augmont Enterprises IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹172 (57.33%) 65 ↓ / 172 ↑</t>
+          <t>₹190 (24.11%) 190 ↓ / 190 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -982,42 +982,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹825.00 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>19-Aug 9:01</t>
+          <t>19-Aug 14:56</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1029,17 +1029,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mopshop Distribution BSE SMEO</t>
+          <t>Tempsens Instruments (India) IPOU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹22 (15.94%) 10 ↓ / 22 ↑</t>
+          <t>₹185 (61.67%) 65 ↓ / 185 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1049,89 +1049,89 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹27.26 Cr</t>
+          <t>₹650.00 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 22</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>19-Aug 8:55</t>
+          <t>19-Aug 14:58</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMEO</t>
+          <t>Mopshop Distribution BSE SMEO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹22 (15.94%) 10 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.56x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹26.73 Cr</t>
+          <t>₹27.26 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0</t>
+          <t>19-Aug GMP: 22</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>19-Aug 8:58</t>
+          <t>19-Aug 14:56</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹30 (18.75%) 7 ↓ / 30 ↑</t>
+          <t>₹20 (12.50%) 7 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.69x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 30</t>
+          <t>19-Aug GMP: 20</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>19-Aug 8:54</t>
+          <t>19-Aug 14:53</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1230,109 +1230,109 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOO</t>
+          <t>Dhanwel Hybrid Seeds BSE SMEO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹77 (21.39%) 17 ↓ / 77 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4.34x</t>
+          <t>0.07x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹26.73 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 77</t>
+          <t>19-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>19-Aug 8:56</t>
+          <t>19-Aug 15:01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOO</t>
+          <t>Sunshine Pictures IPOO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹5 (5.38%) 2 ↓ / 8 ↑</t>
+          <t>₹78 (21.67%) 17 ↓ / 78 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.36x</t>
+          <t>15.39x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹367.18 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 5</t>
+          <t>18-Aug GMP: 77</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>19-Aug 8:55</t>
+          <t>19-Aug 15:00</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1364,12 +1364,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMECT</t>
+          <t>Shankesh Jewellers IPOO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹3.5 (3.76%) 2 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1379,52 +1379,52 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.95x</t>
+          <t>0.81x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹64.83 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>18-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>19-Aug 8:54</t>
+          <t>19-Aug 14:57</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1436,17 +1436,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹40 (19.90%) 17 ↓ / 41 ↑</t>
+          <t>₹44 (21.89%) 17 ↓ / 44 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3.25x</t>
+          <t>44.16x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 40</t>
+          <t>19-Aug GMP: 44</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>19-Aug 9:02</t>
+          <t>19-Aug 14:57</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹1 (1.67%) 1 ↓ / 4.50 ↑</t>
+          <t>₹0.5 (0.83%) 0.50 ↓ / 4.50 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.25x</t>
+          <t>1.23x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 1</t>
+          <t>19-Aug GMP: 0.5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>19-Aug 9:01</t>
+          <t>19-Aug 14:54</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1632,79 +1632,79 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems BSE SMEC</t>
+          <t>Fascinate Textiles NSE SMECT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹43 (32.58%) 12 ↓ / 43 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>203.36x</t>
+          <t>1.38x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹60.98 Cr</t>
+          <t>₹64.83 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 30</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 43</t>
+          <t>19-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>19-Aug 8:58</t>
+          <t>19-Aug 15:02</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Skytech Infinite Platform NSE SMEC</t>
+          <t>ENS Enterprises BSE SMEC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹1 (1.30%) 1 ↓ / 13 ↑</t>
+          <t>₹4 (4.35%) 4 ↓ / 4 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1714,32 +1714,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.04x</t>
+          <t>13.11x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹22.68 Cr</t>
+          <t>₹33.14 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 10</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 1</t>
+          <t>18-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1754,24 +1754,24 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>19-Aug 9:02</t>
+          <t>19-Aug 14:57</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMEC</t>
+          <t>Skytech Infinite Platform NSE SMEC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹4 (4.35%) 4 ↓ / 4 ↑</t>
+          <t>₹1 (1.30%) 1 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>13.11x</t>
+          <t>2.04x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹33.14 Cr</t>
+          <t>₹22.68 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 4</t>
+          <t>18-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1821,24 +1821,24 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>19-Aug 9:02</t>
+          <t>19-Aug 15:01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Credent Connect NSE SMECAllotted</t>
+          <t>Technocrats Plasma Systems BSE SMEC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹63 (33.33%) 35 ↓ / 75 ↑</t>
+          <t>₹43 (32.58%) 12 ↓ / 43 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1848,47 +1848,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>153.13x</t>
+          <t>203.36x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹93.90 Cr</t>
+          <t>₹60.98 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 75</t>
+          <t>14-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 45</t>
+          <t>18-Aug GMP: 43</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>19-Aug 8:58</t>
+          <t>19-Aug 15:01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1900,62 +1900,62 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMELT</t>
+          <t>Credent Connect NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹78 (41.27%) 35 ↓ / 78 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3.87x</t>
+          <t>153.13x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
+          <t>₹93.90 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 0</t>
+          <t>13-Aug GMP: 75</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>17-Aug GMP: 45</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>19-Aug 8:57</t>
+          <t>19-Aug 14:58</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1967,47 +1967,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Shiprocket IPOLT</t>
+          <t>Q&amp;T Foods BSE SMEL@115.00 (0%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹35 (36.08%) 14 ↓ / 36.50 ↑</t>
+          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>102.28x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹26.25 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 34</t>
+          <t>12-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 34</t>
+          <t>14-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2017,24 +2017,24 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 35</t>
+          <t>19-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>19-Aug 9:02</t>
+          <t>19-Aug 9:31</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOLT</t>
+          <t>Behari Lal Engineering IPOL@465.00 (63.16%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>19-Aug 8:54</t>
+          <t>19-Aug 9:32</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2101,12 +2101,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods BSE SMELT</t>
+          <t>Pramodini Medicare NSE SMEL@120.00 (1.69%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2116,17 +2116,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>3.87x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹26.25 Cr</t>
+          <t>₹69.04 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 10</t>
+          <t>12-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 1</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2151,79 +2151,79 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 1</t>
+          <t>19-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>19-Aug 8:59</t>
+          <t>19-Aug 9:29</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food IPOL@165.00 (17.86%)</t>
+          <t>Shiprocket IPOL@131.00 (35.05%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹19.7 (14.07%) 18 ↓ / 27 ↑</t>
+          <t>₹35 (36.08%) 14 ↓ / 36.50 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>59.08x</t>
+          <t>102.28x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹1553.00 Cr</t>
+          <t>₹1617.48 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 22.5</t>
+          <t>12-Aug GMP: 34</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 26</t>
+          <t>14-Aug GMP: 34</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 19.7</t>
+          <t>19-Aug GMP: 35</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>18-Aug 9:34</t>
+          <t>19-Aug 9:33</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2235,47 +2235,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sham Foam BSE SMEL@104.00 (-20%)</t>
+          <t>Milky Mist Dairy Food IPOL@165.00 (17.86%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹1.5 (1.15%) 1.50 ↓ / 9 ↑</t>
+          <t>₹19.7 (14.07%) 18 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.4x</t>
+          <t>59.08x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹40.48 Cr</t>
+          <t>₹1553.00 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>11-Aug GMP: 22.5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 4</t>
+          <t>13-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2285,84 +2285,84 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 1.5</t>
+          <t>18-Aug GMP: 19.7</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>18-Aug 9:28</t>
+          <t>18-Aug 9:34</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOL@980.00 (21.44%)</t>
+          <t>Sham Foam BSE SMEL@104.00 (-20%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹116 (14.37%) 115 ↓ / 220 ↑</t>
+          <t>₹1.5 (1.15%) 1.50 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>70.27x</t>
+          <t>2.4x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹939.70 Cr</t>
+          <t>₹40.48 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 127</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 154</t>
+          <t>13-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 116</t>
+          <t>18-Aug GMP: 1.5</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>17-Aug 8:53</t>
+          <t>18-Aug 9:28</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -2436,62 +2436,62 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LEAP India IPOL@165.90 (4.34%)</t>
+          <t>Molbio Diagnostics IPOL@980.00 (21.44%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
+          <t>₹116 (14.37%) 115 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.82x</t>
+          <t>70.27x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>807</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹2480.00 Cr</t>
+          <t>₹939.70 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>10-Aug GMP: 127</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 13</t>
+          <t>12-Aug GMP: 154</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 13</t>
+          <t>17-Aug GMP: 116</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>14-Aug 9:28</t>
+          <t>17-Aug 8:53</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2503,47 +2503,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Optimystix Entertainment NSE SMEL@180 (2.86%)</t>
+          <t>LEAP India IPOL@165.90 (4.34%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 5 ↑</t>
+          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.05x</t>
+          <t>8.82x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>159</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹108.50 Cr</t>
+          <t>₹2480.00 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 0</t>
+          <t>7-Aug GMP: 15</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>11-Aug GMP: 13</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 13</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>14-Aug 9:35</t>
+          <t>14-Aug 9:28</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kwick Forensic Solutions BSE SMEU</t>
+          <t>Annu Projects IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -519,36 +519,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>₹175.06 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>28-Aug</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>31-Aug</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1-Sep</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>19-Aug 5:55</t>
+          <t>20-Aug 9:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -560,17 +568,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sumax Engineering NSE SMEU</t>
+          <t>Kwick Forensic Solutions BSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹20 (19.80%) 20 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -578,44 +586,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹53.40 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>19-Aug 14:59</t>
+          <t>20-Aug 5:55</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -627,17 +627,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOU</t>
+          <t>Sumax Engineering NSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹30 (29.70%) 20 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -647,42 +647,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹135.73 Cr</t>
+          <t>₹53.40 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>19-Aug 15:02</t>
+          <t>20-Aug 8:56</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -694,17 +694,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Skyways Air IPOU</t>
+          <t>Hy-Tech Engineers IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹40 (28.99%) 19 ↓ / 40 ↑</t>
+          <t>₹5 (9.43%) 5 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹135.73 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>19-Aug 14:53</t>
+          <t>20-Aug 9:02</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -761,17 +761,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOU</t>
+          <t>Skyways Air IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹150 (15.18%) 150 ↓ / 150 ↑</t>
+          <t>₹42 (30.43%) 19 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -781,17 +781,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹1757.00 Cr</t>
+          <t>₹582.80 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>19-Aug 14:55</t>
+          <t>20-Aug 9:00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -828,17 +828,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Madhur Knit NSE SMEU</t>
+          <t>Symbiotec Pharmalab IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹220 (22.27%) 220 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹53.27 Cr</t>
+          <t>₹1757.00 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>19-Aug 14:56</t>
+          <t>20-Aug 9:02</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ABH Healthcare NSE SMEU</t>
+          <t>Madhur Knit NSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹34.98 Cr</t>
+          <t>₹53.27 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -935,44 +935,44 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>19-Aug 15:01</t>
+          <t>20-Aug 8:59</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOU</t>
+          <t>ABH Healthcare NSE SMEU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹190 (24.11%) 190 ↓ / 190 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -982,64 +982,64 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹825.00 Cr</t>
+          <t>₹34.98 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>19-Aug 14:56</t>
+          <t>20-Aug 8:59</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOU</t>
+          <t>Augmont Enterprises IPOU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹185 (61.67%) 65 ↓ / 185 ↑</t>
+          <t>₹280 (35.53%) 190 ↓ / 280 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1049,42 +1049,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹825.00 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>19-Aug 14:58</t>
+          <t>20-Aug 8:56</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1096,109 +1096,109 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mopshop Distribution BSE SMEO</t>
+          <t>Tempsens Instruments (India) IPOO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹22 (15.94%) 10 ↓ / 22 ↑</t>
+          <t>₹220 (73.33%) 65 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.56x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹27.26 Cr</t>
+          <t>₹650.00 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 22</t>
+          <t>20-Aug GMP: 220</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>19-Aug 14:56</t>
+          <t>20-Aug 8:55</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOO</t>
+          <t>Mopshop Distribution BSE SMEO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹20 (12.50%) 7 ↓ / 30 ↑</t>
+          <t>₹5 (3.62%) 5 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.69x</t>
+          <t>0.78x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹550.00 Cr</t>
+          <t>₹27.26 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 20</t>
+          <t>19-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1218,54 +1218,54 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>19-Aug 14:53</t>
+          <t>20-Aug 9:01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMEO</t>
+          <t>Gaja Alternative Asset Management IPOO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹23 (14.37%) 7 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.07x</t>
+          <t>0.9x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹26.73 Cr</t>
+          <t>₹550.00 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0</t>
+          <t>19-Aug GMP: 23</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1285,126 +1285,126 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>19-Aug 15:01</t>
+          <t>20-Aug 8:54</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOO</t>
+          <t>Dhanwel Hybrid Seeds BSE SMEO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹78 (21.67%) 17 ↓ / 78 ↑</t>
+          <t>₹12 (12.12%) 12 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>15.39x</t>
+          <t>0.09x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹26.73 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 77</t>
+          <t>19-Aug GMP: 12</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>19-Aug 15:00</t>
+          <t>20-Aug 8:55</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOO</t>
+          <t>Sunshine Pictures IPOCT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹3.5 (3.76%) 2 ↓ / 8 ↑</t>
+          <t>₹77 (21.39%) 17 ↓ / 77 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.81x</t>
+          <t>18.47x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹367.18 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 5</t>
+          <t>18-Aug GMP: 77</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>20-Aug GMP: 77</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>19-Aug 14:57</t>
+          <t>20-Aug 8:55</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1431,62 +1431,62 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOCT</t>
+          <t>Shankesh Jewellers IPOCT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹44 (21.89%) 17 ↓ / 44 ↑</t>
+          <t>₹2.5 (2.69%) 2 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.16x</t>
+          <t>0.94x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 30</t>
+          <t>18-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 44</t>
+          <t>20-Aug GMP: 2.5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>19-Aug 14:57</t>
+          <t>20-Aug 9:02</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1565,47 +1565,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks IPOCT</t>
+          <t>Lalithaa Jewellery Mart IPOC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹0.5 (0.83%) 0.50 ↓ / 4.50 ↑</t>
+          <t>₹54 (26.87%) 17 ↓ / 54 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.23x</t>
+          <t>66.63x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹2600.04 Cr</t>
+          <t>₹1700.00 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 1.7</t>
+          <t>17-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0.5</t>
+          <t>19-Aug GMP: 54</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>19-Aug 14:54</t>
+          <t>20-Aug 8:56</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1632,12 +1632,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMECT</t>
+          <t>Horizon Industrial Parks IPOC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1.3 (2.17%) 1 ↓ / 4.50 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1647,32 +1647,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.38x</t>
+          <t>1.52x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹64.83 Cr</t>
+          <t>₹2600.04 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>17-Aug GMP: 1.7</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0</t>
+          <t>19-Aug GMP: 1.3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1687,24 +1687,24 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>19-Aug 15:02</t>
+          <t>20-Aug 8:59</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMEC</t>
+          <t>Fascinate Textiles NSE SMEC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹4 (4.35%) 4 ↓ / 4 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1714,64 +1714,64 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>13.11x</t>
+          <t>1.48x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹33.14 Cr</t>
+          <t>₹64.83 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 4</t>
+          <t>19-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>19-Aug 14:57</t>
+          <t>20-Aug 9:02</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Skytech Infinite Platform NSE SMEC</t>
+          <t>ENS Enterprises BSE SMEC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹1 (1.30%) 1 ↓ / 13 ↑</t>
+          <t>₹4 (4.35%) 4 ↓ / 4 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.04x</t>
+          <t>13.11x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹22.68 Cr</t>
+          <t>₹33.14 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 10</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 1</t>
+          <t>18-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1821,59 +1821,59 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>19-Aug 15:01</t>
+          <t>20-Aug 9:00</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems BSE SMEC</t>
+          <t>Skytech Infinite Platform NSE SMEC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹43 (32.58%) 12 ↓ / 43 ↑</t>
+          <t>₹1 (1.30%) 1 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>203.36x</t>
+          <t>2.04x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹60.98 Cr</t>
+          <t>₹22.68 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 30</t>
+          <t>14-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 43</t>
+          <t>18-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1888,24 +1888,24 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>19-Aug 15:01</t>
+          <t>20-Aug 8:58</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Credent Connect NSE SMECAllotted</t>
+          <t>Technocrats Plasma Systems BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹78 (41.27%) 35 ↓ / 78 ↑</t>
+          <t>₹41 (31.06%) 12 ↓ / 43 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1915,47 +1915,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>153.13x</t>
+          <t>203.36x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹93.90 Cr</t>
+          <t>₹60.98 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 75</t>
+          <t>14-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 45</t>
+          <t>18-Aug GMP: 43</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>19-Aug 14:58</t>
+          <t>20-Aug 8:53</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1967,114 +1967,114 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods BSE SMEL@115.00 (0%)</t>
+          <t>Credent Connect NSE SMELT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
+          <t>₹92 (48.68%) 35 ↓ / 92 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>153.13x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹26.25 Cr</t>
+          <t>₹93.90 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 10</t>
+          <t>13-Aug GMP: 75</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 1</t>
+          <t>17-Aug GMP: 45</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 1</t>
+          <t>20-Aug GMP: 92</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>19-Aug 9:31</t>
+          <t>20-Aug 8:53</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOL@465.00 (63.16%)</t>
+          <t>Q&amp;T Foods BSE SMEL@115.00 (0%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹133 (46.67%) 25 ↓ / 133 ↑</t>
+          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>118.07x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹26.25 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 74</t>
+          <t>12-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 83</t>
+          <t>14-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2084,64 +2084,64 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 133</t>
+          <t>19-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>19-Aug 9:32</t>
+          <t>19-Aug 9:31</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMEL@120.00 (1.69%)</t>
+          <t>Behari Lal Engineering IPOL@465.00 (63.16%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹133 (46.67%) 25 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3.87x</t>
+          <t>118.07x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>285</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 0</t>
+          <t>12-Aug GMP: 74</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 83</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0</t>
+          <t>19-Aug GMP: 133</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>19-Aug 9:29</t>
+          <t>19-Aug 9:32</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2168,47 +2168,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Shiprocket IPOL@131.00 (35.05%)</t>
+          <t>Pramodini Medicare NSE SMEL@120.00 (1.69%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹35 (36.08%) 14 ↓ / 36.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>102.28x</t>
+          <t>3.87x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹69.04 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 34</t>
+          <t>12-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 34</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 35</t>
+          <t>19-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>19-Aug 9:33</t>
+          <t>19-Aug 9:29</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2235,62 +2235,62 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food IPOL@165.00 (17.86%)</t>
+          <t>Shiprocket IPOL@131.00 (35.05%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹19.7 (14.07%) 18 ↓ / 27 ↑</t>
+          <t>₹35 (36.08%) 14 ↓ / 36.50 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>59.08x</t>
+          <t>102.28x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹1553.00 Cr</t>
+          <t>₹1617.48 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 22.5</t>
+          <t>12-Aug GMP: 34</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 26</t>
+          <t>14-Aug GMP: 34</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 19.7</t>
+          <t>19-Aug GMP: 35</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>18-Aug 9:34</t>
+          <t>19-Aug 9:33</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2302,47 +2302,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sham Foam BSE SMEL@104.00 (-20%)</t>
+          <t>Milky Mist Dairy Food IPOL@165.00 (17.86%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹1.5 (1.15%) 1.50 ↓ / 9 ↑</t>
+          <t>₹19.7 (14.07%) 18 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.4x</t>
+          <t>59.08x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹40.48 Cr</t>
+          <t>₹1553.00 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>11-Aug GMP: 22.5</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 4</t>
+          <t>13-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2352,131 +2352,131 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 1.5</t>
+          <t>18-Aug GMP: 19.7</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>18-Aug 9:28</t>
+          <t>18-Aug 9:34</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOL@1200.00 (37.77%)</t>
+          <t>Sham Foam BSE SMEL@104.00 (-20%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹262 (30.08%) 146 ↓ / 276 ↑</t>
+          <t>₹1.5 (1.15%) 1.50 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>75.06x</t>
+          <t>2.4x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
+          <t>₹40.48 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 250</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 276</t>
+          <t>13-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 262</t>
+          <t>18-Aug GMP: 1.5</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>17-Aug 8:54</t>
+          <t>18-Aug 9:28</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOL@980.00 (21.44%)</t>
+          <t>Dhoot Transmission IPOL@1200.00 (37.77%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹116 (14.37%) 115 ↓ / 220 ↑</t>
+          <t>₹262 (30.08%) 146 ↓ / 276 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>70.27x</t>
+          <t>75.06x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>871</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹939.70 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 127</t>
+          <t>10-Aug GMP: 250</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 154</t>
+          <t>12-Aug GMP: 276</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 116</t>
+          <t>17-Aug GMP: 262</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>17-Aug 8:53</t>
+          <t>17-Aug 8:54</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2503,62 +2503,62 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LEAP India IPOL@165.90 (4.34%)</t>
+          <t>Molbio Diagnostics IPOL@980.00 (21.44%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹13 (8.18%) 3 ↓ / 19.50 ↑</t>
+          <t>₹116 (14.37%) 115 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.82x</t>
+          <t>70.27x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>807</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹2480.00 Cr</t>
+          <t>₹939.70 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>7-Aug GMP: 15</t>
+          <t>10-Aug GMP: 127</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 13</t>
+          <t>12-Aug GMP: 154</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>12-Aug</t>
+          <t>13-Aug</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 13</t>
+          <t>17-Aug GMP: 116</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>14-Aug 9:28</t>
+          <t>17-Aug 8:53</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,12 +501,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Annu Projects IPOU</t>
+          <t>Rays of Belief IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -519,44 +519,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹175.06 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>20-Aug 9:02</t>
+          <t>20-Aug 13:30</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -573,7 +565,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹15 (0.00%) 15 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +578,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-</t>
@@ -615,7 +611,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>20-Aug 5:55</t>
+          <t>20-Aug 14:57</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -627,17 +623,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sumax Engineering NSE SMEU</t>
+          <t>Annu Projects IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹30 (29.70%) 20 ↓ / 30 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -647,17 +643,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹53.40 Cr</t>
+          <t>₹175.06 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -682,7 +678,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>20-Aug 8:56</t>
+          <t>20-Aug 15:01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -694,17 +690,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOU</t>
+          <t>Sumax Engineering NSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹5 (9.43%) 5 ↓ / 5 ↑</t>
+          <t>₹30 (29.70%) 20 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -714,42 +710,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹135.73 Cr</t>
+          <t>₹53.40 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>20-Aug 9:02</t>
+          <t>20-Aug 14:54</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -761,17 +757,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Skyways Air IPOU</t>
+          <t>Madhur Knit NSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹42 (30.43%) 19 ↓ / 42 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -781,17 +777,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹53.27 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -816,7 +812,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>20-Aug 9:00</t>
+          <t>20-Aug 14:59</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -828,12 +824,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOU</t>
+          <t>Skyways Air IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹220 (22.27%) 220 ↓ / 220 ↑</t>
+          <t>₹42 (30.43%) 19 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -848,17 +844,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹1757.00 Cr</t>
+          <t>₹582.80 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -883,7 +879,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>20-Aug 9:02</t>
+          <t>20-Aug 14:55</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -895,7 +891,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Madhur Knit NSE SMEU</t>
+          <t>ABH Healthcare NSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -915,12 +911,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹53.27 Cr</t>
+          <t>₹34.98 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -950,29 +946,29 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>20-Aug 8:59</t>
+          <t>20-Aug 14:59</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ABH Healthcare NSE SMEU</t>
+          <t>Symbiotec Pharmalab IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹240 (24.29%) 220 ↓ / 240 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -982,17 +978,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹34.98 Cr</t>
+          <t>₹1757.00 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1017,29 +1013,29 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>20-Aug 8:59</t>
+          <t>20-Aug 14:55</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOU</t>
+          <t>Hy-Tech Engineers IPOU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹280 (35.53%) 190 ↓ / 280 ↑</t>
+          <t>₹2 (3.77%) 2 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1049,42 +1045,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹825.00 Cr</t>
+          <t>₹135.73 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>20-Aug 8:56</t>
+          <t>20-Aug 14:59</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1096,17 +1092,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOO</t>
+          <t>Augmont Enterprises IPOU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹220 (73.33%) 65 ↓ / 220 ↑</t>
+          <t>₹285 (36.17%) 190 ↓ / 285 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1116,42 +1112,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹825.00 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 220</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>20-Aug 8:55</t>
+          <t>20-Aug 15:00</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1163,67 +1159,67 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mopshop Distribution BSE SMEO</t>
+          <t>Tempsens Instruments (India) IPOO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹5 (3.62%) 5 ↓ / 22 ↑</t>
+          <t>₹232 (77.33%) 65 ↓ / 232 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.78x</t>
+          <t>4.8x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹27.26 Cr</t>
+          <t>₹650.00 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 5</t>
+          <t>20-Aug GMP: 232</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>20-Aug 9:01</t>
+          <t>20-Aug 14:53</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1235,17 +1231,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹23 (14.37%) 7 ↓ / 30 ↑</t>
+          <t>₹14 (8.75%) 7 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.9x</t>
+          <t>2.12x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1285,7 +1281,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>20-Aug 8:54</t>
+          <t>20-Aug 14:58</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1312,7 +1308,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.09x</t>
+          <t>0.61x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1352,7 +1348,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>20-Aug 8:55</t>
+          <t>20-Aug 14:54</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1364,114 +1360,114 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOCT</t>
+          <t>Mopshop Distribution BSE SMEO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹77 (21.39%) 17 ↓ / 77 ↑</t>
+          <t>₹1 (0.72%) 1 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18.47x</t>
+          <t>1x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹27.26 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 77</t>
+          <t>19-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 77</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>20-Aug 8:55</t>
+          <t>20-Aug 14:56</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOCT</t>
+          <t>Sunshine Pictures IPOCT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹2.5 (2.69%) 2 ↓ / 8 ↑</t>
+          <t>₹79 (21.94%) 17 ↓ / 79 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.94x</t>
+          <t>84.51x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹367.18 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 5</t>
+          <t>18-Aug GMP: 77</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 2.5</t>
+          <t>20-Aug GMP: 79</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1486,7 +1482,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>20-Aug 9:02</t>
+          <t>20-Aug 15:02</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1565,62 +1561,62 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOC</t>
+          <t>Shankesh Jewellers IPOCT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹54 (26.87%) 17 ↓ / 54 ↑</t>
+          <t>₹1 (1.08%) 1 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>66.63x</t>
+          <t>1.99x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 30</t>
+          <t>18-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 54</t>
+          <t>20-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>20-Aug 8:56</t>
+          <t>20-Aug 15:01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1637,7 +1633,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹1.3 (2.17%) 1 ↓ / 4.50 ↑</t>
+          <t>₹2.35 (3.92%) 1 ↓ / 4.50 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1687,7 +1683,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>20-Aug 8:59</t>
+          <t>20-Aug 14:55</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1754,7 +1750,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>20-Aug 9:02</t>
+          <t>20-Aug 15:00</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1766,62 +1762,62 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMEC</t>
+          <t>Lalithaa Jewellery Mart IPOC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹4 (4.35%) 4 ↓ / 4 ↑</t>
+          <t>₹60 (29.85%) 17 ↓ / 60 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>13.11x</t>
+          <t>66.63x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹33.14 Cr</t>
+          <t>₹1700.00 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>17-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 4</t>
+          <t>19-Aug GMP: 54</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>20-Aug 9:00</t>
+          <t>20-Aug 14:56</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1833,47 +1829,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Skytech Infinite Platform NSE SMEC</t>
+          <t>Technocrats Plasma Systems BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹1 (1.30%) 1 ↓ / 13 ↑</t>
+          <t>₹59 (44.70%) 12 ↓ / 59 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.04x</t>
+          <t>203.36x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹22.68 Cr</t>
+          <t>₹60.98 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 10</t>
+          <t>14-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 1</t>
+          <t>18-Aug GMP: 43</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1888,59 +1884,59 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>20-Aug 8:58</t>
+          <t>20-Aug 14:59</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems BSE SMECAllotted</t>
+          <t>ENS Enterprises BSE SMEC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹41 (31.06%) 12 ↓ / 43 ↑</t>
+          <t>₹6 (6.52%) 4 ↓ / 6 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>203.36x</t>
+          <t>13.11x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹60.98 Cr</t>
+          <t>₹33.14 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 30</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 43</t>
+          <t>18-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1955,7 +1951,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>20-Aug 8:53</t>
+          <t>20-Aug 14:53</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1967,181 +1963,181 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Credent Connect NSE SMELT</t>
+          <t>Skytech Infinite Platform NSE SMEC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹92 (48.68%) 35 ↓ / 92 ↑</t>
+          <t>₹1 (1.30%) 1 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>153.13x</t>
+          <t>2.04x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹93.90 Cr</t>
+          <t>₹22.68 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 75</t>
+          <t>14-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 45</t>
+          <t>18-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 92</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>20-Aug 8:53</t>
+          <t>20-Aug 14:58</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods BSE SMEL@115.00 (0%)</t>
+          <t>Credent Connect NSE SMEL@359.10 (90%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
+          <t>₹92 (48.68%) 35 ↓ / 92 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>153.13x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹26.25 Cr</t>
+          <t>₹93.90 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 10</t>
+          <t>13-Aug GMP: 75</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 1</t>
+          <t>17-Aug GMP: 45</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 1</t>
+          <t>20-Aug GMP: 92</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>19-Aug 9:31</t>
+          <t>20-Aug 9:30</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOL@465.00 (63.16%)</t>
+          <t>Q&amp;T Foods BSE SMEL@115.00 (0%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹133 (46.67%) 25 ↓ / 133 ↑</t>
+          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>118.07x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹26.25 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 74</t>
+          <t>12-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 83</t>
+          <t>14-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2151,64 +2147,64 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 133</t>
+          <t>19-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>19-Aug 9:32</t>
+          <t>19-Aug 9:31</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMEL@120.00 (1.69%)</t>
+          <t>Shiprocket IPOL@131.00 (35.05%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹35 (36.08%) 14 ↓ / 36.50 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3.87x</t>
+          <t>102.28x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
+          <t>₹1617.48 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 0</t>
+          <t>12-Aug GMP: 34</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 34</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2218,12 +2214,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0</t>
+          <t>19-Aug GMP: 35</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>19-Aug 9:29</t>
+          <t>19-Aug 9:33</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2235,47 +2231,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Shiprocket IPOL@131.00 (35.05%)</t>
+          <t>Pramodini Medicare NSE SMEL@120.00 (1.69%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹35 (36.08%) 14 ↓ / 36.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>102.28x</t>
+          <t>3.87x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹69.04 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 34</t>
+          <t>12-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 34</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2285,12 +2281,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 35</t>
+          <t>19-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>19-Aug 9:33</t>
+          <t>19-Aug 9:29</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2302,62 +2298,62 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food IPOL@165.00 (17.86%)</t>
+          <t>Behari Lal Engineering IPOL@465.00 (63.16%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹19.7 (14.07%) 18 ↓ / 27 ↑</t>
+          <t>₹133 (46.67%) 25 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>59.08x</t>
+          <t>118.07x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>285</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹1553.00 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 22.5</t>
+          <t>12-Aug GMP: 74</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 26</t>
+          <t>14-Aug GMP: 83</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 19.7</t>
+          <t>19-Aug GMP: 133</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>18-Aug 9:34</t>
+          <t>19-Aug 9:32</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2369,47 +2365,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sham Foam BSE SMEL@104.00 (-20%)</t>
+          <t>Milky Mist Dairy Food IPOL@165.00 (17.86%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹1.5 (1.15%) 1.50 ↓ / 9 ↑</t>
+          <t>₹19.7 (14.07%) 18 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.4x</t>
+          <t>59.08x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹40.48 Cr</t>
+          <t>₹1553.00 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>11-Aug GMP: 22.5</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 4</t>
+          <t>13-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2419,131 +2415,131 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 1.5</t>
+          <t>18-Aug GMP: 19.7</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>18-Aug 9:28</t>
+          <t>18-Aug 9:34</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOL@1200.00 (37.77%)</t>
+          <t>Sham Foam BSE SMEL@104.00 (-20%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹262 (30.08%) 146 ↓ / 276 ↑</t>
+          <t>₹1.5 (1.15%) 1.50 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>75.06x</t>
+          <t>2.4x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
+          <t>₹40.48 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 250</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 276</t>
+          <t>13-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 262</t>
+          <t>18-Aug GMP: 1.5</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>17-Aug 8:54</t>
+          <t>18-Aug 9:28</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics IPOL@980.00 (21.44%)</t>
+          <t>Dhoot Transmission IPOL@1200.00 (37.77%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹116 (14.37%) 115 ↓ / 220 ↑</t>
+          <t>₹262 (30.08%) 146 ↓ / 276 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>70.27x</t>
+          <t>75.06x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>871</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹939.70 Cr</t>
+          <t>₹3066.89 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 127</t>
+          <t>10-Aug GMP: 250</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 154</t>
+          <t>12-Aug GMP: 276</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2553,12 +2549,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 116</t>
+          <t>17-Aug GMP: 262</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>17-Aug 8:53</t>
+          <t>17-Aug 8:54</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>20-Aug 13:30</t>
+          <t>21-Aug 5:55</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>20-Aug 14:57</t>
+          <t>21-Aug 8:36</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>20-Aug 15:01</t>
+          <t>21-Aug 8:31</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹30 (29.70%) 20 ↓ / 30 ↑</t>
+          <t>₹32 (31.68%) 20 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>20-Aug 14:54</t>
+          <t>21-Aug 8:37</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>20-Aug 14:59</t>
+          <t>21-Aug 8:30</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹42 (30.43%) 19 ↓ / 42 ↑</t>
+          <t>₹42 (30.43%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>20-Aug 14:55</t>
+          <t>21-Aug 8:33</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>20-Aug 14:59</t>
+          <t>21-Aug 8:33</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹240 (24.29%) 220 ↓ / 240 ↑</t>
+          <t>₹320 (32.39%) 220 ↓ / 320 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>20-Aug 14:55</t>
+          <t>21-Aug 8:32</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹2 (3.77%) 2 ↓ / 5 ↑</t>
+          <t>₹22 (41.51%) 5 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>20-Aug 14:59</t>
+          <t>21-Aug 8:32</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1092,12 +1092,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOU</t>
+          <t>Augmont Enterprises IPOO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹285 (36.17%) 190 ↓ / 285 ↑</t>
+          <t>₹300 (38.07%) 190 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>21-Aug GMP: 300</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>20-Aug 15:00</t>
+          <t>21-Aug 8:29</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹232 (77.33%) 65 ↓ / 232 ↑</t>
+          <t>₹270 (90.00%) 65 ↓ / 270 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.8x</t>
+          <t>5.95x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 232</t>
+          <t>20-Aug GMP: 270</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>20-Aug 14:53</t>
+          <t>21-Aug 8:31</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1226,22 +1226,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOO</t>
+          <t>Gaja Alternative Asset Management IPOCT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹14 (8.75%) 7 ↓ / 30 ↑</t>
+          <t>₹18.5 (11.56%) 7 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.12x</t>
+          <t>2.56x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>21-Aug GMP: 18.5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>20-Aug 14:58</t>
+          <t>21-Aug 8:30</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1293,22 +1293,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMEO</t>
+          <t>Dhanwel Hybrid Seeds BSE SMECT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹12 (12.12%) 12 ↓ / 12 ↑</t>
+          <t>₹5 (5.05%) 5 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.61x</t>
+          <t>0.75x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>21-Aug GMP: 5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>20-Aug 14:54</t>
+          <t>21-Aug 8:34</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1360,7 +1360,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mopshop Distribution BSE SMEO</t>
+          <t>Mopshop Distribution BSE SMECT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1x</t>
+          <t>1.07x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>21-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>20-Aug 14:56</t>
+          <t>21-Aug 8:29</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1427,12 +1427,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOCT</t>
+          <t>Sunshine Pictures IPOC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹79 (21.94%) 17 ↓ / 79 ↑</t>
+          <t>₹80 (22.22%) 17 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>84.51x</t>
+          <t>105.81x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 79</t>
+          <t>20-Aug GMP: 80</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>20-Aug 15:02</t>
+          <t>21-Aug 8:29</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1561,22 +1561,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOCT</t>
+          <t>Shankesh Jewellers IPOC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹1 (1.08%) 1 ↓ / 8 ↑</t>
+          <t>₹5 (5.38%) 2 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.99x</t>
+          <t>2.8x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 1</t>
+          <t>20-Aug GMP: 5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>20-Aug 15:01</t>
+          <t>21-Aug 8:33</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1628,17 +1628,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks IPOC</t>
+          <t>Horizon Industrial Parks IPOCAllotted</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹2.35 (3.92%) 1 ↓ / 4.50 ↑</t>
+          <t>₹3.4 (5.67%) 1 ↓ / 4.50 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>20-Aug 14:55</t>
+          <t>21-Aug 8:30</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>20-Aug 15:00</t>
+          <t>21-Aug 8:36</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1762,12 +1762,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOC</t>
+          <t>Lalithaa Jewellery Mart IPOCAllotted</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹60 (29.85%) 17 ↓ / 60 ↑</t>
+          <t>₹60 (29.85%) 17 ↓ / 61 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>20-Aug 14:56</t>
+          <t>21-Aug 8:31</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1829,17 +1829,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems BSE SMECAllotted</t>
+          <t>Technocrats Plasma Systems BSE SMELT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹59 (44.70%) 12 ↓ / 59 ↑</t>
+          <t>₹70 (53.03%) 12 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>21-Aug GMP: 70</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>20-Aug 14:59</t>
+          <t>21-Aug 8:28</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1896,12 +1896,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMEC</t>
+          <t>ENS Enterprises BSE SMELT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹6 (6.52%) 4 ↓ / 6 ↑</t>
+          <t>₹5 (5.43%) 4 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>21-Aug GMP: 5</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>20-Aug 14:53</t>
+          <t>21-Aug 8:34</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1963,7 +1963,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Skytech Infinite Platform NSE SMEC</t>
+          <t>Skytech Infinite Platform NSE SMELT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2013,12 +2013,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>21-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>20-Aug 14:58</t>
+          <t>21-Aug 8:34</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -611,7 +611,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>21-Aug 8:36</t>
+          <t>21-Aug 15:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -623,17 +623,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Annu Projects IPOU</t>
+          <t>Lumino Industries IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹45 (54.88%) 45 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -643,42 +643,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹175.06 Cr</t>
+          <t>₹700.00 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>182</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>21-Aug 8:31</t>
+          <t>21-Aug 14:57</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>21-Aug 8:37</t>
+          <t>21-Aug 14:57</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -757,12 +757,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Madhur Knit NSE SMEU</t>
+          <t>Annu Projects IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹4 (4.04%) 4 ↓ / 4 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -777,42 +777,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹53.27 Cr</t>
+          <t>₹175.06 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>21-Aug 8:30</t>
+          <t>21-Aug 14:58</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -824,17 +824,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Skyways Air IPOU</t>
+          <t>ABH Healthcare NSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹42 (30.43%) 19 ↓ / 50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -844,17 +844,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹34.98 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -879,19 +879,19 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>21-Aug 8:33</t>
+          <t>21-Aug 14:56</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ABH Healthcare NSE SMEU</t>
+          <t>Madhur Knit NSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹34.98 Cr</t>
+          <t>₹53.27 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>21-Aug 8:33</t>
+          <t>21-Aug 14:55</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>21-Aug 8:32</t>
+          <t>21-Aug 15:01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>21-Aug 8:32</t>
+          <t>21-Aug 14:53</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1092,12 +1092,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOO</t>
+          <t>Skyways Air IPOU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹300 (38.07%) 190 ↓ / 300 ↑</t>
+          <t>₹45 (32.61%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1112,42 +1112,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹825.00 Cr</t>
+          <t>₹582.80 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 300</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>21-Aug 8:29</t>
+          <t>21-Aug 14:59</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1159,62 +1159,62 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOO</t>
+          <t>Augmont Enterprises IPOO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹270 (90.00%) 65 ↓ / 270 ↑</t>
+          <t>₹300 (38.07%) 190 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5.95x</t>
+          <t>1.77x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹825.00 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 270</t>
+          <t>21-Aug GMP: 300</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>21-Aug 8:31</t>
+          <t>21-Aug 14:55</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1226,62 +1226,62 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOCT</t>
+          <t>Tempsens Instruments (India) IPOO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹18.5 (11.56%) 7 ↓ / 30 ↑</t>
+          <t>₹277 (92.33%) 65 ↓ / 277 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.56x</t>
+          <t>18.02x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹550.00 Cr</t>
+          <t>₹650.00 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 23</t>
+          <t>20-Aug GMP: 270</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 18.5</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>21-Aug 8:30</t>
+          <t>21-Aug 14:58</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMECT</t>
+          <t>Gaja Alternative Asset Management IPOCT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹5 (5.05%) 5 ↓ / 12 ↑</t>
+          <t>₹13 (8.12%) 7 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1308,32 +1308,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.75x</t>
+          <t>21.05x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹26.73 Cr</t>
+          <t>₹550.00 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 12</t>
+          <t>19-Aug GMP: 23</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 5</t>
+          <t>21-Aug GMP: 13</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>21-Aug 8:34</t>
+          <t>21-Aug 14:53</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.07x</t>
+          <t>1.52x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>21-Aug 8:29</t>
+          <t>21-Aug 14:57</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1427,67 +1427,67 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOC</t>
+          <t>Dhanwel Hybrid Seeds BSE SMECT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹80 (22.22%) 17 ↓ / 80 ↑</t>
+          <t>₹1 (1.01%) 1 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>105.81x</t>
+          <t>1.51x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹26.73 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 77</t>
+          <t>19-Aug GMP: 12</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 80</t>
+          <t>21-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>21-Aug 8:29</t>
+          <t>21-Aug 14:58</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -1561,47 +1561,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOC</t>
+          <t>Sunshine Pictures IPOC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹5 (5.38%) 2 ↓ / 8 ↑</t>
+          <t>₹72 (20.00%) 17 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.8x</t>
+          <t>105.81x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹367.18 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 5</t>
+          <t>18-Aug GMP: 77</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 5</t>
+          <t>20-Aug GMP: 80</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>21-Aug 8:33</t>
+          <t>21-Aug 15:00</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1628,12 +1628,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks IPOCAllotted</t>
+          <t>Shankesh Jewellers IPOC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹3.4 (5.67%) 1 ↓ / 4.50 ↑</t>
+          <t>₹5 (5.38%) 2 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1643,47 +1643,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.52x</t>
+          <t>2.8x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹2600.04 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 1.7</t>
+          <t>18-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 1.3</t>
+          <t>20-Aug GMP: 5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>21-Aug 8:30</t>
+          <t>21-Aug 14:54</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>21-Aug 8:36</t>
+          <t>21-Aug 14:59</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1762,47 +1762,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOCAllotted</t>
+          <t>Horizon Industrial Parks IPOCAllotted</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹60 (29.85%) 17 ↓ / 61 ↑</t>
+          <t>₹3.6 (6.00%) 1 ↓ / 4.50 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>66.63x</t>
+          <t>1.52x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹2600.04 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 30</t>
+          <t>17-Aug GMP: 1.7</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 54</t>
+          <t>19-Aug GMP: 1.3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>21-Aug 8:31</t>
+          <t>21-Aug 14:57</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1829,62 +1829,62 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems BSE SMELT</t>
+          <t>Lalithaa Jewellery Mart IPOCAllotted</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹70 (53.03%) 12 ↓ / 70 ↑</t>
+          <t>₹54 (26.87%) 17 ↓ / 61 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>203.36x</t>
+          <t>66.63x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹60.98 Cr</t>
+          <t>₹1700.00 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 30</t>
+          <t>17-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 43</t>
+          <t>19-Aug GMP: 54</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 70</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>21-Aug 8:28</t>
+          <t>21-Aug 15:00</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1896,47 +1896,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMELT</t>
+          <t>Skytech Infinite Platform NSE SMEL@74.00 (-3.9%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹5 (5.43%) 4 ↓ / 5 ↑</t>
+          <t>₹1 (1.30%) 1 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13.11x</t>
+          <t>2.04x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹33.14 Cr</t>
+          <t>₹22.68 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 4</t>
+          <t>18-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1946,64 +1946,64 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 5</t>
+          <t>21-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>21-Aug 8:34</t>
+          <t>21-Aug 9:28</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Skytech Infinite Platform NSE SMELT</t>
+          <t>ENS Enterprises BSE SMEL@96.00 (4.35%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹1 (1.30%) 1 ↓ / 13 ↑</t>
+          <t>₹5 (5.43%) 4 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.04x</t>
+          <t>13.11x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹22.68 Cr</t>
+          <t>₹33.14 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 10</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 1</t>
+          <t>18-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2013,79 +2013,79 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 1</t>
+          <t>21-Aug GMP: 5</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>21-Aug 8:34</t>
+          <t>21-Aug 9:30</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Credent Connect NSE SMEL@359.10 (90%)</t>
+          <t>Technocrats Plasma Systems BSE SMEL@230.00 (74.24%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹92 (48.68%) 35 ↓ / 92 ↑</t>
+          <t>₹70 (53.03%) 12 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>153.13x</t>
+          <t>203.36x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹93.90 Cr</t>
+          <t>₹60.98 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 75</t>
+          <t>14-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 45</t>
+          <t>18-Aug GMP: 43</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 92</t>
+          <t>21-Aug GMP: 70</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>20-Aug 9:30</t>
+          <t>21-Aug 9:36</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2097,67 +2097,67 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods BSE SMEL@115.00 (0%)</t>
+          <t>Credent Connect NSE SMEL@359.10 (90%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
+          <t>₹92 (48.68%) 35 ↓ / 92 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>153.13x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹26.25 Cr</t>
+          <t>₹93.90 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 10</t>
+          <t>13-Aug GMP: 75</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 1</t>
+          <t>17-Aug GMP: 45</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 1</t>
+          <t>20-Aug GMP: 92</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>19-Aug 9:31</t>
+          <t>20-Aug 9:30</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -2231,47 +2231,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMEL@120.00 (1.69%)</t>
+          <t>Behari Lal Engineering IPOL@465.00 (63.16%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹133 (46.67%) 25 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3.87x</t>
+          <t>118.07x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>285</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 0</t>
+          <t>12-Aug GMP: 74</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 83</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0</t>
+          <t>19-Aug GMP: 133</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>19-Aug 9:29</t>
+          <t>19-Aug 9:32</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2298,47 +2298,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOL@465.00 (63.16%)</t>
+          <t>Q&amp;T Foods BSE SMEL@115.00 (0%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹133 (46.67%) 25 ↓ / 133 ↑</t>
+          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>118.07x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹26.25 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 74</t>
+          <t>12-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 83</t>
+          <t>14-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2348,79 +2348,79 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 133</t>
+          <t>19-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>19-Aug 9:32</t>
+          <t>19-Aug 9:31</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food IPOL@165.00 (17.86%)</t>
+          <t>Pramodini Medicare NSE SMEL@120.00 (1.69%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹19.7 (14.07%) 18 ↓ / 27 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>59.08x</t>
+          <t>3.87x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹1553.00 Cr</t>
+          <t>₹69.04 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 22.5</t>
+          <t>12-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 26</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 19.7</t>
+          <t>19-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>18-Aug 9:34</t>
+          <t>19-Aug 9:29</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2432,47 +2432,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sham Foam BSE SMEL@104.00 (-20%)</t>
+          <t>Milky Mist Dairy Food IPOL@165.00 (17.86%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹1.5 (1.15%) 1.50 ↓ / 9 ↑</t>
+          <t>₹19.7 (14.07%) 18 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.4x</t>
+          <t>59.08x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹40.48 Cr</t>
+          <t>₹1553.00 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>11-Aug GMP: 22.5</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 4</t>
+          <t>13-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2482,84 +2482,84 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 1.5</t>
+          <t>18-Aug GMP: 19.7</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>18-Aug 9:28</t>
+          <t>18-Aug 9:34</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dhoot Transmission IPOL@1200.00 (37.77%)</t>
+          <t>Sham Foam BSE SMEL@104.00 (-20%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹262 (30.08%) 146 ↓ / 276 ↑</t>
+          <t>₹1.5 (1.15%) 1.50 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>75.06x</t>
+          <t>2.4x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹3066.89 Cr</t>
+          <t>₹40.48 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 250</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 276</t>
+          <t>13-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 262</t>
+          <t>18-Aug GMP: 1.5</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>17-Aug 8:54</t>
+          <t>18-Aug 9:28</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>21-Aug 5:55</t>
+          <t>22-Aug 5:55</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹15 (0.00%) 15 ↓ / 15 ↑</t>
+          <t>₹43 (47.78%) 15 ↓ / 43 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -580,15 +580,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>₹50.77 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>27-Aug</t>
@@ -611,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>21-Aug 15:00</t>
+          <t>22-Aug 9:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -628,7 +632,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹45 (54.88%) 45 ↓ / 45 ↑</t>
+          <t>₹46 (56.10%) 46 ↓ / 46 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -678,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>21-Aug 14:57</t>
+          <t>22-Aug 8:59</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -745,7 +749,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>21-Aug 14:57</t>
+          <t>22-Aug 9:00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -812,7 +816,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>21-Aug 14:58</t>
+          <t>22-Aug 8:56</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -879,7 +883,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>21-Aug 14:56</t>
+          <t>22-Aug 9:02</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -946,7 +950,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>21-Aug 14:55</t>
+          <t>22-Aug 8:59</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -963,7 +967,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹320 (32.39%) 220 ↓ / 320 ↑</t>
+          <t>₹345 (34.92%) 220 ↓ / 345 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,7 +1017,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>21-Aug 15:01</t>
+          <t>22-Aug 8:57</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1080,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>21-Aug 14:53</t>
+          <t>22-Aug 9:01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1147,7 +1151,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>21-Aug 14:59</t>
+          <t>22-Aug 9:00</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1164,7 +1168,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹300 (38.07%) 190 ↓ / 300 ↑</t>
+          <t>₹310 (39.34%) 190 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1174,7 +1178,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.77x</t>
+          <t>2.88x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1194,7 +1198,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 300</t>
+          <t>21-Aug GMP: 310</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1214,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>21-Aug 14:55</t>
+          <t>22-Aug 9:00</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1231,7 +1235,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹277 (92.33%) 65 ↓ / 277 ↑</t>
+          <t>₹290 (96.67%) 65 ↓ / 290 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,7 +1245,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>18.02x</t>
+          <t>21.69x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1281,7 +1285,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>21-Aug 14:58</t>
+          <t>22-Aug 8:57</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1293,22 +1297,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOCT</t>
+          <t>Gaja Alternative Asset Management IPOC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹13 (8.12%) 7 ↓ / 30 ↑</t>
+          <t>₹19 (11.88%) 7 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>21.05x</t>
+          <t>32.98x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1333,7 +1337,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 13</t>
+          <t>21-Aug GMP: 19</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1348,7 +1352,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>21-Aug 14:53</t>
+          <t>22-Aug 8:56</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1360,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mopshop Distribution BSE SMECT</t>
+          <t>Mopshop Distribution BSE SMEC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1375,7 +1379,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.52x</t>
+          <t>1.59x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1415,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>21-Aug 14:57</t>
+          <t>22-Aug 8:58</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1427,7 +1431,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMECT</t>
+          <t>Dhanwel Hybrid Seeds BSE SMEC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1442,7 +1446,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.51x</t>
+          <t>1.65x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1482,7 +1486,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>21-Aug 14:58</t>
+          <t>22-Aug 8:57</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1561,17 +1565,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOC</t>
+          <t>Sunshine Pictures IPOCAllotted</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹72 (20.00%) 17 ↓ / 80 ↑</t>
+          <t>₹62 (17.22%) 17 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1616,7 +1620,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>21-Aug 15:00</t>
+          <t>22-Aug 8:56</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1628,17 +1632,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOC</t>
+          <t>Shankesh Jewellers IPOCAllotted</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹5 (5.38%) 2 ↓ / 8 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1683,7 +1687,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>21-Aug 14:54</t>
+          <t>22-Aug 8:54</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1750,7 +1754,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>21-Aug 14:59</t>
+          <t>22-Aug 8:57</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1767,12 +1771,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹3.6 (6.00%) 1 ↓ / 4.50 ↑</t>
+          <t>₹2.5 (4.17%) 1 ↓ / 4.50 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1817,7 +1821,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>21-Aug 14:57</t>
+          <t>22-Aug 8:54</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1834,7 +1838,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹54 (26.87%) 17 ↓ / 61 ↑</t>
+          <t>₹66 (32.84%) 17 ↓ / 66 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1884,7 +1888,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>21-Aug 15:00</t>
+          <t>22-Aug 8:55</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>22-Aug 9:00</t>
+          <t>22-Aug 14:53</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>22-Aug 8:59</t>
+          <t>22-Aug 14:53</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>22-Aug 9:00</t>
+          <t>22-Aug 15:01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>22-Aug 8:56</t>
+          <t>22-Aug 14:56</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>22-Aug 9:02</t>
+          <t>22-Aug 14:58</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>22-Aug 8:59</t>
+          <t>22-Aug 14:56</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹345 (34.92%) 220 ↓ / 345 ↑</t>
+          <t>₹365 (36.94%) 220 ↓ / 365 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>22-Aug 8:57</t>
+          <t>22-Aug 14:58</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹22 (41.51%) 5 ↓ / 22 ↑</t>
+          <t>₹25 (47.17%) 5 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>22-Aug 9:01</t>
+          <t>22-Aug 15:00</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹45 (32.61%) 19 ↓ / 50 ↑</t>
+          <t>₹42 (30.43%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>22-Aug 9:00</t>
+          <t>22-Aug 14:56</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹310 (39.34%) 190 ↓ / 310 ↑</t>
+          <t>₹370 (46.95%) 190 ↓ / 370 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>22-Aug 9:00</t>
+          <t>22-Aug 14:57</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹290 (96.67%) 65 ↓ / 290 ↑</t>
+          <t>₹315 (105.00%) 65 ↓ / 315 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>22-Aug 8:57</t>
+          <t>22-Aug 15:01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹19 (11.88%) 7 ↓ / 30 ↑</t>
+          <t>₹17.5 (10.94%) 7 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>22-Aug 8:56</t>
+          <t>22-Aug 15:01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>22-Aug 8:58</t>
+          <t>22-Aug 15:00</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>22-Aug 8:57</t>
+          <t>22-Aug 15:00</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹62 (17.22%) 17 ↓ / 80 ↑</t>
+          <t>₹65 (18.06%) 17 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>22-Aug 8:56</t>
+          <t>22-Aug 14:53</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 8 ↑</t>
+          <t>₹2 (2.15%) 1 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>22-Aug 8:54</t>
+          <t>22-Aug 14:55</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>22-Aug 8:57</t>
+          <t>22-Aug 15:02</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>22-Aug 8:54</t>
+          <t>22-Aug 14:59</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹66 (32.84%) 17 ↓ / 66 ↑</t>
+          <t>₹70 (34.83%) 17 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>22-Aug 8:55</t>
+          <t>22-Aug 14:53</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>22-Aug 5:55</t>
+          <t>23-Aug 5:55</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -560,17 +560,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kwick Forensic Solutions BSE SMEU</t>
+          <t>Complete Sports and Management BSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹43 (47.78%) 15 ↓ / 43 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -578,44 +578,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹50.77 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>22-Aug 14:53</t>
+          <t>23-Aug 5:55</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -627,12 +619,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lumino Industries IPOU</t>
+          <t>Kwick Forensic Solutions BSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹46 (56.10%) 46 ↓ / 46 ↑</t>
+          <t>₹51 (56.67%) 15 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -647,17 +639,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹700.00 Cr</t>
+          <t>₹50.77 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -682,7 +674,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>22-Aug 14:53</t>
+          <t>23-Aug 8:55</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -694,17 +686,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sumax Engineering NSE SMEU</t>
+          <t>Lumino Industries IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹32 (31.68%) 20 ↓ / 32 ↑</t>
+          <t>₹52 (63.41%) 46 ↓ / 52 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -714,42 +706,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹53.40 Cr</t>
+          <t>₹700.00 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>182</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>22-Aug 15:01</t>
+          <t>23-Aug 8:56</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -816,7 +808,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>22-Aug 14:56</t>
+          <t>23-Aug 8:55</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -828,17 +820,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ABH Healthcare NSE SMEU</t>
+          <t>Sumax Engineering NSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹32 (31.68%) 20 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -848,12 +840,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹34.98 Cr</t>
+          <t>₹53.40 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -863,49 +855,49 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>22-Aug 14:58</t>
+          <t>23-Aug 8:56</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Madhur Knit NSE SMEU</t>
+          <t>Skyways Air IPOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹37 (26.81%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -915,19 +907,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>₹582.80 Cr</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>₹53.27 Cr</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>24-Aug</t>
@@ -950,7 +942,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>22-Aug 14:56</t>
+          <t>23-Aug 8:57</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -962,17 +954,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOU</t>
+          <t>ABH Healthcare NSE SMEU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹365 (36.94%) 220 ↓ / 365 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -982,17 +974,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹1757.00 Cr</t>
+          <t>₹34.98 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1017,29 +1009,29 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>22-Aug 14:58</t>
+          <t>23-Aug 8:59</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOU</t>
+          <t>Madhur Knit NSE SMEU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹25 (47.17%) 5 ↓ / 25 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1049,17 +1041,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹135.73 Cr</t>
+          <t>₹53.27 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1084,7 +1076,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>22-Aug 15:00</t>
+          <t>23-Aug 8:59</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1096,17 +1088,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Skyways Air IPOU</t>
+          <t>Hy-Tech Engineers IPOU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹42 (30.43%) 19 ↓ / 50 ↑</t>
+          <t>₹27 (50.94%) 5 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1116,17 +1108,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹135.73 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1151,7 +1143,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>22-Aug 14:56</t>
+          <t>23-Aug 8:58</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1163,12 +1155,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOO</t>
+          <t>Symbiotec Pharmalab IPOU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹370 (46.95%) 190 ↓ / 370 ↑</t>
+          <t>₹410 (41.50%) 220 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1178,47 +1170,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.88x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹825.00 Cr</t>
+          <t>₹1757.00 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 310</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>22-Aug 14:57</t>
+          <t>23-Aug 8:53</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1230,12 +1222,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOO</t>
+          <t>Augmont Enterprises IPOO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹315 (105.00%) 65 ↓ / 315 ↑</t>
+          <t>₹395 (50.13%) 190 ↓ / 395 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1245,47 +1237,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>21.69x</t>
+          <t>2.88x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹825.00 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 270</t>
+          <t>21-Aug GMP: 310</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>22-Aug 15:01</t>
+          <t>23-Aug 8:53</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1297,62 +1289,62 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOC</t>
+          <t>Tempsens Instruments (India) IPOO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹17.5 (10.94%) 7 ↓ / 30 ↑</t>
+          <t>₹321 (107.00%) 65 ↓ / 321 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>32.98x</t>
+          <t>21.69x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹550.00 Cr</t>
+          <t>₹650.00 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 23</t>
+          <t>20-Aug GMP: 270</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 19</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>22-Aug 15:01</t>
+          <t>23-Aug 9:01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1364,47 +1356,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mopshop Distribution BSE SMEC</t>
+          <t>Gaja Alternative Asset Management IPOC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹1 (0.72%) 1 ↓ / 22 ↑</t>
+          <t>₹17 (10.62%) 7 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.59x</t>
+          <t>32.98x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹27.26 Cr</t>
+          <t>₹550.00 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 5</t>
+          <t>19-Aug GMP: 23</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 1</t>
+          <t>21-Aug GMP: 19</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1419,12 +1411,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>22-Aug 15:00</t>
+          <t>23-Aug 8:59</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1478,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>22-Aug 15:00</t>
+          <t>23-Aug 9:01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1565,67 +1557,67 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOCAllotted</t>
+          <t>Mopshop Distribution BSE SMEC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹65 (18.06%) 17 ↓ / 80 ↑</t>
+          <t>₹1 (0.72%) 1 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>105.81x</t>
+          <t>1.59x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹27.26 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 77</t>
+          <t>19-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 80</t>
+          <t>21-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>22-Aug 14:53</t>
+          <t>23-Aug 8:57</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1679,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>22-Aug 14:55</t>
+          <t>23-Aug 8:59</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1699,114 +1691,114 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMEC</t>
+          <t>Sunshine Pictures IPOCAllotted</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹68 (18.89%) 17 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.48x</t>
+          <t>105.81x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹64.83 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>18-Aug GMP: 77</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0</t>
+          <t>20-Aug GMP: 80</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>22-Aug 15:02</t>
+          <t>23-Aug 8:56</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks IPOCAllotted</t>
+          <t>Lalithaa Jewellery Mart IPOCAllotted</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹2.5 (4.17%) 1 ↓ / 4.50 ↑</t>
+          <t>₹77 (38.31%) 17 ↓ / 77 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.52x</t>
+          <t>66.63x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹2600.04 Cr</t>
+          <t>₹1700.00 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 1.7</t>
+          <t>17-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 1.3</t>
+          <t>19-Aug GMP: 54</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1821,7 +1813,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>22-Aug 14:59</t>
+          <t>23-Aug 9:01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1833,47 +1825,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOCAllotted</t>
+          <t>Fascinate Textiles NSE SMEC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹70 (34.83%) 17 ↓ / 70 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>66.63x</t>
+          <t>1.48x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹64.83 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 30</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 54</t>
+          <t>19-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1888,126 +1880,126 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>22-Aug 14:53</t>
+          <t>23-Aug 9:01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Skytech Infinite Platform NSE SMEL@74.00 (-3.9%)</t>
+          <t>Horizon Industrial Parks IPOCAllotted</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹1 (1.30%) 1 ↓ / 13 ↑</t>
+          <t>₹3 (5.00%) 1 ↓ / 4.50 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.04x</t>
+          <t>1.52x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹22.68 Cr</t>
+          <t>₹2600.04 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 10</t>
+          <t>17-Aug GMP: 1.7</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 1</t>
+          <t>19-Aug GMP: 1.3</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 1</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>21-Aug 9:28</t>
+          <t>23-Aug 9:02</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMEL@96.00 (4.35%)</t>
+          <t>Skytech Infinite Platform NSE SMEL@74.00 (-3.9%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹5 (5.43%) 4 ↓ / 5 ↑</t>
+          <t>₹1 (1.30%) 1 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>13.11x</t>
+          <t>2.04x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹33.14 Cr</t>
+          <t>₹22.68 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 4</t>
+          <t>18-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2017,64 +2009,64 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 5</t>
+          <t>21-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>21-Aug 9:30</t>
+          <t>21-Aug 9:28</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems BSE SMEL@230.00 (74.24%)</t>
+          <t>ENS Enterprises BSE SMEL@96.00 (4.35%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹70 (53.03%) 12 ↓ / 70 ↑</t>
+          <t>₹5 (5.43%) 4 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>203.36x</t>
+          <t>13.11x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹60.98 Cr</t>
+          <t>₹33.14 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 30</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 43</t>
+          <t>18-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2084,12 +2076,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 70</t>
+          <t>21-Aug GMP: 5</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>21-Aug 9:36</t>
+          <t>21-Aug 9:30</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2101,62 +2093,62 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Credent Connect NSE SMEL@359.10 (90%)</t>
+          <t>Technocrats Plasma Systems BSE SMEL@230.00 (74.24%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹92 (48.68%) 35 ↓ / 92 ↑</t>
+          <t>₹70 (53.03%) 12 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>153.13x</t>
+          <t>203.36x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹93.90 Cr</t>
+          <t>₹60.98 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 75</t>
+          <t>14-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 45</t>
+          <t>18-Aug GMP: 43</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 92</t>
+          <t>21-Aug GMP: 70</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>20-Aug 9:30</t>
+          <t>21-Aug 9:36</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2168,12 +2160,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Shiprocket IPOL@131.00 (35.05%)</t>
+          <t>Credent Connect NSE SMEL@359.10 (90%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹35 (36.08%) 14 ↓ / 36.50 ↑</t>
+          <t>₹92 (48.68%) 35 ↓ / 92 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2183,47 +2175,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>102.28x</t>
+          <t>153.13x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹93.90 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 34</t>
+          <t>13-Aug GMP: 75</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 34</t>
+          <t>17-Aug GMP: 45</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 35</t>
+          <t>20-Aug GMP: 92</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>19-Aug 9:33</t>
+          <t>20-Aug 9:30</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2235,12 +2227,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOL@465.00 (63.16%)</t>
+          <t>Shiprocket IPOL@131.00 (35.05%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹133 (46.67%) 25 ↓ / 133 ↑</t>
+          <t>₹35 (36.08%) 14 ↓ / 36.50 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2250,32 +2242,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>118.07x</t>
+          <t>102.28x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹1617.48 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 74</t>
+          <t>12-Aug GMP: 34</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 83</t>
+          <t>14-Aug GMP: 34</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2285,12 +2277,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 133</t>
+          <t>19-Aug GMP: 35</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>19-Aug 9:32</t>
+          <t>19-Aug 9:33</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2302,12 +2294,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods BSE SMEL@115.00 (0%)</t>
+          <t>Pramodini Medicare NSE SMEL@120.00 (1.69%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2317,17 +2309,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>3.87x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹26.25 Cr</t>
+          <t>₹69.04 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2337,12 +2329,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 10</t>
+          <t>12-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 1</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2352,29 +2344,29 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 1</t>
+          <t>19-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>19-Aug 9:31</t>
+          <t>19-Aug 9:29</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMEL@120.00 (1.69%)</t>
+          <t>Q&amp;T Foods BSE SMEL@115.00 (0%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2384,17 +2376,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3.87x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
+          <t>₹26.25 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2404,12 +2396,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 0</t>
+          <t>12-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2419,79 +2411,79 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0</t>
+          <t>19-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>19-Aug 9:29</t>
+          <t>19-Aug 9:31</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food IPOL@165.00 (17.86%)</t>
+          <t>Behari Lal Engineering IPOL@465.00 (63.16%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹19.7 (14.07%) 18 ↓ / 27 ↑</t>
+          <t>₹133 (46.67%) 25 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>59.08x</t>
+          <t>118.07x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>285</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹1553.00 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 22.5</t>
+          <t>12-Aug GMP: 74</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 26</t>
+          <t>14-Aug GMP: 83</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 19.7</t>
+          <t>19-Aug GMP: 133</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>18-Aug 9:34</t>
+          <t>19-Aug 9:32</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,12 +501,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rays of Belief IPOU</t>
+          <t>Priority Jewels IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -526,29 +526,13 @@
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1-Sep</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3-Sep</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>4-Sep</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>8-Sep</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>23-Aug 5:55</t>
+          <t>23-Aug 13:40</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -560,7 +544,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Complete Sports and Management BSE SMEU</t>
+          <t>Rays of Belief IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -587,22 +571,22 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -619,17 +603,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kwick Forensic Solutions BSE SMEU</t>
+          <t>Complete Sports and Management BSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹51 (56.67%) 15 ↓ / 51 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -637,44 +621,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹50.77 Cr</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>23-Aug 8:55</t>
+          <t>23-Aug 5:55</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -686,12 +662,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lumino Industries IPOU</t>
+          <t>Kwick Forensic Solutions BSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹52 (63.41%) 46 ↓ / 52 ↑</t>
+          <t>₹61 (67.78%) 15 ↓ / 61 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -706,17 +682,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹700.00 Cr</t>
+          <t>₹50.77 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -741,7 +717,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>23-Aug 8:56</t>
+          <t>23-Aug 14:55</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -753,17 +729,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Annu Projects IPOU</t>
+          <t>Lumino Industries IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹4 (4.04%) 4 ↓ / 4 ↑</t>
+          <t>₹52 (63.41%) 46 ↓ / 52 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -773,42 +749,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹175.06 Cr</t>
+          <t>₹700.00 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>182</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>23-Aug 8:55</t>
+          <t>23-Aug 15:00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -820,17 +796,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sumax Engineering NSE SMEU</t>
+          <t>Annu Projects IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹32 (31.68%) 20 ↓ / 32 ↑</t>
+          <t>₹4 (4.04%) 4 ↓ / 4 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -840,17 +816,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹53.40 Cr</t>
+          <t>₹175.06 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -875,7 +851,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>23-Aug 8:56</t>
+          <t>23-Aug 14:57</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -887,12 +863,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Skyways Air IPOU</t>
+          <t>Sumax Engineering NSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹37 (26.81%) 19 ↓ / 50 ↑</t>
+          <t>₹32 (31.68%) 20 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -907,42 +883,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹53.40 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>23-Aug 8:57</t>
+          <t>23-Aug 14:56</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1009,7 +985,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>23-Aug 8:59</t>
+          <t>23-Aug 15:02</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1021,17 +997,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Madhur Knit NSE SMEU</t>
+          <t>Skyways Air IPOU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹34 (24.64%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1041,19 +1017,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>₹582.80 Cr</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>₹53.27 Cr</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>24-Aug</t>
@@ -1076,7 +1052,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>23-Aug 8:59</t>
+          <t>23-Aug 14:53</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1088,17 +1064,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOU</t>
+          <t>Madhur Knit NSE SMEU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹27 (50.94%) 5 ↓ / 27 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1108,17 +1084,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹135.73 Cr</t>
+          <t>₹53.27 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1143,7 +1119,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>23-Aug 8:58</t>
+          <t>23-Aug 14:55</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1155,17 +1131,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOU</t>
+          <t>Hy-Tech Engineers IPOU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹410 (41.50%) 220 ↓ / 410 ↑</t>
+          <t>₹29 (54.72%) 5 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1175,17 +1151,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹1757.00 Cr</t>
+          <t>₹135.73 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1210,7 +1186,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>23-Aug 8:53</t>
+          <t>23-Aug 15:00</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1222,62 +1198,62 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOO</t>
+          <t>Symbiotec Pharmalab IPOU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹395 (50.13%) 190 ↓ / 395 ↑</t>
+          <t>₹409 (41.40%) 220 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.88x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹825.00 Cr</t>
+          <t>₹1757.00 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 310</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>23-Aug 8:53</t>
+          <t>23-Aug 14:55</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1289,62 +1265,62 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOO</t>
+          <t>Augmont Enterprises IPOO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹321 (107.00%) 65 ↓ / 321 ↑</t>
+          <t>₹380 (48.22%) 190 ↓ / 395 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>21.69x</t>
+          <t>2.88x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹825.00 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 270</t>
+          <t>21-Aug GMP: 310</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>23-Aug 9:01</t>
+          <t>23-Aug 15:01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1356,62 +1332,62 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOC</t>
+          <t>Tempsens Instruments (India) IPOO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹17 (10.62%) 7 ↓ / 30 ↑</t>
+          <t>₹321 (107.00%) 65 ↓ / 321 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>32.98x</t>
+          <t>21.69x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹550.00 Cr</t>
+          <t>₹650.00 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 23</t>
+          <t>20-Aug GMP: 270</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 19</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>23-Aug 8:59</t>
+          <t>23-Aug 14:53</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1423,47 +1399,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMEC</t>
+          <t>Gaja Alternative Asset Management IPOC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹1 (1.01%) 1 ↓ / 12 ↑</t>
+          <t>₹17.25 (10.78%) 7 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.65x</t>
+          <t>32.98x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹26.73 Cr</t>
+          <t>₹550.00 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 12</t>
+          <t>19-Aug GMP: 23</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 1</t>
+          <t>21-Aug GMP: 19</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1478,12 +1454,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>23-Aug 9:01</t>
+          <t>23-Aug 14:56</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1533,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mopshop Distribution BSE SMEC</t>
+          <t>Dhanwel Hybrid Seeds BSE SMEC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹1 (0.72%) 1 ↓ / 22 ↑</t>
+          <t>₹1 (1.01%) 1 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1572,27 +1548,27 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.59x</t>
+          <t>1.65x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹27.26 Cr</t>
+          <t>₹26.73 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 5</t>
+          <t>19-Aug GMP: 12</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1612,7 +1588,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>23-Aug 8:57</t>
+          <t>23-Aug 14:56</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1624,12 +1600,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOCAllotted</t>
+          <t>Mopshop Distribution BSE SMEC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹2 (2.15%) 1 ↓ / 8 ↑</t>
+          <t>₹1 (0.72%) 1 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1639,99 +1615,99 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.8x</t>
+          <t>1.59x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹367.18 Cr</t>
+          <t>₹27.26 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 5</t>
+          <t>19-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 5</t>
+          <t>21-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>23-Aug 8:59</t>
+          <t>23-Aug 15:02</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOCAllotted</t>
+          <t>Shankesh Jewellers IPOCAllotted</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹68 (18.89%) 17 ↓ / 80 ↑</t>
+          <t>₹2 (2.15%) 1 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>105.81x</t>
+          <t>2.8x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 77</t>
+          <t>18-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 80</t>
+          <t>20-Aug GMP: 5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1746,7 +1722,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>23-Aug 8:56</t>
+          <t>23-Aug 14:53</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1758,62 +1734,62 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOCAllotted</t>
+          <t>Sunshine Pictures IPOCAllotted</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹77 (38.31%) 17 ↓ / 77 ↑</t>
+          <t>₹68 (18.89%) 17 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>66.63x</t>
+          <t>105.81x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 30</t>
+          <t>18-Aug GMP: 77</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 54</t>
+          <t>20-Aug GMP: 80</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>23-Aug 9:01</t>
+          <t>23-Aug 15:00</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1825,12 +1801,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMEC</t>
+          <t>Horizon Industrial Parks IPOCAllotted</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1.5 (2.50%) 1 ↓ / 4.50 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1840,32 +1816,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.48x</t>
+          <t>1.52x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹64.83 Cr</t>
+          <t>₹2600.04 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>17-Aug GMP: 1.7</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0</t>
+          <t>19-Aug GMP: 1.3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1880,59 +1856,59 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>23-Aug 9:01</t>
+          <t>23-Aug 14:56</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks IPOCAllotted</t>
+          <t>Fascinate Textiles NSE SMEC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹3 (5.00%) 1 ↓ / 4.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.52x</t>
+          <t>1.48x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹2600.04 Cr</t>
+          <t>₹64.83 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 1.7</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 1.3</t>
+          <t>19-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1947,79 +1923,79 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>23-Aug 9:02</t>
+          <t>23-Aug 14:56</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Skytech Infinite Platform NSE SMEL@74.00 (-3.9%)</t>
+          <t>Lalithaa Jewellery Mart IPOCAllotted</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹1 (1.30%) 1 ↓ / 13 ↑</t>
+          <t>₹74 (36.82%) 17 ↓ / 77 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.04x</t>
+          <t>66.63x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹22.68 Cr</t>
+          <t>₹1700.00 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 10</t>
+          <t>17-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 1</t>
+          <t>19-Aug GMP: 54</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 1</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>21-Aug 9:28</t>
+          <t>23-Aug 14:54</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -2160,79 +2136,79 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Credent Connect NSE SMEL@359.10 (90%)</t>
+          <t>Skytech Infinite Platform NSE SMEL@74.00 (-3.9%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹92 (48.68%) 35 ↓ / 92 ↑</t>
+          <t>₹1 (1.30%) 1 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>153.13x</t>
+          <t>2.04x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹93.90 Cr</t>
+          <t>₹22.68 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 75</t>
+          <t>14-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 45</t>
+          <t>18-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 92</t>
+          <t>21-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>20-Aug 9:30</t>
+          <t>21-Aug 9:28</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Shiprocket IPOL@131.00 (35.05%)</t>
+          <t>Credent Connect NSE SMEL@359.10 (90%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹35 (36.08%) 14 ↓ / 36.50 ↑</t>
+          <t>₹92 (48.68%) 35 ↓ / 92 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2242,47 +2218,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>102.28x</t>
+          <t>153.13x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹93.90 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 34</t>
+          <t>13-Aug GMP: 75</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 34</t>
+          <t>17-Aug GMP: 45</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 35</t>
+          <t>20-Aug GMP: 92</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>19-Aug 9:33</t>
+          <t>20-Aug 9:30</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2294,47 +2270,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMEL@120.00 (1.69%)</t>
+          <t>Behari Lal Engineering IPOL@465.00 (63.16%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹133 (46.67%) 25 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3.87x</t>
+          <t>118.07x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>285</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 0</t>
+          <t>12-Aug GMP: 74</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 83</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2344,12 +2320,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0</t>
+          <t>19-Aug GMP: 133</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>19-Aug 9:29</t>
+          <t>19-Aug 9:32</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2428,47 +2404,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOL@465.00 (63.16%)</t>
+          <t>Pramodini Medicare NSE SMEL@120.00 (1.69%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹133 (46.67%) 25 ↓ / 133 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>118.07x</t>
+          <t>3.87x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹69.04 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 74</t>
+          <t>12-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 83</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2478,12 +2454,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 133</t>
+          <t>19-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>19-Aug 9:32</t>
+          <t>19-Aug 9:29</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2495,67 +2471,67 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sham Foam BSE SMEL@104.00 (-20%)</t>
+          <t>Shiprocket IPOL@131.00 (35.05%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹1.5 (1.15%) 1.50 ↓ / 9 ↑</t>
+          <t>₹35 (36.08%) 14 ↓ / 36.50 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.4x</t>
+          <t>102.28x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹40.48 Cr</t>
+          <t>₹1617.48 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>12-Aug GMP: 34</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 4</t>
+          <t>14-Aug GMP: 34</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>14-Aug</t>
+          <t>17-Aug</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 1.5</t>
+          <t>19-Aug GMP: 35</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>18-Aug 9:28</t>
+          <t>19-Aug 9:33</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Priority Jewels IPOU</t>
+          <t>Paluck Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -519,20 +519,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>₹33.00 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>28-Aug</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1-Sep</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2-Sep</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4-Sep</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>23-Aug 13:40</t>
+          <t>24-Aug 8:20</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -544,12 +568,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rays of Belief IPOU</t>
+          <t>Shanti Inorganics NSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -562,36 +586,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>₹41.50 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>2-Sep</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>3-Sep</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>4-Sep</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8-Sep</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>23-Aug 5:55</t>
+          <t>24-Aug 8:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -603,7 +635,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Complete Sports and Management BSE SMEU</t>
+          <t>Rays of Belief IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -621,36 +653,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>₹125.00 Cr</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>23-Aug 5:55</t>
+          <t>24-Aug 8:58</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -662,17 +702,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kwick Forensic Solutions BSE SMEU</t>
+          <t>Complete Sports and Management BSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹61 (67.78%) 15 ↓ / 61 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -682,42 +722,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹50.77 Cr</t>
+          <t>₹74.93 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>23-Aug 14:55</t>
+          <t>24-Aug 8:56</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -729,17 +769,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lumino Industries IPOU</t>
+          <t>Priority Jewels IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹52 (63.41%) 46 ↓ / 52 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -749,42 +789,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹700.00 Cr</t>
+          <t>₹91.50 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>23-Aug 15:00</t>
+          <t>24-Aug 8:55</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -796,17 +836,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Annu Projects IPOU</t>
+          <t>Lumino Industries IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹4 (4.04%) 4 ↓ / 4 ↑</t>
+          <t>₹49 (59.76%) 46 ↓ / 52 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -816,42 +856,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹175.06 Cr</t>
+          <t>₹700.00 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>182</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>23-Aug 14:57</t>
+          <t>24-Aug 8:54</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -863,17 +903,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sumax Engineering NSE SMEU</t>
+          <t>Kwick Forensic Solutions BSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹32 (31.68%) 20 ↓ / 32 ↑</t>
+          <t>₹61 (67.78%) 15 ↓ / 61 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -883,42 +923,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹53.40 Cr</t>
+          <t>₹50.77 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>23-Aug 14:56</t>
+          <t>24-Aug 8:56</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -930,17 +970,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ABH Healthcare NSE SMEU</t>
+          <t>Sumax Engineering NSE SMEU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹32 (31.68%) 20 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -950,12 +990,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹34.98 Cr</t>
+          <t>₹53.40 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -965,49 +1005,49 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>23-Aug 15:02</t>
+          <t>24-Aug 9:02</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Skyways Air IPOU</t>
+          <t>Annu Projects IPOU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹34 (24.64%) 19 ↓ / 50 ↑</t>
+          <t>₹4 (4.04%) 4 ↓ / 4 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1017,42 +1057,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹175.06 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>23-Aug 14:53</t>
+          <t>24-Aug 9:02</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1064,17 +1104,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Madhur Knit NSE SMEU</t>
+          <t>Skyways Air IPOO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹32 (23.19%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1084,22 +1124,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>₹582.80 Cr</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>₹53.27 Cr</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>24-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1119,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>23-Aug 14:55</t>
+          <t>24-Aug 8:53</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1131,17 +1171,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOU</t>
+          <t>ABH Healthcare NSE SMEO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹29 (54.72%) 5 ↓ / 29 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1151,22 +1191,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹135.73 Cr</t>
+          <t>₹34.98 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>24-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1186,19 +1226,19 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>23-Aug 15:00</t>
+          <t>24-Aug 8:57</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOU</t>
+          <t>Symbiotec Pharmalab IPOO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1233,7 +1273,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>24-Aug GMP: 409</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1253,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>23-Aug 14:55</t>
+          <t>24-Aug 8:53</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1265,62 +1305,62 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOO</t>
+          <t>Madhur Knit NSE SMEO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹380 (48.22%) 190 ↓ / 395 ↑</t>
+          <t>₹9 (9.00%) 9 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.88x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹825.00 Cr</t>
+          <t>₹53.27 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 310</t>
+          <t>24-Aug GMP: 9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>23-Aug 15:01</t>
+          <t>24-Aug 8:58</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1332,62 +1372,62 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOO</t>
+          <t>Hy-Tech Engineers IPOO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹321 (107.00%) 65 ↓ / 321 ↑</t>
+          <t>₹25 (47.17%) 5 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>21.69x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹135.73 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 270</t>
+          <t>24-Aug GMP: 25</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>23-Aug 14:53</t>
+          <t>24-Aug 8:57</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1399,62 +1439,62 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOC</t>
+          <t>Augmont Enterprises IPOO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹17.25 (10.78%) 7 ↓ / 30 ↑</t>
+          <t>₹380 (48.22%) 190 ↓ / 395 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>32.98x</t>
+          <t>2.88x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹550.00 Cr</t>
+          <t>₹825.00 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 23</t>
+          <t>21-Aug GMP: 310</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 19</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>23-Aug 14:56</t>
+          <t>24-Aug 8:59</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1533,114 +1573,114 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMEC</t>
+          <t>Tempsens Instruments (India) IPOCT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹1 (1.01%) 1 ↓ / 12 ↑</t>
+          <t>₹313 (104.33%) 65 ↓ / 321 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.65x</t>
+          <t>21.69x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹26.73 Cr</t>
+          <t>₹650.00 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 12</t>
+          <t>20-Aug GMP: 270</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 1</t>
+          <t>24-Aug GMP: 313</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>23-Aug 14:56</t>
+          <t>24-Aug 8:57</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mopshop Distribution BSE SMEC</t>
+          <t>Gaja Alternative Asset Management IPOC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹1 (0.72%) 1 ↓ / 22 ↑</t>
+          <t>₹17 (10.62%) 7 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.59x</t>
+          <t>32.98x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹27.26 Cr</t>
+          <t>₹550.00 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 5</t>
+          <t>19-Aug GMP: 23</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 1</t>
+          <t>21-Aug GMP: 19</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1655,24 +1695,24 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>23-Aug 15:02</t>
+          <t>24-Aug 9:02</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOCAllotted</t>
+          <t>Mopshop Distribution BSE SMEC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹2 (2.15%) 1 ↓ / 8 ↑</t>
+          <t>₹1 (0.72%) 1 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1682,131 +1722,131 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.8x</t>
+          <t>1.59x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹367.18 Cr</t>
+          <t>₹27.26 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 5</t>
+          <t>19-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 5</t>
+          <t>21-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>23-Aug 14:53</t>
+          <t>24-Aug 8:56</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOCAllotted</t>
+          <t>Dhanwel Hybrid Seeds BSE SMEC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹68 (18.89%) 17 ↓ / 80 ↑</t>
+          <t>₹1 (1.01%) 1 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>105.81x</t>
+          <t>1.65x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹26.73 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 77</t>
+          <t>19-Aug GMP: 12</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 80</t>
+          <t>21-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>23-Aug 15:00</t>
+          <t>24-Aug 8:54</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks IPOCAllotted</t>
+          <t>Shankesh Jewellers IPOCAllotted</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹1.5 (2.50%) 1 ↓ / 4.50 ↑</t>
+          <t>₹2 (2.15%) 1 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1816,47 +1856,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.52x</t>
+          <t>2.8x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹2600.04 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 1.7</t>
+          <t>18-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 1.3</t>
+          <t>20-Aug GMP: 5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>23-Aug 14:56</t>
+          <t>24-Aug 8:58</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1868,74 +1908,74 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMEC</t>
+          <t>Sunshine Pictures IPOCAllotted</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹65 (18.06%) 17 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.48x</t>
+          <t>105.81x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹64.83 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>18-Aug GMP: 77</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0</t>
+          <t>20-Aug GMP: 80</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>23-Aug 14:56</t>
+          <t>24-Aug 9:01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOCAllotted</t>
+          <t>Lalithaa Jewellery Mart IPOLT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1985,12 +2025,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>24-Aug GMP: 74</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>23-Aug 14:54</t>
+          <t>24-Aug 8:58</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2002,129 +2042,129 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMEL@96.00 (4.35%)</t>
+          <t>Fascinate Textiles NSE SMELT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹5 (5.43%) 4 ↓ / 5 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>13.11x</t>
+          <t>1.48x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹33.14 Cr</t>
+          <t>₹64.83 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 4</t>
+          <t>19-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 5</t>
+          <t>24-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>21-Aug 9:30</t>
+          <t>24-Aug 9:01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems BSE SMEL@230.00 (74.24%)</t>
+          <t>Horizon Industrial Parks IPOLT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹70 (53.03%) 12 ↓ / 70 ↑</t>
+          <t>₹1.5 (2.50%) 1 ↓ / 4.50 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>203.36x</t>
+          <t>1.52x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹60.98 Cr</t>
+          <t>₹2600.04 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 30</t>
+          <t>17-Aug GMP: 1.7</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 43</t>
+          <t>19-Aug GMP: 1.3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 70</t>
+          <t>24-Aug GMP: 1.5</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>21-Aug 9:36</t>
+          <t>24-Aug 8:59</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2203,62 +2243,62 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Credent Connect NSE SMEL@359.10 (90%)</t>
+          <t>ENS Enterprises BSE SMEL@96.00 (4.35%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹92 (48.68%) 35 ↓ / 92 ↑</t>
+          <t>₹5 (5.43%) 4 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>153.13x</t>
+          <t>13.11x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹93.90 Cr</t>
+          <t>₹33.14 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 75</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 45</t>
+          <t>18-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 92</t>
+          <t>21-Aug GMP: 5</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>20-Aug 9:30</t>
+          <t>21-Aug 9:30</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2270,62 +2310,62 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOL@465.00 (63.16%)</t>
+          <t>Technocrats Plasma Systems BSE SMEL@230.00 (74.24%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹133 (46.67%) 25 ↓ / 133 ↑</t>
+          <t>₹70 (53.03%) 12 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>118.07x</t>
+          <t>203.36x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹60.98 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 74</t>
+          <t>14-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 83</t>
+          <t>18-Aug GMP: 43</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 133</t>
+          <t>21-Aug GMP: 70</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>19-Aug 9:32</t>
+          <t>21-Aug 9:36</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2337,79 +2377,79 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods BSE SMEL@115.00 (0%)</t>
+          <t>Credent Connect NSE SMEL@359.10 (90%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
+          <t>₹92 (48.68%) 35 ↓ / 92 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>153.13x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹26.25 Cr</t>
+          <t>₹93.90 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 10</t>
+          <t>13-Aug GMP: 75</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 1</t>
+          <t>17-Aug GMP: 45</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 1</t>
+          <t>20-Aug GMP: 92</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>19-Aug 9:31</t>
+          <t>20-Aug 9:30</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pramodini Medicare NSE SMEL@120.00 (1.69%)</t>
+          <t>Q&amp;T Foods BSE SMEL@115.00 (0%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2419,17 +2459,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3.87x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹69.04 Cr</t>
+          <t>₹26.25 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2439,12 +2479,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 0</t>
+          <t>12-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2454,17 +2494,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0</t>
+          <t>19-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>19-Aug 9:29</t>
+          <t>19-Aug 9:31</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,12 +501,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Paluck Technologies BSE SMEU</t>
+          <t>Rays of Belief IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>239</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹33.00 Cr</t>
+          <t>₹125.00 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>24-Aug 8:20</t>
+          <t>24-Aug 14:59</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹41.50 Cr</t>
+          <t>₹47.24 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Rays of Belief IPOU</t>
+          <t>Complete Sports and Management BSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -655,42 +655,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹125.00 Cr</t>
+          <t>₹74.93 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>28-Aug</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>1-Sep</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3-Sep</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>2-Sep</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>4-Sep</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>8-Sep</t>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>24-Aug 8:58</t>
+          <t>24-Aug 14:57</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Complete Sports and Management BSE SMEU</t>
+          <t>Paluck Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹74.93 Cr</t>
+          <t>₹33.00 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>24-Aug 8:56</t>
+          <t>24-Aug 14:57</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹18 (9.00%) 18 ↓ / 18 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24-Aug 8:55</t>
+          <t>24-Aug 14:56</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lumino Industries IPOU</t>
+          <t>Kwick Forensic Solutions BSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹49 (59.76%) 46 ↓ / 52 ↑</t>
+          <t>₹61 (67.78%) 15 ↓ / 61 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹700.00 Cr</t>
+          <t>₹50.77 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>24-Aug 8:54</t>
+          <t>24-Aug 14:53</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -903,12 +903,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kwick Forensic Solutions BSE SMEU</t>
+          <t>Lumino Industries IPOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹61 (67.78%) 15 ↓ / 61 ↑</t>
+          <t>₹46 (56.10%) 46 ↓ / 52 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹50.77 Cr</t>
+          <t>₹700.00 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>182</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>24-Aug 8:56</t>
+          <t>24-Aug 14:59</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -970,17 +970,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sumax Engineering NSE SMEU</t>
+          <t>Annu Projects IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹32 (31.68%) 20 ↓ / 32 ↑</t>
+          <t>₹4 (4.04%) 4 ↓ / 4 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -990,17 +990,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹53.40 Cr</t>
+          <t>₹175.06 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>24-Aug 9:02</t>
+          <t>24-Aug 14:59</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1037,17 +1037,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Annu Projects IPOU</t>
+          <t>Sumax Engineering NSE SMEU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹4 (4.04%) 4 ↓ / 4 ↑</t>
+          <t>₹32 (31.68%) 20 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹175.06 Cr</t>
+          <t>₹53.40 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>24-Aug 9:02</t>
+          <t>24-Aug 14:54</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1104,42 +1104,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Skyways Air IPOO</t>
+          <t>Madhur Knit NSE SMEO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹32 (23.19%) 19 ↓ / 50 ↑</t>
+          <t>₹16 (16.00%) 9 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.24x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹53.27 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 32</t>
+          <t>24-Aug GMP: 16</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>24-Aug 8:53</t>
+          <t>24-Aug 14:54</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.33x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>24-Aug 8:57</t>
+          <t>24-Aug 14:53</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1238,12 +1238,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOO</t>
+          <t>Skyways Air IPOO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹409 (41.40%) 220 ↓ / 410 ↑</t>
+          <t>₹33 (23.91%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1253,27 +1253,27 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.92x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹1757.00 Cr</t>
+          <t>₹582.80 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 409</t>
+          <t>24-Aug GMP: 33</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>24-Aug 8:53</t>
+          <t>24-Aug 14:57</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1305,42 +1305,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Madhur Knit NSE SMEO</t>
+          <t>Hy-Tech Engineers IPOO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹9 (9.00%) 9 ↓ / 9 ↑</t>
+          <t>₹35 (66.04%) 5 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6.08x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹53.27 Cr</t>
+          <t>₹135.73 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 9</t>
+          <t>24-Aug GMP: 35</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>24-Aug 8:58</t>
+          <t>24-Aug 14:57</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1372,12 +1372,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOO</t>
+          <t>Symbiotec Pharmalab IPOO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹25 (47.17%) 5 ↓ / 27 ↑</t>
+          <t>₹388 (39.27%) 220 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1387,27 +1387,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.69x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹135.73 Cr</t>
+          <t>₹1757.00 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 25</t>
+          <t>24-Aug GMP: 388</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>24-Aug 8:57</t>
+          <t>24-Aug 14:53</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹380 (48.22%) 190 ↓ / 395 ↑</t>
+          <t>₹372 (47.21%) 190 ↓ / 395 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.88x</t>
+          <t>12.99x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>24-Aug 8:59</t>
+          <t>24-Aug 15:00</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹313 (104.33%) 65 ↓ / 321 ↑</t>
+          <t>₹325 (108.33%) 65 ↓ / 325 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>21.69x</t>
+          <t>160.21x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 313</t>
+          <t>24-Aug GMP: 325</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>24-Aug 8:57</t>
+          <t>24-Aug 15:01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹17 (10.62%) 7 ↓ / 30 ↑</t>
+          <t>₹16.25 (10.16%) 7 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>24-Aug 9:02</t>
+          <t>24-Aug 15:02</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1707,12 +1707,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mopshop Distribution BSE SMEC</t>
+          <t>Dhanwel Hybrid Seeds BSE SMEC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹1 (0.72%) 1 ↓ / 22 ↑</t>
+          <t>₹1 (1.01%) 1 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1722,27 +1722,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.59x</t>
+          <t>1.65x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹27.26 Cr</t>
+          <t>₹26.73 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 5</t>
+          <t>19-Aug GMP: 12</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>24-Aug 8:56</t>
+          <t>24-Aug 14:53</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1774,12 +1774,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMEC</t>
+          <t>Mopshop Distribution BSE SMEC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹1 (1.01%) 1 ↓ / 12 ↑</t>
+          <t>₹1 (0.72%) 1 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.65x</t>
+          <t>1.59x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹26.73 Cr</t>
+          <t>₹27.26 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 12</t>
+          <t>19-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>24-Aug 8:54</t>
+          <t>24-Aug 14:59</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹2 (2.15%) 1 ↓ / 8 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>24-Aug 8:58</t>
+          <t>24-Aug 14:57</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹65 (18.06%) 17 ↓ / 80 ↑</t>
+          <t>₹59 (16.39%) 17 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>24-Aug 9:01</t>
+          <t>24-Aug 14:53</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1975,47 +1975,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOLT</t>
+          <t>Horizon Industrial Parks IPOL@60.25 (0.42%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹74 (36.82%) 17 ↓ / 77 ↑</t>
+          <t>₹1.5 (2.50%) 1 ↓ / 4.50 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>66.63x</t>
+          <t>1.52x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹2600.04 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 30</t>
+          <t>17-Aug GMP: 1.7</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 54</t>
+          <t>19-Aug GMP: 1.3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 74</t>
+          <t>24-Aug GMP: 1.5</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>24-Aug 8:58</t>
+          <t>24-Aug 9:37</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>24-Aug 9:01</t>
+          <t>24-Aug 9:32</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2109,47 +2109,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks IPOLT</t>
+          <t>Lalithaa Jewellery Mart IPOL@265.00 (31.84%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹1.5 (2.50%) 1 ↓ / 4.50 ↑</t>
+          <t>₹74 (36.82%) 17 ↓ / 77 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.52x</t>
+          <t>66.63x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹2600.04 Cr</t>
+          <t>₹1700.00 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 1.7</t>
+          <t>17-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 1.3</t>
+          <t>19-Aug GMP: 54</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2159,12 +2159,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 1.5</t>
+          <t>24-Aug GMP: 74</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>24-Aug 8:59</t>
+          <t>24-Aug 9:33</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2243,47 +2243,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMEL@96.00 (4.35%)</t>
+          <t>Technocrats Plasma Systems BSE SMEL@230.00 (74.24%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹5 (5.43%) 4 ↓ / 5 ↑</t>
+          <t>₹70 (53.03%) 12 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>13.11x</t>
+          <t>203.36x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹33.14 Cr</t>
+          <t>₹60.98 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 4</t>
+          <t>18-Aug GMP: 43</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 5</t>
+          <t>21-Aug GMP: 70</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>21-Aug 9:30</t>
+          <t>21-Aug 9:36</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2310,47 +2310,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems BSE SMEL@230.00 (74.24%)</t>
+          <t>ENS Enterprises BSE SMEL@96.00 (4.35%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹70 (53.03%) 12 ↓ / 70 ↑</t>
+          <t>₹5 (5.43%) 4 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>203.36x</t>
+          <t>13.11x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹60.98 Cr</t>
+          <t>₹33.14 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 30</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 43</t>
+          <t>18-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 70</t>
+          <t>21-Aug GMP: 5</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>21-Aug 9:36</t>
+          <t>21-Aug 9:30</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2444,47 +2444,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods BSE SMEL@115.00 (0%)</t>
+          <t>Behari Lal Engineering IPOL@465.00 (63.16%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
+          <t>₹133 (46.67%) 25 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>118.07x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>285</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹26.25 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 10</t>
+          <t>12-Aug GMP: 74</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 1</t>
+          <t>14-Aug GMP: 83</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,64 +2494,64 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 1</t>
+          <t>19-Aug GMP: 133</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>19-Aug 9:31</t>
+          <t>19-Aug 9:32</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Shiprocket IPOL@131.00 (35.05%)</t>
+          <t>Q&amp;T Foods BSE SMEL@115.00 (0%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹35 (36.08%) 14 ↓ / 36.50 ↑</t>
+          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>102.28x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹1617.48 Cr</t>
+          <t>₹26.25 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 34</t>
+          <t>12-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 34</t>
+          <t>14-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 35</t>
+          <t>19-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>19-Aug 9:33</t>
+          <t>19-Aug 9:31</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,17 +501,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rays of Belief IPOU</t>
+          <t>ESDS Software Solution IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹130 (30.30%) 130 ↓ / 130 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>429</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹125.00 Cr</t>
+          <t>₹720.00 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>28-Aug</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>1-Sep</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3-Sep</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>2-Sep</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>4-Sep</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>8-Sep</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>24-Aug 14:59</t>
+          <t>25-Aug 8:58</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -568,12 +568,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shanti Inorganics NSE SMEU</t>
+          <t>Rays of Belief IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -588,42 +588,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>239</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹47.24 Cr</t>
+          <t>₹125.00 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>7-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>24-Aug 8:00</t>
+          <t>25-Aug 9:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -635,17 +635,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Complete Sports and Management BSE SMEU</t>
+          <t>Shanti Inorganics NSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹25 (30.12%) 25 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -655,42 +655,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹74.93 Cr</t>
+          <t>₹47.24 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>24-Aug 14:57</t>
+          <t>25-Aug 9:00</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Paluck Technologies BSE SMEU</t>
+          <t>Complete Sports and Management BSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹33.00 Cr</t>
+          <t>₹74.93 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>24-Aug 14:57</t>
+          <t>25-Aug 8:57</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -769,17 +769,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Priority Jewels IPOU</t>
+          <t>Paluck Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹18 (9.00%) 18 ↓ / 18 ↑</t>
+          <t>₹10 (20.83%) 10 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -789,17 +789,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹91.50 Cr</t>
+          <t>₹33.00 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24-Aug 14:56</t>
+          <t>25-Aug 9:01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -836,17 +836,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kwick Forensic Solutions BSE SMEU</t>
+          <t>Priority Jewels IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹61 (67.78%) 15 ↓ / 61 ↑</t>
+          <t>₹28 (14.00%) 28 ↓ / 28 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -856,42 +856,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹50.77 Cr</t>
+          <t>₹91.50 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>24-Aug 14:53</t>
+          <t>25-Aug 8:53</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -903,12 +903,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lumino Industries IPOU</t>
+          <t>Kwick Forensic Solutions BSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹46 (56.10%) 46 ↓ / 52 ↑</t>
+          <t>₹64 (71.11%) 15 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹700.00 Cr</t>
+          <t>₹50.77 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>24-Aug 14:59</t>
+          <t>25-Aug 9:01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -970,17 +970,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Annu Projects IPOU</t>
+          <t>Lumino Industries IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹4 (4.04%) 4 ↓ / 4 ↑</t>
+          <t>₹47 (57.32%) 46 ↓ / 52 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -990,42 +990,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹175.06 Cr</t>
+          <t>₹700.00 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>182</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>24-Aug 14:59</t>
+          <t>25-Aug 8:58</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1037,17 +1037,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sumax Engineering NSE SMEU</t>
+          <t>Annu Projects IPOO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹32 (31.68%) 20 ↓ / 32 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 4 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹53.40 Cr</t>
+          <t>₹175.06 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>25-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>24-Aug 14:54</t>
+          <t>25-Aug 8:58</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1104,32 +1104,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Madhur Knit NSE SMEO</t>
+          <t>Sumax Engineering NSE SMEO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹16 (16.00%) 9 ↓ / 16 ↑</t>
+          <t>₹32 (31.68%) 20 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.24x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹53.27 Cr</t>
+          <t>₹53.40 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1139,27 +1139,27 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 16</t>
+          <t>25-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>24-Aug 14:54</t>
+          <t>25-Aug 8:58</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1171,32 +1171,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ABH Healthcare NSE SMEO</t>
+          <t>Madhur Knit NSE SMEO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹16 (16.00%) 9 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.33x</t>
+          <t>0.32x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹34.98 Cr</t>
+          <t>₹53.27 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 0</t>
+          <t>24-Aug GMP: 16</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1226,54 +1226,54 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>24-Aug 14:53</t>
+          <t>25-Aug 9:00</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Skyways Air IPOO</t>
+          <t>ABH Healthcare NSE SMEO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹33 (23.91%) 19 ↓ / 50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.92x</t>
+          <t>0.36x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹34.98 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 33</t>
+          <t>24-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1293,54 +1293,54 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>24-Aug 14:57</t>
+          <t>25-Aug 8:58</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOO</t>
+          <t>Skyways Air IPOO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹35 (66.04%) 5 ↓ / 35 ↑</t>
+          <t>₹32 (23.19%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6.08x</t>
+          <t>1.16x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹135.73 Cr</t>
+          <t>₹582.80 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 35</t>
+          <t>24-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>24-Aug 14:57</t>
+          <t>25-Aug 8:59</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1372,42 +1372,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOO</t>
+          <t>Hy-Tech Engineers IPOO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹388 (39.27%) 220 ↓ / 410 ↑</t>
+          <t>₹30 (56.60%) 5 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.69x</t>
+          <t>7.84x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹1757.00 Cr</t>
+          <t>₹135.73 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 388</t>
+          <t>24-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>24-Aug 14:53</t>
+          <t>25-Aug 8:57</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1439,12 +1439,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOO</t>
+          <t>Symbiotec Pharmalab IPOO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹372 (47.21%) 190 ↓ / 395 ↑</t>
+          <t>₹340 (34.41%) 220 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1454,47 +1454,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12.99x</t>
+          <t>0.85x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹825.00 Cr</t>
+          <t>₹1757.00 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 310</t>
+          <t>24-Aug GMP: 335</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>24-Aug 15:00</t>
+          <t>25-Aug 8:57</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1573,62 +1573,62 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOCT</t>
+          <t>Augmont Enterprises IPOCT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹325 (108.33%) 65 ↓ / 325 ↑</t>
+          <t>₹325 (41.24%) 190 ↓ / 395 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>160.21x</t>
+          <t>15.21x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹825.00 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 270</t>
+          <t>21-Aug GMP: 310</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 325</t>
+          <t>25-Aug GMP: 325</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>24-Aug 15:01</t>
+          <t>25-Aug 8:55</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1640,62 +1640,62 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOC</t>
+          <t>Tempsens Instruments (India) IPOC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹16.25 (10.16%) 7 ↓ / 30 ↑</t>
+          <t>₹317 (105.67%) 65 ↓ / 321 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>32.98x</t>
+          <t>184.22x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹550.00 Cr</t>
+          <t>₹650.00 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 23</t>
+          <t>20-Aug GMP: 270</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 19</t>
+          <t>24-Aug GMP: 313</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>24-Aug 15:02</t>
+          <t>25-Aug 9:01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1707,47 +1707,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMEC</t>
+          <t>Gaja Alternative Asset Management IPOCAllotted</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹1 (1.01%) 1 ↓ / 12 ↑</t>
+          <t>₹15.5 (9.69%) 7 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.65x</t>
+          <t>32.98x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹26.73 Cr</t>
+          <t>₹550.00 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 12</t>
+          <t>19-Aug GMP: 23</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 1</t>
+          <t>21-Aug GMP: 19</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1762,24 +1762,24 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>24-Aug 14:53</t>
+          <t>25-Aug 8:53</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mopshop Distribution BSE SMEC</t>
+          <t>Dhanwel Hybrid Seeds BSE SMEC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹1 (0.72%) 1 ↓ / 22 ↑</t>
+          <t>₹1 (1.01%) 1 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.59x</t>
+          <t>1.65x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹27.26 Cr</t>
+          <t>₹26.73 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 5</t>
+          <t>19-Aug GMP: 12</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>24-Aug 14:59</t>
+          <t>25-Aug 9:00</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1841,12 +1841,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOCAllotted</t>
+          <t>Mopshop Distribution BSE SMEC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 8 ↑</t>
+          <t>₹1 (0.72%) 1 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1856,131 +1856,131 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.8x</t>
+          <t>1.59x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹367.18 Cr</t>
+          <t>₹27.26 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 5</t>
+          <t>19-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 5</t>
+          <t>21-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>24-Aug 14:57</t>
+          <t>25-Aug 8:53</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOCAllotted</t>
+          <t>Fascinate Textiles NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹59 (16.39%) 17 ↓ / 80 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>105.81x</t>
+          <t>1.48x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹64.83 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 77</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 80</t>
+          <t>19-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>24-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>24-Aug 14:53</t>
+          <t>25-Aug 5:55</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks IPOL@60.25 (0.42%)</t>
+          <t>Shankesh Jewellers IPOLT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹1.5 (2.50%) 1 ↓ / 4.50 ↑</t>
+          <t>₹2.75 (2.96%) 1 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1990,47 +1990,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.52x</t>
+          <t>2.8x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹2600.04 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 1.7</t>
+          <t>18-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 1.3</t>
+          <t>20-Aug GMP: 5</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 1.5</t>
+          <t>25-Aug GMP: 2.75</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>24-Aug 9:37</t>
+          <t>25-Aug 8:55</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2042,114 +2042,114 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMELT</t>
+          <t>Sunshine Pictures IPOLT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹50 (13.89%) 17 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.48x</t>
+          <t>105.81x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹64.83 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>18-Aug GMP: 77</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0</t>
+          <t>20-Aug GMP: 80</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 0</t>
+          <t>25-Aug GMP: 50</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>24-Aug 9:32</t>
+          <t>25-Aug 8:55</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOL@265.00 (31.84%)</t>
+          <t>Horizon Industrial Parks IPOL@60.25 (0.42%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹74 (36.82%) 17 ↓ / 77 ↑</t>
+          <t>₹1.5 (2.50%) 1 ↓ / 4.50 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>66.63x</t>
+          <t>1.52x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹2600.04 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 30</t>
+          <t>17-Aug GMP: 1.7</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 54</t>
+          <t>19-Aug GMP: 1.3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2159,12 +2159,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 74</t>
+          <t>24-Aug GMP: 1.5</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>24-Aug 9:33</t>
+          <t>24-Aug 9:37</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2176,114 +2176,114 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Skytech Infinite Platform NSE SMEL@74.00 (-3.9%)</t>
+          <t>Lalithaa Jewellery Mart IPOL@265.00 (31.84%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹1 (1.30%) 1 ↓ / 13 ↑</t>
+          <t>₹74 (36.82%) 17 ↓ / 77 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.04x</t>
+          <t>66.63x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹22.68 Cr</t>
+          <t>₹1700.00 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 10</t>
+          <t>17-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 1</t>
+          <t>19-Aug GMP: 54</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 1</t>
+          <t>24-Aug GMP: 74</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>21-Aug 9:28</t>
+          <t>24-Aug 9:33</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems BSE SMEL@230.00 (74.24%)</t>
+          <t>Skytech Infinite Platform NSE SMEL@74.00 (-3.9%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹70 (53.03%) 12 ↓ / 70 ↑</t>
+          <t>₹1 (1.30%) 1 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>203.36x</t>
+          <t>2.04x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹60.98 Cr</t>
+          <t>₹22.68 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 30</t>
+          <t>14-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 43</t>
+          <t>18-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2293,64 +2293,64 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 70</t>
+          <t>21-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>21-Aug 9:36</t>
+          <t>21-Aug 9:28</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMEL@96.00 (4.35%)</t>
+          <t>Technocrats Plasma Systems BSE SMEL@230.00 (74.24%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹5 (5.43%) 4 ↓ / 5 ↑</t>
+          <t>₹70 (53.03%) 12 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>13.11x</t>
+          <t>203.36x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹33.14 Cr</t>
+          <t>₹60.98 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>14-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 4</t>
+          <t>18-Aug GMP: 43</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 5</t>
+          <t>21-Aug GMP: 70</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>21-Aug 9:30</t>
+          <t>21-Aug 9:36</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2377,62 +2377,62 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Credent Connect NSE SMEL@359.10 (90%)</t>
+          <t>ENS Enterprises BSE SMEL@96.00 (4.35%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹92 (48.68%) 35 ↓ / 92 ↑</t>
+          <t>₹5 (5.43%) 4 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>153.13x</t>
+          <t>13.11x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹93.90 Cr</t>
+          <t>₹33.14 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 75</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 45</t>
+          <t>18-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 92</t>
+          <t>21-Aug GMP: 5</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>20-Aug 9:30</t>
+          <t>21-Aug 9:30</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2444,12 +2444,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOL@465.00 (63.16%)</t>
+          <t>Credent Connect NSE SMEL@359.10 (90%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹133 (46.67%) 25 ↓ / 133 ↑</t>
+          <t>₹92 (48.68%) 35 ↓ / 92 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2459,47 +2459,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>118.07x</t>
+          <t>153.13x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹93.90 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 74</t>
+          <t>13-Aug GMP: 75</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 83</t>
+          <t>17-Aug GMP: 45</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 133</t>
+          <t>20-Aug GMP: 92</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>19-Aug 9:32</t>
+          <t>20-Aug 9:30</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2511,47 +2511,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods BSE SMEL@115.00 (0%)</t>
+          <t>Behari Lal Engineering IPOL@465.00 (63.16%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹1 (0.87%) 1 ↓ / 21 ↑</t>
+          <t>₹133 (46.67%) 25 ↓ / 133 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>118.07x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>285</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹26.25 Cr</t>
+          <t>₹301.62 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 10</t>
+          <t>12-Aug GMP: 74</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 1</t>
+          <t>14-Aug GMP: 83</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 1</t>
+          <t>19-Aug GMP: 133</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>19-Aug 9:31</t>
+          <t>19-Aug 9:32</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,17 +501,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ESDS Software Solution IPOU</t>
+          <t>Pernia's Pop-up Studio IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹130 (30.30%) 130 ↓ / 130 ↑</t>
+          <t>₹-- (%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -519,44 +519,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>429</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹720.00 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+          <t>₹680.00 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>25-Aug 8:58</t>
+          <t>25-Aug 14:51</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -623,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25-Aug 9:00</t>
+          <t>25-Aug 14:55</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -635,17 +627,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shanti Inorganics NSE SMEU</t>
+          <t>Phychem Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹25 (30.12%) 25 ↓ / 25 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -655,17 +647,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹47.24 Cr</t>
+          <t>₹14.58 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -690,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25-Aug 9:00</t>
+          <t>25-Aug 15:00</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -702,17 +694,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Complete Sports and Management BSE SMEU</t>
+          <t>Shanti Inorganics NSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹25 (30.12%) 25 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -722,42 +714,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹74.93 Cr</t>
+          <t>₹47.24 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25-Aug 8:57</t>
+          <t>25-Aug 14:59</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -769,17 +761,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Paluck Technologies BSE SMEU</t>
+          <t>Ashutosh Fibre NSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹10 (20.83%) 10 ↓ / 10 ↑</t>
+          <t>₹-- (%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -789,42 +781,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹33.00 Cr</t>
+          <t>₹56.35 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>25-Aug 9:01</t>
+          <t>25-Aug 9:10</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -836,17 +828,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Priority Jewels IPOU</t>
+          <t>Complete Sports and Management BSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹28 (14.00%) 28 ↓ / 28 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -856,17 +848,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹91.50 Cr</t>
+          <t>₹74.93 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -891,7 +883,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>25-Aug 8:53</t>
+          <t>25-Aug 14:54</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -903,17 +895,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kwick Forensic Solutions BSE SMEU</t>
+          <t>Priority Jewels IPOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹64 (71.11%) 15 ↓ / 64 ↑</t>
+          <t>₹28 (14.00%) 28 ↓ / 28 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -923,42 +915,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹50.77 Cr</t>
+          <t>₹91.50 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>25-Aug 9:01</t>
+          <t>25-Aug 14:54</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -970,17 +962,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lumino Industries IPOU</t>
+          <t>Paluck Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹47 (57.32%) 46 ↓ / 52 ↑</t>
+          <t>₹10 (20.83%) 10 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -990,42 +982,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹700.00 Cr</t>
+          <t>₹33.00 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>25-Aug 8:58</t>
+          <t>25-Aug 14:53</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1037,17 +1029,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Annu Projects IPOO</t>
+          <t>ESDS Software Solution IPOU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 4 ↑</t>
+          <t>₹255 (59.44%) 255 ↓ / 255 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1057,42 +1049,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>429</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹175.06 Cr</t>
+          <t>₹720.00 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 0</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>25-Aug 8:58</t>
+          <t>25-Aug 15:02</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1104,17 +1096,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sumax Engineering NSE SMEO</t>
+          <t>Lumino Industries IPOU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹32 (31.68%) 20 ↓ / 32 ↑</t>
+          <t>₹49 (59.76%) 46 ↓ / 52 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1124,42 +1116,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹53.40 Cr</t>
+          <t>₹700.00 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>182</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 32</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>25-Aug 8:58</t>
+          <t>25-Aug 14:57</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1171,62 +1163,62 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Madhur Knit NSE SMEO</t>
+          <t>Kwick Forensic Solutions BSE SMEU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹16 (16.00%) 9 ↓ / 16 ↑</t>
+          <t>₹64 (71.11%) 15 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.32x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹53.27 Cr</t>
+          <t>₹50.77 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 16</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>25-Aug 9:00</t>
+          <t>25-Aug 14:53</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1238,12 +1230,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ABH Healthcare NSE SMEO</t>
+          <t>Annu Projects IPOO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 4 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1253,47 +1245,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.36x</t>
+          <t>0.2x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹34.98 Cr</t>
+          <t>₹175.06 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 0</t>
+          <t>25-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>25-Aug 8:58</t>
+          <t>25-Aug 14:57</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1305,12 +1297,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Skyways Air IPOO</t>
+          <t>Sumax Engineering NSE SMEO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹32 (23.19%) 19 ↓ / 50 ↑</t>
+          <t>₹35 (34.65%) 20 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1320,47 +1312,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.16x</t>
+          <t>2.31x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹53.40 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 32</t>
+          <t>25-Aug GMP: 35</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>25-Aug 8:59</t>
+          <t>25-Aug 14:58</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1372,42 +1364,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOO</t>
+          <t>ABH Healthcare NSE SMEO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹30 (56.60%) 5 ↓ / 30 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.84x</t>
+          <t>0.77x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹135.73 Cr</t>
+          <t>₹34.98 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 30</t>
+          <t>24-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1427,54 +1419,54 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>25-Aug 8:57</t>
+          <t>25-Aug 15:02</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOO</t>
+          <t>Madhur Knit NSE SMEO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹340 (34.41%) 220 ↓ / 410 ↑</t>
+          <t>₹16 (16.00%) 9 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.85x</t>
+          <t>0.39x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹1757.00 Cr</t>
+          <t>₹53.27 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 335</t>
+          <t>24-Aug GMP: 16</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1494,7 +1486,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>25-Aug 8:57</t>
+          <t>25-Aug 15:00</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1573,62 +1565,62 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOCT</t>
+          <t>Hy-Tech Engineers IPOO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹325 (41.24%) 190 ↓ / 395 ↑</t>
+          <t>₹30 (56.60%) 5 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>15.21x</t>
+          <t>17x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹825.00 Cr</t>
+          <t>₹135.73 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 310</t>
+          <t>24-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 325</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>25-Aug 8:55</t>
+          <t>25-Aug 14:58</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1640,62 +1632,62 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOC</t>
+          <t>Skyways Air IPOO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹317 (105.67%) 65 ↓ / 321 ↑</t>
+          <t>₹29 (21.01%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>184.22x</t>
+          <t>2.16x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹582.80 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 270</t>
+          <t>24-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 313</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>25-Aug 9:01</t>
+          <t>25-Aug 15:01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1707,62 +1699,62 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOCAllotted</t>
+          <t>Symbiotec Pharmalab IPOO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹15.5 (9.69%) 7 ↓ / 30 ↑</t>
+          <t>₹350 (35.43%) 220 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>32.98x</t>
+          <t>1.68x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹550.00 Cr</t>
+          <t>₹1757.00 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 23</t>
+          <t>24-Aug GMP: 335</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 19</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>25-Aug 8:53</t>
+          <t>25-Aug 14:53</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1774,146 +1766,146 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMEC</t>
+          <t>Augmont Enterprises IPOCT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹1 (1.01%) 1 ↓ / 12 ↑</t>
+          <t>₹320 (40.61%) 190 ↓ / 395 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.65x</t>
+          <t>90.36x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹26.73 Cr</t>
+          <t>₹825.00 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 12</t>
+          <t>21-Aug GMP: 310</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 1</t>
+          <t>25-Aug GMP: 320</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>25-Aug 9:00</t>
+          <t>25-Aug 15:01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mopshop Distribution BSE SMEC</t>
+          <t>Tempsens Instruments (India) IPOC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹1 (0.72%) 1 ↓ / 22 ↑</t>
+          <t>₹307 (102.33%) 65 ↓ / 321 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.59x</t>
+          <t>184.22x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹27.26 Cr</t>
+          <t>₹650.00 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 5</t>
+          <t>20-Aug GMP: 270</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 1</t>
+          <t>24-Aug GMP: 313</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>25-Aug 8:53</t>
+          <t>25-Aug 15:00</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMECAllotted</t>
+          <t>Mopshop Distribution BSE SMEC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1 (0.72%) 1 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1923,47 +1915,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.48x</t>
+          <t>1.59x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹64.83 Cr</t>
+          <t>₹27.26 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>19-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0</t>
+          <t>21-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 0</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>25-Aug 5:55</t>
+          <t>25-Aug 14:54</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1975,12 +1967,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOLT</t>
+          <t>Dhanwel Hybrid Seeds BSE SMEC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹2.75 (2.96%) 1 ↓ / 8 ↑</t>
+          <t>₹1 (1.01%) 1 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1990,64 +1982,64 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.8x</t>
+          <t>1.65x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹367.18 Cr</t>
+          <t>₹26.73 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 5</t>
+          <t>19-Aug GMP: 12</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 5</t>
+          <t>21-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 2.75</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>25-Aug 8:55</t>
+          <t>25-Aug 14:58</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOLT</t>
+          <t>Gaja Alternative Asset Management IPOCAllotted</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹50 (13.89%) 17 ↓ / 80 ↑</t>
+          <t>₹19 (11.88%) 7 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2057,47 +2049,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>105.81x</t>
+          <t>32.98x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹550.00 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 77</t>
+          <t>19-Aug GMP: 23</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 80</t>
+          <t>21-Aug GMP: 19</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 50</t>
+          <t>26-Aug</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>25-Aug 8:55</t>
+          <t>25-Aug 14:53</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2109,12 +2101,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks IPOL@60.25 (0.42%)</t>
+          <t>Fascinate Textiles NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹1.5 (2.50%) 1 ↓ / 4.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2124,32 +2116,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.52x</t>
+          <t>1.48x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹2600.04 Cr</t>
+          <t>₹64.83 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 1.7</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 1.3</t>
+          <t>19-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2159,79 +2151,79 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 1.5</t>
+          <t>24-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>24-Aug 9:37</t>
+          <t>25-Aug 5:55</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOL@265.00 (31.84%)</t>
+          <t>Sunshine Pictures IPOL@395.90 (9.97%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹74 (36.82%) 17 ↓ / 77 ↑</t>
+          <t>₹50 (13.89%) 17 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>66.63x</t>
+          <t>105.81x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 30</t>
+          <t>18-Aug GMP: 77</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 54</t>
+          <t>20-Aug GMP: 80</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 74</t>
+          <t>25-Aug GMP: 50</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>24-Aug 9:33</t>
+          <t>25-Aug 9:30</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2243,12 +2235,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Skytech Infinite Platform NSE SMEL@74.00 (-3.9%)</t>
+          <t>Shankesh Jewellers IPOL@103.30 (11.08%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹1 (1.30%) 1 ↓ / 13 ↑</t>
+          <t>₹2.75 (2.96%) 1 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2258,114 +2250,114 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.04x</t>
+          <t>2.8x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹22.68 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 10</t>
+          <t>18-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 1</t>
+          <t>20-Aug GMP: 5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 1</t>
+          <t>25-Aug GMP: 2.75</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>21-Aug 9:28</t>
+          <t>25-Aug 9:36</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems BSE SMEL@230.00 (74.24%)</t>
+          <t>Horizon Industrial Parks IPOL@60.25 (0.42%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹70 (53.03%) 12 ↓ / 70 ↑</t>
+          <t>₹1.5 (2.50%) 1 ↓ / 4.50 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>203.36x</t>
+          <t>1.52x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹60.98 Cr</t>
+          <t>₹2600.04 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 30</t>
+          <t>17-Aug GMP: 1.7</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 43</t>
+          <t>19-Aug GMP: 1.3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 70</t>
+          <t>24-Aug GMP: 1.5</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>21-Aug 9:36</t>
+          <t>24-Aug 9:37</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2377,62 +2369,62 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMEL@96.00 (4.35%)</t>
+          <t>Lalithaa Jewellery Mart IPOL@265.00 (31.84%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹5 (5.43%) 4 ↓ / 5 ↑</t>
+          <t>₹74 (36.82%) 17 ↓ / 77 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>13.11x</t>
+          <t>66.63x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹33.14 Cr</t>
+          <t>₹1700.00 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>17-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 4</t>
+          <t>19-Aug GMP: 54</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 5</t>
+          <t>24-Aug GMP: 74</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>21-Aug 9:30</t>
+          <t>24-Aug 9:33</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2444,62 +2436,62 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Credent Connect NSE SMEL@359.10 (90%)</t>
+          <t>ENS Enterprises BSE SMEL@96.00 (4.35%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹92 (48.68%) 35 ↓ / 92 ↑</t>
+          <t>₹5 (5.43%) 4 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>153.13x</t>
+          <t>13.11x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹93.90 Cr</t>
+          <t>₹33.14 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 75</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 45</t>
+          <t>18-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 92</t>
+          <t>21-Aug GMP: 5</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>20-Aug 9:30</t>
+          <t>21-Aug 9:30</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2511,67 +2503,67 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering IPOL@465.00 (63.16%)</t>
+          <t>Skytech Infinite Platform NSE SMEL@74.00 (-3.9%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹133 (46.67%) 25 ↓ / 133 ↑</t>
+          <t>₹1 (1.30%) 1 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>118.07x</t>
+          <t>2.04x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹301.62 Cr</t>
+          <t>₹22.68 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>12-Aug GMP: 74</t>
+          <t>14-Aug GMP: 10</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 83</t>
+          <t>18-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 133</t>
+          <t>21-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>19-Aug 9:32</t>
+          <t>21-Aug 9:28</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,12 +501,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pernia's Pop-up Studio IPOU</t>
+          <t>Rays of Belief IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -519,36 +519,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹680.00 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>₹125.00 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>7-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>25-Aug 14:51</t>
+          <t>26-Aug 8:53</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -560,17 +568,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rays of Belief IPOU</t>
+          <t>Ashutosh Fibre NSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹13 (14.13%) 13 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -580,42 +588,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹125.00 Cr</t>
+          <t>₹56.35 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>2-Sep</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>3-Sep</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>4-Sep</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8-Sep</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25-Aug 14:55</t>
+          <t>26-Aug 9:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -627,17 +635,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Phychem Technologies BSE SMEU</t>
+          <t>Shanti Inorganics NSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹31 (37.35%) 25 ↓ / 31 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -647,17 +655,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹14.58 Cr</t>
+          <t>₹47.24 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -682,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25-Aug 15:00</t>
+          <t>26-Aug 8:57</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -694,17 +702,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Shanti Inorganics NSE SMEU</t>
+          <t>Phychem Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹25 (30.12%) 25 ↓ / 25 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -714,17 +722,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹47.24 Cr</t>
+          <t>₹14.58 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -749,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25-Aug 14:59</t>
+          <t>26-Aug 9:00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -761,12 +769,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ashutosh Fibre NSE SMEU</t>
+          <t>Pernia's Pop-up Studio IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹-- (%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -781,17 +789,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>575</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹56.35 Cr</t>
+          <t>₹680.00 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -816,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>25-Aug 9:10</t>
+          <t>26-Aug 8:57</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -883,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>25-Aug 14:54</t>
+          <t>26-Aug 8:55</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -895,17 +903,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Priority Jewels IPOU</t>
+          <t>ESDS Software Solution IPOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹28 (14.00%) 28 ↓ / 28 ↑</t>
+          <t>₹280 (65.27%) 275 ↓ / 280 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -915,17 +923,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>429</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹91.50 Cr</t>
+          <t>₹720.00 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -950,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>25-Aug 14:54</t>
+          <t>26-Aug 8:53</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -967,7 +975,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹10 (20.83%) 10 ↓ / 10 ↑</t>
+          <t>₹18 (37.50%) 10 ↓ / 18 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1017,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>25-Aug 14:53</t>
+          <t>26-Aug 8:54</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1029,17 +1037,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ESDS Software Solution IPOU</t>
+          <t>Priority Jewels IPOU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹255 (59.44%) 255 ↓ / 255 ↑</t>
+          <t>₹30 (15.00%) 28 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1049,17 +1057,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹720.00 Cr</t>
+          <t>₹91.50 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1084,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>25-Aug 15:02</t>
+          <t>26-Aug 9:02</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1096,12 +1104,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lumino Industries IPOU</t>
+          <t>Kwick Forensic Solutions BSE SMEU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹49 (59.76%) 46 ↓ / 52 ↑</t>
+          <t>₹64 (71.11%) 15 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1116,17 +1124,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹700.00 Cr</t>
+          <t>₹50.77 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1151,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>25-Aug 14:57</t>
+          <t>26-Aug 8:55</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1163,12 +1171,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kwick Forensic Solutions BSE SMEU</t>
+          <t>Lumino Industries IPOU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹64 (71.11%) 15 ↓ / 64 ↑</t>
+          <t>₹46 (56.10%) 46 ↓ / 52 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1183,17 +1191,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹50.77 Cr</t>
+          <t>₹700.00 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>182</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1218,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>25-Aug 14:53</t>
+          <t>26-Aug 8:59</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1245,7 +1253,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.2x</t>
+          <t>0.34x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1285,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>25-Aug 14:57</t>
+          <t>26-Aug 9:01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1312,7 +1320,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.31x</t>
+          <t>3.24x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1352,7 +1360,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>25-Aug 14:58</t>
+          <t>26-Aug 8:54</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1379,7 +1387,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.77x</t>
+          <t>0.79x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1419,7 +1427,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>25-Aug 15:02</t>
+          <t>26-Aug 8:54</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1431,42 +1439,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Madhur Knit NSE SMEO</t>
+          <t>Symbiotec Pharmalab IPOO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹16 (16.00%) 9 ↓ / 16 ↑</t>
+          <t>₹352 (35.63%) 220 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.39x</t>
+          <t>1.95x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹53.27 Cr</t>
+          <t>₹1757.00 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 16</t>
+          <t>24-Aug GMP: 335</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1486,7 +1494,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>25-Aug 15:00</t>
+          <t>26-Aug 9:00</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1565,42 +1573,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOO</t>
+          <t>Madhur Knit NSE SMEO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹30 (56.60%) 5 ↓ / 30 ↑</t>
+          <t>₹16 (16.00%) 9 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>17x</t>
+          <t>0.42x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹135.73 Cr</t>
+          <t>₹53.27 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 30</t>
+          <t>24-Aug GMP: 16</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1620,7 +1628,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>25-Aug 14:58</t>
+          <t>26-Aug 9:00</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1647,7 +1655,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.16x</t>
+          <t>2.46x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1687,7 +1695,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>25-Aug 15:01</t>
+          <t>26-Aug 8:58</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1699,42 +1707,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOO</t>
+          <t>Hy-Tech Engineers IPOO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹350 (35.43%) 220 ↓ / 410 ↑</t>
+          <t>₹30 (56.60%) 5 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.68x</t>
+          <t>19.57x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹1757.00 Cr</t>
+          <t>₹135.73 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 335</t>
+          <t>24-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1754,7 +1762,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>25-Aug 14:53</t>
+          <t>26-Aug 8:59</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1766,12 +1774,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOCT</t>
+          <t>Augmont Enterprises IPOC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹320 (40.61%) 190 ↓ / 395 ↑</t>
+          <t>₹315 (39.97%) 190 ↓ / 395 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1781,7 +1789,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>90.36x</t>
+          <t>111.18x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1806,7 +1814,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 320</t>
+          <t>25-Aug GMP: 315</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1821,7 +1829,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>25-Aug 15:01</t>
+          <t>26-Aug 8:59</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1833,12 +1841,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOC</t>
+          <t>Tempsens Instruments (India) IPOCAllotted</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹307 (102.33%) 65 ↓ / 321 ↑</t>
+          <t>₹312 (104.00%) 65 ↓ / 321 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1888,7 +1896,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>25-Aug 15:00</t>
+          <t>26-Aug 8:57</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1900,12 +1908,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mopshop Distribution BSE SMEC</t>
+          <t>Fascinate Textiles NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹1 (0.72%) 1 ↓ / 22 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1915,47 +1923,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.59x</t>
+          <t>1.48x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹27.26 Cr</t>
+          <t>₹64.83 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 5</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 1</t>
+          <t>19-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>24-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>25-Aug 14:54</t>
+          <t>26-Aug 5:55</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1967,47 +1975,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMEC</t>
+          <t>Gaja Alternative Asset Management IPOLT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹1 (1.01%) 1 ↓ / 12 ↑</t>
+          <t>₹18.5 (11.56%) 7 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.65x</t>
+          <t>32.98x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹26.73 Cr</t>
+          <t>₹550.00 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 12</t>
+          <t>19-Aug GMP: 23</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 1</t>
+          <t>21-Aug GMP: 19</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2017,64 +2025,64 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>26-Aug GMP: 18.5</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>25-Aug 14:58</t>
+          <t>26-Aug 8:55</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOCAllotted</t>
+          <t>Dhanwel Hybrid Seeds BSE SMELT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹19 (11.88%) 7 ↓ / 30 ↑</t>
+          <t>₹1 (1.01%) 1 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>32.98x</t>
+          <t>1.65x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹550.00 Cr</t>
+          <t>₹26.73 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 23</t>
+          <t>19-Aug GMP: 12</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 19</t>
+          <t>21-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2084,29 +2092,29 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>26-Aug</t>
+          <t>26-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>25-Aug 14:53</t>
+          <t>26-Aug 9:02</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMECAllotted</t>
+          <t>Mopshop Distribution BSE SMELT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1 (0.72%) 1 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2116,47 +2124,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.48x</t>
+          <t>1.59x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹64.83 Cr</t>
+          <t>₹27.26 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>19-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0</t>
+          <t>21-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 0</t>
+          <t>26-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>25-Aug 5:55</t>
+          <t>26-Aug 8:55</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2168,47 +2176,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOL@395.90 (9.97%)</t>
+          <t>Shankesh Jewellers IPOL@103.30 (11.08%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹50 (13.89%) 17 ↓ / 80 ↑</t>
+          <t>₹2.75 (2.96%) 1 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>105.81x</t>
+          <t>2.8x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 77</t>
+          <t>18-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 80</t>
+          <t>20-Aug GMP: 5</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2218,12 +2226,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 50</t>
+          <t>25-Aug GMP: 2.75</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>25-Aug 9:30</t>
+          <t>25-Aug 9:36</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2235,47 +2243,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOL@103.30 (11.08%)</t>
+          <t>Sunshine Pictures IPOL@395.90 (9.97%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹2.75 (2.96%) 1 ↓ / 8 ↑</t>
+          <t>₹50 (13.89%) 17 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.8x</t>
+          <t>105.81x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹367.18 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 5</t>
+          <t>18-Aug GMP: 77</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 5</t>
+          <t>20-Aug GMP: 80</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2285,12 +2293,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 2.75</t>
+          <t>25-Aug GMP: 50</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>25-Aug 9:36</t>
+          <t>25-Aug 9:30</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2302,47 +2310,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks IPOL@60.25 (0.42%)</t>
+          <t>Lalithaa Jewellery Mart IPOL@265.00 (31.84%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹1.5 (2.50%) 1 ↓ / 4.50 ↑</t>
+          <t>₹74 (36.82%) 17 ↓ / 77 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.52x</t>
+          <t>66.63x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹2600.04 Cr</t>
+          <t>₹1700.00 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 1.7</t>
+          <t>17-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 1.3</t>
+          <t>19-Aug GMP: 54</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2352,12 +2360,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 1.5</t>
+          <t>24-Aug GMP: 74</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>24-Aug 9:37</t>
+          <t>24-Aug 9:33</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2369,47 +2377,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOL@265.00 (31.84%)</t>
+          <t>Horizon Industrial Parks IPOL@60.25 (0.42%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹74 (36.82%) 17 ↓ / 77 ↑</t>
+          <t>₹1.5 (2.50%) 1 ↓ / 4.50 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>66.63x</t>
+          <t>1.52x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹2600.04 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 30</t>
+          <t>17-Aug GMP: 1.7</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 54</t>
+          <t>19-Aug GMP: 1.3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2419,12 +2427,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 74</t>
+          <t>24-Aug GMP: 1.5</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>24-Aug 9:33</t>
+          <t>24-Aug 9:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,12 +501,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rays of Belief IPOU</t>
+          <t>Deepa Jewellers IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -519,21 +519,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹125.00 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>1-Sep</t>
@@ -556,7 +544,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>26-Aug 8:53</t>
+          <t>26-Aug 13:10</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -568,17 +556,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ashutosh Fibre NSE SMEU</t>
+          <t>Rays of Belief IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹13 (14.13%) 13 ↓ / 13 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -588,42 +576,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>239</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹56.35 Cr</t>
+          <t>₹125.00 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>7-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>26-Aug 9:02</t>
+          <t>26-Aug 14:35</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -635,17 +623,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shanti Inorganics NSE SMEU</t>
+          <t>Ashutosh Fibre NSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹31 (37.35%) 25 ↓ / 31 ↑</t>
+          <t>₹15 (16.30%) 13 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -655,17 +643,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹47.24 Cr</t>
+          <t>₹56.35 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -690,7 +678,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>26-Aug 8:57</t>
+          <t>26-Aug 14:34</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -702,17 +690,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Phychem Technologies BSE SMEU</t>
+          <t>Shanti Inorganics NSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹31 (37.35%) 25 ↓ / 31 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -722,17 +710,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹14.58 Cr</t>
+          <t>₹47.24 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -757,7 +745,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>26-Aug 9:00</t>
+          <t>26-Aug 14:32</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -769,7 +757,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pernia's Pop-up Studio IPOU</t>
+          <t>Phychem Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -789,17 +777,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹680.00 Cr</t>
+          <t>₹14.58 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -824,7 +812,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>26-Aug 8:57</t>
+          <t>26-Aug 14:30</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -836,7 +824,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Complete Sports and Management BSE SMEU</t>
+          <t>Pernia's Pop-up Studio IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -856,42 +844,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>575</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹74.93 Cr</t>
+          <t>₹680.00 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>26-Aug 8:55</t>
+          <t>26-Aug 14:35</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -903,17 +891,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ESDS Software Solution IPOU</t>
+          <t>Complete Sports and Management BSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹280 (65.27%) 275 ↓ / 280 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -923,17 +911,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹720.00 Cr</t>
+          <t>₹74.93 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -958,7 +946,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>26-Aug 8:53</t>
+          <t>26-Aug 14:30</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -970,17 +958,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Paluck Technologies BSE SMEU</t>
+          <t>ESDS Software Solution IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹18 (37.50%) 10 ↓ / 18 ↑</t>
+          <t>₹330 (76.92%) 275 ↓ / 330 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -990,17 +978,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>429</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹33.00 Cr</t>
+          <t>₹720.00 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1025,7 +1013,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>26-Aug 8:54</t>
+          <t>26-Aug 14:34</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1037,17 +1025,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Priority Jewels IPOU</t>
+          <t>Paluck Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹30 (15.00%) 28 ↓ / 30 ↑</t>
+          <t>₹25 (52.08%) 10 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1057,17 +1045,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹91.50 Cr</t>
+          <t>₹33.00 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1092,7 +1080,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>26-Aug 9:02</t>
+          <t>26-Aug 14:34</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1104,17 +1092,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kwick Forensic Solutions BSE SMEU</t>
+          <t>Priority Jewels IPOU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹64 (71.11%) 15 ↓ / 64 ↑</t>
+          <t>₹30 (15.00%) 28 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1124,42 +1112,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹50.77 Cr</t>
+          <t>₹91.50 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>26-Aug 8:55</t>
+          <t>26-Aug 14:29</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1171,12 +1159,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lumino Industries IPOU</t>
+          <t>Kwick Forensic Solutions BSE SMEU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹46 (56.10%) 46 ↓ / 52 ↑</t>
+          <t>₹64 (71.11%) 15 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1191,17 +1179,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹700.00 Cr</t>
+          <t>₹50.77 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1226,7 +1214,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>26-Aug 8:59</t>
+          <t>26-Aug 14:33</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1238,109 +1226,109 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Annu Projects IPOO</t>
+          <t>Lumino Industries IPOU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 4 ↑</t>
+          <t>₹46 (56.10%) 46 ↓ / 52 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.34x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹175.06 Cr</t>
+          <t>₹700.00 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>182</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 0</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>26-Aug 9:01</t>
+          <t>26-Aug 14:28</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sumax Engineering NSE SMEO</t>
+          <t>Annu Projects IPOO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹35 (34.65%) 20 ↓ / 35 ↑</t>
+          <t>₹4 (4.04%) 4 ↓ / 4 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.24x</t>
+          <t>0.44x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹53.40 Cr</t>
+          <t>₹175.06 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 35</t>
+          <t>25-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1360,44 +1348,44 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>26-Aug 8:54</t>
+          <t>26-Aug 14:36</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ABH Healthcare NSE SMEO</t>
+          <t>Sumax Engineering NSE SMEO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹30 (29.70%) 20 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.79x</t>
+          <t>8.15x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹34.98 Cr</t>
+          <t>₹53.40 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1407,74 +1395,74 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 0</t>
+          <t>25-Aug GMP: 35</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>26-Aug 8:54</t>
+          <t>26-Aug 14:29</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOO</t>
+          <t>ABH Healthcare NSE SMEO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹352 (35.63%) 220 ↓ / 410 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.95x</t>
+          <t>0.91x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹1757.00 Cr</t>
+          <t>₹34.98 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 335</t>
+          <t>24-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1494,12 +1482,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>26-Aug 9:00</t>
+          <t>26-Aug 14:28</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -1573,42 +1561,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Madhur Knit NSE SMEO</t>
+          <t>Symbiotec Pharmalab IPOO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹16 (16.00%) 9 ↓ / 16 ↑</t>
+          <t>₹340 (34.41%) 220 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.42x</t>
+          <t>4.69x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹53.27 Cr</t>
+          <t>₹1757.00 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 16</t>
+          <t>24-Aug GMP: 335</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1628,7 +1616,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>26-Aug 9:00</t>
+          <t>26-Aug 14:32</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1640,42 +1628,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Skyways Air IPOO</t>
+          <t>Madhur Knit NSE SMEO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹29 (21.01%) 19 ↓ / 50 ↑</t>
+          <t>₹16 (16.00%) 9 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.46x</t>
+          <t>0.63x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹53.27 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 32</t>
+          <t>24-Aug GMP: 16</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1695,7 +1683,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>26-Aug 8:58</t>
+          <t>26-Aug 14:29</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1707,42 +1695,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOO</t>
+          <t>Skyways Air IPOO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹30 (56.60%) 5 ↓ / 30 ↑</t>
+          <t>₹29 (21.01%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>19.57x</t>
+          <t>4.46x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹135.73 Cr</t>
+          <t>₹582.80 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 30</t>
+          <t>24-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1762,7 +1750,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>26-Aug 8:59</t>
+          <t>26-Aug 14:32</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1774,62 +1762,62 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOC</t>
+          <t>Hy-Tech Engineers IPOO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹315 (39.97%) 190 ↓ / 395 ↑</t>
+          <t>₹40 (75.47%) 5 ↓ / 40 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>111.18x</t>
+          <t>44.31x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹825.00 Cr</t>
+          <t>₹135.73 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 310</t>
+          <t>24-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 315</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>26-Aug 8:59</t>
+          <t>26-Aug 14:35</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1841,62 +1829,62 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOCAllotted</t>
+          <t>Augmont Enterprises IPOC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹312 (104.00%) 65 ↓ / 321 ↑</t>
+          <t>₹320 (40.61%) 190 ↓ / 395 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>184.22x</t>
+          <t>111.18x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹825.00 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 270</t>
+          <t>21-Aug GMP: 310</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 313</t>
+          <t>25-Aug GMP: 315</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>26-Aug 8:57</t>
+          <t>26-Aug 14:31</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1908,141 +1896,141 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMECAllotted</t>
+          <t>Tempsens Instruments (India) IPOCAllotted</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹300 (100.00%) 65 ↓ / 321 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.48x</t>
+          <t>184.22x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹64.83 Cr</t>
+          <t>₹650.00 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>20-Aug GMP: 270</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0</t>
+          <t>24-Aug GMP: 313</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 0</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>26-Aug 5:55</t>
+          <t>26-Aug 14:30</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOLT</t>
+          <t>Fascinate Textiles NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹18.5 (11.56%) 7 ↓ / 30 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>32.98x</t>
+          <t>1.48x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹550.00 Cr</t>
+          <t>₹64.83 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 23</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 19</t>
+          <t>19-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>26-Aug GMP: 18.5</t>
+          <t>24-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>26-Aug 8:55</t>
+          <t>26-Aug 5:55</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMELT</t>
+          <t>Dhanwel Hybrid Seeds BSE SMEL@99.00 (0%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2097,7 +2085,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>26-Aug 9:02</t>
+          <t>26-Aug 9:37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2109,7 +2097,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mopshop Distribution BSE SMELT</t>
+          <t>Mopshop Distribution BSE SMEL@137.00 (-0.72%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2164,7 +2152,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>26-Aug 8:55</t>
+          <t>26-Aug 9:28</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2176,62 +2164,62 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOL@103.30 (11.08%)</t>
+          <t>Gaja Alternative Asset Management IPOL@185.00 (15.62%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹2.75 (2.96%) 1 ↓ / 8 ↑</t>
+          <t>₹18.5 (11.56%) 7 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.8x</t>
+          <t>32.98x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>₹550.00 Cr</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>₹367.18 Cr</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 5</t>
+          <t>19-Aug GMP: 23</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 5</t>
+          <t>21-Aug GMP: 19</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 2.75</t>
+          <t>26-Aug GMP: 18.5</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>25-Aug 9:36</t>
+          <t>26-Aug 9:34</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2243,47 +2231,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOL@395.90 (9.97%)</t>
+          <t>Shankesh Jewellers IPOL@103.30 (11.08%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹50 (13.89%) 17 ↓ / 80 ↑</t>
+          <t>₹2.75 (2.96%) 1 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>105.81x</t>
+          <t>2.8x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 77</t>
+          <t>18-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 80</t>
+          <t>20-Aug GMP: 5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2293,12 +2281,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 50</t>
+          <t>25-Aug GMP: 2.75</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>25-Aug 9:30</t>
+          <t>25-Aug 9:36</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2310,62 +2298,62 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOL@265.00 (31.84%)</t>
+          <t>Sunshine Pictures IPOL@395.90 (9.97%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹74 (36.82%) 17 ↓ / 77 ↑</t>
+          <t>₹50 (13.89%) 17 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>66.63x</t>
+          <t>105.81x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 30</t>
+          <t>18-Aug GMP: 77</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 54</t>
+          <t>20-Aug GMP: 80</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 74</t>
+          <t>25-Aug GMP: 50</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>24-Aug 9:33</t>
+          <t>25-Aug 9:30</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2377,47 +2365,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks IPOL@60.25 (0.42%)</t>
+          <t>Lalithaa Jewellery Mart IPOL@265.00 (31.84%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹1.5 (2.50%) 1 ↓ / 4.50 ↑</t>
+          <t>₹74 (36.82%) 17 ↓ / 77 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.52x</t>
+          <t>66.63x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹2600.04 Cr</t>
+          <t>₹1700.00 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 1.7</t>
+          <t>17-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 1.3</t>
+          <t>19-Aug GMP: 54</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2427,12 +2415,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 1.5</t>
+          <t>24-Aug GMP: 74</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>24-Aug 9:37</t>
+          <t>24-Aug 9:33</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2444,62 +2432,62 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMEL@96.00 (4.35%)</t>
+          <t>Horizon Industrial Parks IPOL@60.25 (0.42%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹5 (5.43%) 4 ↓ / 5 ↑</t>
+          <t>₹1.5 (2.50%) 1 ↓ / 4.50 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>13.11x</t>
+          <t>1.52x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹33.14 Cr</t>
+          <t>₹2600.04 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>17-Aug GMP: 1.7</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 4</t>
+          <t>19-Aug GMP: 1.3</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 5</t>
+          <t>24-Aug GMP: 1.5</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>21-Aug 9:30</t>
+          <t>24-Aug 9:37</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2511,47 +2499,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Skytech Infinite Platform NSE SMEL@74.00 (-3.9%)</t>
+          <t>ENS Enterprises BSE SMEL@96.00 (4.35%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹1 (1.30%) 1 ↓ / 13 ↑</t>
+          <t>₹5 (5.43%) 4 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.04x</t>
+          <t>13.11x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹22.68 Cr</t>
+          <t>₹33.14 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 10</t>
+          <t>14-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 1</t>
+          <t>18-Aug GMP: 4</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2561,17 +2549,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 1</t>
+          <t>21-Aug GMP: 5</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>21-Aug 9:28</t>
+          <t>21-Aug 9:30</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,12 +501,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deepa Jewellers IPOU</t>
+          <t>Rays of Belief IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (%) 0 ↓ / 0 ↑</t>
+          <t>₹10 (4.18%) 10 ↓ / 18 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -519,9 +519,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹125.00 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>1-Sep</t>
@@ -544,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>26-Aug 13:10</t>
+          <t>27-Aug 16:30</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -556,17 +568,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rays of Belief IPOU</t>
+          <t>Deepa Jewellers IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹25 (14.12%) 25 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -576,17 +588,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹125.00 Cr</t>
+          <t>₹459.72 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -611,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>26-Aug 14:35</t>
+          <t>27-Aug 16:34</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -623,17 +635,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ashutosh Fibre NSE SMEU</t>
+          <t>Farm Peace BSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹15 (16.30%) 13 ↓ / 15 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -643,47 +655,47 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹56.35 Cr</t>
+          <t>₹32.00 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>7-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>26-Aug 14:34</t>
+          <t>27-Aug 16:33</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -745,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>26-Aug 14:32</t>
+          <t>27-Aug 16:36</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -757,7 +769,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Phychem Technologies BSE SMEU</t>
+          <t>Purple Style Labs IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -777,17 +789,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>575</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹14.58 Cr</t>
+          <t>₹680.00 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -812,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>26-Aug 14:30</t>
+          <t>27-Aug 16:31</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -824,17 +836,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pernia's Pop-up Studio IPOU</t>
+          <t>Ashutosh Fibre NSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹37 (40.22%) 13 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -844,17 +856,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹680.00 Cr</t>
+          <t>₹56.35 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -879,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>26-Aug 14:35</t>
+          <t>27-Aug 16:31</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -891,17 +903,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Complete Sports and Management BSE SMEU</t>
+          <t>Phychem Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹3 (5.56%) 3 ↓ / 3 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -911,42 +923,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹74.93 Cr</t>
+          <t>₹14.58 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>26-Aug 14:30</t>
+          <t>27-Aug 16:30</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -958,17 +970,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ESDS Software Solution IPOU</t>
+          <t>Complete Sports and Management BSE SMEU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹330 (76.92%) 275 ↓ / 330 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -978,17 +990,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹720.00 Cr</t>
+          <t>₹74.93 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1013,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>26-Aug 14:34</t>
+          <t>27-Aug 16:34</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1025,12 +1037,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Paluck Technologies BSE SMEU</t>
+          <t>ESDS Software Solution IPOU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹25 (52.08%) 10 ↓ / 25 ↑</t>
+          <t>₹335 (78.09%) 275 ↓ / 365 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1045,17 +1057,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>429</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹33.00 Cr</t>
+          <t>₹720.00 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1080,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>26-Aug 14:34</t>
+          <t>27-Aug 16:36</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1097,7 +1109,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹30 (15.00%) 28 ↓ / 30 ↑</t>
+          <t>₹37 (18.50%) 20 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1147,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>26-Aug 14:29</t>
+          <t>27-Aug 16:33</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1159,12 +1171,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kwick Forensic Solutions BSE SMEU</t>
+          <t>Paluck Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹64 (71.11%) 15 ↓ / 64 ↑</t>
+          <t>₹25 (52.08%) 10 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1179,42 +1191,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹50.77 Cr</t>
+          <t>₹33.00 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>26-Aug 14:33</t>
+          <t>27-Aug 16:33</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1226,12 +1238,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lumino Industries IPOU</t>
+          <t>Lumino Industries IPOO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹46 (56.10%) 46 ↓ / 52 ↑</t>
+          <t>₹56 (68.29%) 46 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,7 +1253,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.35x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1261,7 +1273,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>27-Aug GMP: 56</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1281,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>26-Aug 14:28</t>
+          <t>27-Aug 16:28</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1293,67 +1305,67 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Annu Projects IPOO</t>
+          <t>Kwick Forensic Solutions BSE SMEO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹4 (4.04%) 4 ↓ / 4 ↑</t>
+          <t>₹64 (71.11%) 15 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.44x</t>
+          <t>6.45x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹175.06 Cr</t>
+          <t>₹50.77 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 0</t>
+          <t>27-Aug GMP: 64</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>26-Aug 14:36</t>
+          <t>27-Aug 16:28</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1377,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹30 (29.70%) 20 ↓ / 35 ↑</t>
+          <t>₹25 (24.75%) 20 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1375,7 +1387,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.15x</t>
+          <t>18.84x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1415,7 +1427,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>26-Aug 14:29</t>
+          <t>27-Aug 16:30</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1427,62 +1439,62 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ABH Healthcare NSE SMEO</t>
+          <t>Annu Projects IPOO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹7 (7.07%) 4 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.91x</t>
+          <t>0.87x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹34.98 Cr</t>
+          <t>₹175.06 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 0</t>
+          <t>25-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>26-Aug 14:28</t>
+          <t>27-Aug 16:36</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1561,47 +1573,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOO</t>
+          <t>Madhur Knit NSE SMECT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹340 (34.41%) 220 ↓ / 410 ↑</t>
+          <t>₹2 (2.00%) 2 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4.69x</t>
+          <t>1.5x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹1757.00 Cr</t>
+          <t>₹53.27 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 335</t>
+          <t>24-Aug GMP: 16</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>27-Aug GMP: 2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1616,7 +1628,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>26-Aug 14:32</t>
+          <t>27-Aug 16:30</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1628,47 +1640,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Madhur Knit NSE SMEO</t>
+          <t>Symbiotec Pharmalab IPOCT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹16 (16.00%) 9 ↓ / 16 ↑</t>
+          <t>₹265 (26.82%) 220 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.63x</t>
+          <t>74.98x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹53.27 Cr</t>
+          <t>₹1757.00 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 16</t>
+          <t>24-Aug GMP: 335</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>27-Aug GMP: 265</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1683,7 +1695,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>26-Aug 14:29</t>
+          <t>27-Aug 16:30</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1695,47 +1707,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Skyways Air IPOO</t>
+          <t>ABH Healthcare NSE SMECT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹29 (21.01%) 19 ↓ / 50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4.46x</t>
+          <t>1.43x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹34.98 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 32</t>
+          <t>24-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>27-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1750,59 +1762,59 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>26-Aug 14:32</t>
+          <t>27-Aug 16:31</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOO</t>
+          <t>Skyways Air IPOCT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹40 (75.47%) 5 ↓ / 40 ↑</t>
+          <t>₹45 (32.61%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.31x</t>
+          <t>71.01x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹135.73 Cr</t>
+          <t>₹582.80 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 30</t>
+          <t>24-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>27-Aug GMP: 45</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1817,7 +1829,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>26-Aug 14:35</t>
+          <t>27-Aug 16:31</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1829,62 +1841,62 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOC</t>
+          <t>Hy-Tech Engineers IPOCT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹320 (40.61%) 190 ↓ / 395 ↑</t>
+          <t>₹45 (84.91%) 5 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>111.18x</t>
+          <t>246.27x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹825.00 Cr</t>
+          <t>₹135.73 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 310</t>
+          <t>24-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 315</t>
+          <t>27-Aug GMP: 45</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>26-Aug 14:31</t>
+          <t>27-Aug 16:32</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1896,62 +1908,62 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOCAllotted</t>
+          <t>Augmont Enterprises IPOC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹300 (100.00%) 65 ↓ / 321 ↑</t>
+          <t>₹300 (38.07%) 190 ↓ / 395 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>184.22x</t>
+          <t>111.18x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹825.00 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 270</t>
+          <t>21-Aug GMP: 310</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 313</t>
+          <t>25-Aug GMP: 315</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>26-Aug 14:30</t>
+          <t>27-Aug 16:35</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1963,79 +1975,79 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMECAllotted</t>
+          <t>Tempsens Instruments (India) IPOCAllotted</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹307 (102.33%) 65 ↓ / 321 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.48x</t>
+          <t>184.22x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹64.83 Cr</t>
+          <t>₹650.00 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>20-Aug GMP: 270</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0</t>
+          <t>24-Aug GMP: 313</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 0</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>26-Aug 5:55</t>
+          <t>27-Aug 16:32</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMEL@99.00 (0%)</t>
+          <t>Fascinate Textiles NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹1 (1.01%) 1 ↓ / 12 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2045,47 +2057,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.65x</t>
+          <t>1.48x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹26.73 Cr</t>
+          <t>₹64.83 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 12</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 1</t>
+          <t>19-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>26-Aug GMP: 1</t>
+          <t>24-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>26-Aug 9:37</t>
+          <t>27-Aug 5:55</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2097,12 +2109,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mopshop Distribution BSE SMEL@137.00 (-0.72%)</t>
+          <t>Dhanwel Hybrid Seeds BSE SMEL@99.00 (0%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹1 (0.72%) 1 ↓ / 22 ↑</t>
+          <t>₹1 (1.01%) 1 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2112,27 +2124,27 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.59x</t>
+          <t>1.65x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹27.26 Cr</t>
+          <t>₹26.73 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 5</t>
+          <t>19-Aug GMP: 12</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2152,7 +2164,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>26-Aug 9:28</t>
+          <t>26-Aug 9:37</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2231,12 +2243,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOL@103.30 (11.08%)</t>
+          <t>Mopshop Distribution BSE SMEL@137.00 (-0.72%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹2.75 (2.96%) 1 ↓ / 8 ↑</t>
+          <t>₹1 (0.72%) 1 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2246,52 +2258,52 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.8x</t>
+          <t>1.59x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹367.18 Cr</t>
+          <t>₹27.26 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 5</t>
+          <t>19-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 5</t>
+          <t>21-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 2.75</t>
+          <t>26-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>25-Aug 9:36</t>
+          <t>26-Aug 9:28</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -2365,62 +2377,62 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOL@265.00 (31.84%)</t>
+          <t>Shankesh Jewellers IPOL@103.30 (11.08%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹74 (36.82%) 17 ↓ / 77 ↑</t>
+          <t>₹2.75 (2.96%) 1 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>66.63x</t>
+          <t>2.8x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹367.18 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 30</t>
+          <t>18-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 54</t>
+          <t>20-Aug GMP: 5</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 74</t>
+          <t>25-Aug GMP: 2.75</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>24-Aug 9:33</t>
+          <t>25-Aug 9:36</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2432,47 +2444,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks IPOL@60.25 (0.42%)</t>
+          <t>Lalithaa Jewellery Mart IPOL@265.00 (31.84%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹1.5 (2.50%) 1 ↓ / 4.50 ↑</t>
+          <t>₹74 (36.82%) 17 ↓ / 77 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.52x</t>
+          <t>66.63x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹2600.04 Cr</t>
+          <t>₹1700.00 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 1.7</t>
+          <t>17-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 1.3</t>
+          <t>19-Aug GMP: 54</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2482,12 +2494,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 1.5</t>
+          <t>24-Aug GMP: 74</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>24-Aug 9:37</t>
+          <t>24-Aug 9:33</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2499,62 +2511,62 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ENS Enterprises BSE SMEL@96.00 (4.35%)</t>
+          <t>Horizon Industrial Parks IPOL@60.25 (0.42%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹5 (5.43%) 4 ↓ / 5 ↑</t>
+          <t>₹1.5 (2.50%) 1 ↓ / 4.50 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>13.11x</t>
+          <t>1.52x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹33.14 Cr</t>
+          <t>₹2600.04 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>14-Aug GMP: 0</t>
+          <t>17-Aug GMP: 1.7</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 4</t>
+          <t>19-Aug GMP: 1.3</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>19-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 5</t>
+          <t>24-Aug GMP: 1.5</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>21-Aug 9:30</t>
+          <t>24-Aug 9:37</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>27-Aug 16:30</t>
+          <t>27-Aug 19:28</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -573,12 +573,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹25 (14.12%) 25 ↓ / 25 ↑</t>
+          <t>₹43 (24.29%) 43 ↓ / 43 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>27-Aug 16:34</t>
+          <t>27-Aug 19:28</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>27-Aug 16:33</t>
+          <t>27-Aug 19:34</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>27-Aug 16:36</t>
+          <t>27-Aug 19:35</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>27-Aug 16:31</t>
+          <t>27-Aug 19:28</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>27-Aug 16:31</t>
+          <t>27-Aug 19:35</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>27-Aug 16:30</t>
+          <t>27-Aug 19:30</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>27-Aug 16:34</t>
+          <t>27-Aug 19:35</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹335 (78.09%) 275 ↓ / 365 ↑</t>
+          <t>₹336 (78.32%) 275 ↓ / 365 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>27-Aug 16:36</t>
+          <t>27-Aug 19:34</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>27-Aug 16:33</t>
+          <t>27-Aug 19:32</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>27-Aug 16:33</t>
+          <t>27-Aug 19:37</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹56 (68.29%) 46 ↓ / 56 ↑</t>
+          <t>₹55 (67.07%) 46 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.35x</t>
+          <t>1.51x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 56</t>
+          <t>27-Aug GMP: 55</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>27-Aug 16:28</t>
+          <t>27-Aug 19:34</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6.45x</t>
+          <t>7.51x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>27-Aug 16:28</t>
+          <t>27-Aug 19:33</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹25 (24.75%) 20 ↓ / 35 ↑</t>
+          <t>₹35 (34.65%) 20 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18.84x</t>
+          <t>20.8x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>27-Aug 16:30</t>
+          <t>27-Aug 19:29</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.87x</t>
+          <t>0.88x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>27-Aug 16:36</t>
+          <t>27-Aug 19:28</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Madhur Knit NSE SMECT</t>
+          <t>Madhur Knit NSE SMEC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>27-Aug 16:30</t>
+          <t>27-Aug 19:33</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1640,12 +1640,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOCT</t>
+          <t>Symbiotec Pharmalab IPOC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹265 (26.82%) 220 ↓ / 410 ↑</t>
+          <t>₹267 (27.02%) 220 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>74.98x</t>
+          <t>75.08x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 265</t>
+          <t>27-Aug GMP: 267</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>27-Aug 16:30</t>
+          <t>27-Aug 19:34</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ABH Healthcare NSE SMECT</t>
+          <t>ABH Healthcare NSE SMEC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.43x</t>
+          <t>1.44x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>27-Aug 16:31</t>
+          <t>27-Aug 19:30</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1774,12 +1774,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Skyways Air IPOCT</t>
+          <t>Skyways Air IPOC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹45 (32.61%) 19 ↓ / 50 ↑</t>
+          <t>₹44 (31.88%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>71.01x</t>
+          <t>71.25x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 45</t>
+          <t>27-Aug GMP: 44</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>27-Aug 16:31</t>
+          <t>27-Aug 19:28</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1841,7 +1841,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOCT</t>
+          <t>Hy-Tech Engineers IPOC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>246.27x</t>
+          <t>247.39x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>27-Aug 16:32</t>
+          <t>27-Aug 19:29</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>27-Aug 16:35</t>
+          <t>27-Aug 19:32</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹307 (102.33%) 65 ↓ / 321 ↑</t>
+          <t>₹320 (106.67%) 65 ↓ / 321 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>27-Aug 16:32</t>
+          <t>27-Aug 19:28</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,12 +506,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹10 (4.18%) 10 ↓ / 18 ↑</t>
+          <t>₹29 (12.13%) 10 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>27-Aug 19:28</t>
+          <t>28-Aug 20:31</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹43 (24.29%) 43 ↓ / 43 ↑</t>
+          <t>₹47 (26.55%) 47 ↓ / 47 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>27-Aug 19:28</t>
+          <t>28-Aug 20:32</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>27-Aug 19:34</t>
+          <t>28-Aug 20:35</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>27-Aug 19:35</t>
+          <t>28-Aug 20:34</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹20 (3.48%) 20 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>27-Aug 19:28</t>
+          <t>28-Aug 20:30</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>27-Aug 19:35</t>
+          <t>28-Aug 20:37</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>27-Aug 19:30</t>
+          <t>28-Aug 20:36</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -970,7 +970,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Complete Sports and Management BSE SMEU</t>
+          <t>Complete Sports and Management BSE SMEO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.13x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>28-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>27-Aug 19:35</t>
+          <t>28-Aug 20:35</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1037,12 +1037,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ESDS Software Solution IPOU</t>
+          <t>ESDS Software Solution IPOO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹336 (78.32%) 275 ↓ / 365 ↑</t>
+          <t>₹380 (88.58%) 275 ↓ / 380 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.21x</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>28-Aug GMP: 380</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>27-Aug 19:34</t>
+          <t>28-Aug 20:33</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1104,22 +1104,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Priority Jewels IPOU</t>
+          <t>Priority Jewels IPOO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹37 (18.50%) 20 ↓ / 37 ↑</t>
+          <t>₹45 (22.50%) 20 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.93x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>28-Aug GMP: 45</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>27-Aug 19:32</t>
+          <t>28-Aug 20:32</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Paluck Technologies BSE SMEU</t>
+          <t>Paluck Technologies BSE SMEO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>18.18x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>28-Aug GMP: 25</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>27-Aug 19:37</t>
+          <t>28-Aug 20:32</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹55 (67.07%) 46 ↓ / 55 ↑</t>
+          <t>₹59 (71.95%) 46 ↓ / 59 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.51x</t>
+          <t>5.14x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 55</t>
+          <t>27-Aug GMP: 56</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>27-Aug 19:34</t>
+          <t>28-Aug 20:35</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.51x</t>
+          <t>20.67x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>27-Aug 19:33</t>
+          <t>28-Aug 20:36</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1372,12 +1372,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sumax Engineering NSE SMEO</t>
+          <t>Sumax Engineering NSE SMEC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹35 (34.65%) 20 ↓ / 35 ↑</t>
+          <t>₹36 (35.64%) 20 ↓ / 36 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20.8x</t>
+          <t>162.94x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>28-Aug GMP: 36</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>27-Aug 19:29</t>
+          <t>28-Aug 20:36</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1439,22 +1439,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Annu Projects IPOO</t>
+          <t>Annu Projects IPOC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹7 (7.07%) 4 ↓ / 7 ↑</t>
+          <t>₹1 (1.01%) 1 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.88x</t>
+          <t>2.93x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>28-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>27-Aug 19:28</t>
+          <t>28-Aug 20:36</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Madhur Knit NSE SMEC</t>
+          <t>Madhur Knit NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>27-Aug 19:33</t>
+          <t>28-Aug 20:31</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹267 (27.02%) 220 ↓ / 410 ↑</t>
+          <t>₹265 (26.82%) 220 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 267</t>
+          <t>27-Aug GMP: 270</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>27-Aug 19:34</t>
+          <t>28-Aug 20:32</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ABH Healthcare NSE SMEC</t>
+          <t>ABH Healthcare NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>27-Aug 19:30</t>
+          <t>28-Aug 20:36</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹44 (31.88%) 19 ↓ / 50 ↑</t>
+          <t>₹39 (28.26%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>27-Aug 19:28</t>
+          <t>28-Aug 20:36</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>27-Aug 19:29</t>
+          <t>28-Aug 20:35</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1908,12 +1908,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOC</t>
+          <t>Augmont Enterprises IPOCAllotted</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹300 (38.07%) 190 ↓ / 395 ↑</t>
+          <t>₹301 (38.20%) 190 ↓ / 395 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>27-Aug 19:32</t>
+          <t>28-Aug 20:29</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1975,134 +1975,134 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOCAllotted</t>
+          <t>Fascinate Textiles NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹320 (106.67%) 65 ↓ / 321 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>184.22x</t>
+          <t>1.48x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹64.83 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 270</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 313</t>
+          <t>19-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>24-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>27-Aug 19:28</t>
+          <t>28-Aug 5:55</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMECAllotted</t>
+          <t>Tempsens Instruments (India) IPOL@634.00 (111.33%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹330 (110.00%) 65 ↓ / 330 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.48x</t>
+          <t>184.22x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹64.83 Cr</t>
+          <t>₹650.00 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>20-Aug GMP: 270</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0</t>
+          <t>24-Aug GMP: 313</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 0</t>
+          <t>28-Aug GMP: 330</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>27-Aug 5:55</t>
+          <t>28-Aug 9:35</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>28-Aug 20:31</t>
+          <t>29-Aug 14:54</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹47 (26.55%) 47 ↓ / 47 ↑</t>
+          <t>₹53 (29.94%) 47 ↓ / 53 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>28-Aug 20:32</t>
+          <t>29-Aug 15:01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>28-Aug 20:35</t>
+          <t>29-Aug 14:54</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>28-Aug 20:34</t>
+          <t>29-Aug 14:59</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹20 (3.48%) 20 ↓ / 20 ↑</t>
+          <t>₹30 (5.22%) 30 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>28-Aug 20:30</t>
+          <t>29-Aug 15:00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>28-Aug 20:37</t>
+          <t>29-Aug 14:53</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>28-Aug 20:36</t>
+          <t>29-Aug 14:57</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>28-Aug 20:35</t>
+          <t>29-Aug 15:02</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 380</t>
+          <t>28-Aug GMP: 360</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>28-Aug 20:33</t>
+          <t>29-Aug 14:54</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹45 (22.50%) 20 ↓ / 45 ↑</t>
+          <t>₹47 (23.50%) 20 ↓ / 47 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>28-Aug 20:32</t>
+          <t>29-Aug 14:54</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>28-Aug 20:32</t>
+          <t>29-Aug 14:55</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹59 (71.95%) 46 ↓ / 59 ↑</t>
+          <t>₹61 (74.39%) 46 ↓ / 61.50 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>28-Aug 20:35</t>
+          <t>29-Aug 14:54</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹64 (71.11%) 15 ↓ / 64 ↑</t>
+          <t>₹70 (77.78%) 15 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>28-Aug 20:36</t>
+          <t>29-Aug 14:55</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>28-Aug 20:36</t>
+          <t>29-Aug 14:56</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>28-Aug 20:36</t>
+          <t>29-Aug 14:59</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>28-Aug 20:31</t>
+          <t>29-Aug 14:54</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1640,12 +1640,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOC</t>
+          <t>Symbiotec Pharmalab IPOCAllotted</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹265 (26.82%) 220 ↓ / 410 ↑</t>
+          <t>₹249 (25.20%) 220 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>28-Aug 20:32</t>
+          <t>29-Aug 14:53</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>28-Aug 20:36</t>
+          <t>29-Aug 14:55</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1774,12 +1774,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Skyways Air IPOC</t>
+          <t>Skyways Air IPOCAllotted</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹39 (28.26%) 19 ↓ / 50 ↑</t>
+          <t>₹40 (28.99%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>28-Aug 20:36</t>
+          <t>29-Aug 14:59</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1841,12 +1841,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOC</t>
+          <t>Hy-Tech Engineers IPOCAllotted</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹45 (84.91%) 5 ↓ / 45 ↑</t>
+          <t>₹43 (81.13%) 5 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>28-Aug 20:35</t>
+          <t>29-Aug 14:58</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹301 (38.20%) 190 ↓ / 395 ↑</t>
+          <t>₹292 (37.06%) 190 ↓ / 395 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>28-Aug 20:29</t>
+          <t>29-Aug 14:58</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>28-Aug 5:55</t>
+          <t>29-Aug 5:55</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹29 (12.13%) 10 ↓ / 29 ↑</t>
+          <t>₹35 (14.64%) 10 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>29-Aug 14:54</t>
+          <t>30-Aug 14:36</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹53 (29.94%) 47 ↓ / 53 ↑</t>
+          <t>₹43 (24.29%) 43 ↓ / 53 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>29-Aug 15:01</t>
+          <t>30-Aug 14:31</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>29-Aug 14:54</t>
+          <t>30-Aug 14:33</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>29-Aug 14:59</t>
+          <t>30-Aug 14:28</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹30 (5.22%) 30 ↓ / 30 ↑</t>
+          <t>₹28 (4.87%) 28 ↓ / 34 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>29-Aug 15:00</t>
+          <t>30-Aug 14:32</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>29-Aug 14:53</t>
+          <t>30-Aug 14:32</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>29-Aug 14:57</t>
+          <t>30-Aug 14:34</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>29-Aug 15:02</t>
+          <t>30-Aug 14:33</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹380 (88.58%) 275 ↓ / 380 ↑</t>
+          <t>₹372 (86.71%) 275 ↓ / 372 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>29-Aug 14:54</t>
+          <t>30-Aug 14:33</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹47 (23.50%) 20 ↓ / 47 ↑</t>
+          <t>₹45 (22.50%) 20 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>29-Aug 14:54</t>
+          <t>30-Aug 14:28</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>29-Aug 14:55</t>
+          <t>30-Aug 14:34</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹61 (74.39%) 46 ↓ / 61.50 ↑</t>
+          <t>₹62 (75.61%) 46 ↓ / 63 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>29-Aug 14:54</t>
+          <t>30-Aug 14:31</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>29-Aug 14:55</t>
+          <t>30-Aug 14:30</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>29-Aug 14:56</t>
+          <t>30-Aug 14:29</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>29-Aug 14:59</t>
+          <t>30-Aug 14:30</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>29-Aug 14:54</t>
+          <t>30-Aug 14:35</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹249 (25.20%) 220 ↓ / 410 ↑</t>
+          <t>₹240 (24.29%) 220 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>29-Aug 14:53</t>
+          <t>30-Aug 14:29</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>29-Aug 14:55</t>
+          <t>30-Aug 14:32</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹40 (28.99%) 19 ↓ / 50 ↑</t>
+          <t>₹39.5 (28.62%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>29-Aug 14:59</t>
+          <t>30-Aug 14:28</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>29-Aug 14:58</t>
+          <t>30-Aug 14:37</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹292 (37.06%) 190 ↓ / 395 ↑</t>
+          <t>₹290 (36.80%) 190 ↓ / 395 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>29-Aug 14:58</t>
+          <t>30-Aug 14:30</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>29-Aug 5:55</t>
+          <t>30-Aug 5:55</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>30-Aug 14:36</t>
+          <t>30-Aug 19:36</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹43 (24.29%) 43 ↓ / 53 ↑</t>
+          <t>₹45 (25.42%) 45 ↓ / 53 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>30-Aug 14:31</t>
+          <t>30-Aug 19:31</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>30-Aug 14:33</t>
+          <t>30-Aug 19:31</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>30-Aug 14:28</t>
+          <t>30-Aug 19:31</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>30-Aug 14:32</t>
+          <t>30-Aug 19:35</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>30-Aug 14:32</t>
+          <t>30-Aug 19:29</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>30-Aug 14:34</t>
+          <t>30-Aug 19:33</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30-Aug 14:33</t>
+          <t>30-Aug 19:36</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹372 (86.71%) 275 ↓ / 372 ↑</t>
+          <t>₹355 (82.75%) 275 ↓ / 372 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>30-Aug 14:33</t>
+          <t>30-Aug 19:36</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>30-Aug 14:28</t>
+          <t>30-Aug 19:32</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>30-Aug 14:34</t>
+          <t>30-Aug 19:35</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹62 (75.61%) 46 ↓ / 63 ↑</t>
+          <t>₹60 (73.17%) 46 ↓ / 63 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>30-Aug 14:31</t>
+          <t>30-Aug 19:32</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>30-Aug 14:30</t>
+          <t>30-Aug 19:35</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>30-Aug 14:29</t>
+          <t>30-Aug 19:29</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>30-Aug 14:30</t>
+          <t>30-Aug 19:29</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>30-Aug 14:35</t>
+          <t>30-Aug 19:30</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹240 (24.29%) 220 ↓ / 410 ↑</t>
+          <t>₹243 (24.60%) 220 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>30-Aug 14:29</t>
+          <t>30-Aug 19:35</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>30-Aug 14:32</t>
+          <t>30-Aug 19:33</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>30-Aug 14:28</t>
+          <t>30-Aug 19:29</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>30-Aug 14:37</t>
+          <t>30-Aug 19:28</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>30-Aug 14:30</t>
+          <t>30-Aug 19:35</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,17 +501,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rays of Belief IPOU</t>
+          <t>Fly-Hi Maritime BSE SMEU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹35 (14.64%) 10 ↓ / 35 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹125.00 Cr</t>
+          <t>₹52.63 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -556,12 +556,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>30-Aug 19:36</t>
+          <t>31-Aug 14:57</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹45 (25.42%) 45 ↓ / 53 ↑</t>
+          <t>₹42 (23.73%) 42 ↓ / 53 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>30-Aug 19:31</t>
+          <t>31-Aug 14:53</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>30-Aug 19:31</t>
+          <t>31-Aug 15:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -702,17 +702,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Shanti Inorganics NSE SMEU</t>
+          <t>Rays of Belief IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹31 (37.35%) 25 ↓ / 31 ↑</t>
+          <t>₹25 (10.46%) 10 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -722,42 +722,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>239</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹47.24 Cr</t>
+          <t>₹125.00 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>7-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>30-Aug 19:31</t>
+          <t>31-Aug 14:55</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -769,12 +769,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Purple Style Labs IPOU</t>
+          <t>Purple Style Labs IPOO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹28 (4.87%) 28 ↓ / 34 ↑</t>
+          <t>₹5 (0.87%) 5 ↓ / 34 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.09x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>31-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>30-Aug 19:35</t>
+          <t>31-Aug 14:56</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -836,7 +836,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ashutosh Fibre NSE SMEU</t>
+          <t>Ashutosh Fibre NSE SMEO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.14x</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>31-Aug GMP: 37</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>30-Aug 19:29</t>
+          <t>31-Aug 14:58</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -903,22 +903,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Phychem Technologies BSE SMEU</t>
+          <t>Phychem Technologies BSE SMEO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹3 (5.56%) 3 ↓ / 3 ↑</t>
+          <t>₹1 (1.85%) 1 ↓ / 3 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.17x</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>31-Aug GMP: 1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>30-Aug 19:33</t>
+          <t>31-Aug 15:00</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -970,62 +970,62 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Complete Sports and Management BSE SMEO</t>
+          <t>Shanti Inorganics NSE SMEO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹31 (37.35%) 25 ↓ / 31 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.13x</t>
+          <t>0.85x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹74.93 Cr</t>
+          <t>₹47.24 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 0</t>
+          <t>31-Aug GMP: 31</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30-Aug 19:36</t>
+          <t>31-Aug 14:56</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1037,12 +1037,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ESDS Software Solution IPOO</t>
+          <t>Paluck Technologies BSE SMEO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹355 (82.75%) 275 ↓ / 372 ↑</t>
+          <t>₹30 (62.50%) 10 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1052,27 +1052,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.21x</t>
+          <t>67.54x</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹720.00 Cr</t>
+          <t>₹33.00 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 360</t>
+          <t>28-Aug GMP: 25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>30-Aug 19:36</t>
+          <t>31-Aug 15:00</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1104,42 +1104,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Priority Jewels IPOO</t>
+          <t>ESDS Software Solution IPOO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹45 (22.50%) 20 ↓ / 45 ↑</t>
+          <t>₹324 (75.52%) 275 ↓ / 372 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.93x</t>
+          <t>20.75x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>429</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹91.50 Cr</t>
+          <t>₹720.00 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 45</t>
+          <t>28-Aug GMP: 360</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>30-Aug 19:32</t>
+          <t>31-Aug 14:53</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1171,42 +1171,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Paluck Technologies BSE SMEO</t>
+          <t>Complete Sports and Management BSE SMEO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹25 (52.08%) 10 ↓ / 25 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>18.18x</t>
+          <t>0.13x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹33.00 Cr</t>
+          <t>₹74.93 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 25</t>
+          <t>28-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>30-Aug 19:35</t>
+          <t>31-Aug 14:59</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1238,62 +1238,62 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lumino Industries IPOO</t>
+          <t>Priority Jewels IPOO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹60 (73.17%) 46 ↓ / 63 ↑</t>
+          <t>₹45 (22.50%) 20 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5.14x</t>
+          <t>22.35x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹700.00 Cr</t>
+          <t>₹91.50 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 56</t>
+          <t>28-Aug GMP: 45</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>30-Aug 19:32</t>
+          <t>31-Aug 14:55</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1305,7 +1305,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kwick Forensic Solutions BSE SMEO</t>
+          <t>Kwick Forensic Solutions BSE SMECT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20.67x</t>
+          <t>154.9x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>31-Aug GMP: 70</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>30-Aug 19:35</t>
+          <t>31-Aug 15:01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1372,62 +1372,62 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sumax Engineering NSE SMEC</t>
+          <t>Lumino Industries IPOCT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹36 (35.64%) 20 ↓ / 36 ↑</t>
+          <t>₹54 (65.85%) 46 ↓ / 63 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>162.94x</t>
+          <t>67.01x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹53.40 Cr</t>
+          <t>₹700.00 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>182</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 35</t>
+          <t>27-Aug GMP: 56</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 36</t>
+          <t>31-Aug GMP: 54</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>30-Aug 19:29</t>
+          <t>31-Aug 15:01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1439,47 +1439,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Annu Projects IPOC</t>
+          <t>Sumax Engineering NSE SMEC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹1 (1.01%) 1 ↓ / 7 ↑</t>
+          <t>₹36 (35.64%) 20 ↓ / 36 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.93x</t>
+          <t>162.94x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹175.06 Cr</t>
+          <t>₹53.40 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 0</t>
+          <t>25-Aug GMP: 35</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 1</t>
+          <t>28-Aug GMP: 36</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>30-Aug 19:29</t>
+          <t>31-Aug 14:55</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Madhur Knit NSE SMECAllotted</t>
+          <t>Annu Projects IPOC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹2 (2.00%) 2 ↓ / 16 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1588,99 +1588,99 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.5x</t>
+          <t>2.93x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹53.27 Cr</t>
+          <t>₹175.06 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 16</t>
+          <t>25-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 2</t>
+          <t>28-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>30-Aug 19:30</t>
+          <t>31-Aug 14:57</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOCAllotted</t>
+          <t>Madhur Knit NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹243 (24.60%) 220 ↓ / 410 ↑</t>
+          <t>₹2 (2.00%) 2 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>75.08x</t>
+          <t>1.5x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹1757.00 Cr</t>
+          <t>₹53.27 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 335</t>
+          <t>24-Aug GMP: 16</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 270</t>
+          <t>27-Aug GMP: 2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>30-Aug 19:35</t>
+          <t>31-Aug 14:58</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1707,47 +1707,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ABH Healthcare NSE SMECAllotted</t>
+          <t>Symbiotec Pharmalab IPOCAllotted</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹205 (20.75%) 205 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.44x</t>
+          <t>75.08x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹34.98 Cr</t>
+          <t>₹1757.00 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 0</t>
+          <t>24-Aug GMP: 335</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 0</t>
+          <t>27-Aug GMP: 270</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1762,59 +1762,59 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>30-Aug 19:33</t>
+          <t>31-Aug 14:58</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Skyways Air IPOCAllotted</t>
+          <t>Hy-Tech Engineers IPOCAllotted</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹39.5 (28.62%) 19 ↓ / 50 ↑</t>
+          <t>₹42 (79.25%) 5 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>71.25x</t>
+          <t>247.39x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹135.73 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 32</t>
+          <t>24-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 44</t>
+          <t>27-Aug GMP: 45</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>30-Aug 19:29</t>
+          <t>31-Aug 14:56</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1841,47 +1841,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOCAllotted</t>
+          <t>ABH Healthcare NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹43 (81.13%) 5 ↓ / 45 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>247.39x</t>
+          <t>1.44x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹135.73 Cr</t>
+          <t>₹34.98 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 30</t>
+          <t>24-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 45</t>
+          <t>27-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>30-Aug 19:28</t>
+          <t>31-Aug 14:53</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOCAllotted</t>
+          <t>Skyways Air IPOCAllotted</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹290 (36.80%) 190 ↓ / 395 ↑</t>
+          <t>₹36 (26.09%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1923,47 +1923,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>111.18x</t>
+          <t>71.25x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹825.00 Cr</t>
+          <t>₹582.80 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 310</t>
+          <t>24-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 315</t>
+          <t>27-Aug GMP: 44</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>30-Aug 19:35</t>
+          <t>31-Aug 14:59</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>30-Aug 5:55</t>
+          <t>31-Aug 5:55</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2042,62 +2042,62 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOL@634.00 (111.33%)</t>
+          <t>Augmont Enterprises IPOL@961.00 (21.95%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹330 (110.00%) 65 ↓ / 330 ↑</t>
+          <t>₹290 (36.80%) 190 ↓ / 395 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>184.22x</t>
+          <t>111.18x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹825.00 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 270</t>
+          <t>21-Aug GMP: 310</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 313</t>
+          <t>25-Aug GMP: 315</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 330</t>
+          <t>31-Aug GMP: 290</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>28-Aug 9:35</t>
+          <t>31-Aug 9:29</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2109,114 +2109,114 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMEL@99.00 (0%)</t>
+          <t>Tempsens Instruments (India) IPOL@634.00 (111.33%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹1 (1.01%) 1 ↓ / 12 ↑</t>
+          <t>₹330 (110.00%) 65 ↓ / 330 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.65x</t>
+          <t>184.22x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹26.73 Cr</t>
+          <t>₹650.00 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 12</t>
+          <t>20-Aug GMP: 270</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 1</t>
+          <t>24-Aug GMP: 313</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>26-Aug GMP: 1</t>
+          <t>28-Aug GMP: 330</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>26-Aug 9:37</t>
+          <t>28-Aug 9:35</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOL@185.00 (15.62%)</t>
+          <t>Mopshop Distribution BSE SMEL@137.00 (-0.72%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹18.5 (11.56%) 7 ↓ / 30 ↑</t>
+          <t>₹1 (0.72%) 1 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>32.98x</t>
+          <t>1.59x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹550.00 Cr</t>
+          <t>₹27.26 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 23</t>
+          <t>19-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 19</t>
+          <t>21-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2226,29 +2226,29 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>26-Aug GMP: 18.5</t>
+          <t>26-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>26-Aug 9:34</t>
+          <t>26-Aug 9:28</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mopshop Distribution BSE SMEL@137.00 (-0.72%)</t>
+          <t>Dhanwel Hybrid Seeds BSE SMEL@99.00 (0%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹1 (0.72%) 1 ↓ / 22 ↑</t>
+          <t>₹1 (1.01%) 1 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2258,27 +2258,27 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.59x</t>
+          <t>1.65x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹27.26 Cr</t>
+          <t>₹26.73 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 5</t>
+          <t>19-Aug GMP: 12</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>26-Aug 9:28</t>
+          <t>26-Aug 9:37</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2310,12 +2310,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOL@395.90 (9.97%)</t>
+          <t>Gaja Alternative Asset Management IPOL@185.00 (15.62%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹50 (13.89%) 17 ↓ / 80 ↑</t>
+          <t>₹18.5 (11.56%) 7 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2325,47 +2325,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>105.81x</t>
+          <t>32.98x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹550.00 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 77</t>
+          <t>19-Aug GMP: 23</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 80</t>
+          <t>21-Aug GMP: 19</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 50</t>
+          <t>26-Aug GMP: 18.5</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>25-Aug 9:30</t>
+          <t>26-Aug 9:34</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2444,62 +2444,62 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOL@265.00 (31.84%)</t>
+          <t>Sunshine Pictures IPOL@395.90 (9.97%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹74 (36.82%) 17 ↓ / 77 ↑</t>
+          <t>₹50 (13.89%) 17 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>66.63x</t>
+          <t>105.81x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹282.14 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 30</t>
+          <t>18-Aug GMP: 77</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 54</t>
+          <t>20-Aug GMP: 80</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 74</t>
+          <t>25-Aug GMP: 50</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>24-Aug 9:33</t>
+          <t>25-Aug 9:30</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2511,47 +2511,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks IPOL@60.25 (0.42%)</t>
+          <t>Lalithaa Jewellery Mart IPOL@265.00 (31.84%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹1.5 (2.50%) 1 ↓ / 4.50 ↑</t>
+          <t>₹74 (36.82%) 17 ↓ / 77 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.52x</t>
+          <t>66.63x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹2600.04 Cr</t>
+          <t>₹1700.00 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 1.7</t>
+          <t>17-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 1.3</t>
+          <t>19-Aug GMP: 54</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 1.5</t>
+          <t>24-Aug GMP: 74</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>24-Aug 9:37</t>
+          <t>24-Aug 9:33</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fly-Hi Maritime BSE SMEU</t>
+          <t>Kanohar Electricals IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -519,66 +519,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹52.63 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1-Sep</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3-Sep</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>4-Sep</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>8-Sep</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>31-Aug 14:57</t>
+          <t>1-Sep 5:55</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Deepa Jewellers IPOU</t>
+          <t>Veegaland Developers IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹42 (23.73%) 42 ↓ / 53 ↑</t>
+          <t>₹14 (10.00%) 14 ↓ / 14 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -588,42 +560,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹459.72 Cr</t>
+          <t>₹210.00 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>10-Sep</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>31-Aug 14:53</t>
+          <t>1-Sep 13:53</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -635,7 +607,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Farm Peace BSE SMEU</t>
+          <t>Qualiance International NSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -655,89 +627,89 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>127</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹32.00 Cr</t>
+          <t>₹45.11 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>9-Sep</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8-Sep</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>31-Aug 15:02</t>
+          <t>1-Sep 14:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Rays of Belief IPOU</t>
+          <t>Farm Peace BSE SMEO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹25 (10.46%) 10 ↓ / 35 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.01x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹125.00 Cr</t>
+          <t>₹32.00 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>1-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -757,74 +729,74 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>31-Aug 14:55</t>
+          <t>1-Sep 14:00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Purple Style Labs IPOO</t>
+          <t>Rays of Belief IPOO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹5 (0.87%) 5 ↓ / 34 ↑</t>
+          <t>₹48 (20.08%) 10 ↓ / 48 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.09x</t>
+          <t>0.83x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>239</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹680.00 Cr</t>
+          <t>₹125.00 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 5</t>
+          <t>1-Sep GMP: 48</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>7-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>31-Aug 14:56</t>
+          <t>1-Sep 14:00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -836,32 +808,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ashutosh Fibre NSE SMEO</t>
+          <t>Fly-Hi Maritime BSE SMEO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹37 (40.22%) 13 ↓ / 37 ↑</t>
+          <t>₹9 (8.82%) 5 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.14x</t>
+          <t>0.01x</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹56.35 Cr</t>
+          <t>₹52.63 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -871,94 +843,94 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 37</t>
+          <t>1-Sep GMP: 9</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>7-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>31-Aug 14:58</t>
+          <t>1-Sep 14:01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Phychem Technologies BSE SMEO</t>
+          <t>Deepa Jewellers IPOO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹1 (1.85%) 1 ↓ / 3 ↑</t>
+          <t>₹44 (24.86%) 44 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.17x</t>
+          <t>0.6x</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹14.58 Cr</t>
+          <t>₹459.72 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 1</t>
+          <t>1-Sep GMP: 44</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>7-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>31-Aug 15:00</t>
+          <t>1-Sep 13:59</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -970,42 +942,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shanti Inorganics NSE SMEO</t>
+          <t>Purple Style Labs IPOO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹31 (37.35%) 25 ↓ / 31 ↑</t>
+          <t>₹2 (0.35%) 2 ↓ / 34 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.85x</t>
+          <t>0.22x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>575</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹47.24 Cr</t>
+          <t>₹680.00 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 31</t>
+          <t>31-Aug GMP: 7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1025,7 +997,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>31-Aug 14:56</t>
+          <t>1-Sep 13:53</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1037,62 +1009,62 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Paluck Technologies BSE SMEO</t>
+          <t>Phychem Technologies BSE SMEO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹30 (62.50%) 10 ↓ / 30 ↑</t>
+          <t>₹1 (1.85%) 1 ↓ / 3 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>67.54x</t>
+          <t>1.61x</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹33.00 Cr</t>
+          <t>₹14.58 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 25</t>
+          <t>31-Aug GMP: 1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>31-Aug 15:00</t>
+          <t>1-Sep 14:02</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1104,62 +1076,62 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ESDS Software Solution IPOO</t>
+          <t>Shanti Inorganics NSE SMEO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹324 (75.52%) 275 ↓ / 372 ↑</t>
+          <t>₹10 (12.05%) 10 ↓ / 31 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20.75x</t>
+          <t>3.19x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹720.00 Cr</t>
+          <t>₹47.24 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 360</t>
+          <t>31-Aug GMP: 31</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>31-Aug 14:53</t>
+          <t>1-Sep 13:53</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1171,62 +1143,62 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Complete Sports and Management BSE SMEO</t>
+          <t>Ashutosh Fibre NSE SMEO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹27 (29.35%) 13 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.13x</t>
+          <t>4.2x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹74.93 Cr</t>
+          <t>₹56.35 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 0</t>
+          <t>31-Aug GMP: 45</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>31-Aug 14:59</t>
+          <t>1-Sep 13:56</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1238,47 +1210,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Priority Jewels IPOO</t>
+          <t>ESDS Software Solution IPOCT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹45 (22.50%) 20 ↓ / 45 ↑</t>
+          <t>₹257 (59.91%) 257 ↓ / 372 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>22.35x</t>
+          <t>67.26x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>429</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹91.50 Cr</t>
+          <t>₹720.00 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 45</t>
+          <t>28-Aug GMP: 360</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>1-Sep GMP: 257</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1293,7 +1265,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>31-Aug 14:55</t>
+          <t>1-Sep 13:57</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1305,62 +1277,62 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kwick Forensic Solutions BSE SMECT</t>
+          <t>Complete Sports and Management BSE SMECT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹70 (77.78%) 15 ↓ / 70 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>154.9x</t>
+          <t>0.71x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹50.77 Cr</t>
+          <t>₹74.93 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 64</t>
+          <t>28-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 70</t>
+          <t>1-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>31-Aug 15:01</t>
+          <t>1-Sep 14:02</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1372,62 +1344,62 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lumino Industries IPOCT</t>
+          <t>Priority Jewels IPOCT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹54 (65.85%) 46 ↓ / 63 ↑</t>
+          <t>₹40 (20.00%) 20 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>67.01x</t>
+          <t>71.02x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹700.00 Cr</t>
+          <t>₹91.50 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 56</t>
+          <t>28-Aug GMP: 45</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 54</t>
+          <t>1-Sep GMP: 40</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>31-Aug 15:01</t>
+          <t>1-Sep 13:59</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1439,62 +1411,62 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sumax Engineering NSE SMEC</t>
+          <t>Paluck Technologies BSE SMECT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹36 (35.64%) 20 ↓ / 36 ↑</t>
+          <t>₹30 (62.50%) 10 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>162.94x</t>
+          <t>504.26x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹53.40 Cr</t>
+          <t>₹33.00 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 35</t>
+          <t>28-Aug GMP: 25</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 36</t>
+          <t>1-Sep GMP: 30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>31-Aug 14:55</t>
+          <t>1-Sep 14:01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1573,129 +1545,129 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Annu Projects IPOC</t>
+          <t>Lumino Industries IPOC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 7 ↑</t>
+          <t>₹40 (48.78%) 40 ↓ / 63 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.93x</t>
+          <t>124.02x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹175.06 Cr</t>
+          <t>₹700.00 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>182</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 0</t>
+          <t>27-Aug GMP: 56</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 1</t>
+          <t>31-Aug GMP: 48</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>31-Aug 14:57</t>
+          <t>1-Sep 13:53</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Madhur Knit NSE SMECAllotted</t>
+          <t>Kwick Forensic Solutions BSE SMEC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹2 (2.00%) 2 ↓ / 16 ↑</t>
+          <t>₹85 (94.44%) 15 ↓ / 85 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.5x</t>
+          <t>289x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹53.27 Cr</t>
+          <t>₹50.77 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 16</t>
+          <t>27-Aug GMP: 64</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 2</t>
+          <t>31-Aug GMP: 85</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>31-Aug 14:58</t>
+          <t>1-Sep 14:00</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1707,129 +1679,129 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOCAllotted</t>
+          <t>Annu Projects IPOCAllotted</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹205 (20.75%) 205 ↓ / 410 ↑</t>
+          <t>₹-3 (-3.03%) -3 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>75.08x</t>
+          <t>2.93x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹1757.00 Cr</t>
+          <t>₹175.06 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 335</t>
+          <t>25-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 270</t>
+          <t>28-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>31-Aug 14:58</t>
+          <t>1-Sep 13:57</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOCAllotted</t>
+          <t>Sumax Engineering NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹42 (79.25%) 5 ↓ / 45 ↑</t>
+          <t>₹30 (29.70%) 20 ↓ / 36 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>247.39x</t>
+          <t>162.94x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹135.73 Cr</t>
+          <t>₹53.40 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 30</t>
+          <t>25-Aug GMP: 35</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 45</t>
+          <t>28-Aug GMP: 36</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>31-Aug 14:56</t>
+          <t>1-Sep 13:56</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1841,7 +1813,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ABH Healthcare NSE SMECAllotted</t>
+          <t>Fascinate Textiles NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1856,47 +1828,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.44x</t>
+          <t>1.48x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹34.98 Cr</t>
+          <t>₹64.83 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
+          <t>11-Aug GMP: 0</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>19-Aug GMP: 0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>20-Aug</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>24-Aug GMP: 0</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>27-Aug GMP: 0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>28-Aug</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>1-Sep</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>31-Aug 14:53</t>
+          <t>1-Sep 5:55</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1908,47 +1880,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Skyways Air IPOCAllotted</t>
+          <t>Madhur Knit NSE SMEL@100.00 (0%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹36 (26.09%) 19 ↓ / 50 ↑</t>
+          <t>₹2 (2.00%) 2 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>71.25x</t>
+          <t>1.5x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹53.27 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 32</t>
+          <t>24-Aug GMP: 16</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 44</t>
+          <t>27-Aug GMP: 2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1958,12 +1930,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>1-Sep GMP: 2</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>31-Aug 14:59</t>
+          <t>1-Sep 9:30</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1975,79 +1947,79 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMECAllotted</t>
+          <t>Symbiotec Pharmalab IPOL@988.00 (0%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹185 (18.72%) 185 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.48x</t>
+          <t>75.08x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹64.83 Cr</t>
+          <t>₹1757.00 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>24-Aug GMP: 335</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0</t>
+          <t>27-Aug GMP: 270</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 0</t>
+          <t>1-Sep GMP: 185</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>31-Aug 5:55</t>
+          <t>1-Sep 9:36</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOL@961.00 (21.95%)</t>
+          <t>Skyways Air IPOL@124.00 (-10.14%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹290 (36.80%) 190 ↓ / 395 ↑</t>
+          <t>₹33 (23.91%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2057,47 +2029,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>111.18x</t>
+          <t>71.25x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹825.00 Cr</t>
+          <t>₹582.80 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 310</t>
+          <t>24-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 315</t>
+          <t>27-Aug GMP: 44</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 290</t>
+          <t>1-Sep GMP: 33</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>31-Aug 9:29</t>
+          <t>1-Sep 9:32</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2109,263 +2081,263 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOL@634.00 (111.33%)</t>
+          <t>ABH Healthcare NSE SMEL@99.00 (-2.94%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹330 (110.00%) 65 ↓ / 330 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>184.22x</t>
+          <t>1.44x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹34.98 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 270</t>
+          <t>24-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 313</t>
+          <t>27-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 330</t>
+          <t>1-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>28-Aug 9:35</t>
+          <t>1-Sep 9:29</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mopshop Distribution BSE SMEL@137.00 (-0.72%)</t>
+          <t>Hy-Tech Engineers IPOL@75.00 (41.51%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹1 (0.72%) 1 ↓ / 22 ↑</t>
+          <t>₹39 (73.58%) 5 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.59x</t>
+          <t>247.39x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹27.26 Cr</t>
+          <t>₹135.73 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 5</t>
+          <t>24-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 1</t>
+          <t>27-Aug GMP: 45</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>26-Aug GMP: 1</t>
+          <t>1-Sep GMP: 39</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>26-Aug 9:28</t>
+          <t>1-Sep 9:31</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMEL@99.00 (0%)</t>
+          <t>Augmont Enterprises IPOL@961.00 (21.95%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹1 (1.01%) 1 ↓ / 12 ↑</t>
+          <t>₹290 (36.80%) 190 ↓ / 395 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.65x</t>
+          <t>111.18x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹26.73 Cr</t>
+          <t>₹825.00 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 12</t>
+          <t>21-Aug GMP: 310</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 1</t>
+          <t>25-Aug GMP: 315</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>26-Aug GMP: 1</t>
+          <t>31-Aug GMP: 290</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>26-Aug 9:37</t>
+          <t>31-Aug 9:29</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOL@185.00 (15.62%)</t>
+          <t>Tempsens Instruments (India) IPOL@634.00 (111.33%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹18.5 (11.56%) 7 ↓ / 30 ↑</t>
+          <t>₹330 (110.00%) 65 ↓ / 330 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>32.98x</t>
+          <t>184.22x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹550.00 Cr</t>
+          <t>₹650.00 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 23</t>
+          <t>20-Aug GMP: 270</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 19</t>
+          <t>24-Aug GMP: 313</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>26-Aug GMP: 18.5</t>
+          <t>28-Aug GMP: 330</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>26-Aug 9:34</t>
+          <t>28-Aug 9:35</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2377,12 +2349,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers IPOL@103.30 (11.08%)</t>
+          <t>Dhanwel Hybrid Seeds BSE SMEL@99.00 (0%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹2.75 (2.96%) 1 ↓ / 8 ↑</t>
+          <t>₹1 (1.01%) 1 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2392,64 +2364,64 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.8x</t>
+          <t>1.65x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹367.18 Cr</t>
+          <t>₹26.73 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 5</t>
+          <t>19-Aug GMP: 12</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 5</t>
+          <t>21-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 2.75</t>
+          <t>26-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>25-Aug 9:36</t>
+          <t>26-Aug 9:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPOL@395.90 (9.97%)</t>
+          <t>Gaja Alternative Asset Management IPOL@185.00 (15.62%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹50 (13.89%) 17 ↓ / 80 ↑</t>
+          <t>₹18.5 (11.56%) 7 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2459,47 +2431,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>105.81x</t>
+          <t>32.98x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹282.14 Cr</t>
+          <t>₹550.00 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 77</t>
+          <t>19-Aug GMP: 23</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 80</t>
+          <t>21-Aug GMP: 19</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>21-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 50</t>
+          <t>26-Aug GMP: 18.5</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>25-Aug 9:30</t>
+          <t>26-Aug 9:34</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2511,67 +2483,67 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart IPOL@265.00 (31.84%)</t>
+          <t>Mopshop Distribution BSE SMEL@137.00 (-0.72%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹74 (36.82%) 17 ↓ / 77 ↑</t>
+          <t>₹1 (0.72%) 1 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>66.63x</t>
+          <t>1.59x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹1700.00 Cr</t>
+          <t>₹27.26 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>17-Aug GMP: 30</t>
+          <t>19-Aug GMP: 5</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 54</t>
+          <t>21-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>24-Aug</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 74</t>
+          <t>26-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>24-Aug 9:33</t>
+          <t>26-Aug 9:28</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹14 (10.00%) 14 ↓ / 14 ↑</t>
+          <t>₹18 (12.86%) 18 ↓ / 18 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1-Sep 13:53</t>
+          <t>1-Sep 18:58</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Qualiance International NSE SMEU</t>
+          <t>Pranav Constructions IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -625,44 +625,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>₹45.11 Cr</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8-Sep</t>
+          <t>9-Sep</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9-Sep</t>
+          <t>10-Sep</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1-Sep 14:02</t>
+          <t>1-Sep 16:50</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -674,109 +662,109 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Farm Peace BSE SMEO</t>
+          <t>Qualiance International NSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹50 (39.37%) 50 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.01x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>127</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹32.00 Cr</t>
+          <t>₹45.11 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 0</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>9-Sep</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>8-Sep</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1-Sep 14:00</t>
+          <t>1-Sep 19:00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rays of Belief IPOO</t>
+          <t>Fly-Hi Maritime BSE SMEO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹48 (20.08%) 10 ↓ / 48 ↑</t>
+          <t>₹9 (8.82%) 5 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.83x</t>
+          <t>0.01x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹125.00 Cr</t>
+          <t>₹52.63 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 48</t>
+          <t>1-Sep GMP: 9</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -796,54 +784,54 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1-Sep 14:00</t>
+          <t>1-Sep 19:01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fly-Hi Maritime BSE SMEO</t>
+          <t>Deepa Jewellers IPOO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹9 (8.82%) 5 ↓ / 9 ↑</t>
+          <t>₹44 (24.86%) 44 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.01x</t>
+          <t>0.88x</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹52.63 Cr</t>
+          <t>₹459.72 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 9</t>
+          <t>1-Sep GMP: 44</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -863,54 +851,54 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1-Sep 14:01</t>
+          <t>1-Sep 18:55</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Deepa Jewellers IPOO</t>
+          <t>Farm Peace BSE SMEO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹44 (24.86%) 44 ↓ / 55 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.6x</t>
+          <t>0.01x</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹459.72 Cr</t>
+          <t>₹32.00 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 44</t>
+          <t>1-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -930,74 +918,74 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1-Sep 13:59</t>
+          <t>1-Sep 19:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Purple Style Labs IPOO</t>
+          <t>Rays of Belief IPOO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹2 (0.35%) 2 ↓ / 34 ↑</t>
+          <t>₹38 (15.90%) 10 ↓ / 48 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.22x</t>
+          <t>1.18x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>239</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹680.00 Cr</t>
+          <t>₹125.00 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 7</t>
+          <t>1-Sep GMP: 38</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>7-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1-Sep 13:53</t>
+          <t>1-Sep 18:57</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1009,42 +997,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Phychem Technologies BSE SMEO</t>
+          <t>Ashutosh Fibre NSE SMEO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹1 (1.85%) 1 ↓ / 3 ↑</t>
+          <t>₹20 (21.74%) 13 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.61x</t>
+          <t>5.59x</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹14.58 Cr</t>
+          <t>₹56.35 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 1</t>
+          <t>31-Aug GMP: 45</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1064,7 +1052,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1-Sep 14:02</t>
+          <t>1-Sep 18:58</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1076,42 +1064,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shanti Inorganics NSE SMEO</t>
+          <t>Phychem Technologies BSE SMEO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹10 (12.05%) 10 ↓ / 31 ↑</t>
+          <t>₹1 (1.85%) 1 ↓ / 3 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.19x</t>
+          <t>1.97x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹47.24 Cr</t>
+          <t>₹14.58 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 31</t>
+          <t>31-Aug GMP: 1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1131,7 +1119,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1-Sep 13:53</t>
+          <t>1-Sep 18:53</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1143,42 +1131,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ashutosh Fibre NSE SMEO</t>
+          <t>Purple Style Labs IPOO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹27 (29.35%) 13 ↓ / 45 ↑</t>
+          <t>₹5 (0.87%) 5 ↓ / 34 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.2x</t>
+          <t>0.25x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>575</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹56.35 Cr</t>
+          <t>₹680.00 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 45</t>
+          <t>31-Aug GMP: 7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1198,7 +1186,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1-Sep 13:56</t>
+          <t>1-Sep 19:00</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1210,62 +1198,62 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ESDS Software Solution IPOCT</t>
+          <t>Shanti Inorganics NSE SMEO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹257 (59.91%) 257 ↓ / 372 ↑</t>
+          <t>₹10 (12.05%) 10 ↓ / 31 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>67.26x</t>
+          <t>3.89x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹720.00 Cr</t>
+          <t>₹47.24 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 360</t>
+          <t>31-Aug GMP: 31</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 257</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1-Sep 13:57</t>
+          <t>1-Sep 19:00</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1277,47 +1265,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Complete Sports and Management BSE SMECT</t>
+          <t>ESDS Software Solution IPOCAllotted</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹273 (63.64%) 273 ↓ / 372 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.71x</t>
+          <t>142.88x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>429</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹74.93 Cr</t>
+          <t>₹720.00 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 0</t>
+          <t>28-Aug GMP: 360</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 0</t>
+          <t>1-Sep GMP: 273</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1332,7 +1320,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1-Sep 14:02</t>
+          <t>1-Sep 18:59</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1344,12 +1332,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Priority Jewels IPOCT</t>
+          <t>Paluck Technologies BSE SMEC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹40 (20.00%) 20 ↓ / 45 ↑</t>
+          <t>₹20 (41.67%) 10 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1359,32 +1347,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>71.02x</t>
+          <t>789.16x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹91.50 Cr</t>
+          <t>₹33.00 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 45</t>
+          <t>28-Aug GMP: 25</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 40</t>
+          <t>1-Sep GMP: 20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1399,7 +1387,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1-Sep 13:59</t>
+          <t>1-Sep 18:54</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1411,47 +1399,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Paluck Technologies BSE SMECT</t>
+          <t>Complete Sports and Management BSE SMEC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹30 (62.50%) 10 ↓ / 30 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>504.26x</t>
+          <t>3.45x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹33.00 Cr</t>
+          <t>₹74.93 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 25</t>
+          <t>28-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 30</t>
+          <t>1-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1466,7 +1454,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1-Sep 14:01</t>
+          <t>1-Sep 19:00</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1545,62 +1533,62 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lumino Industries IPOC</t>
+          <t>Priority Jewels IPOC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹40 (48.78%) 40 ↓ / 63 ↑</t>
+          <t>₹23 (11.50%) 20 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>124.02x</t>
+          <t>100.45x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹700.00 Cr</t>
+          <t>₹91.50 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 56</t>
+          <t>28-Aug GMP: 45</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 48</t>
+          <t>1-Sep GMP: 23</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1-Sep 13:53</t>
+          <t>1-Sep 19:01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1667,7 +1655,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1-Sep 14:00</t>
+          <t>1-Sep 18:59</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1679,114 +1667,114 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Annu Projects IPOCAllotted</t>
+          <t>Lumino Industries IPOC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹-3 (-3.03%) -3 ↓ / 7 ↑</t>
+          <t>₹40 (48.78%) 40 ↓ / 63 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.93x</t>
+          <t>124.02x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹175.06 Cr</t>
+          <t>₹700.00 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>182</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 0</t>
+          <t>27-Aug GMP: 56</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 1</t>
+          <t>31-Aug GMP: 48</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1-Sep 13:57</t>
+          <t>1-Sep 18:58</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sumax Engineering NSE SMECAllotted</t>
+          <t>Annu Projects IPOCAllotted</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹30 (29.70%) 20 ↓ / 36 ↑</t>
+          <t>₹-5 (-5.05%) -5 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>162.94x</t>
+          <t>2.93x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹53.40 Cr</t>
+          <t>₹175.06 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 35</t>
+          <t>25-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 36</t>
+          <t>28-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1801,91 +1789,91 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1-Sep 13:56</t>
+          <t>1-Sep 18:59</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Fascinate Textiles NSE SMECAllotted</t>
+          <t>Sumax Engineering NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹30 (29.70%) 20 ↓ / 36 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.48x</t>
+          <t>162.94x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹64.83 Cr</t>
+          <t>₹53.40 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>11-Aug GMP: 0</t>
+          <t>25-Aug GMP: 35</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 0</t>
+          <t>28-Aug GMP: 36</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>20-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 0</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1-Sep 5:55</t>
+          <t>1-Sep 18:59</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Madhur Knit NSE SMEL@100.00 (0%)</t>
+          <t>Fascinate Textiles NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹2 (2.00%) 2 ↓ / 16 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1895,99 +1883,99 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.5x</t>
+          <t>1.48x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹53.27 Cr</t>
+          <t>₹64.83 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 16</t>
+          <t>11-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 2</t>
+          <t>19-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>20-Aug</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 2</t>
+          <t>24-Aug GMP: 0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1-Sep 9:30</t>
+          <t>1-Sep 5:55</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOL@988.00 (0%)</t>
+          <t>Hy-Tech Engineers IPOL@75.00 (41.51%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹185 (18.72%) 185 ↓ / 410 ↑</t>
+          <t>₹39 (73.58%) 5 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>75.08x</t>
+          <t>247.39x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹1757.00 Cr</t>
+          <t>₹135.73 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 335</t>
+          <t>24-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 270</t>
+          <t>27-Aug GMP: 45</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1997,12 +1985,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 185</t>
+          <t>1-Sep GMP: 39</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1-Sep 9:36</t>
+          <t>1-Sep 9:31</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2014,47 +2002,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Skyways Air IPOL@124.00 (-10.14%)</t>
+          <t>ABH Healthcare NSE SMEL@99.00 (-2.94%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹33 (23.91%) 19 ↓ / 50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>71.25x</t>
+          <t>1.44x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹582.80 Cr</t>
+          <t>₹34.98 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 32</t>
+          <t>24-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 44</t>
+          <t>27-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2064,29 +2052,29 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 33</t>
+          <t>1-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1-Sep 9:32</t>
+          <t>1-Sep 9:29</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ABH Healthcare NSE SMEL@99.00 (-2.94%)</t>
+          <t>Madhur Knit NSE SMEL@100.00 (0%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹2 (2.00%) 2 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2096,17 +2084,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.44x</t>
+          <t>1.5x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹34.98 Cr</t>
+          <t>₹53.27 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2116,12 +2104,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 0</t>
+          <t>24-Aug GMP: 16</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 0</t>
+          <t>27-Aug GMP: 2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2131,64 +2119,64 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 0</t>
+          <t>1-Sep GMP: 2</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1-Sep 9:29</t>
+          <t>1-Sep 9:30</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOL@75.00 (41.51%)</t>
+          <t>Skyways Air IPOL@124.00 (-10.14%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹39 (73.58%) 5 ↓ / 45 ↑</t>
+          <t>₹33 (23.91%) 19 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>247.39x</t>
+          <t>71.25x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹135.73 Cr</t>
+          <t>₹582.80 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 30</t>
+          <t>24-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 45</t>
+          <t>27-Aug GMP: 44</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2198,12 +2186,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 39</t>
+          <t>1-Sep GMP: 33</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1-Sep 9:31</t>
+          <t>1-Sep 9:32</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2215,62 +2203,62 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOL@961.00 (21.95%)</t>
+          <t>Symbiotec Pharmalab IPOL@988.00 (0%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹290 (36.80%) 190 ↓ / 395 ↑</t>
+          <t>₹185 (18.72%) 185 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>111.18x</t>
+          <t>75.08x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹825.00 Cr</t>
+          <t>₹1757.00 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 310</t>
+          <t>24-Aug GMP: 335</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 315</t>
+          <t>27-Aug GMP: 270</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 290</t>
+          <t>1-Sep GMP: 185</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>31-Aug 9:29</t>
+          <t>1-Sep 9:36</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2282,62 +2270,62 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOL@634.00 (111.33%)</t>
+          <t>Augmont Enterprises IPOL@961.00 (21.95%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹330 (110.00%) 65 ↓ / 330 ↑</t>
+          <t>₹290 (36.80%) 190 ↓ / 395 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>184.22x</t>
+          <t>111.18x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹825.00 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 270</t>
+          <t>21-Aug GMP: 310</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 313</t>
+          <t>25-Aug GMP: 315</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 330</t>
+          <t>31-Aug GMP: 290</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>28-Aug 9:35</t>
+          <t>31-Aug 9:29</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2349,114 +2337,114 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMEL@99.00 (0%)</t>
+          <t>Tempsens Instruments (India) IPOL@634.00 (111.33%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹1 (1.01%) 1 ↓ / 12 ↑</t>
+          <t>₹330 (110.00%) 65 ↓ / 330 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.65x</t>
+          <t>184.22x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹26.73 Cr</t>
+          <t>₹650.00 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 12</t>
+          <t>20-Aug GMP: 270</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 1</t>
+          <t>24-Aug GMP: 313</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>26-Aug GMP: 1</t>
+          <t>28-Aug GMP: 330</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>26-Aug 9:37</t>
+          <t>28-Aug 9:35</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOL@185.00 (15.62%)</t>
+          <t>Dhanwel Hybrid Seeds BSE SMEL@99.00 (0%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹18.5 (11.56%) 7 ↓ / 30 ↑</t>
+          <t>₹1 (1.01%) 1 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>32.98x</t>
+          <t>1.65x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹550.00 Cr</t>
+          <t>₹26.73 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 23</t>
+          <t>19-Aug GMP: 12</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 19</t>
+          <t>21-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2466,64 +2454,64 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>26-Aug GMP: 18.5</t>
+          <t>26-Aug GMP: 1</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>26-Aug 9:34</t>
+          <t>26-Aug 9:37</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mopshop Distribution BSE SMEL@137.00 (-0.72%)</t>
+          <t>Gaja Alternative Asset Management IPOL@185.00 (15.62%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹1 (0.72%) 1 ↓ / 22 ↑</t>
+          <t>₹18.5 (11.56%) 7 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.59x</t>
+          <t>32.98x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹27.26 Cr</t>
+          <t>₹550.00 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 5</t>
+          <t>19-Aug GMP: 23</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 1</t>
+          <t>21-Aug GMP: 19</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2533,17 +2521,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>26-Aug GMP: 1</t>
+          <t>26-Aug GMP: 18.5</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>26-Aug 9:28</t>
+          <t>26-Aug 9:34</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -528,7 +528,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1-Sep 5:55</t>
+          <t>2-Sep 5:55</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1-Sep 18:58</t>
+          <t>2-Sep 12:57</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pranav Constructions IPOU</t>
+          <t>Amtech Esters BSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -626,31 +626,35 @@
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7-Sep</t>
+          <t>9-Sep</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9-Sep</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1-Sep 16:50</t>
+          <t>2-Sep 10:00</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -662,17 +666,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Qualiance International NSE SMEU</t>
+          <t>Asset Reconstruction IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹50 (39.37%) 50 ↓ / 50 ↑</t>
+          <t>₹-- (%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -680,44 +684,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹45.11 Cr</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>9-Sep</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8-Sep</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1-Sep 19:00</t>
+          <t>2-Sep 10:40</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -729,79 +725,79 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fly-Hi Maritime BSE SMEO</t>
+          <t>Pranav Constructions IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹9 (8.82%) 5 ↓ / 9 ↑</t>
+          <t>₹25 (20.16%) 23 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.01x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹52.63 Cr</t>
+          <t>₹351.03 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 9</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>9-Sep</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>10-Sep</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1-Sep 19:01</t>
+          <t>2-Sep 13:01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Deepa Jewellers IPOO</t>
+          <t>Qualiance International NSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹44 (24.86%) 44 ↓ / 55 ↑</t>
+          <t>₹50 (39.37%) 50 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -811,47 +807,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.88x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>127</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹459.72 Cr</t>
+          <t>₹45.11 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 44</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>9-Sep</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>8-Sep</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1-Sep 18:55</t>
+          <t>2-Sep 12:56</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -863,42 +859,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Farm Peace BSE SMEO</t>
+          <t>Deepa Jewellers IPOO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹26 (14.69%) 26 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.01x</t>
+          <t>2.25x</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹32.00 Cr</t>
+          <t>₹459.72 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 0</t>
+          <t>1-Sep GMP: 44</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -918,24 +914,24 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1-Sep 19:02</t>
+          <t>2-Sep 13:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rays of Belief IPOO</t>
+          <t>Fly-Hi Maritime BSE SMEO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹38 (15.90%) 10 ↓ / 48 ↑</t>
+          <t>₹15 (14.71%) 5 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -945,27 +941,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.18x</t>
+          <t>0.04x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹125.00 Cr</t>
+          <t>₹52.63 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 38</t>
+          <t>1-Sep GMP: 12.5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -985,74 +981,74 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1-Sep 18:57</t>
+          <t>2-Sep 12:59</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ashutosh Fibre NSE SMEO</t>
+          <t>Rays of Belief IPOO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹20 (21.74%) 13 ↓ / 45 ↑</t>
+          <t>₹30 (12.55%) 10 ↓ / 48 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.59x</t>
+          <t>2.58x</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>239</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹56.35 Cr</t>
+          <t>₹125.00 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 45</t>
+          <t>1-Sep GMP: 38</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>7-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1-Sep 18:58</t>
+          <t>2-Sep 12:56</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1064,12 +1060,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Phychem Technologies BSE SMEO</t>
+          <t>Farm Peace BSE SMEO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹1 (1.85%) 1 ↓ / 3 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1079,17 +1075,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.97x</t>
+          <t>0.04x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹14.58 Cr</t>
+          <t>₹32.00 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1099,44 +1095,44 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 1</t>
+          <t>1-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>7-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1-Sep 18:53</t>
+          <t>2-Sep 12:56</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Purple Style Labs IPOO</t>
+          <t>Phychem Technologies BSE SMECT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹5 (0.87%) 5 ↓ / 34 ↑</t>
+          <t>₹1 (1.85%) 1 ↓ / 3 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1146,32 +1142,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.25x</t>
+          <t>3.84x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹680.00 Cr</t>
+          <t>₹14.58 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 7</t>
+          <t>31-Aug GMP: 1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>2-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1186,7 +1182,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1-Sep 19:00</t>
+          <t>2-Sep 12:58</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1198,47 +1194,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shanti Inorganics NSE SMEO</t>
+          <t>Ashutosh Fibre NSE SMECT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹10 (12.05%) 10 ↓ / 31 ↑</t>
+          <t>₹35 (38.04%) 10 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3.89x</t>
+          <t>26.96x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹47.24 Cr</t>
+          <t>₹56.35 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 31</t>
+          <t>31-Aug GMP: 45</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>2-Sep GMP: 35</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1253,7 +1249,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1-Sep 19:00</t>
+          <t>2-Sep 12:55</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1265,62 +1261,62 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ESDS Software Solution IPOCAllotted</t>
+          <t>Purple Style Labs IPOCT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹273 (63.64%) 273 ↓ / 372 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 34 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>142.88x</t>
+          <t>0.84x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>575</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹720.00 Cr</t>
+          <t>₹680.00 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 360</t>
+          <t>31-Aug GMP: 7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 273</t>
+          <t>2-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1-Sep 18:59</t>
+          <t>2-Sep 12:58</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1332,12 +1328,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Paluck Technologies BSE SMEC</t>
+          <t>Shanti Inorganics NSE SMECT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹20 (41.67%) 10 ↓ / 30 ↑</t>
+          <t>₹25 (30.12%) 25 ↓ / 36 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1347,47 +1343,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>789.16x</t>
+          <t>51.91x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹33.00 Cr</t>
+          <t>₹47.24 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 25</t>
+          <t>31-Aug GMP: 31</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 20</t>
+          <t>2-Sep GMP: 25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1-Sep 18:54</t>
+          <t>2-Sep 12:54</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1399,47 +1395,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Complete Sports and Management BSE SMEC</t>
+          <t>Paluck Technologies BSE SMEC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹20 (41.67%) 10 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3.45x</t>
+          <t>789.16x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹74.93 Cr</t>
+          <t>₹33.00 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 0</t>
+          <t>28-Aug GMP: 25</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 0</t>
+          <t>1-Sep GMP: 20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1454,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1-Sep 19:00</t>
+          <t>2-Sep 12:54</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1538,7 +1534,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹23 (11.50%) 20 ↓ / 45 ↑</t>
+          <t>₹30 (15.00%) 20 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1573,7 +1569,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 23</t>
+          <t>1-Sep GMP: 31</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1588,7 +1584,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1-Sep 19:01</t>
+          <t>2-Sep 12:55</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1600,12 +1596,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kwick Forensic Solutions BSE SMEC</t>
+          <t>ESDS Software Solution IPOC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹85 (94.44%) 15 ↓ / 85 ↑</t>
+          <t>₹252 (58.74%) 252 ↓ / 372 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1615,47 +1611,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>289x</t>
+          <t>142.88x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>429</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹50.77 Cr</t>
+          <t>₹720.00 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 64</t>
+          <t>28-Aug GMP: 360</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 85</t>
+          <t>1-Sep GMP: 255</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1-Sep 18:59</t>
+          <t>2-Sep 12:58</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1667,62 +1663,62 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lumino Industries IPOC</t>
+          <t>Complete Sports and Management BSE SMEC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹40 (48.78%) 40 ↓ / 63 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>124.02x</t>
+          <t>3.45x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹700.00 Cr</t>
+          <t>₹74.93 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 56</t>
+          <t>28-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 48</t>
+          <t>1-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1-Sep 18:58</t>
+          <t>2-Sep 12:59</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1734,79 +1730,79 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Annu Projects IPOCAllotted</t>
+          <t>Kwick Forensic Solutions BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹-5 (-5.05%) -5 ↓ / 7 ↑</t>
+          <t>₹78 (86.67%) 15 ↓ / 85 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.93x</t>
+          <t>289x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹175.06 Cr</t>
+          <t>₹50.77 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 0</t>
+          <t>27-Aug GMP: 64</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 1</t>
+          <t>31-Aug GMP: 85</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1-Sep 18:59</t>
+          <t>2-Sep 12:58</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sumax Engineering NSE SMECAllotted</t>
+          <t>Lumino Industries IPOCAllotted</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹30 (29.70%) 20 ↓ / 36 ↑</t>
+          <t>₹32.5 (39.63%) 32.50 ↓ / 63 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1816,47 +1812,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>162.94x</t>
+          <t>124.02x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹53.40 Cr</t>
+          <t>₹700.00 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>182</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 35</t>
+          <t>27-Aug GMP: 56</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 36</t>
+          <t>31-Aug GMP: 48</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1-Sep 18:59</t>
+          <t>2-Sep 12:55</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1923,7 +1919,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1-Sep 5:55</t>
+          <t>2-Sep 5:55</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1935,62 +1931,62 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPOL@75.00 (41.51%)</t>
+          <t>Sumax Engineering NSE SMEL@111.00 (9.9%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹39 (73.58%) 5 ↓ / 45 ↑</t>
+          <t>₹22 (21.78%) 20 ↓ / 36 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>247.39x</t>
+          <t>162.94x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹135.73 Cr</t>
+          <t>₹53.40 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 30</t>
+          <t>25-Aug GMP: 35</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 45</t>
+          <t>28-Aug GMP: 36</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 39</t>
+          <t>2-Sep GMP: 22</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1-Sep 9:31</t>
+          <t>2-Sep 9:36</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2002,12 +1998,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ABH Healthcare NSE SMEL@99.00 (-2.94%)</t>
+          <t>Annu Projects IPOL@72.00 (-27.27%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-7 (-7.07%) -7 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2017,47 +2013,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.44x</t>
+          <t>2.93x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹34.98 Cr</t>
+          <t>₹175.06 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 0</t>
+          <t>25-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 0</t>
+          <t>28-Aug GMP: 1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 0</t>
+          <t>2-Sep GMP: -7</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1-Sep 9:29</t>
+          <t>2-Sep 9:36</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2203,47 +2199,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab IPOL@988.00 (0%)</t>
+          <t>Hy-Tech Engineers IPOL@75.00 (41.51%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹185 (18.72%) 185 ↓ / 410 ↑</t>
+          <t>₹39 (73.58%) 5 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>75.08x</t>
+          <t>247.39x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹1757.00 Cr</t>
+          <t>₹135.73 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 335</t>
+          <t>24-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>27-Aug GMP: 270</t>
+          <t>27-Aug GMP: 45</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2253,12 +2249,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 185</t>
+          <t>1-Sep GMP: 39</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1-Sep 9:36</t>
+          <t>1-Sep 9:31</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2270,62 +2266,62 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Augmont Enterprises IPOL@961.00 (21.95%)</t>
+          <t>Symbiotec Pharmalab IPOL@988.00 (0%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹290 (36.80%) 190 ↓ / 395 ↑</t>
+          <t>₹185 (18.72%) 185 ↓ / 410 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>111.18x</t>
+          <t>75.08x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹825.00 Cr</t>
+          <t>₹1757.00 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 310</t>
+          <t>24-Aug GMP: 335</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 315</t>
+          <t>27-Aug GMP: 270</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 290</t>
+          <t>1-Sep GMP: 185</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>31-Aug 9:29</t>
+          <t>1-Sep 9:36</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2337,196 +2333,196 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) IPOL@634.00 (111.33%)</t>
+          <t>ABH Healthcare NSE SMEL@99.00 (-2.94%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹330 (110.00%) 65 ↓ / 330 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>184.22x</t>
+          <t>1.44x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹650.00 Cr</t>
+          <t>₹34.98 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>20-Aug GMP: 270</t>
+          <t>24-Aug GMP: 0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>24-Aug GMP: 313</t>
+          <t>27-Aug GMP: 0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>25-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 330</t>
+          <t>1-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>28-Aug 9:35</t>
+          <t>1-Sep 9:29</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dhanwel Hybrid Seeds BSE SMEL@99.00 (0%)</t>
+          <t>Augmont Enterprises IPOL@961.00 (21.95%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹1 (1.01%) 1 ↓ / 12 ↑</t>
+          <t>₹290 (36.80%) 190 ↓ / 395 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.65x</t>
+          <t>111.18x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹26.73 Cr</t>
+          <t>₹825.00 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 12</t>
+          <t>21-Aug GMP: 310</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 1</t>
+          <t>25-Aug GMP: 315</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>27-Aug</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>26-Aug GMP: 1</t>
+          <t>31-Aug GMP: 290</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>26-Aug 9:37</t>
+          <t>31-Aug 9:29</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management IPOL@185.00 (15.62%)</t>
+          <t>Tempsens Instruments (India) IPOL@634.00 (111.33%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹18.5 (11.56%) 7 ↓ / 30 ↑</t>
+          <t>₹330 (110.00%) 65 ↓ / 330 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>32.98x</t>
+          <t>184.22x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹550.00 Cr</t>
+          <t>₹650.00 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>19-Aug GMP: 23</t>
+          <t>20-Aug GMP: 270</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>21-Aug GMP: 19</t>
+          <t>24-Aug GMP: 313</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>24-Aug</t>
+          <t>25-Aug</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>26-Aug GMP: 18.5</t>
+          <t>28-Aug GMP: 330</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>26-Aug 9:34</t>
+          <t>28-Aug 9:35</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2-Sep 12:57</t>
+          <t>2-Sep 18:34</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹25 (20.16%) 23 ↓ / 25 ↑</t>
+          <t>₹27 (21.77%) 23 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2-Sep 13:01</t>
+          <t>2-Sep 18:28</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹50 (39.37%) 50 ↓ / 50 ↑</t>
+          <t>₹55 (43.31%) 50 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2-Sep 12:56</t>
+          <t>2-Sep 18:33</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹26 (14.69%) 26 ↓ / 55 ↑</t>
+          <t>₹28 (15.82%) 28 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.25x</t>
+          <t>3.69x</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2-Sep 13:02</t>
+          <t>2-Sep 18:30</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹15 (14.71%) 5 ↓ / 15 ↑</t>
+          <t>₹20 (19.61%) 5 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.04x</t>
+          <t>0.08x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2-Sep 12:59</t>
+          <t>2-Sep 18:34</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹30 (12.55%) 10 ↓ / 48 ↑</t>
+          <t>₹32 (13.39%) 10 ↓ / 48 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.58x</t>
+          <t>3.63x</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2-Sep 12:56</t>
+          <t>2-Sep 18:33</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.04x</t>
+          <t>0.06x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2-Sep 12:56</t>
+          <t>2-Sep 18:35</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1127,7 +1127,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Phychem Technologies BSE SMECT</t>
+          <t>Phychem Technologies BSE SMEC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3.84x</t>
+          <t>20.79x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2-Sep 12:58</t>
+          <t>2-Sep 18:29</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1194,12 +1194,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ashutosh Fibre NSE SMECT</t>
+          <t>Ashutosh Fibre NSE SMEC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹35 (38.04%) 10 ↓ / 45 ↑</t>
+          <t>₹33 (35.87%) 10 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>26.96x</t>
+          <t>144.65x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2-Sep GMP: 35</t>
+          <t>2-Sep GMP: 33</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2-Sep 12:55</t>
+          <t>2-Sep 18:31</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1261,12 +1261,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Purple Style Labs IPOCT</t>
+          <t>Purple Style Labs IPOC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 34 ↑</t>
+          <t>₹1 (0.17%) 1 ↓ / 34 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.84x</t>
+          <t>1.36x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2-Sep GMP: 0</t>
+          <t>2-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2-Sep 12:58</t>
+          <t>2-Sep 18:35</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1328,22 +1328,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Shanti Inorganics NSE SMECT</t>
+          <t>Shanti Inorganics NSE SMEC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹25 (30.12%) 25 ↓ / 36 ↑</t>
+          <t>₹13 (15.66%) 13 ↓ / 36 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>51.91x</t>
+          <t>142.17x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2-Sep GMP: 25</t>
+          <t>2-Sep GMP: 13</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2-Sep 12:54</t>
+          <t>2-Sep 18:33</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹20 (41.67%) 10 ↓ / 30 ↑</t>
+          <t>₹10 (20.83%) 10 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2-Sep 12:54</t>
+          <t>2-Sep 18:34</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2-Sep 12:55</t>
+          <t>2-Sep 18:37</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹252 (58.74%) 252 ↓ / 372 ↑</t>
+          <t>₹245 (57.11%) 245 ↓ / 372 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2-Sep 12:58</t>
+          <t>2-Sep 18:34</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2-Sep 12:59</t>
+          <t>2-Sep 18:35</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2-Sep 12:58</t>
+          <t>2-Sep 18:29</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹32.5 (39.63%) 32.50 ↓ / 63 ↑</t>
+          <t>₹35.5 (43.29%) 35.50 ↓ / 63 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2-Sep 12:55</t>
+          <t>2-Sep 18:32</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,17 +501,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kanohar Electricals IPOU</t>
+          <t>Veegaland Developers IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹18 (12.86%) 18 ↓ / 18 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -519,16 +519,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹210.00 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>10-Sep</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15-Sep</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>16-Sep</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>18-Sep</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2-Sep 5:55</t>
+          <t>3-Sep 12:59</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -540,17 +568,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Veegaland Developers IPOU</t>
+          <t>Amtech Esters BSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹18 (12.86%) 18 ↓ / 18 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -560,42 +588,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹210.00 Cr</t>
+          <t>₹17.88 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>9-Sep</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>11-Sep</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>15-Sep</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>16-Sep</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2-Sep 18:34</t>
+          <t>3-Sep 13:01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -607,12 +635,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Amtech Esters BSE SMEU</t>
+          <t>Asset Reconstruction IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹-- (%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -625,13 +653,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>₹732.97 Cr</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>9-Sep</t>
@@ -654,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2-Sep 10:00</t>
+          <t>3-Sep 12:56</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -666,17 +702,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Asset Reconstruction IPOU</t>
+          <t>Glass Wall Systems IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹-- (%) 0 ↓ / 0 ↑</t>
+          <t>₹20 (10.99%) 20 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -684,36 +720,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>₹427.89 Cr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>10-Sep</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>11-Sep</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>15-Sep</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2-Sep 10:40</t>
+          <t>3-Sep 12:59</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -725,17 +769,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pranav Constructions IPOU</t>
+          <t>Prasol Chemicals IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹27 (21.77%) 23 ↓ / 27 ↑</t>
+          <t>₹14 (2.07%) 14 ↓ / 14 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -745,42 +789,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹351.03 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>9-Sep</t>
+          <t>10-Sep</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2-Sep 18:28</t>
+          <t>3-Sep 12:56</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -792,12 +836,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Qualiance International NSE SMEU</t>
+          <t>Kanohar Electricals IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹55 (43.31%) 50 ↓ / 55 ↑</t>
+          <t>₹150 (23.73%) 150 ↓ / 150 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -812,42 +856,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹45.11 Cr</t>
+          <t>₹1055.74 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8-Sep</t>
+          <t>10-Sep</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9-Sep</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2-Sep 18:33</t>
+          <t>3-Sep 12:57</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -859,62 +903,62 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Deepa Jewellers IPOO</t>
+          <t>Pranav Constructions IPOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹28 (15.82%) 28 ↓ / 55 ↑</t>
+          <t>₹27 (21.77%) 23 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.69x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹459.72 Cr</t>
+          <t>₹351.03 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 44</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>9-Sep</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>10-Sep</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2-Sep 18:30</t>
+          <t>3-Sep 13:00</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -926,62 +970,62 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fly-Hi Maritime BSE SMEO</t>
+          <t>Apana Logistics BSE SMEU</t>
         </is>
       </c>
       <c r="B10" 